--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_GLI_1676729</t>
+          <t>KHCN_TMNLMT_BDH_0297148</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,11 +544,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -556,17 +551,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Rơ Ô WÊ</t>
+          <t>Lê Đình Khánh</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0396081566</t>
+          <t>0388773033</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Thôn Ia Prông</t>
+          <t>Cát Minh, Xã Cát Minh, Huyện Phù Cát, Tỉnh Bình Định</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -581,32 +576,34 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
+          <t>1. KH đã báo cn:  
+2. KH phản ánh:Hệ thống nlmt ko chạy ra kw, cứ đang chạy đỏ rồi lại đứng lại. Sản lượng ra thì thấp,  
+3. KH yêu cầu: Qua hỗ trợ, xử lý, hướng dẫn cho KH hiểu. KH sẽ sẵn sàng trả thêm phí nếu phát sinh thêm và cũng sẵn sàng hỗ trợ nếu xử lý dứt điểm được cho KH.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10:43 26/03/2026</t>
+          <t>16:28 26/03/2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>10:43 27/03/2026</t>
+          <t>16:28 27/03/2026</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -621,19 +618,19 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Nguyễn Hà Nguyên</t>
+          <t>Nguyễn Quang Toàn</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>060709</t>
+          <t>293989</t>
         </is>
       </c>
       <c r="Y2" s="2">
         <v>46107</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -642,12 +639,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -659,7 +656,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -679,37 +676,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VCC_YCTX_AGG_38601541770843310</t>
+          <t>KHDN_TT.GPTH_BDG_1495422</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Anh Bảo</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0903856444</t>
+          <t>0918236379</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Phường Rạch Giá, Tỉnh An Giang</t>
+          <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,7 +721,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -729,22 +731,24 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>KH chưa thấy có ai liên hệ để tư vấn nlmt.</t>
+          <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
+2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
+3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10:23 26/03/2026</t>
+          <t>16:08 26/03/2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>10:23 27/03/2026</t>
+          <t>16:08 27/03/2026</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -759,65 +763,65 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Đặng Hoàng Đen</t>
+          <t>Nguyễn Thành Long</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>284210</t>
+          <t>282101</t>
         </is>
       </c>
       <c r="Y3" s="2">
         <v>46107</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bảo dưỡng vệ sinh máy giặt lồng ngang</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VCC_HS_HPG_1774273311688</t>
+          <t>KHCN_TT.GPTH_HCM_1647671</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -825,6 +829,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -832,22 +841,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nguyễn Trọng</t>
+          <t>Bùi Châu Thùy Linh</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0357948736</t>
+          <t>0852842882</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>chỉ số nhà 469 khu nhà ở Himlam Hùng Vương phường Hồng Bàng, Phường Hồng Bàng, Thành phố Hải Phòng</t>
+          <t>Phường Bình Hưng Hòa, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -857,32 +866,34 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Đơn hàng đặt từ 23/3, KH hẹn 24/3 mà ko có ai liên hệ, KH yêu cầu liên hệ với KH.</t>
+          <t>CN báo sự cố hộ KH
+1. KH phản ánh: Ivt thông số bị chênh lệch khoảng 40-50 số điện so với đồng hồ điện lực
+2. KH yêu cầu: Xử lý càng nhanh càng tốt vì nhà KH cho thuê.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>09:04 26/03/2026</t>
+          <t>14:14 26/03/2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>14:00 26/03/2026</t>
+          <t>14:14 27/03/2026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -892,28 +903,28 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Đào Văn Sơn</t>
+          <t>Lê Khánh Toàn</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>079457</t>
+          <t>475483</t>
         </is>
       </c>
       <c r="Y4" s="2">
         <v>46107</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -930,32 +941,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VCC_HS_HPG_1774334874358</t>
+          <t>0901/NLMT/VCCTNH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -970,22 +981,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Đỗ Thánh</t>
+          <t>Nguyễn Hải Lương</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0919152922</t>
+          <t>0983730342</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5/98/162 trung lực hải an hải phòng, Phường Hải An, Thành phố Hải Phòng</t>
+          <t>Thị trấn Tân Châu,Huyện Tân Châu,Tỉnh Tây Ninh</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -995,32 +1006,34 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Đơn hàng đặt từ 24/3, KH hẹn hôm nay mà vẫn chưa thấy ai liên hệ.</t>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Hệ của KH sản lượng rất thấp, hqua nắng to cả ngày 39 độ mà ko được nổi 200kw trên hệ 52kw của KH.
+3. KH yêu cầu: Kiểm tra đo đạc lại thiết bị, và xem thiết kế lại đường đi dòng điện 3 pha, và xem có phương án để tối ưu sản lượng cho KH ko tư vấn, hướng dẫn cho KH.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>08:59 26/03/2026</t>
+          <t>08:00 27/03/2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>14:00 26/03/2026</t>
+          <t>09:00 30/03/2026</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1030,50 +1043,50 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Chưa tính KPI</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Đào Văn Lập</t>
+          <t>Trần Văn Quy</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>017781</t>
+          <t>470911</t>
         </is>
       </c>
       <c r="Y5" s="2">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>truongdv17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,7 +1106,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_NTN_0270887</t>
+          <t>KHCN_TT.GPTH_TNH_1639818</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1101,6 +1114,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -1108,22 +1126,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nguyễn Tri Long</t>
+          <t>Lý Đức Huy</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0937339339</t>
+          <t>0903101647</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>KP4, Phường Thanh Sơn, Thành phố Phan Rang-Tháp Chàm, Tỉnh Ninh Thuận</t>
+          <t>khu phố An Thới</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1138,56 +1156,56 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>KH đã báo CN: a Vương, nhưng CN bảo KH gọi tổng đài
-KH phản ánh: cần NVKT tới hỗ trợ tải app và hướng dẫn dùng app đo năng lượng mặt trời
-KH yêu cầu: KT qua hỗ trợ cài app đo NLMT</t>
+          <t>CN báo sự cố hộ KH
+1. KH phản ánh: Pin lưu trữ đang bị hỏng và mất luôn nguồn pin lưu trữ.
+2. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>08:36 26/03/2026</t>
+          <t>14:47 26/03/2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>08:36 27/03/2026</t>
+          <t>14:47 27/03/2026</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Trần Diệu Mai</t>
+          <t>Nguyễn Quốc Hưng</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>291295</t>
+          <t>467401</t>
         </is>
       </c>
       <c r="Y6" s="2">
         <v>46107</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1213,416 +1231,421 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Tấm pin NLMT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_DNG_38420986565488944</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Huỳnh Thanh Vũ</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0905337005</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sơn Trà Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Tư vấn sản phẩm/dịch vụ</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>KH cần NV tư vấn liên hệ lại</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>14:08 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>14:08 27/03/2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lê Quốc Nguyên</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>411194</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_GLI_1676729</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Rơ Ô WÊ</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0396081566</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Thôn Ia Prông</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai chậm</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>10:43 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>10:43 27/03/2026</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nguyễn Hà Nguyên</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>060709</t>
+        </is>
+      </c>
+      <c r="Y8" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>KHCN_NLMT_NTN_0241352</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Nguyễn Văn Sanh</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0913785605</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Ivt bị lỗi ko hoạt động, KH ktra thấy còn ko chạy
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra, khắc phục tình trạng này cho KH</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>08:25 26/03/2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>08:25 27/03/2026</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>Vũ Đình Minh</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>006275</t>
-        </is>
-      </c>
-      <c r="Y7" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VCC_HS_NBH_1774400384952</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bùi Nhất Quyết</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0988910177</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Giao thủy Nam định, Xã Giao Thủy, Tỉnh Ninh Bình</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Liên hệ chậm</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>KH phản ánh chưa có NVKT nào liên hệ đặt lịch. yêu cầu phản hồi gấp</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>08:00 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>14:00 26/03/2026</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Nguyễn Tiến Đức</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>058408</t>
-        </is>
-      </c>
-      <c r="Y8" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Hỗ trợ kiểm tra</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DH_B2C_HNI_1772685977872</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Đào Thị Bích Nga</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0332262246</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>56B ngõ 31 Nguyễn Cao</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>bảo dưỡng điều hòa xong máy kêu ù ù</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>10:33 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>10:33 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Nguyễn Tuấn Anh</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>055461</t>
         </is>
       </c>
       <c r="Y9" s="2">
         <v>46107</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -1634,515 +1657,658 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Hỗ trợ kiểm tra</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DH_B2C_HNI_1772685977872</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Đào Thị Bích Nga</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0332262246</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>56B ngõ 31 Nguyễn Cao</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>bảo dưỡng điều hòa xong máy kêu ù ù</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10:33 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>10:33 27/03/2026</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lê Duy Tuấn</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>293859</t>
+        </is>
+      </c>
+      <c r="Y10" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HDG_1304433</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0377883716</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH yêu cầu NVKT qua lại thiết bị inverter của KH 
 Số liên hệ:</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>09:00 27/03/2026</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>Hoàng Văn Phong</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>291011</t>
         </is>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y11" s="2">
         <v>46107</v>
       </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1169983</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Đường Quyền Hồng</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0907395121</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Ấp 4, Xã Phước Kiển, Huyện Nhà Bè, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: Lỗi CP bị cúp điện dưới nhà, hiện tại điện ko sử dụng được.
 3. KH yêu cầu: Qua kiểm tra, hỗ trợ, khắc phục gấp cho KH giờ nhà KH đang ko có điện để sử dụng.</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>09:32 26/03/2026</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>09:32 27/03/2026</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>Đoàn Văn Lượng</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>410048</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y12" s="2">
         <v>46107</v>
       </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_KHA_1631515</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Phạm Hải Triều</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0903576559</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
 2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>08:00 26/03/2026</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>09:00 27/03/2026</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>Phan Trọng Nghĩa</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>234935</t>
         </is>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y13" s="2">
         <v>46107</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1646163</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0973721368</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Triệu Xuyên, Long xuyên</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH đã báo cn a Long gđ kỹ thuật, a Dương Đăng Minh chủ ký HĐ, a Vương lắp đặt.
 2. KH phản ánh: Bị nhảy áp liên tục 1 tháng phải nhảy 20 ngày rơi vào khoảng 2h đêm và 12h trưa ban ngày, và chập tối lúc GĐ đang vào sinh hoạt. CN nhiều lần xuống ktra và kiến nghị nhưng có câu trả lời KH ko được hài lòng lắm. Đặc biệt là a Long GĐ KT có thái độ là đổ cho GĐ tắt áp, KH bức xúc vì KH bỏ đồng tiền ra mà lại đổ lỗi cho nhà KH. KH cũng báo với a Dương Đăng Minh, a Minh cũng bảo là để cháu bảo ae xuống thế nọ thế kia khất để ra giêng để sửa mà giờ hết tháng rồi vẫn ko thấy đâu.
@@ -2150,335 +2316,190 @@
 ***SĐT liên hệ: 0945268772, chú Bồng</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>14:58 25/03/2026</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>14:58 26/03/2026</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>23:00 06/04/2026</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y14" s="2">
         <v>46106</v>
       </c>
-      <c r="Z13">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="Z14">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1600729</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Nguyễn Khương</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0977113014</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
 2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
 3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>09:20 25/03/2026</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>17:25 27/03/2026</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Phạm Khắc Việt</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>048379</t>
-        </is>
-      </c>
-      <c r="Y14" s="2">
-        <v>46106</v>
-      </c>
-      <c r="Z14">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng vệ sinh máy giặt lồng ngang</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VCC_HS_HCM_1774251437661</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Chii Dung</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0938355255</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>số 3/97 Bình Thuận 2, Thuận Giao, Phường Thuận An, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Đơn hàng làm xong vào 24/3, vẫn đang trong hạn BH 72h
-1. KH phản ánh: Sau khi bảo dưỡng vệ sinh máy giặt nó kêu dứt, kêu e e và có mùi khét, hư máy luôn rồi, ko giặt được nữa luôn.
-2. KH yêu cầu: Cho KT khác qua, có tay nghề và chuyên nghiệp hơn để kiểm tra, xử lý cho KH trước 11h trưa nay nếu ko KH sẽ báo lên truy cục.</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>08:39 25/03/2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>08:39 26/03/2026</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Toản</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>427880</t>
         </is>
       </c>
       <c r="Y15" s="2">
         <v>46106</v>
       </c>
       <c r="Z15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2614,7 +2635,7 @@
         <v>46106</v>
       </c>
       <c r="Z16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2760,7 +2781,7 @@
         <v>46105</v>
       </c>
       <c r="Z17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2876,12 +2897,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>09:29 27/03/2026</t>
+          <t>17:30 31/03/2026</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2903,7 +2924,7 @@
         <v>46107</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -3047,7 +3068,7 @@
         <v>46105</v>
       </c>
       <c r="Z19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3192,7 +3213,7 @@
         <v>46105</v>
       </c>
       <c r="Z20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3320,7 +3341,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3337,7 +3358,7 @@
         <v>46105</v>
       </c>
       <c r="Z21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3465,7 +3486,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3482,7 +3503,7 @@
         <v>46105</v>
       </c>
       <c r="Z22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3623,7 +3644,7 @@
         <v>46105</v>
       </c>
       <c r="Z23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3749,7 +3770,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3766,7 +3787,7 @@
         <v>46107</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3812,12 +3833,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18082025-2969/HD/STRIDESOLAR-HXL</t>
+          <t>1808-2969/BBBG/CNCTHCM-STRIDESOLAR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3827,7 +3848,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Lê Xuân Hùng</t>
+          <t>CÔNG TY TNHH STRIDE SOLAR</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3847,7 +3868,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3889,7 +3910,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3906,7 +3927,7 @@
         <v>46104</v>
       </c>
       <c r="Z25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -4051,7 +4072,7 @@
         <v>46104</v>
       </c>
       <c r="Z26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -4196,7 +4217,7 @@
         <v>46104</v>
       </c>
       <c r="Z27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4217,12 +4238,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4237,17 +4258,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VCC_YCTX_HNI_37719882009122300</t>
+          <t>100901-KD/HDMB-2021/GLI-TT</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4257,193 +4278,50 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Trần Văn Thắng</t>
+          <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0818091565</t>
+          <t>0862000202</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Thế giới ẩm thực Xứ Đoài, Lai Xá, xã Kim Chung, Hoài Đức, Xã Hoài Đức, Thành phố Hà Nội</t>
+          <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Ý thức trách nhiệm</t>
+          <t>Inverter không hoạt động</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
-        <is>
-          <t>KH yêu cầu báo KT khác liên hệ để tư vấn, KT hiện tại hẹn KH xong ko đến. KH đợi cả ngày ko báo lấy 1 câu. Mất thời gian của KH.</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>08:00 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>09:00 24/03/2026</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Nguyễn Thành Vinh</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>413306</t>
-        </is>
-      </c>
-      <c r="Y28" s="2">
-        <v>46104</v>
-      </c>
-      <c r="Z28">
-        <v>3</v>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>P.KDNLMT</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>P.KDNLMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>GLI</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>100901-KD/HDMB-2021/GLI-TT</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Đồn Biên Phòng 723</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0862000202</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Đồn Biên Phòng 723</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Inverter không hoạt động</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo 
 2.Đã báo qua đâu: KH gọi TĐ
@@ -4451,6 +4329,151 @@
 4. KH yêu cầu KT qua kiểm tra xử lý cho KH.</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>08:00 23/03/2026</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>12:45 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nguyễn Hà Nguyên</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>060709</t>
+        </is>
+      </c>
+      <c r="Y28" s="2">
+        <v>46104</v>
+      </c>
+      <c r="Z28">
+        <v>4</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Công tắc thông minh</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNG_1416913</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Lê Đắc Quỳ</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0915313915</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
+3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
@@ -4458,7 +4481,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>12:45 31/03/2026</t>
+          <t>08:55 30/03/2026</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4473,23 +4496,23 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Nguyễn Hà Nguyên</t>
+          <t>Ngô Văn Minh</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>060709</t>
+          <t>083585</t>
         </is>
       </c>
       <c r="Y29" s="2">
         <v>46104</v>
       </c>
       <c r="Z29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4499,19 +4522,19 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4521,17 +4544,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Công tắc thông minh</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1416913</t>
+          <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4541,7 +4564,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4551,22 +4574,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Lê Đắc Quỳ</t>
+          <t>Dương Văn Quân</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0915313915</t>
+          <t>0359999199</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
+          <t>xã Hoàng Vân</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4581,160 +4604,15 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>08:00 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>08:55 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Ngô Văn Minh</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>083585</t>
-        </is>
-      </c>
-      <c r="Y30" s="2">
-        <v>46104</v>
-      </c>
-      <c r="Z30">
-        <v>3</v>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BGG_1597213</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Dương Văn Quân</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0359999199</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>xã Hoàng Vân</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -4742,290 +4620,145 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>18:00 26/03/2026</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>408869</t>
         </is>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y30" s="2">
         <v>46104</v>
       </c>
-      <c r="Z31">
-        <v>3</v>
-      </c>
-      <c r="AA31" t="inlineStr">
+      <c r="Z30">
+        <v>4</v>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1660328</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_CMU_1384534</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Mỹ Hằng</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0973631132</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Đường 21, Ấp Vinh Sơn</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Nguyễn Đức Hiếu</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0949001616</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Khóm 10</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>CN báo sự cố hộ KH.
-1. KH phản ánh: Ko vào được app để theo dõi hiệu suất.
-2. KH yêu cầu: Qua hỗ trợ, hướng dẫn KH kết nối lại app để theo dõi hiệu suất nlmt</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>15:56 20/03/2026</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>17:30 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Phan Hải Sơn</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>408703</t>
-        </is>
-      </c>
-      <c r="Y32" s="2">
-        <v>46101</v>
-      </c>
-      <c r="Z32">
-        <v>6</v>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_CMU_1384534</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Nguyễn Đức Hiếu</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0949001616</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Khóm 10</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.Đã báo cho ai:  KT Thái
@@ -5034,14 +4767,292 @@
 5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>09:44 20/03/2026</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>19:55 27/03/2026</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Võ Duy Khang</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>473069</t>
+        </is>
+      </c>
+      <c r="Y31" s="2">
+        <v>46101</v>
+      </c>
+      <c r="Z31">
+        <v>7</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_NAN_37485587203842849</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Xuân Hương</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0974371218</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Tư vấn sản phẩm/dịch vụ</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>15:32 20/03/2026</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>17:15 02/04/2026</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Trần Bình Thanh</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>069159</t>
+        </is>
+      </c>
+      <c r="Y32" s="2">
+        <v>46101</v>
+      </c>
+      <c r="Z32">
+        <v>7</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>P.KDNLMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CRP2501952</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH UNIVERSAL SCIENTIFIC INDUSTRIAL VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0985479660</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Lô đất CN4.1H</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>CN báo sự cố hộ KH
+1. KH phản ánh: Máy chủ scada mất tín hiệu và ko kết nối được với ivt
+2. KH yêu cầu: Qua triển khai, xử lý gấp cho KHDN</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09:44 20/03/2026</t>
+          <t>10:55 19/03/2026</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>19:55 27/03/2026</t>
+          <t>18:00 30/03/2026</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5051,50 +5062,50 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Võ Duy Khang</t>
+          <t>Lương Ngọc Hưng</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>473069</t>
+          <t>284060</t>
         </is>
       </c>
       <c r="Y33" s="2">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>vinhvv4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5114,7 +5125,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VCC_YCTX_NAN_37485587203842849</t>
+          <t>KHCN_TT.GPTH_HCM_1638575</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5122,24 +5133,29 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Xuân Hương</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0974371218</t>
+          <t>0911937779</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
+          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -5154,32 +5170,34 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
+3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>15:32 20/03/2026</t>
+          <t>09:25 19/03/2026</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17:15 02/04/2026</t>
+          <t>08:35 25/04/2026</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5194,33 +5212,33 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Trần Bình Thanh</t>
+          <t>Lê Đức Cảnh</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>069159</t>
+          <t>291002</t>
         </is>
       </c>
       <c r="Y34" s="2">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5250,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5252,37 +5270,42 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CRP2501952</t>
+          <t>KHCN_TT.GPTH_BNH_1615873</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH UNIVERSAL SCIENTIFIC INDUSTRIAL VIỆT NAM</t>
+          <t>Công Ty Tnhh Thương Mại Vận Tải Hùng Vĩ</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0985479660</t>
+          <t>0989558605</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Lô đất CN4.1H</t>
+          <t>Phường Xương Giang,Thành phố Bắc Giang,Tỉnh Bắc Giang</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5302,24 +5325,24 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>CN báo sự cố hộ KH
-1. KH phản ánh: Máy chủ scada mất tín hiệu và ko kết nối được với ivt
-2. KH yêu cầu: Qua triển khai, xử lý gấp cho KHDN</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Từ hqua tầm 10h tối, KH nghe thấy tiếng oạch 1 cái rồi mất điện xong 1 lúc sau lại thấy có ngay, KH ktra thì thấy biến tần ko chạy và thấy báo đỏ, ko hoạt động, theo dõi trên đt cũng thấy đang có vấn đề.
+3. KH yêu cầu: Qua hỗ trợ, kiểm tra nguyên nhân dẫn đến tình trạng và khắc phục cho KH.</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10:55 19/03/2026</t>
+          <t>09:25 18/03/2026</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>18:00 30/03/2026</t>
+          <t>18:00 29/03/2026</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5329,70 +5352,70 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Lương Ngọc Hưng</t>
+          <t>Hoàng Văn Chính</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>284060</t>
+          <t>284663</t>
         </is>
       </c>
       <c r="Y35" s="2">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>vinhvv4</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1638575</t>
+          <t>VCC_HS_HPG_1773463559534</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5400,71 +5423,64 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
+          <t>Anh Nhuận</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0911937779</t>
+          <t>0398685088</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
+          <t>493 đông hải hải an, Phường Hải An, Hải Phòng</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Liên hệ chậm</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
-3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
+          <t>KH gọi lên TĐ phản ánh KH đặt lịch bảo dưỡng từ ngày 14/3 nhưng ko có kỹ thuật liên hệ hẹn lịch, kh rất bức xúc yc kiểm tra lý do và yêu cầu VCC phản hồi thông tin cho kh qua email: hoanphihoan1987@gmail.com</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09:25 19/03/2026</t>
+          <t>13:31 16/03/2026</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>08:35 25/04/2026</t>
+          <t>09:00 17/03/2026</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5479,23 +5495,23 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Phạm Quang Toàn</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>048813</t>
         </is>
       </c>
       <c r="Y36" s="2">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5517,7 +5533,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5532,47 +5548,47 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1615873</t>
+          <t>KHDN_TT.GPTH_NBH_1627573</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Công Ty Tnhh Thương Mại Vận Tải Hùng Vĩ</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ GIANG HOÀNG HẢI</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0989558605</t>
+          <t>0836461111</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Phường Xương Giang,Thành phố Bắc Giang,Tỉnh Bắc Giang</t>
+          <t>Đường vĩnh lợi, phố mỹ lộ, p hoa lư, ninh bình</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5587,298 +5603,15 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Từ hqua tầm 10h tối, KH nghe thấy tiếng oạch 1 cái rồi mất điện xong 1 lúc sau lại thấy có ngay, KH ktra thì thấy biến tần ko chạy và thấy báo đỏ, ko hoạt động, theo dõi trên đt cũng thấy đang có vấn đề.
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra nguyên nhân dẫn đến tình trạng và khắc phục cho KH.</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>09:25 18/03/2026</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>18:00 29/03/2026</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Hoàng Văn Chính</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>284663</t>
-        </is>
-      </c>
-      <c r="Y37" s="2">
-        <v>46099</v>
-      </c>
-      <c r="Z37">
-        <v>8</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>VCC_HS_HPG_1773463559534</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Anh Nhuận</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0398685088</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>493 đông hải hải an, Phường Hải An, Hải Phòng</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Liên hệ chậm</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>KH gọi lên TĐ phản ánh KH đặt lịch bảo dưỡng từ ngày 14/3 nhưng ko có kỹ thuật liên hệ hẹn lịch, kh rất bức xúc yc kiểm tra lý do và yêu cầu VCC phản hồi thông tin cho kh qua email: hoanphihoan1987@gmail.com</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>13:31 16/03/2026</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>09:00 17/03/2026</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Phạm Quang Toàn</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>048813</t>
-        </is>
-      </c>
-      <c r="Y38" s="2">
-        <v>46097</v>
-      </c>
-      <c r="Z38">
-        <v>10</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_NBH_1627573</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ GIANG HOÀNG HẢI</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0836461111</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Đường vĩnh lợi, phố mỹ lộ, p hoa lư, ninh bình</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
         <is>
           <t>CN báo sự cố cho KH (0985951652)
 1.Đã báo chi nhánh chưa: có báo
@@ -5888,434 +5621,288 @@
 4. KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>10:57 17/03/2026</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>09:00 01/04/2026</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>11:46 10/04/2026</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Phạm Văn Đông</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>449553</t>
         </is>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y37" s="2">
         <v>46098</v>
       </c>
-      <c r="Z39">
-        <v>9</v>
-      </c>
-      <c r="AA39" t="inlineStr">
+      <c r="Z37">
+        <v>10</v>
+      </c>
+      <c r="AA37" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HCM_1646383</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Nghĩa</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0945919596</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>08:00 16/03/2026</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>08:45 12/04/2026</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lê Đức Cảnh</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>291002</t>
+        </is>
+      </c>
+      <c r="Y38" s="2">
+        <v>46097</v>
+      </c>
+      <c r="Z38">
+        <v>11</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNI_1514345</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>KHCN_PINNLMT_BGG_0345907</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Anh Thành</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0963715467</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>thôn Phù Mã</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Lê Văn Mạnh</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0987567050</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1.Đã báo chi nhánh chưa: chưa báo
-2.Đã báo qua đâu: gọi điện lên TĐ.
-3.KH phản ánh về vấn đề: Pin lưu trữ bị lỗi.
-4. KH yêu cầu KT qua kiểm tra gấp cho KH</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>10:32 17/03/2026</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>11:44 07/04/2026</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Phạm Văn Tình</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>463011</t>
-        </is>
-      </c>
-      <c r="Y40" s="2">
-        <v>46098</v>
-      </c>
-      <c r="Z40">
-        <v>9</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1646383</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Nguyễn Hữu Nghĩa</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0945919596</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>08:00 16/03/2026</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>08:45 12/04/2026</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Lê Đức Cảnh</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>291002</t>
-        </is>
-      </c>
-      <c r="Y41" s="2">
-        <v>46097</v>
-      </c>
-      <c r="Z41">
-        <v>10</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_BGG_0345907</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Lê Văn Mạnh</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0987567050</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.KH báo cho GĐ Trường 
@@ -6324,280 +5911,280 @@
  5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>10:21 10/03/2026</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>20:40 26/03/2026</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
         <is>
           <t>Thân Đức Giang</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>081984</t>
         </is>
       </c>
-      <c r="Y42" s="2">
+      <c r="Y39" s="2">
         <v>46091</v>
       </c>
-      <c r="Z42">
-        <v>16</v>
-      </c>
-      <c r="AA42" t="inlineStr">
+      <c r="Z39">
+        <v>17</v>
+      </c>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>QTI</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QTI_0991884</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Nguyễn Thị Như Mỹ</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>0963369267</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
 2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
 3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>08:00 09/03/2026</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>09:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>11:45 10/04/2026</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Trương Thành</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>462341</t>
         </is>
       </c>
-      <c r="Y43" s="2">
+      <c r="Y40" s="2">
         <v>46090</v>
       </c>
-      <c r="Z43">
-        <v>17</v>
-      </c>
-      <c r="AA43" t="inlineStr">
+      <c r="Z40">
+        <v>18</v>
+      </c>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>QNI</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_KTM_0284233</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Nguyễn Xuân Quyết</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>0981397050</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Khối phố 6, Thị trấn Plei Kần, Huyện Ngọc Hồi, Tỉnh Kon Tum</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo 
 2.Đã báo cho ai:  NV Văn
@@ -6606,145 +6193,145 @@
 5.	 KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>14:54 05/03/2026</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>17:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Đỗ Lê Thanh Dĩnh</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>041111</t>
         </is>
       </c>
-      <c r="Y44" s="2">
+      <c r="Y41" s="2">
         <v>46086</v>
       </c>
-      <c r="Z44">
-        <v>21</v>
-      </c>
-      <c r="AA44" t="inlineStr">
+      <c r="Z41">
+        <v>22</v>
+      </c>
+      <c r="AA41" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Nguyễn Phú Quý</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>0947110192</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -6752,14 +6339,438 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>15:09 03/03/2026</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>12:55 15/03/2026</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lê Đức Cảnh</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>291002</t>
+        </is>
+      </c>
+      <c r="Y42" s="2">
+        <v>46084</v>
+      </c>
+      <c r="Z42">
+        <v>24</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Trường Tiểu Học Quỳnh Hưng</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0963785576</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1. Kh chưa báo cn
+2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
+3. Kh yc: Yc cn hỗ trợ</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>16:54 26/02/2026</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>18:00 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lê Văn Toán</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>119464</t>
+        </is>
+      </c>
+      <c r="Y43" s="2">
+        <v>46079</v>
+      </c>
+      <c r="Z43">
+        <v>29</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>tietvt16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_DNI_1659133</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0907002673</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1. Kh đã báo cn
+2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
+3. kh yc: YC cn hỗ trợ sớm</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>13:30 23/02/2026</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>18:30 21/03/2026</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Tâm Định</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>450471</t>
+        </is>
+      </c>
+      <c r="Y44" s="2">
+        <v>46076</v>
+      </c>
+      <c r="Z44">
+        <v>32</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>KHCN_PINNLMT_NAN_0334667</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Lê Trung An</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0865878212</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>- KH phản ánh ivt mới mang bảo hành về được mấy hôm lại lỗi không sử dụng được
+- KH Yc cho nv qua htro khắc phục triệt để</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>15:09 03/03/2026</t>
+          <t>16:02 26/01/2026</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>12:55 15/03/2026</t>
+          <t>10:00 30/03/2026</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6774,19 +6785,19 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Nguyễn Minh Linh</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>285776</t>
         </is>
       </c>
       <c r="Y45" s="2">
-        <v>46084</v>
+        <v>46048</v>
       </c>
       <c r="Z45">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6822,42 +6833,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Trường Tiểu Học Quỳnh Hưng</t>
+          <t>Trương Công An</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0963785576</t>
+          <t>0914531694</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+          <t>khối 2</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -6867,7 +6883,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -6877,7 +6893,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -6887,19 +6903,18 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1. Kh chưa báo cn
-2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
-3. Kh yc: Yc cn hỗ trợ</t>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>16:54 26/02/2026</t>
+          <t>08:00 19/01/2026</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>18:00 31/03/2026</t>
+          <t>22:00 17/04/2026</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6909,50 +6924,50 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Lê Văn Toán</t>
+          <t>Lê Văn Anh</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>119464</t>
+          <t>069170</t>
         </is>
       </c>
       <c r="Y46" s="2">
-        <v>46079</v>
+        <v>46041</v>
       </c>
       <c r="Z46">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6967,12 +6982,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_DNI_1659133</t>
+          <t>KHDN_TT.GPTH_QNH_1468057</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6980,11 +6995,6 @@
           <t>B2B</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
@@ -6992,17 +7002,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẦU TƯ VÀ PHÁT TRIỂN BẤT ĐỘNG SẢN TOÀN CẦU</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0907002673</t>
+          <t>0989815656</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+          <t>Phường Bãi Cháy,Thành phố Hạ Long,Tỉnh Quảng Ninh</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7022,438 +7032,15 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
-        <is>
-          <t>1. Kh đã báo cn
-2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
-3. kh yc: YC cn hỗ trợ sớm</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>13:30 23/02/2026</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>18:30 21/03/2026</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Nguyễn Hữu Tâm Định</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>450471</t>
-        </is>
-      </c>
-      <c r="Y47" s="2">
-        <v>46076</v>
-      </c>
-      <c r="Z47">
-        <v>31</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_NAN_0334667</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Lê Trung An</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0865878212</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>- KH phản ánh ivt mới mang bảo hành về được mấy hôm lại lỗi không sử dụng được
-- KH Yc cho nv qua htro khắc phục triệt để</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>16:02 26/01/2026</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>10:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Nguyễn Minh Linh</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>285776</t>
-        </is>
-      </c>
-      <c r="Y48" s="2">
-        <v>46048</v>
-      </c>
-      <c r="Z48">
-        <v>59</v>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Trương Công An</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>0914531694</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>khối 2</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>08:00 19/01/2026</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>22:00 17/04/2026</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Lê Văn Anh</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>069170</t>
-        </is>
-      </c>
-      <c r="Y49" s="2">
-        <v>46041</v>
-      </c>
-      <c r="Z49">
-        <v>66</v>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_QNH_1468057</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẦU TƯ VÀ PHÁT TRIỂN BẤT ĐỘNG SẢN TOÀN CẦU</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0989815656</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Phường Bãi Cháy,Thành phố Hạ Long,Tỉnh Quảng Ninh</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
         <is>
           <t>1. Kh chưa báo cn
 2. Kh phản ánh:
@@ -7463,424 +7050,424 @@
 *Ghi chú: sdt phản ánh 0981972868</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>08:19 15/01/2026</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>16:00 20/01/2026</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Lê Thanh Tú</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>113238</t>
         </is>
       </c>
-      <c r="Y50" s="2">
+      <c r="Y47" s="2">
         <v>46037</v>
       </c>
-      <c r="Z50">
-        <v>70</v>
-      </c>
-      <c r="AA50" t="inlineStr">
+      <c r="Z47">
+        <v>71</v>
+      </c>
+      <c r="AA47" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_0885867</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Nguyễn Đức Hùng</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>0396264028</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>1. Đã báo CN: Chưa báo
 2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
 3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>08:00 14/01/2026</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>17:00 25/02/2026</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Trần Xuân Kương</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>289759</t>
         </is>
       </c>
-      <c r="Y51" s="2">
+      <c r="Y48" s="2">
         <v>46036</v>
       </c>
-      <c r="Z51">
-        <v>71</v>
-      </c>
-      <c r="AA51" t="inlineStr">
+      <c r="Z48">
+        <v>72</v>
+      </c>
+      <c r="AA48" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>M&amp;E</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Bếp từ</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Nguyễn Quang Vũ</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0983034568</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>CNCT Viettel Bắc Ninh</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
 Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>08:00 05/01/2026</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>10:25 03/04/2026</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Đinh Thị Ngọc</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>205029</t>
         </is>
       </c>
-      <c r="Y52" s="2">
+      <c r="Y49" s="2">
         <v>46027</v>
       </c>
-      <c r="Z52">
-        <v>80</v>
-      </c>
-      <c r="AA52" t="inlineStr">
+      <c r="Z49">
+        <v>81</v>
+      </c>
+      <c r="AA49" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>Anhnt631</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Dịch vụ khác</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>0962892720</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -7888,53 +7475,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>08:00 10/12/2025</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>15:00 16/12/2025</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y53" s="2">
+      <c r="Y50" s="2">
         <v>46001</v>
       </c>
-      <c r="Z53">
-        <v>106</v>
-      </c>
-      <c r="AA53" t="inlineStr">
+      <c r="Z50">
+        <v>107</v>
+      </c>
+      <c r="AA50" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>vinhvv4</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -1783,12 +1783,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -7518,12 +7518,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>vinhvv4</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -511,12 +511,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+          <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VCC_HS_CMU_1774325231892</t>
+          <t>VCC_HS_QTI_1774347935114</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,11 +544,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -556,17 +551,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Viết Đông</t>
+          <t>Anhh Bảo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0902575123</t>
+          <t>0387766616</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Long điền ,đông hải,bạc liêu, Phường Bạc Liêu, Tỉnh Cà Mau</t>
+          <t>TDP7 xã Minh Hoá, Quảng Trị, Xã Minh Hóa, Tỉnh Quảng Trị</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -581,22 +576,22 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trước bán</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Phàn nàn, Góp Ý</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Liên hệ chậm</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>KT ko vệ sinh cục nóng mà vẫn thu tiền đủ, KH càm thấy ko hài lòng.</t>
+          <t>KH hẹn 25/3 mà ko thấy ai liên hệ yêu cầu KT liên hệ trao đổi với KH.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -621,12 +616,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Nguyễn Trí Đạt</t>
+          <t>Phạm Ngọc Hiếu</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>437699</t>
+          <t>285546</t>
         </is>
       </c>
       <c r="Y2" s="2">
@@ -659,27 +654,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Chi phí đến nhà kiểm tra DV Home Services (trong trường hợp KH không phát sinh đơn dịch vụ hoặc vật tư)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_LCI_1631825</t>
+          <t>VCC_HS_QNH_1773466348941</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -687,11 +682,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -699,22 +689,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Hoàng Thị Khuyên</t>
+          <t>Nguyễn Văn Thiết</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0915964280</t>
+          <t>0912811551</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Phường Duyên Hải, Thành phố Lào Cai, Tỉnh Lào Cai</t>
+          <t>Nhà máy fanstech khu công nghiệp Bắc Tiền Phong phường Phong Cốc Quảng Ninh, Phường Phong Cốc, Tỉnh Quảng Ninh</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -724,25 +714,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trước bán</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Liên hệ chậm</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN nhưng chưa được hỗ trợ
-2. KH phản ánh: Điện chỉ ăn vào điện lưới quốc gia mất 1,6-2tr tiền điện và khi mất điện ko tự động nhảy sang điện nlmt mà mất điện hết toàn bộ. KH lắp 3 pha nhưng thấy chỉ hỗ trợ điện 1 pha.
-3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH.
-***SĐT phản ánh: 0359247000</t>
+          <t>KH hẹn vào 15/3 mà ko thấy ai liên hệ.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -757,7 +744,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -767,12 +754,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Trần Hữu Tuân</t>
+          <t>Nguyễn Việt An</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>431016</t>
+          <t>419449</t>
         </is>
       </c>
       <c r="Y3" s="2">
@@ -783,7 +770,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -800,62 +787,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VCC_HS_QTI_1774347935114</t>
+          <t>KHDN_TT.GPTH_BDG_1495422</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Anhh Bảo</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0387766616</t>
+          <t>0918236379</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>TDP7 xã Minh Hoá, Quảng Trị, Xã Minh Hóa, Tỉnh Quảng Trị</t>
+          <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -865,37 +857,39 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>KH hẹn 25/3 mà ko thấy ai liên hệ yêu cầu KT liên hệ trao đổi với KH.</t>
+          <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
+2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
+3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>13:30 27/03/2026</t>
+          <t>16:08 26/03/2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>09:00 30/03/2026</t>
+          <t>09:00 05/04/2026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -905,23 +899,23 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Nguyễn Bá Huy</t>
+          <t>Trần Văn Thắng</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>069300</t>
+          <t>470289</t>
         </is>
       </c>
       <c r="Y4" s="2">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -938,32 +932,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>CNTT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chi phí đến nhà kiểm tra DV Home Services (trong trường hợp KH không phát sinh đơn dịch vụ hoặc vật tư)</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VCC_HS_QNH_1773466348941</t>
+          <t>KHCN_TT.GPTH_DNG_1240036</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -978,22 +972,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thiết</t>
+          <t>Nguyễn Văn Thiên</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0912811551</t>
+          <t>0935302100</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Nhà máy fanstech khu công nghiệp Bắc Tiền Phong phường Phong Cốc Quảng Ninh, Phường Phong Cốc, Tỉnh Quảng Ninh</t>
+          <t>48 nguyễn đình chiểu, Phường Khuê Mỹ, Quận Ngũ Hành Sơn, Thành phố Đà Nẵng</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1003,27 +997,28 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>KH hẹn vào 15/3 mà ko thấy ai liên hệ.</t>
+          <t>1. KH phản ánh: Camera bị rớt không kết nối được, và cả mật khẩu wifi
+2. KH yêu cầu: Hỗ trợ KH cài đặt lại camera.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>13:30 27/03/2026</t>
+          <t>10:11 27/03/2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1033,7 +1028,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1043,12 +1038,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Nguyễn Việt An</t>
+          <t>Trần Xuân Bách</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>419449</t>
+          <t>071337</t>
         </is>
       </c>
       <c r="Y5" s="2">
@@ -1059,29 +1054,29 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KHCN_TMNLMT_BDH_0297148</t>
+          <t>0901/NLMT/VCCTNH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1116,17 +1111,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lê Đình Khánh</t>
+          <t>Nguyễn Hải Lương</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0388773033</t>
+          <t>0983730342</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cát Minh, Xã Cát Minh, Huyện Phù Cát, Tỉnh Bình Định</t>
+          <t>Thị trấn Tân Châu,Huyện Tân Châu,Tỉnh Tây Ninh</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1151,24 +1146,24 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn:  
-2. KH phản ánh:Hệ thống nlmt ko chạy ra kw, cứ đang chạy đỏ rồi lại đứng lại. Sản lượng ra thì thấp,  
-3. KH yêu cầu: Qua hỗ trợ, xử lý, hướng dẫn cho KH hiểu. KH sẽ sẵn sàng trả thêm phí nếu phát sinh thêm và cũng sẵn sàng hỗ trợ nếu xử lý dứt điểm được cho KH.</t>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Hệ của KH sản lượng rất thấp, hqua nắng to cả ngày 39 độ mà ko được nổi 200kw trên hệ 52kw của KH.
+3. KH yêu cầu: Kiểm tra đo đạc lại thiết bị, và xem thiết kế lại đường đi dòng điện 3 pha, và xem có phương án để tối ưu sản lượng cho KH ko tư vấn, hướng dẫn cho KH.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>16:28 26/03/2026</t>
+          <t>08:00 27/03/2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>16:28 27/03/2026</t>
+          <t>09:00 30/03/2026</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1178,38 +1173,38 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Nguyễn Quang Toàn</t>
+          <t>Nguyễn Quốc Hưng</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>293989</t>
+          <t>467401</t>
         </is>
       </c>
       <c r="Y6" s="2">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>truongdv17</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1241,12 +1236,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_BDG_1495422</t>
+          <t>KHCN_TT.GPTH_TNH_1639818</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1256,27 +1251,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
+          <t>Lý Đức Huy</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0918236379</t>
+          <t>0903101647</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
+          <t>khu phố An Thới</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1291,29 +1286,29 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
-2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
-3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
+          <t>CN báo sự cố hộ KH
+1. KH phản ánh: Pin lưu trữ đang bị hỏng và mất luôn nguồn pin lưu trữ.
+2. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>16:08 26/03/2026</t>
+          <t>14:47 26/03/2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>09:00 05/04/2026</t>
+          <t>08:55 04/04/2026</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1328,12 +1323,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Trần Văn Thắng</t>
+          <t>Nguyễn Quốc Hưng</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>470289</t>
+          <t>467401</t>
         </is>
       </c>
       <c r="Y7" s="2">
@@ -1366,7 +1361,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1376,17 +1371,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1240036</t>
+          <t>KHCN_TT.GPTH_GLI_1676729</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1394,6 +1389,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -1401,17 +1401,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thiên</t>
+          <t>Rơ Ô WÊ</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0935302100</t>
+          <t>0396081566</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>48 nguyễn đình chiểu, Phường Khuê Mỹ, Quận Ngũ Hành Sơn, Thành phố Đà Nẵng</t>
+          <t>Thôn Ia Prông</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1426,33 +1426,32 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1. KH phản ánh: Camera bị rớt không kết nối được, và cả mật khẩu wifi
-2. KH yêu cầu: Hỗ trợ KH cài đặt lại camera.</t>
+          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10:11 27/03/2026</t>
+          <t>10:43 26/03/2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>09:00 30/03/2026</t>
+          <t>08:35 31/03/2026</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1467,19 +1466,19 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Trần Xuân Bách</t>
+          <t>Nguyễn Hà Nguyên</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>071337</t>
+          <t>060709</t>
         </is>
       </c>
       <c r="Y8" s="2">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1500,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1525,7 +1524,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0901/NLMT/VCCTNH</t>
+          <t>KHCN_NLMT_NTN_0241352</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1540,17 +1539,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nguyễn Hải Lương</t>
+          <t>Nguyễn Văn Sanh</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0983730342</t>
+          <t>0913785605</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Thị trấn Tân Châu,Huyện Tân Châu,Tỉnh Tây Ninh</t>
+          <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1575,24 +1574,24 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
-2. KH phản ánh: Hệ của KH sản lượng rất thấp, hqua nắng to cả ngày 39 độ mà ko được nổi 200kw trên hệ 52kw của KH.
-3. KH yêu cầu: Kiểm tra đo đạc lại thiết bị, và xem thiết kế lại đường đi dòng điện 3 pha, và xem có phương án để tối ưu sản lượng cho KH ko tư vấn, hướng dẫn cho KH.</t>
+2. KH phản ánh: Ivt bị lỗi ko hoạt động, KH ktra thấy còn ko chạy
+3. KH yêu cầu: Qua hỗ trợ, kiểm tra, khắc phục tình trạng này cho KH</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>08:00 27/03/2026</t>
+          <t>08:25 26/03/2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>09:00 30/03/2026</t>
+          <t>16:50 30/03/2026</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1607,45 +1606,45 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Hưng</t>
+          <t>Nguyễn Văn Vương</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>467401</t>
+          <t>069846</t>
         </is>
       </c>
       <c r="Y9" s="2">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1665,7 +1664,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNH_1639818</t>
+          <t>KHCN_TT.GPTH_HDG_1304417</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1685,22 +1684,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lý Đức Huy</t>
+          <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0903101647</t>
+          <t>0377883716</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>khu phố An Thới</t>
+          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1715,29 +1714,29 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>CN báo sự cố hộ KH
-1. KH phản ánh: Pin lưu trữ đang bị hỏng và mất luôn nguồn pin lưu trữ.
-2. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này cho KH.</t>
+          <t>KH chưa báo CN
+KH yêu cầu NVKT qua lại thiết bị inverter của KH 
+Số liên hệ:</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>14:47 26/03/2026</t>
+          <t>08:00 26/03/2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>08:55 04/04/2026</t>
+          <t>17:25 02/04/2026</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1752,12 +1751,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Hưng</t>
+          <t>Hoàng Văn Phong</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>467401</t>
+          <t>291011</t>
         </is>
       </c>
       <c r="Y10" s="2">
@@ -1785,12 +1784,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1810,7 +1809,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_GLI_1676729</t>
+          <t>KHCN_TT.GPTH_HCM_1169983</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1818,11 +1817,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -1830,17 +1824,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Rơ Ô WÊ</t>
+          <t>Đường Quyền Hồng</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0396081566</t>
+          <t>0907395121</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Thôn Ia Prông</t>
+          <t>Ấp 4, Xã Phước Kiển, Huyện Nhà Bè, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1855,32 +1849,34 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: Lỗi CP bị cúp điện dưới nhà, hiện tại điện ko sử dụng được.
+3. KH yêu cầu: Qua kiểm tra, hỗ trợ, khắc phục gấp cho KH giờ nhà KH đang ko có điện để sử dụng.</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>10:43 26/03/2026</t>
+          <t>09:32 26/03/2026</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>08:35 31/03/2026</t>
+          <t>16:05 31/03/2026</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1895,12 +1891,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Nguyễn Hà Nguyên</t>
+          <t>Điểu Ngọc Lâm</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>060709</t>
+          <t>432612</t>
         </is>
       </c>
       <c r="Y11" s="2">
@@ -1916,12 +1912,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1949,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KHCN_NLMT_NTN_0241352</t>
+          <t>KHCN_TT.GPTH_KHA_1631515</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1961,6 +1957,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -1968,22 +1969,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Sanh</t>
+          <t>Phạm Hải Triều</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0913785605</t>
+          <t>0903576559</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
+          <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2008,19 +2009,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Ivt bị lỗi ko hoạt động, KH ktra thấy còn ko chạy
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra, khắc phục tình trạng này cho KH</t>
+          <t>CN báo sự cố hộ KH
+1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
+2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>08:25 26/03/2026</t>
+          <t>08:00 26/03/2026</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>14:00 27/03/2026</t>
+          <t>17:35 27/03/2026</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2030,17 +2031,17 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vương</t>
+          <t>Phan Trọng Nghĩa</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>069846</t>
+          <t>234935</t>
         </is>
       </c>
       <c r="Y12" s="2">
@@ -2073,7 +2074,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2093,12 +2094,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HDG_1304417</t>
+          <t>KHDN_TT.GPTH_HNI_1646163</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2108,22 +2109,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hồng Khánh</t>
+          <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0377883716</t>
+          <t>0973721368</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
+          <t>Triệu Xuyên, Long xuyên</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2143,445 +2144,15 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN
-KH yêu cầu NVKT qua lại thiết bị inverter của KH 
-Số liên hệ:</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>08:00 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>17:25 02/04/2026</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Hoàng Văn Phong</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>291011</t>
-        </is>
-      </c>
-      <c r="Y13" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z13">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1169983</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Đường Quyền Hồng</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0907395121</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Ấp 4, Xã Phước Kiển, Huyện Nhà Bè, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: Lỗi CP bị cúp điện dưới nhà, hiện tại điện ko sử dụng được.
-3. KH yêu cầu: Qua kiểm tra, hỗ trợ, khắc phục gấp cho KH giờ nhà KH đang ko có điện để sử dụng.</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>09:32 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>16:05 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Điểu Ngọc Lâm</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>432612</t>
-        </is>
-      </c>
-      <c r="Y14" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z14">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_KHA_1631515</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Phạm Hải Triều</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0903576559</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>CN báo sự cố hộ KH
-1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
-2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>08:00 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>17:35 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Phan Trọng Nghĩa</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>234935</t>
-        </is>
-      </c>
-      <c r="Y15" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z15">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HNI_1646163</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0973721368</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Triệu Xuyên, Long xuyên</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
         <is>
           <t>1. KH đã báo cn a Long gđ kỹ thuật, a Dương Đăng Minh chủ ký HĐ, a Vương lắp đặt.
 2. KH phản ánh: Bị nhảy áp liên tục 1 tháng phải nhảy 20 ngày rơi vào khoảng 2h đêm và 12h trưa ban ngày, và chập tối lúc GĐ đang vào sinh hoạt. CN nhiều lần xuống ktra và kiến nghị nhưng có câu trả lời KH ko được hài lòng lắm. Đặc biệt là a Long GĐ KT có thái độ là đổ cho GĐ tắt áp, KH bức xúc vì KH bỏ đồng tiền ra mà lại đổ lỗi cho nhà KH. KH cũng báo với a Dương Đăng Minh, a Minh cũng bảo là để cháu bảo ae xuống thế nọ thế kia khất để ra giêng để sửa mà giờ hết tháng rồi vẫn ko thấy đâu.
@@ -2589,430 +2160,430 @@
 ***SĐT liên hệ: 0945268772, chú Bồng</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>14:58 25/03/2026</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>23:00 06/04/2026</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y13" s="2">
         <v>46106</v>
       </c>
-      <c r="Z16">
+      <c r="Z13">
         <v>2</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1600729</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Nguyễn Khương</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0977113014</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
 2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
 3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>09:20 25/03/2026</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>17:25 27/03/2026</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Phạm Khắc Việt</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>048379</t>
         </is>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y14" s="2">
         <v>46106</v>
       </c>
-      <c r="Z17">
+      <c r="Z14">
         <v>2</v>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_NTN_0470662</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Lê Anh Tuấn</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0949186789</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Phường Phan Rang ,Tỉnh Ninh Thuận</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>CN 0962600057 báo sự cố hộ KH, trước lắp đặt cho KH giờ chuyển công tác.
 1. KH phản ánh: Lỗi ivt ko hoạt động, ko nạp và xả ra được
 2. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này cho KH</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>08:25 25/03/2026</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>19:50 28/03/2026</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Nguyễn Văn Vương</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>069846</t>
         </is>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y15" s="2">
         <v>46106</v>
       </c>
-      <c r="Z18">
+      <c r="Z15">
         <v>2</v>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VPC_1503902</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Nguyễn Việt Hùng</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0966547344</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH đang dùng NLMT hiện tại bị lỗi biến tần, ko kết nối được app
@@ -3020,14 +2591,446 @@
 NOTE: địa chỉ hiện tại của KH: thôn phú mỹ, xã tiến thắng, Hà Nội</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>15:34 24/03/2026</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>17:30 01/04/2026</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Phạm Văn Nghĩa</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>023020</t>
+        </is>
+      </c>
+      <c r="Y16" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z16">
+        <v>3</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BDG_1352264</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Nguyễn Liễu Thông</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0362126000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>không hoạt động</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>09:29 26/03/2026</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>09:00 01/04/2026</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Toản</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>427880</t>
+        </is>
+      </c>
+      <c r="Y17" s="2">
+        <v>46107</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NTN_1595255</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Mỹ Linh</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0976685068</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1/19 Hàm Nghi, Phước Mỹ, Phan Rang, Ninh Thuận</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1. KH phản ánh: ko tải được app về được và ko xem được mức điện tiêu thụ.
+2. KH yêu cầu: Hỗ trợ cho KH tải app và đăng nhập để xem hiệu suất nlmt.</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>16:44 24/03/2026</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>17:30 29/03/2026</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bùi Khắc Hoàng Linh</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>454887</t>
+        </is>
+      </c>
+      <c r="Y18" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z18">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_PTO_1620637</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Nguyễn Đình Mạnh</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0988308581</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>KH chưa báo CN
+KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
+KH yêu cầu chuyển KT xuống xử lý gấp</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>15:34 24/03/2026</t>
+          <t>15:09 24/03/2026</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17:30 01/04/2026</t>
+          <t>09:10 29/03/2026</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3042,12 +3045,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Phạm Văn Nghĩa</t>
+          <t>Bùi Anh Nguyễn</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>023020</t>
+          <t>414445</t>
         </is>
       </c>
       <c r="Y19" s="2">
@@ -3075,12 +3078,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3095,12 +3098,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BDG_1352264</t>
+          <t>KHCN_TT.GPTH_DLK_1648454</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3110,7 +3113,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3120,17 +3123,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nguyễn Liễu Thông</t>
+          <t>Huỳnh Chí Băng</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0362126000</t>
+          <t>0366448992</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ph</t>
+          <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3160,17 +3163,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>không hoạt động</t>
+          <t>KH đã báo CN: a Nguyễn Văn Hà	nửa thasg nhưng chưa có ai đến hỗ trợ
+KH phản ánh hệ thống điện năng lượng mặt trời ko hoạt động
+KH yêu cầu xử lý gấp</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09:29 26/03/2026</t>
+          <t>15:19 24/03/2026</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>17:30 31/03/2026</t>
+          <t>10:50 31/03/2026</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3185,19 +3190,19 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Toản</t>
+          <t>Nguyễn Văn Hà</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>427880</t>
+          <t>008244</t>
         </is>
       </c>
       <c r="Y20" s="2">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="Z20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3218,12 +3223,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3233,52 +3238,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>CNTT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Camera 360 độ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NTN_1595255</t>
+          <t>299/2025/HĐKT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Silver</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Mỹ Linh</t>
+          <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0976685068</t>
+          <t>0869217169</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1/19 Hàm Nghi, Phước Mỹ, Phan Rang, Ninh Thuận</t>
+          <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3298,584 +3298,10 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
-        <is>
-          <t>1. KH phản ánh: ko tải được app về được và ko xem được mức điện tiêu thụ.
-2. KH yêu cầu: Hỗ trợ cho KH tải app và đăng nhập để xem hiệu suất nlmt.</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>16:44 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>17:30 29/03/2026</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Bùi Khắc Hoàng Linh</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>454887</t>
-        </is>
-      </c>
-      <c r="Y21" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z21">
-        <v>3</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_PTO_1620637</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Nguyễn Đình Mạnh</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0988308581</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN
-KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
-KH yêu cầu chuyển KT xuống xử lý gấp</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>15:09 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>09:10 29/03/2026</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Bùi Anh Nguyễn</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>414445</t>
-        </is>
-      </c>
-      <c r="Y22" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z22">
-        <v>3</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1653908</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Tài</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0916371137</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>xóm 5 hưng Thịnh Cũ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Ivt vẫn hoạt động bthg nhưng vào app chỉ thấy dừng ở 20% và ko kiểm tra được lượng điện vào bao nhiêu.
-3. KH yêu cầu: Kiểm tra xem thiết bị có vấn đề gì không và hướng dẫn KH theo dõi hiệu suất.</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>08:32 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>20:05 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Phan Bùi Nam</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>119107</t>
-        </is>
-      </c>
-      <c r="Y23" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z23">
-        <v>3</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>DLK</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DLK_1648454</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Huỳnh Chí Băng</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0366448992</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>KH đã báo CN: a Nguyễn Văn Hà	nửa thasg nhưng chưa có ai đến hỗ trợ
-KH phản ánh hệ thống điện năng lượng mặt trời ko hoạt động
-KH yêu cầu xử lý gấp</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>15:19 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>10:50 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Hà</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>008244</t>
-        </is>
-      </c>
-      <c r="Y24" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z24">
-        <v>3</v>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CNTT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Camera 360 độ</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>299/2025/HĐKT</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0869217169</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: camera 360 chưa kết nối được hệ thống điều khiển, chưa lên được tivi để xem và cũng như pccc rừng mùa khô.
@@ -3883,578 +3309,578 @@
 ***SĐT liên hệ: 0988867428, Anh Thức</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>08:45 24/03/2026</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>23:05 30/03/2026</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Võ Trọng Đức</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>293804</t>
         </is>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y21" s="2">
         <v>46105</v>
       </c>
-      <c r="Z25">
+      <c r="Z21">
         <v>3</v>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>tietvt16</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>CNTT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1265325</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Bích Loan</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0946842984</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Bích Loan Cống Hội Đồng Nguyên</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>cammera bị off 1 cai</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>10:28 26/03/2026</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>17:30 28/03/2026</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Lý Hoài Bảo</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>433302</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y22" s="2">
         <v>46107</v>
       </c>
-      <c r="Z26">
+      <c r="Z22">
         <v>1</v>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>Tuyendv</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HYN_1630850</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI ĐẦU TƯ PHÁT TRIỂN MINH GIA</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>0965326111</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Số 93 Chu Mạnh Trinh,Phường Hiến Nam,Thành phố Hưng Yên,Tỉnh Hưng Yên</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>KH cần hỗ trợ chuyển đường dây điện 1 phòng trong nhà vào hệ thống điện NLMT 
 Quán cf góc kdt 379 Hưng Hà Thái Bình 
 Số liên hệ: chị Hường</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>15:02 23/03/2026</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>17:45 29/03/2026</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Nguyễn Duy Đức</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>282796</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y23" s="2">
         <v>46104</v>
       </c>
-      <c r="Z27">
+      <c r="Z23">
         <v>4</v>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BPC_1427400</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Công Ty Tnhh Phúc An Solutions</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>0972342939</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Cục pin lưu trữ đang ko hoạt động, ko sử dụng được.
 3. KH yêu cầu: Có KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>14:29 23/03/2026</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>07:20 02/04/2026</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Phạm Trung Hiếu</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>264250</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y24" s="2">
         <v>46104</v>
       </c>
-      <c r="Z28">
+      <c r="Z24">
         <v>4</v>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>GLI</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>100901-KD/HDMB-2021/GLI-TT</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0862000202</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo 
 2.Đã báo qua đâu: KH gọi TĐ
@@ -4462,290 +3888,290 @@
 4. KH yêu cầu KT qua kiểm tra xử lý cho KH.</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>12:45 31/03/2026</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Nguyễn Hà Nguyên</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>060709</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y25" s="2">
         <v>46104</v>
       </c>
-      <c r="Z29">
+      <c r="Z25">
         <v>4</v>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>truongdv17</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>DNG</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Công tắc thông minh</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNG_1416913</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Lê Đắc Quỳ</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>0915313915</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>08:55 30/03/2026</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Ngô Văn Minh</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>083585</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y26" s="2">
         <v>46104</v>
       </c>
-      <c r="Z30">
+      <c r="Z26">
         <v>4</v>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Dương Văn Quân</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0359999199</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>xã Hoàng Vân</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -4753,145 +4179,145 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>18:00 26/03/2026</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>408869</t>
         </is>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y27" s="2">
         <v>46104</v>
       </c>
-      <c r="Z31">
+      <c r="Z27">
         <v>4</v>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1384534</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Nguyễn Đức Hiếu</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>0949001616</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Khóm 10</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.Đã báo cho ai:  KT Thái
@@ -4900,568 +4326,568 @@
 5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>09:44 20/03/2026</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>19:55 27/03/2026</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Võ Duy Khang</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>473069</t>
         </is>
       </c>
-      <c r="Y32" s="2">
+      <c r="Y28" s="2">
         <v>46101</v>
       </c>
-      <c r="Z32">
+      <c r="Z28">
         <v>7</v>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>VCC_YCTX_NAN_37485587203842849</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Xuân Hương</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>0974371218</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Trước bán</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Tư vấn sản phẩm/dịch vụ</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>15:32 20/03/2026</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>17:15 02/04/2026</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Trần Bình Thanh</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>069159</t>
         </is>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y29" s="2">
         <v>46101</v>
       </c>
-      <c r="Z33">
+      <c r="Z29">
         <v>7</v>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>P.KDNLMT</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>P.KDNLMT</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>CRP2501952</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH UNIVERSAL SCIENTIFIC INDUSTRIAL VIỆT NAM</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>0985479660</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Lô đất CN4.1H</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>CN báo sự cố hộ KH
 1. KH phản ánh: Máy chủ scada mất tín hiệu và ko kết nối được với ivt
 2. KH yêu cầu: Qua triển khai, xử lý gấp cho KHDN</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>10:55 19/03/2026</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>18:00 30/03/2026</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Lương Ngọc Hưng</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>284060</t>
         </is>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y30" s="2">
         <v>46100</v>
       </c>
-      <c r="Z34">
+      <c r="Z30">
         <v>8</v>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>vinhvv4</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1638575</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0911937779</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
 3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>09:25 19/03/2026</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>08:35 25/04/2026</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y31" s="2">
         <v>46100</v>
       </c>
-      <c r="Z35">
+      <c r="Z31">
         <v>8</v>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>NBH</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Acquy lưu trữ</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_NBH_1627573</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ GIANG HOÀNG HẢI</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>0836461111</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Đường vĩnh lợi, phố mỹ lộ, p hoa lư, ninh bình</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>CN báo sự cố cho KH (0985951652)
 1.Đã báo chi nhánh chưa: có báo
@@ -5471,288 +4897,288 @@
 4. KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>10:57 17/03/2026</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>11:46 10/04/2026</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Phạm Văn Đông</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>449553</t>
         </is>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y32" s="2">
         <v>46098</v>
       </c>
-      <c r="Z36">
+      <c r="Z32">
         <v>10</v>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1646383</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Nguyễn Hữu Nghĩa</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>0945919596</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>08:00 16/03/2026</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>08:45 12/04/2026</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y37" s="2">
+      <c r="Y33" s="2">
         <v>46097</v>
       </c>
-      <c r="Z37">
+      <c r="Z33">
         <v>11</v>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_BGG_0404930</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Lê Văn Mạnh</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>0987567050</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.KH báo cho GĐ Trường 
@@ -5761,280 +5187,280 @@
  5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>10:21 10/03/2026</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>09:00 30/03/2026</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Thân Đức Giang</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>081984</t>
         </is>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y34" s="2">
         <v>46091</v>
       </c>
-      <c r="Z38">
+      <c r="Z34">
         <v>17</v>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>QTI</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QTI_0991884</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Nguyễn Thị Như Mỹ</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>0963369267</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
 2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
 3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>08:00 09/03/2026</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>11:45 10/04/2026</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Trương Thành</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>462341</t>
         </is>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y35" s="2">
         <v>46090</v>
       </c>
-      <c r="Z39">
+      <c r="Z35">
         <v>18</v>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>QNI</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_KTM_0284233</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Nguyễn Xuân Quyết</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>0981397050</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Khối phố 6, Thị trấn Plei Kần, Huyện Ngọc Hồi, Tỉnh Kon Tum</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo 
 2.Đã báo cho ai:  NV Văn
@@ -6043,145 +5469,145 @@
 5.	 KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>14:54 05/03/2026</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>17:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Đỗ Lê Thanh Dĩnh</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>041111</t>
         </is>
       </c>
-      <c r="Y40" s="2">
+      <c r="Y36" s="2">
         <v>46086</v>
       </c>
-      <c r="Z40">
+      <c r="Z36">
         <v>22</v>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Nguyễn Phú Quý</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>0947110192</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -6189,14 +5615,582 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>15:09 03/03/2026</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>12:55 15/03/2026</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lê Đức Cảnh</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>291002</t>
+        </is>
+      </c>
+      <c r="Y37" s="2">
+        <v>46084</v>
+      </c>
+      <c r="Z37">
+        <v>24</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Trường Tiểu Học Quỳnh Hưng</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0963785576</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1. Kh chưa báo cn
+2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
+3. Kh yc: Yc cn hỗ trợ</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>16:54 26/02/2026</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>18:00 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lê Văn Toán</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>119464</t>
+        </is>
+      </c>
+      <c r="Y38" s="2">
+        <v>46079</v>
+      </c>
+      <c r="Z38">
+        <v>29</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>tietvt16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_DNI_1659133</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0907002673</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1. Kh đã báo cn
+2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
+3. kh yc: YC cn hỗ trợ sớm</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>13:30 23/02/2026</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>18:30 21/03/2026</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Tâm Định</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>450471</t>
+        </is>
+      </c>
+      <c r="Y39" s="2">
+        <v>46076</v>
+      </c>
+      <c r="Z39">
+        <v>32</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>KHCN_PINNLMT_NAN_0334667</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Lê Trung An</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0865878212</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>- KH phản ánh ivt mới mang bảo hành về được mấy hôm lại lỗi không sử dụng được
+- KH Yc cho nv qua htro khắc phục triệt để</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16:02 26/01/2026</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>10:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Linh</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>285776</t>
+        </is>
+      </c>
+      <c r="Y40" s="2">
+        <v>46048</v>
+      </c>
+      <c r="Z40">
+        <v>60</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Trương Công An</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0914531694</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>khối 2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>15:09 03/03/2026</t>
+          <t>08:00 19/01/2026</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>12:55 15/03/2026</t>
+          <t>22:00 17/04/2026</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6211,19 +6205,19 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Lê Văn Anh</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>069170</t>
         </is>
       </c>
       <c r="Y41" s="2">
-        <v>46084</v>
+        <v>46041</v>
       </c>
       <c r="Z41">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6249,7 +6243,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6259,42 +6253,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+          <t>KHCN_TT.GPTH_TNN_0885867</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Trường Tiểu Học Quỳnh Hưng</t>
+          <t>Nguyễn Đức Hùng</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0963785576</t>
+          <t>0396264028</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6314,7 +6308,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6324,19 +6318,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1. Kh chưa báo cn
-2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
-3. Kh yc: Yc cn hỗ trợ</t>
+          <t>1. Đã báo CN: Chưa báo
+2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
+3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>16:54 26/02/2026</t>
+          <t>08:00 14/01/2026</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>18:00 31/03/2026</t>
+          <t>17:00 25/02/2026</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6346,50 +6340,50 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Lê Văn Toán</t>
+          <t>Trần Xuân Kương</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>119464</t>
+          <t>289759</t>
         </is>
       </c>
       <c r="Y42" s="2">
-        <v>46079</v>
+        <v>46036</v>
       </c>
       <c r="Z42">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6399,57 +6393,57 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>M&amp;E</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Bếp từ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_DNI_1659133</t>
+          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+          <t>Nguyễn Quang Vũ</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0907002673</t>
+          <t>0983034568</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+          <t>CNCT Viettel Bắc Ninh</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6469,19 +6463,18 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1. Kh đã báo cn
-2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
-3. kh yc: YC cn hỗ trợ sớm</t>
+          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
+Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>13:30 23/02/2026</t>
+          <t>08:00 05/01/2026</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>18:30 21/03/2026</t>
+          <t>10:25 03/04/2026</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6496,19 +6489,19 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Tâm Định</t>
+          <t>Đinh Thị Ngọc</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>450471</t>
+          <t>205029</t>
         </is>
       </c>
       <c r="Y43" s="2">
-        <v>46076</v>
+        <v>46027</v>
       </c>
       <c r="Z43">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6517,12 +6510,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Anhnt631</t>
         </is>
       </c>
     </row>
@@ -6534,52 +6527,52 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Dịch vụ khác</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_NAN_0334667</t>
+          <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Lê Trung An</t>
+          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0865878212</t>
+          <t>0962892720</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+          <t>...</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6594,587 +6587,20 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
-        <is>
-          <t>- KH phản ánh ivt mới mang bảo hành về được mấy hôm lại lỗi không sử dụng được
-- KH Yc cho nv qua htro khắc phục triệt để</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>16:02 26/01/2026</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>10:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Nguyễn Minh Linh</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>285776</t>
-        </is>
-      </c>
-      <c r="Y44" s="2">
-        <v>46048</v>
-      </c>
-      <c r="Z44">
-        <v>60</v>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Trương Công An</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0914531694</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>khối 2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>08:00 19/01/2026</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>22:00 17/04/2026</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Lê Văn Anh</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>069170</t>
-        </is>
-      </c>
-      <c r="Y45" s="2">
-        <v>46041</v>
-      </c>
-      <c r="Z45">
-        <v>67</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_TNN_0885867</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Nguyễn Đức Hùng</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0396264028</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>1. Đã báo CN: Chưa báo
-2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
-3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>08:00 14/01/2026</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>17:00 25/02/2026</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Trần Xuân Kương</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>289759</t>
-        </is>
-      </c>
-      <c r="Y46" s="2">
-        <v>46036</v>
-      </c>
-      <c r="Z46">
-        <v>72</v>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Bếp từ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Nguyễn Quang Vũ</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>0983034568</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>CNCT Viettel Bắc Ninh</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
-Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>08:00 05/01/2026</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>10:25 03/04/2026</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Đinh Thị Ngọc</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>205029</t>
-        </is>
-      </c>
-      <c r="Y47" s="2">
-        <v>46027</v>
-      </c>
-      <c r="Z47">
-        <v>81</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Anhnt631</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Dịch vụ khác</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>23092025/HĐTP-SPT-VIETTEL</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0962892720</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -7182,53 +6608,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>08:00 10/12/2025</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>15:00 16/12/2025</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y48" s="2">
+      <c r="Y44" s="2">
         <v>46001</v>
       </c>
-      <c r="Z48">
+      <c r="Z44">
         <v>107</v>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -616,12 +616,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Đào Văn Tân</t>
+          <t>Đào Văn Sơn</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>160895</t>
+          <t>079457</t>
         </is>
       </c>
       <c r="Y2" s="2">
@@ -939,258 +939,257 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nồi áp suất</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng chuỗi</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thu Thuý</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0968821715</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Hiệu suất thấp</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>14:55 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>14:55 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thu Thúy</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>433273</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VLG_1679600</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Nguyễn Tài Năng</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0916001008</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>A1/38D</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: Chưa thấy lắp đặt nlmt cho KH, CN chỉ thấy nói chung chung là đợi linh kiện về, ko có ngày hẹn cụ thể cho KH.
 3. KH yêu cầu: Có ngày cụ thể cho KH và triển khai lắp đặt cho KH.</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>11:41 30/03/2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>11:41 31/03/2026</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Nguyễn Thành Long</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>282101</t>
-        </is>
-      </c>
-      <c r="Y5" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tuyendv</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_NAN_0334667</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Lê Trung An</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0865878212</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11:30 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>11:30 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Nguyễn Minh Linh</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>285776</t>
         </is>
       </c>
       <c r="Y6" s="2">
@@ -1206,12 +1205,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Tuyendv</t>
         </is>
       </c>
     </row>
@@ -1223,977 +1222,963 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KHCN_PINNLMT_NAN_0334667</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lê Trung An</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0865878212</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn
+2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>11:30 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>11:30 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Linh</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>285776</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1665498</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN TUẤN CƯỜNG</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0914880646</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Thôn 7</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>CN 0981168696  báo sự cố hộ KH
 1. KH phản ánh: Lỗi ivt, mất điện lưới hiện tại pin ko xả được
 2. KH yêu cầu: KHDN là xưởng sản xuất cần qua hỗ trợ, kiểm tra, khắc phục gấp cho KH.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>09:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Lê Duy Tuấn</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>293859</t>
-        </is>
-      </c>
-      <c r="Y7" s="2">
+      <c r="Y8" s="2">
         <v>46111</v>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <v>0</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_NAN_1650078</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN TƯ VẤN THIẾT KẾ VÀ XÂY DỰNG LỘC PHÁT</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0982229238</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Nhà số 9, ngõ 30, đường Trần Tấn, Phường Vinh Lộc, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Nhảy áp ở chỗ cục pin nlmt
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra nguyên nhân và khắc phục dứt điểm cho KH.</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Nguyễn Văn Tân</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>460719</t>
         </is>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y9" s="2">
         <v>46111</v>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <v>0</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1601525</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Hoàng Văn Hoạt</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0344334808</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Thán</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>1. KH đã báo kỹ thuật Thành 0977357868 nhưng chưa được hỗ trợ
 2. KH phản ánh lắp điện NLMT nhưng tiền điện vẫn cao
 3. KH yêu cầu kỹ thuật qua hỗ trợ xử lý</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Nguyễn Thị Nhị</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>239095</t>
         </is>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y10" s="2">
         <v>46111</v>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <v>0</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>YCKS_HDG_TLS/0120467</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Ngô Hữu Thế</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0984379375</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>494 Phố Việt Hòa, Tp Hải Phòng</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>1. KH chưa báo chi nhánh
 2. KH phản ánh sơ đồ đấu nối điện bị sai
 3. KH yêu cầu chi nhánh gửi lại 1 bản hợp đồng sơ đồ đấu nối để KH kiểm tra</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Phạm Quân Khu</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>272645</t>
         </is>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y11" s="2">
         <v>46111</v>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <v>0</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>vinhvv4</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1574225</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Nguyên Văn Tú</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0868081789</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
 2. KH phản ánh NLMT bị hỏng không sử dụng được
 3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Nguyễn Minh Linh</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>285776</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y12" s="2">
         <v>46111</v>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <v>0</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Bàng Lâm Sung</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0968525115</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>tổ 53</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Tấm pin bị rò rỉ/ Lỗi</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1. KH đã LH kỹ thuật nhưng không nghe máy
 2. KH phản ánh NLMT lỗi BMS không nhận pin
 3. KH yêu cầu kỹ thuật liên hệ hỗ trợ</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>09:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Trần Xuân Kương</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>289759</t>
-        </is>
-      </c>
-      <c r="Y12" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>tietvt16</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VCC_HS_HPG_1774354127134</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Bình An</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0389983044</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>thôn Quần Mục 02 - xã Đại Hợp - Kiến Thụy - Hải Phòng</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Liên hệ chậm</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>KH hẹn ngày 26/3 nhưng chưa thấy kỹ thuật liên hệ cần hỗ trợ gấp</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>08:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>14:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Phạm Trung Hiếu</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>070249</t>
         </is>
       </c>
       <c r="Y13" s="2">
@@ -2204,17 +2189,17 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>tietvt16</t>
         </is>
       </c>
     </row>
@@ -2231,22 +2216,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VCC_HS_HNI_1717209486560</t>
+          <t>KHCN_TT.GPTH_HNI_1631868</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2256,7 +2241,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2266,22 +2251,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Nguyễn Linh</t>
+          <t>Nguyễn Thị Thu Hà</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0837480663</t>
+          <t>0989790925</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>khu bê tông hải bối</t>
+          <t>đông xuân, xã sóc sơn</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2291,163 +2276,20 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Inverter không hoạt động</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
-        <is>
-          <t>KH đặt lich bảo dưỡng điều hòa nhưng chưa có ai liên hệ, yêu cầu phản hồi gấp</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>08:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>14:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Lại Thị Thu Hương</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>838368</t>
-        </is>
-      </c>
-      <c r="Y14" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNI_1631868</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Thu Hà</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0989790925</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>đông xuân, xã sóc sơn</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Inverter không hoạt động</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
         <is>
           <t>CN báo hộ: Nguyễn Văn Lâm
 464695
@@ -2456,6 +2298,151 @@
 3. KH yc KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>08:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>09:00 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Vinh</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>469835</t>
+        </is>
+      </c>
+      <c r="Y14" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1641827</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nguyễn Trọng Đạt</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0904113488</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>36 Ngõ 104 Thúy Lĩnh, Phường Hoàng Mai, Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Sản phẩm không sử dụng được / không hoạt động</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>KH chưa báo CN
+ KH đang sd NLMT, nhưng hiện tại hệ thống ko hoạt động, ko phát được điện
+YC KT qua kiểm tra và xử lý</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
@@ -2463,12 +2450,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>09:00 31/03/2026</t>
+          <t>23:55 05/04/2026</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2478,12 +2465,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vinh</t>
+          <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>469835</t>
+          <t>292404</t>
         </is>
       </c>
       <c r="Y15" s="2">
@@ -2511,12 +2498,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2536,37 +2523,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNI_1641827</t>
+          <t>KHDN_TT.GPTH_CTO_1417803</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nguyễn Trọng Đạt</t>
+          <t>công ty TNHH quảng cáo đăng nguyễn</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0904113488</t>
+          <t>0909393390</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36 Ngõ 104 Thúy Lĩnh, Phường Hoàng Mai, Thành phố Hà Nội</t>
+          <t>ô môn</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2586,19 +2568,18 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Sản phẩm không sử dụng được / không hoạt động</t>
+          <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>KH chưa báo CN
- KH đang sd NLMT, nhưng hiện tại hệ thống ko hoạt động, ko phát được điện
-YC KT qua kiểm tra và xử lý</t>
+HIện tại KH cần di dời thiết bị cách đấy khoảng 2-3m , nhờ KT qua hỗ trợ</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2608,12 +2589,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>23:55 05/04/2026</t>
+          <t>09:00 31/03/2026</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2623,12 +2604,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Nguyễn Hoàng Minh</t>
+          <t>Võ Chí Trung</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>292404</t>
+          <t>469593</t>
         </is>
       </c>
       <c r="Y16" s="2">
@@ -2656,12 +2637,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>HUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2676,12 +2657,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Tấm pin NLMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_CTO_1417803</t>
+          <t>KHDN_TT.GPTH_TTH_1626383</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2689,6 +2670,11 @@
           <t>B2B</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
@@ -2696,17 +2682,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>công ty TNHH quảng cáo đăng nguyễn</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT PHÚ HƯNG</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0909393390</t>
+          <t>0985005322</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ô môn</t>
+          <t>19 Trưng Nữ Vương</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2726,159 +2712,15 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Hỗ trợ lắp đặt</t>
+          <t>Hiệu suất sản phẩm kém</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN
-HIện tại KH cần di dời thiết bị cách đấy khoảng 2-3m , nhờ KT qua hỗ trợ</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>08:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>09:00 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Võ Chí Trung</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>469593</t>
-        </is>
-      </c>
-      <c r="Y17" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HUE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_TTH_1626383</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT PHÚ HƯNG</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0985005322</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>19 Trưng Nữ Vương</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Hiệu suất sản phẩm kém</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH đang sử dụng tấm PIN NLMT của VCC, 
@@ -2886,6 +2728,151 @@
 KH YC KT qua kiểm tra và xử lý cho KH gấp</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>08:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>09:00 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lê Văn Đồng</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>422252</t>
+        </is>
+      </c>
+      <c r="Y17" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1631868</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Lê Văn Vĩnh</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0948519572</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>SN 7A ngõ 564/12 đường Nguyễn Văn Cừ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Sản phẩm không sử dụng được / không hoạt động</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>CN báo hộ SDT: 985792828
+KH đang sd NLMT nhưng hiện tại thiết bị ko sản sinh ra điện
+YC KT qua kiểm tra và xử lý cho KH</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>08:00 30/03/2026</t>
@@ -2898,7 +2885,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2908,12 +2895,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Lê Văn Đồng</t>
+          <t>Trần Huy Quý</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>422252</t>
+          <t>437012</t>
         </is>
       </c>
       <c r="Y18" s="2">
@@ -2941,12 +2928,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2966,12 +2953,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNI_1631868</t>
+          <t>KHDN_TT.GPTH_BDG_1495422</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2981,32 +2968,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lê Văn Vĩnh</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0948519572</t>
+          <t>0918236379</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SN 7A ngõ 564/12 đường Nguyễn Văn Cừ</t>
+          <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3016,29 +3003,29 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Sản phẩm không sử dụng được / không hoạt động</t>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>CN báo hộ SDT: 985792828
-KH đang sd NLMT nhưng hiện tại thiết bị ko sản sinh ra điện
-YC KT qua kiểm tra và xử lý cho KH</t>
+          <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
+2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
+3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08:00 30/03/2026</t>
+          <t>16:08 26/03/2026</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09:00 31/03/2026</t>
+          <t>09:00 05/04/2026</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3053,19 +3040,19 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Trần Huy Quý</t>
+          <t>Trần Văn Thắng</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>437012</t>
+          <t>470289</t>
         </is>
       </c>
       <c r="Y19" s="2">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3086,12 +3073,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3101,52 +3088,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>CNTT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_BDG_1495422</t>
+          <t>KHCN_TT.GPTH_DNG_1240036</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VẬN TẢI BẢO LONG PHÁT</t>
+          <t>Nguyễn Văn Thiên</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0918236379</t>
+          <t>0935302100</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Số 617, đường ĐT 743B, khu phố Đông Tân</t>
+          <t>48 nguyễn đình chiểu, Phường Khuê Mỹ, Quận Ngũ Hành Sơn, Thành phố Đà Nẵng</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3171,19 +3153,18 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1. KH báo cn người hỗ trợ trước nhưng ko liên hệ được
-2. KH phản ánh: KH kết nối được app báo lỗi ngoại tuyến
-3. KH yêu cầu: Hỗ trợ, hướng dẫn KH sử dụng, KH hay bị gặp vấn đề này nhiều hỗ trợ KH dứt điểm giúp.</t>
+          <t>1. KH phản ánh: Camera bị rớt không kết nối được, và cả mật khẩu wifi
+2. KH yêu cầu: Hỗ trợ KH cài đặt lại camera.</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>16:08 26/03/2026</t>
+          <t>10:11 27/03/2026</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>09:00 05/04/2026</t>
+          <t>16:50 31/03/2026</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3193,24 +3174,24 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Trần Văn Thắng</t>
+          <t>Phan Văn Tuấn</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>470289</t>
+          <t>271620</t>
         </is>
       </c>
       <c r="Y20" s="2">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="Z20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3219,12 +3200,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3217,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3246,17 +3227,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1240036</t>
+          <t>KHCN_TT.GPTH_GLI_1676729</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3264,6 +3245,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3271,17 +3257,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thiên</t>
+          <t>Rơ Ô WÊ</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0935302100</t>
+          <t>0396081566</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>48 nguyễn đình chiểu, Phường Khuê Mỹ, Quận Ngũ Hành Sơn, Thành phố Đà Nẵng</t>
+          <t>Thôn Ia Prông</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3291,38 +3277,37 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1. KH phản ánh: Camera bị rớt không kết nối được, và cả mật khẩu wifi
-2. KH yêu cầu: Hỗ trợ KH cài đặt lại camera.</t>
+          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10:11 27/03/2026</t>
+          <t>10:43 26/03/2026</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>16:50 31/03/2026</t>
+          <t>08:35 31/03/2026</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3337,19 +3322,19 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Phan Văn Tuấn</t>
+          <t>Nguyễn Hà Nguyên</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>271620</t>
+          <t>060709</t>
         </is>
       </c>
       <c r="Y21" s="2">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="Z21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3375,7 +3360,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3395,7 +3380,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_GLI_1676729</t>
+          <t>KHCN_NLMT_NTN_0241352</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3403,11 +3388,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3415,17 +3395,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Rơ Ô WÊ</t>
+          <t>Nguyễn Văn Sanh</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0396081566</t>
+          <t>0913785605</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Thôn Ia Prông</t>
+          <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3435,37 +3415,39 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>KH phản ánh đã đặt cọc lắp đặt hệ thống điện năng lượng mặt trời 20 ngày rồi nhưng chưa co KT nào qua lắp cho KH. Yêu cầu xử lý gấp</t>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Ivt bị lỗi ko hoạt động, KH ktra thấy còn ko chạy
+3. KH yêu cầu: Qua hỗ trợ, kiểm tra, khắc phục tình trạng này cho KH</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10:43 26/03/2026</t>
+          <t>08:25 26/03/2026</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>08:35 31/03/2026</t>
+          <t>16:50 30/03/2026</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3480,12 +3462,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Nguyễn Hà Nguyên</t>
+          <t>Nguyễn Văn Vương</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>060709</t>
+          <t>069846</t>
         </is>
       </c>
       <c r="Y22" s="2">
@@ -3501,24 +3483,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3538,7 +3520,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KHCN_NLMT_NTN_0241352</t>
+          <t>KHCN_TT.GPTH_HDG_1304417</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3546,6 +3528,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3553,17 +3540,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Sanh</t>
+          <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0913785605</t>
+          <t>0377883716</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>KP2, Thị trấn Phước Dân, Huyện Ninh Phước, Tỉnh Ninh Thuận</t>
+          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3583,29 +3570,29 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Ivt bị lỗi ko hoạt động, KH ktra thấy còn ko chạy
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra, khắc phục tình trạng này cho KH</t>
+          <t>KH chưa báo CN
+KH yêu cầu NVKT qua lại thiết bị inverter của KH 
+Số liên hệ:</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>08:25 26/03/2026</t>
+          <t>08:00 26/03/2026</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>16:50 30/03/2026</t>
+          <t>17:25 02/04/2026</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3615,17 +3602,17 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vương</t>
+          <t>Hoàng Văn Phong</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>069846</t>
+          <t>291011</t>
         </is>
       </c>
       <c r="Y23" s="2">
@@ -3653,12 +3640,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3678,7 +3665,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HDG_1304417</t>
+          <t>KHCN_TT.GPTH_HCM_1169983</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3686,11 +3673,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3698,17 +3680,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hồng Khánh</t>
+          <t>Đường Quyền Hồng</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0377883716</t>
+          <t>0907395121</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
+          <t>Ấp 4, Xã Phước Kiển, Huyện Nhà Bè, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3728,29 +3710,29 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>KH chưa báo CN
-KH yêu cầu NVKT qua lại thiết bị inverter của KH 
-Số liên hệ:</t>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: Lỗi CP bị cúp điện dưới nhà, hiện tại điện ko sử dụng được.
+3. KH yêu cầu: Qua kiểm tra, hỗ trợ, khắc phục gấp cho KH giờ nhà KH đang ko có điện để sử dụng.</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>08:00 26/03/2026</t>
+          <t>09:32 26/03/2026</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>17:25 02/04/2026</t>
+          <t>16:05 31/03/2026</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3760,17 +3742,17 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Hoàng Văn Phong</t>
+          <t>Điểu Ngọc Lâm</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>291011</t>
+          <t>432612</t>
         </is>
       </c>
       <c r="Y24" s="2">
@@ -3798,12 +3780,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3823,7 +3805,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1169983</t>
+          <t>KHCN_TT.GPTH_KHA_1631515</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3831,6 +3813,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3838,22 +3825,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Đường Quyền Hồng</t>
+          <t>Phạm Hải Triều</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0907395121</t>
+          <t>0903576559</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ấp 4, Xã Phước Kiển, Huyện Nhà Bè, Thành phố Hồ Chí Minh</t>
+          <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3878,19 +3865,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: Lỗi CP bị cúp điện dưới nhà, hiện tại điện ko sử dụng được.
-3. KH yêu cầu: Qua kiểm tra, hỗ trợ, khắc phục gấp cho KH giờ nhà KH đang ko có điện để sử dụng.</t>
+          <t>CN báo sự cố hộ KH
+1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
+2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>09:32 26/03/2026</t>
+          <t>08:00 26/03/2026</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16:05 31/03/2026</t>
+          <t>17:35 27/03/2026</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3900,17 +3887,17 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Điểu Ngọc Lâm</t>
+          <t>Phan Trọng Nghĩa</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>432612</t>
+          <t>234935</t>
         </is>
       </c>
       <c r="Y25" s="2">
@@ -3938,12 +3925,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3963,12 +3950,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_KHA_1631515</t>
+          <t>KHDN_TT.GPTH_HNI_1646163</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3978,27 +3965,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Phạm Hải Triều</t>
+          <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0903576559</t>
+          <t>0973721368</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Phường Nha Trang, Tỉnh Khánh Hòa</t>
+          <t>Triệu Xuyên, Long xuyên</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4022,151 +4009,6 @@
         </is>
       </c>
       <c r="R26" t="inlineStr">
-        <is>
-          <t>CN báo sự cố hộ KH
-1. KH phản ánh: Ắc quy, pin gần như ko hoạt động. Chỉ có bám tải, ivt hoạt động
-2. KH yêu cầu: Qua hỗ trợ, kiểm tra, xử lý sớm cho KH.</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>08:00 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>17:35 27/03/2026</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Phan Trọng Nghĩa</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>234935</t>
-        </is>
-      </c>
-      <c r="Y26" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z26">
-        <v>4</v>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HNI_1646163</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Công Ty Tnhh Đầu Tư Xây Dựng Và Thương Mại Triệu Phúc</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0973721368</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Triệu Xuyên, Long xuyên</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
         <is>
           <t>1. KH đã báo cn a Long gđ kỹ thuật, a Dương Đăng Minh chủ ký HĐ, a Vương lắp đặt.
 2. KH phản ánh: Bị nhảy áp liên tục 1 tháng phải nhảy 20 ngày rơi vào khoảng 2h đêm và 12h trưa ban ngày, và chập tối lúc GĐ đang vào sinh hoạt. CN nhiều lần xuống ktra và kiến nghị nhưng có câu trả lời KH ko được hài lòng lắm. Đặc biệt là a Long GĐ KT có thái độ là đổ cho GĐ tắt áp, KH bức xúc vì KH bỏ đồng tiền ra mà lại đổ lỗi cho nhà KH. KH cũng báo với a Dương Đăng Minh, a Minh cũng bảo là để cháu bảo ae xuống thế nọ thế kia khất để ra giêng để sửa mà giờ hết tháng rồi vẫn ko thấy đâu.
@@ -4174,14 +4016,159 @@
 ***SĐT liên hệ: 0945268772, chú Bồng</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>14:58 25/03/2026</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>23:00 06/04/2026</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lê Duy Tuấn</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>293859</t>
+        </is>
+      </c>
+      <c r="Y26" s="2">
+        <v>46106</v>
+      </c>
+      <c r="Z26">
+        <v>5</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BNH_1600729</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Nguyễn Khương</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0977113014</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
+2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
+3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>14:58 25/03/2026</t>
+          <t>09:20 25/03/2026</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>23:00 06/04/2026</t>
+          <t>18:30 30/03/2026</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4191,17 +4178,17 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Lê Duy Tuấn</t>
+          <t>nguyễn văn Tuần</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>293859</t>
+          <t>461581</t>
         </is>
       </c>
       <c r="Y27" s="2">
@@ -4234,7 +4221,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4254,7 +4241,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1600729</t>
+          <t>KHCN_TT.GPTH_VPC_1503902</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4264,7 +4251,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4274,17 +4261,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Nguyễn Khương</t>
+          <t>Nguyễn Việt Hùng</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0977113014</t>
+          <t>0966547344</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
+          <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4294,7 +4281,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4309,155 +4296,10 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
-2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
-3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>09:20 25/03/2026</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>18:30 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>nguyễn văn Tuần</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>461581</t>
-        </is>
-      </c>
-      <c r="Y28" s="2">
-        <v>46106</v>
-      </c>
-      <c r="Z28">
-        <v>5</v>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_VPC_1503902</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Nguyễn Việt Hùng</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0966547344</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH đang dùng NLMT hiện tại bị lỗi biến tần, ko kết nối được app
@@ -4465,14 +4307,157 @@
 NOTE: địa chỉ hiện tại của KH: thôn phú mỹ, xã tiến thắng, Hà Nội</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>15:34 24/03/2026</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>17:30 01/04/2026</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Phạm Văn Nghĩa</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>023020</t>
+        </is>
+      </c>
+      <c r="Y28" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BDG_1352264</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Nguyễn Liễu Thông</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0362126000</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>không hoạt động</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>15:34 24/03/2026</t>
+          <t>09:29 26/03/2026</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>17:30 01/04/2026</t>
+          <t>09:00 01/04/2026</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4487,19 +4472,19 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Phạm Văn Nghĩa</t>
+          <t>Nguyễn Văn Toản</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>023020</t>
+          <t>427880</t>
         </is>
       </c>
       <c r="Y29" s="2">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -4520,12 +4505,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4540,12 +4525,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BDG_1352264</t>
+          <t>KHCN_TT.GPTH_PTO_1620637</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4555,7 +4540,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4565,22 +4550,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Nguyễn Liễu Thông</t>
+          <t>Nguyễn Đình Mạnh</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0362126000</t>
+          <t>0988308581</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ph</t>
+          <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4605,17 +4590,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>không hoạt động</t>
+          <t>KH chưa báo CN
+KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
+KH yêu cầu chuyển KT xuống xử lý gấp</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09:29 26/03/2026</t>
+          <t>15:09 24/03/2026</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09:00 01/04/2026</t>
+          <t>21:10 23/04/2026</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4630,19 +4617,19 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Toản</t>
+          <t>Bùi Anh Nguyễn</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>427880</t>
+          <t>414445</t>
         </is>
       </c>
       <c r="Y30" s="2">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="Z30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4663,12 +4650,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4688,7 +4675,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_PTO_1620637</t>
+          <t>KHCN_TT.GPTH_DLK_1648454</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4708,17 +4695,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nguyễn Đình Mạnh</t>
+          <t>Huỳnh Chí Băng</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0988308581</t>
+          <t>0366448992</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
+          <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4748,19 +4735,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>KH chưa báo CN
-KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
-KH yêu cầu chuyển KT xuống xử lý gấp</t>
+          <t>KH đã báo CN: a Nguyễn Văn Hà	nửa thasg nhưng chưa có ai đến hỗ trợ
+KH phản ánh hệ thống điện năng lượng mặt trời ko hoạt động
+KH yêu cầu xử lý gấp</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>15:09 24/03/2026</t>
+          <t>15:19 24/03/2026</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>21:10 23/04/2026</t>
+          <t>10:50 31/03/2026</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4770,17 +4757,17 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Bùi Anh Nguyễn</t>
+          <t>Nguyễn Văn Hà</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>414445</t>
+          <t>008244</t>
         </is>
       </c>
       <c r="Y31" s="2">
@@ -4808,12 +4795,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4823,47 +4810,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>CNTT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Camera 360 độ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DLK_1648454</t>
+          <t>299/2025/HĐKT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Huỳnh Chí Băng</t>
+          <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0366448992</t>
+          <t>0869217169</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
+          <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4883,155 +4865,15 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
-        <is>
-          <t>KH đã báo CN: a Nguyễn Văn Hà	nửa thasg nhưng chưa có ai đến hỗ trợ
-KH phản ánh hệ thống điện năng lượng mặt trời ko hoạt động
-KH yêu cầu xử lý gấp</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>15:19 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>10:50 31/03/2026</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Hà</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>008244</t>
-        </is>
-      </c>
-      <c r="Y32" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z32">
-        <v>6</v>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CNTT</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Camera 360 độ</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>299/2025/HĐKT</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0869217169</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: camera 360 chưa kết nối được hệ thống điều khiển, chưa lên được tivi để xem và cũng như pccc rừng mùa khô.
@@ -5039,14 +4881,157 @@
 ***SĐT liên hệ: 0988867428, Anh Thức</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>08:45 24/03/2026</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>23:05 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Võ Trọng Đức</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>293804</t>
+        </is>
+      </c>
+      <c r="Y32" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z32">
+        <v>6</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>tietvt16</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_CMU_1265325</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Bích Loan</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0946842984</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bích Loan Cống Hội Đồng Nguyên</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>cammera bị off 1 cai</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08:45 24/03/2026</t>
+          <t>10:28 26/03/2026</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>23:05 30/03/2026</t>
+          <t>17:30 01/04/2026</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5056,28 +5041,28 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Võ Trọng Đức</t>
+          <t>Lý Hoài Bảo</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>293804</t>
+          <t>433302</t>
         </is>
       </c>
       <c r="Y33" s="2">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5087,7 +5072,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>Tuyendv</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5084,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5109,17 +5094,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_CMU_1265325</t>
+          <t>KHCN_TT.GPTH_BPC_1427400</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5129,7 +5114,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5139,22 +5124,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Bích Loan</t>
+          <t>Công Ty Tnhh Phúc An Solutions</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0946842984</t>
+          <t>0972342939</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Bích Loan Cống Hội Đồng Nguyên</t>
+          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5179,17 +5164,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>cammera bị off 1 cai</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Cục pin lưu trữ đang ko hoạt động, ko sử dụng được.
+3. KH yêu cầu: Có KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10:28 26/03/2026</t>
+          <t>14:29 23/03/2026</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17:30 01/04/2026</t>
+          <t>07:20 02/04/2026</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5199,24 +5186,24 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Lý Hoài Bảo</t>
+          <t>Phạm Trung Hiếu</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>433302</t>
+          <t>264250</t>
         </is>
       </c>
       <c r="Y34" s="2">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -5225,24 +5212,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Tuyendv</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5257,42 +5244,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BPC_1427400</t>
+          <t>100901-KD/HDMB-2021/GLI-TT</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Công Ty Tnhh Phúc An Solutions</t>
+          <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0972342939</t>
+          <t>0862000202</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
+          <t>Đồn Biên Phòng 723</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5321,151 +5308,6 @@
         </is>
       </c>
       <c r="R35" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Cục pin lưu trữ đang ko hoạt động, ko sử dụng được.
-3. KH yêu cầu: Có KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>14:29 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>07:20 02/04/2026</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Phạm Trung Hiếu</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>264250</t>
-        </is>
-      </c>
-      <c r="Y35" s="2">
-        <v>46104</v>
-      </c>
-      <c r="Z35">
-        <v>7</v>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GLI</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>100901-KD/HDMB-2021/GLI-TT</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Đồn Biên Phòng 723</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0862000202</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Đồn Biên Phòng 723</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo 
 2.Đã báo qua đâu: KH gọi TĐ
@@ -5473,6 +5315,151 @@
 4. KH yêu cầu KT qua kiểm tra xử lý cho KH.</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>08:00 23/03/2026</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>14:00 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nguyễn Hà Nguyên</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>060709</t>
+        </is>
+      </c>
+      <c r="Y35" s="2">
+        <v>46104</v>
+      </c>
+      <c r="Z35">
+        <v>7</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Công tắc thông minh</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNG_1416913</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Lê Đắc Quỳ</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0915313915</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
+3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
@@ -5480,7 +5467,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>14:00 31/03/2026</t>
+          <t>07:50 08/04/2026</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5490,17 +5477,17 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Nguyễn Hà Nguyên</t>
+          <t>Ngô Văn Minh</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>060709</t>
+          <t>083585</t>
         </is>
       </c>
       <c r="Y36" s="2">
@@ -5511,7 +5498,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5521,19 +5508,19 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5543,17 +5530,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Công tắc thông minh</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1416913</t>
+          <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5563,7 +5550,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5573,22 +5560,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Lê Đắc Quỳ</t>
+          <t>Dương Văn Quân</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0915313915</t>
+          <t>0359999199</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
+          <t>xã Hoàng Vân</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5603,160 +5590,15 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>08:00 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>07:50 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Ngô Văn Minh</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>083585</t>
-        </is>
-      </c>
-      <c r="Y37" s="2">
-        <v>46104</v>
-      </c>
-      <c r="Z37">
-        <v>7</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BGG_1597213</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Dương Văn Quân</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0359999199</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>xã Hoàng Vân</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -5764,145 +5606,145 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>08:00 23/03/2026</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>18:00 26/03/2026</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>408869</t>
         </is>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y37" s="2">
         <v>46104</v>
       </c>
-      <c r="Z38">
+      <c r="Z37">
         <v>7</v>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1384534</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Nguyễn Đức Hiếu</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0949001616</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Khóm 10</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.Đã báo cho ai:  KT Thái
@@ -5911,14 +5753,152 @@
 5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>09:44 20/03/2026</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>23:55 31/03/2026</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Võ Duy Khang</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>473069</t>
+        </is>
+      </c>
+      <c r="Y38" s="2">
+        <v>46101</v>
+      </c>
+      <c r="Z38">
+        <v>10</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>VCC_YCTX_NAN_37485587203842849</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Xuân Hương</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0974371218</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Tư vấn sản phẩm/dịch vụ</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>09:44 20/03/2026</t>
+          <t>15:32 20/03/2026</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>23:55 31/03/2026</t>
+          <t>17:15 02/04/2026</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5933,12 +5913,12 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Võ Duy Khang</t>
+          <t>Trần Bình Thanh</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>473069</t>
+          <t>069159</t>
         </is>
       </c>
       <c r="Y39" s="2">
@@ -5949,29 +5929,29 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.KDNLMT</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.KDNLMT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5991,7 +5971,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VCC_YCTX_NAN_37485587203842849</t>
+          <t>KHCN_TT.GPTH_HCM_1638575</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5999,24 +5979,29 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Xuân Hương</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0974371218</t>
+          <t>0911937779</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Xã Nhân Hòa, Tỉnh Nghệ An</t>
+          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6031,32 +6016,34 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>KH báo chưa thấy có nv liên hệ để tư vấn NLMT.</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
+3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>15:32 20/03/2026</t>
+          <t>09:25 19/03/2026</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>17:15 02/04/2026</t>
+          <t>08:35 25/04/2026</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6066,38 +6053,38 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Trần Bình Thanh</t>
+          <t>Lê Đức Cảnh</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>069159</t>
+          <t>291002</t>
         </is>
       </c>
       <c r="Y40" s="2">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>P.KDNLMT</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6116,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1638575</t>
+          <t>KHCN_TT.GPTH_HCM_1646383</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6144,22 +6131,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
+          <t>Nguyễn Hữu Nghĩa</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0911937779</t>
+          <t>0945919596</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
+          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6179,29 +6166,27 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Sản phẩm bị ngắt quãng/ Không theo dõi và không nghe được</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
-3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
+          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09:25 19/03/2026</t>
+          <t>08:00 16/03/2026</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>08:35 25/04/2026</t>
+          <t>08:45 12/04/2026</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6225,10 +6210,10 @@
         </is>
       </c>
       <c r="Y41" s="2">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="Z41">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6249,12 +6234,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6274,7 +6259,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1646383</t>
+          <t>KHCN_PINNLMT_BGG_0404930</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6284,7 +6269,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6294,22 +6279,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Nghĩa</t>
+          <t>Lê Văn Mạnh</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0945919596</t>
+          <t>0987567050</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6324,158 +6309,15 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
-        <is>
-          <t>KH yc ktra nguyên nhân xảy ra sự cố TT_1772849052506</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>08:00 16/03/2026</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>08:45 12/04/2026</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Lê Đức Cảnh</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>291002</t>
-        </is>
-      </c>
-      <c r="Y42" s="2">
-        <v>46097</v>
-      </c>
-      <c r="Z42">
-        <v>14</v>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_BGG_0404930</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Lê Văn Mạnh</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0987567050</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Xã Liên Chung,Huyện Tân Yên,Tỉnh Bắc Giang</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo
 2.KH báo cho GĐ Trường 
@@ -6484,14 +6326,154 @@
  5.KH yêu cầu KT qua kiểm tra gấp cho KH.</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>10:21 10/03/2026</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>09:00 30/03/2026</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Thân Đức Giang</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>081984</t>
+        </is>
+      </c>
+      <c r="Y42" s="2">
+        <v>46091</v>
+      </c>
+      <c r="Z42">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_QTI_0991884</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Như Mỹ</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0963369267</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
+2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
+3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10:21 10/03/2026</t>
+          <t>08:00 09/03/2026</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>09:00 30/03/2026</t>
+          <t>11:45 10/04/2026</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6501,24 +6483,24 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Thân Đức Giang</t>
+          <t>Trương Thành</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>081984</t>
+          <t>462341</t>
         </is>
       </c>
       <c r="Y43" s="2">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="Z43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6544,7 +6526,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6559,12 +6541,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Tấm pin NLMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QTI_0991884</t>
+          <t>KHCN_PINNLMT_KTM_0284233</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6579,17 +6561,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Như Mỹ</t>
+          <t>Nguyễn Xuân Quyết</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0963369267</t>
+          <t>0981397050</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
+          <t>Khối phố 6, Thị trấn Plei Kần, Huyện Ngọc Hồi, Tỉnh Kon Tum</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6609,7 +6591,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6618,146 +6600,6 @@
         </is>
       </c>
       <c r="R44" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
-2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
-3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>08:00 09/03/2026</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>11:45 10/04/2026</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Trương Thành</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>462341</t>
-        </is>
-      </c>
-      <c r="Y44" s="2">
-        <v>46090</v>
-      </c>
-      <c r="Z44">
-        <v>21</v>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>QNI</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_KTM_0284233</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Nguyễn Xuân Quyết</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0981397050</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Khối phố 6, Thị trấn Plei Kần, Huyện Ngọc Hồi, Tỉnh Kon Tum</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: đã báo 
 2.Đã báo cho ai:  NV Văn
@@ -6766,145 +6608,145 @@
 5.	 KH yêu cầu KT qua kiểm tra gấp cho KH</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>14:54 05/03/2026</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>17:00 31/03/2026</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Đỗ Lê Thanh Dĩnh</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>041111</t>
         </is>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y44" s="2">
         <v>46086</v>
       </c>
-      <c r="Z45">
+      <c r="Z44">
         <v>25</v>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Nguyễn Phú Quý</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>0947110192</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -6912,14 +6754,154 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>15:09 03/03/2026</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>12:55 15/03/2026</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lê Đức Cảnh</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>291002</t>
+        </is>
+      </c>
+      <c r="Y45" s="2">
+        <v>46084</v>
+      </c>
+      <c r="Z45">
+        <v>27</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Trường Tiểu Học Quỳnh Hưng</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0963785576</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1. Kh chưa báo cn
+2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
+3. Kh yc: Yc cn hỗ trợ</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>15:09 03/03/2026</t>
+          <t>16:54 26/02/2026</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>12:55 15/03/2026</t>
+          <t>18:00 31/03/2026</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6929,50 +6911,50 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Lê Văn Toán</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>119464</t>
         </is>
       </c>
       <c r="Y46" s="2">
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="Z46">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>tietvt16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6982,17 +6964,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CNTT</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>081101/HĐMBLĐ-2024/THQUYNHHUNG-NAN</t>
+          <t>KHDN_TT.GPTH_DNI_1659133</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7000,6 +6982,11 @@
           <t>B2B</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
@@ -7007,17 +6994,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Trường Tiểu Học Quỳnh Hưng</t>
+          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0963785576</t>
+          <t>0907002673</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Xóm 6,Xã Quỳnh Hưng,Huyện Quỳnh Lưu,Tỉnh Nghệ An</t>
+          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7027,7 +7014,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -7037,7 +7024,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -7047,19 +7034,19 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1. Kh chưa báo cn
-2. Kh phản ánh: Hiện tại ko có mắt cam nào xem đc, mạng thì vẫn bình thường
-3. Kh yc: Yc cn hỗ trợ</t>
+          <t>1. Kh đã báo cn
+2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
+3. kh yc: YC cn hỗ trợ sớm</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>16:54 26/02/2026</t>
+          <t>13:30 23/02/2026</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>18:00 31/03/2026</t>
+          <t>18:30 21/03/2026</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -7069,50 +7056,50 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lê Văn Toán</t>
+          <t>Nguyễn Hữu Tâm Định</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>119464</t>
+          <t>450471</t>
         </is>
       </c>
       <c r="Y47" s="2">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="Z47">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7127,42 +7114,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_DNI_1659133</t>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+          <t>Trương Công An</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0907002673</t>
+          <t>0914531694</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+          <t>khối 2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7192,19 +7179,18 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1. Kh đã báo cn
-2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
-3. kh yc: YC cn hỗ trợ sớm</t>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>13:30 23/02/2026</t>
+          <t>08:00 19/01/2026</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>18:30 21/03/2026</t>
+          <t>22:00 17/04/2026</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7219,19 +7205,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Tâm Định</t>
+          <t>Lê Văn Anh</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>450471</t>
+          <t>069170</t>
         </is>
       </c>
       <c r="Y48" s="2">
-        <v>46076</v>
+        <v>46041</v>
       </c>
       <c r="Z48">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -7257,7 +7243,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7272,12 +7258,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
+          <t>KHCN_TT.GPTH_TNN_0885867</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7285,11 +7271,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -7297,17 +7278,17 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Trương Công An</t>
+          <t>Nguyễn Đức Hùng</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0914531694</t>
+          <t>0396264028</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>khối 2</t>
+          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -7317,7 +7298,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -7337,18 +7318,19 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
+          <t>1. Đã báo CN: Chưa báo
+2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
+3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>08:00 19/01/2026</t>
+          <t>08:00 14/01/2026</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>22:00 17/04/2026</t>
+          <t>17:00 25/02/2026</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7363,19 +7345,19 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Lê Văn Anh</t>
+          <t>Trần Xuân Kương</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>069170</t>
+          <t>289759</t>
         </is>
       </c>
       <c r="Y49" s="2">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="Z49">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -7401,7 +7383,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7411,17 +7393,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>M&amp;E</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Bếp từ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNN_0885867</t>
+          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7429,6 +7411,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -7436,22 +7423,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Hùng</t>
+          <t>Nguyễn Quang Vũ</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0396264028</t>
+          <t>0983034568</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
+          <t>CNCT Viettel Bắc Ninh</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7476,19 +7463,18 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1. Đã báo CN: Chưa báo
-2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
-3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
+          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
+Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>08:00 14/01/2026</t>
+          <t>08:00 05/01/2026</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>17:00 25/02/2026</t>
+          <t>10:25 03/04/2026</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7503,19 +7489,19 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Trần Xuân Kương</t>
+          <t>Đinh Thị Ngọc</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>289759</t>
+          <t>205029</t>
         </is>
       </c>
       <c r="Y50" s="2">
-        <v>46036</v>
+        <v>46027</v>
       </c>
       <c r="Z50">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -7524,12 +7510,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Anhnt631</t>
         </is>
       </c>
     </row>
@@ -7541,224 +7527,80 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>M&amp;E</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bếp từ</t>
+          <t>Dịch vụ khác</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
+          <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Silver</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nguyễn Quang Vũ</t>
+          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0983034568</t>
+          <t>0962892720</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CNCT Viettel Bắc Ninh</t>
+          <t>...</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
-        <is>
-          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
-Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>08:00 05/01/2026</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>10:25 03/04/2026</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Đinh Thị Ngọc</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>205029</t>
-        </is>
-      </c>
-      <c r="Y51" s="2">
-        <v>46027</v>
-      </c>
-      <c r="Z51">
-        <v>84</v>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Anhnt631</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Dịch vụ khác</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>23092025/HĐTP-SPT-VIETTEL</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>0962892720</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -7766,53 +7608,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>08:00 10/12/2025</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>15:00 16/12/2025</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y52" s="2">
+      <c r="Y51" s="2">
         <v>46001</v>
       </c>
-      <c r="Z52">
+      <c r="Z51">
         <v>110</v>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tấm pin NLMT</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VCC_HS_BNH_1774408109732</t>
+          <t>KHCN_TT.GPTH_HTH_1670859</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nguyễn Khương</t>
+          <t>Phan Đăng Ngân</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0977113014</t>
+          <t>0914669133</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>thôn Nội Viên, xã Tân Chi Xã Tân Chi - Xã Tân Chi - Bắc Ninh</t>
+          <t>268 đường Yên Trung</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -586,27 +586,29 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Phàn nàn, Góp Ý</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Con người</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>vệ sinh tấm pin nlmt, trên app báo 360k mà nhân viên lại báo lại 1 triệu. Báo vệ sinh 2 tuần nay mà chưa thấy ai gọi  (NV Ngô Bắc Việt ). Hỏi xem a Việt có phải người công ty hay không. Nếu không phải người công ty phải báo lại cho anh</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: áp tô mát bên phải bị dập đóng lên ko được, hệ thống chập chờn toàn thấy thông báo điện áp thấp.
+3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>08:00 08/04/2026</t>
+          <t>13:30 08/04/2026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>09:00 09/04/2026</t>
+          <t>13:30 09/04/2026</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -616,17 +618,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>nguyễn văn Tuần</t>
+          <t>Phan Đình Nhâm</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>461581</t>
+          <t>082671</t>
         </is>
       </c>
       <c r="Y2" s="2">
@@ -637,49 +639,49 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Anhnt631</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HUE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+          <t>Tấm pin NLMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VCC_HS_HNI_1775495508218</t>
+          <t>KHCN_TT.GPTH_HUE_1672152</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -687,11 +689,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -699,17 +696,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Trần Minh Khánh</t>
+          <t>Nguyễn Duy Phong</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0372644556</t>
+          <t>0337553979</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>811 Phúc Diễn, Phường Xuân Phương, Thành phố Hà Nội</t>
+          <t>61 Nguyễn Trãi</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -724,34 +721,34 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1. Chưa báo chi nhánh 
-2. Đã gọi qua hotline 
-Kh báo hôm nay kĩ thuật qua. Mà kĩ thuật không ai gọi</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Hệ thống nlmt ko thấy ra điện
+3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>08:00 08/04/2026</t>
+          <t>11:58 08/04/2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>14:00 08/04/2026</t>
+          <t>11:58 09/04/2026</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -761,17 +758,17 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Phạm Văn Tình</t>
+          <t>Nguyễn Đình Thành</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>463011</t>
+          <t>069501</t>
         </is>
       </c>
       <c r="Y3" s="2">
@@ -782,7 +779,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -804,2228 +801,2525 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1632204</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Loan</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0844696772</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Phường Long Biên, Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>CN 0985792828 báo sự cố hộ KH
+1. KH phản ánh: App bị văng hết, thông tin mất hết điện lưới, trắng tinh ko còn gì.
+2. KH yêu cầu: KT đến ktra cài đặt lại hệ thống cho KH.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>11:29 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>11:29 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trần Huy Quý</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>437012</t>
+        </is>
+      </c>
+      <c r="Y4" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>210701/GPTH/HĐMBLĐ-2025/CNCTDLK-STRIDESOLAR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Chung</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0379246357</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Thôn Thọ Lộc</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CN báo sự cố hộ KH
+HĐ 3 bên ký với Stride
+1. KH phản ánh: đang bị hư pin lưu trữ, tình trạng hư lúc hoạt động lúc không kể từ ngày 23/03/2026.
+2. KH yêu cầu: CN cử KT xuống kiểm tra thiết bị và khắc phục tình trạng này cho KH.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10:19 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>10:19 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lê Minh Khôi</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>418109</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>vinhvv4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Tấm pin NLMT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KHCN_PINNLMT_NAN_0281985</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Toàn</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0985701768</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Xã Văn Hiến, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: hiệu suất thấp, tháng trước đạt nhưng tháng này ko đạt hiệu suất.
+3. KH yêu cầu: Cho nv xuống kiểm tra chất lượng tấm pin xem có vấn đề gì không, đo kiểm lại tấm pin.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>10:03 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>10:03 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trần Mạnh Hùng</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>056524</t>
+        </is>
+      </c>
+      <c r="Y6" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1596050</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Minh Khuê</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0355830635</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Phường Nghi Lộc, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn: a Trần Bình Thanh - Kinh doanh
+2. KH phản ánh: hiệu suất giảm 1 nửa, bình thường trời nắng 1 buổi là đầy bình nhưng bây giờ trời nắng cả ngày ko đầy bình.
+3. KH yêu cầu: KT xuống kiểm tra, hỗ trợ, đưa phương án khắc phục tình trạng này cho KH.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>08:48 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>08:48 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trần Trọng Hiếu</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>069197</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0901/NLMT/VCCTNH</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nguyễn Hải Lương</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0983730342</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Thị trấn Tân Châu,Huyện Tân Châu,Tỉnh Tây Ninh</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn: Sự cố từ trước KH vẫn thấy hiệu suất kém
+2. KH phản ánh: Trước đấy công suất là 1 ngày 200kw mà sau khi sự cố phản ánh trước đây CN xử lý xong 1 ngày còn có 193-195kw mà vẫn trời nắng to.
+3. KH yêu cầu: Đo đạc lại thiết bị, từng tấm pin nlmt và có biên bản ghi nhận nghiệm thu là hiệu suất còn bao nhiêu kw và đưa ra phương án xử lý là có cần đưa ra hãng bảo hành không.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>13:36 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:36 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trần Văn Quy</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>470911</t>
+        </is>
+      </c>
+      <c r="Y8" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Tấm pin NLMT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1633298</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nguyễn Viết Trường</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0936626688</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BT T3-14, KĐT Nam Thăng Long, đường Nguyễn Hoàng Tôn</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>CN 0985792828 báo sự cố hộ KH
+1. KH phản ánh: đồng hồ đảo nguồn đang ko theo cài đặt
+2. KH yêu cầu: cài đặt đồng hồ đảo nguồn lại và giải thích cho KH thật là chuẩn.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>11:31 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>11:31 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nguyễn Tiến Lực</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>285897</t>
+        </is>
+      </c>
+      <c r="Y9" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HDG_1472655</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Chỉnh</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0976024133</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Tòng Hóa</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn: Hơn 1 tuần trước, KT có đến 1 lần rồi và xác định là hỏng áp đảo chiều và có thay 1 lần rồi nhưng bị lỗi ngay sau đó.
+2. KH phản ánh: Lỗi tủ điện hệ thống nlmt, đang bị lỗi áp đảo chiều. Khi mất điện phải gạt = tay, hệ thống tự đảo chiều giữa nguồn điện dự phòng và điện lưới nó ko còn nên ko tự động được nữa.
+3. KH yêu cầu: KT xuống kiểm tra và xử lý dứt điểm tình trạng này cho KH.</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>09:19 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>09:19 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thêm</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>285987</t>
+        </is>
+      </c>
+      <c r="Y10" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dịch vụ khác</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VCC_HS_BNH_1774408109732</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Nguyễn Khương</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0977113014</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>thôn Nội Viên, xã Tân Chi Xã Tân Chi - Xã Tân Chi - Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>vệ sinh tấm pin nlmt, trên app báo 360k mà nhân viên lại báo lại 1 triệu. Báo vệ sinh 2 tuần nay mà chưa thấy ai gọi  (NV Ngô Bắc Việt ). Hỏi xem a Việt có phải người công ty hay không. Nếu không phải người công ty phải báo lại cho anh</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>08:00 08/04/2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>09:00 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Phạm Khắc Việt</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>048379</t>
+        </is>
+      </c>
+      <c r="Y11" s="2">
+        <v>46120</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1598580</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Hồ Văn Khương</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0941663636</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Xóm 8</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1. Khách hàng không báo qua chi nhánh 
 2. Khách chỉ báo qua hotline 
 3. Điện nllmt 2 3 hôm nay hiệu số rất thấp.Giờ cao điểm trước đây thu được 5 6 kí giờ chỉ còn 2 3 kí</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>08:00 08/04/2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>09:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Chưa tính KPI</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Nguyễn Đình Trường</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>181241</t>
-        </is>
-      </c>
-      <c r="Y4" s="2">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>22:10 10/04/2026</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Võ Trọng Đức</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>293804</t>
+        </is>
+      </c>
+      <c r="Y12" s="2">
         <v>46120</v>
       </c>
-      <c r="Z4">
+      <c r="Z12">
         <v>0</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VCC_HS_HNI_1775440892465</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Điều hòa</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BGG_1554209</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Đinh Vi</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0942470019</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>L3 Ciputra</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Trần Văn Kiên</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0968518893</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>tổ dân phố chằm</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>- Chưa báo cho chi nhánh 
-- N3 Ciputra hẹn 13h30 gọi lại không thấy ai liên hệ.Khách hàng cần một lịch rõ ràng báo lại cho chị</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>08:00 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>09:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Chưa tính KPI</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lê Duy Tuấn</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>293859</t>
-        </is>
-      </c>
-      <c r="Y5" s="2">
-        <v>46120</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Điều hòa</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BGG_1554209</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Trần Văn Kiên</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0968518893</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>tổ dân phố chằm</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>KH báo dàn lạnh ko lạnh
 ko lên được cửa gió
 YC KT qua kiểm tra bảo hành thiết bị cho KH</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>16:31 07/04/2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>16:31 22/04/2026</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Ngô Văn Đạt</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>488066</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y13" s="2">
         <v>46119</v>
       </c>
-      <c r="Z6">
+      <c r="Z13">
         <v>1</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Anhnt631</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>DTP</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DTP_1495378</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Nguyễn Minh Vũ</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0913649949</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Số 93A, Tân Thuận B,Xã Tân Mỹ,Huyện Lấp Vò,Tỉnh Đồng Tháp</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Sản phẩm không sử dụng được / không hoạt động</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Hệ thống không hoạt động</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>08:00 08/04/2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>09:00 09/04/2026</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Chưa tính KPI</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Lưu Văn Liêm</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>324208</t>
         </is>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y14" s="2">
         <v>46120</v>
       </c>
-      <c r="Z7">
+      <c r="Z14">
         <v>0</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>DNG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNG_1354412</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Nguyễn Hào</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0905852777</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>104 đinh châu</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>- Chưa báo chi nhánh 
 - Báo lên tổng đài 
 -Lắp điện nlmt báo không có điện</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>14:32 07/04/2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>14:32 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>10:25 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ngô Văn Minh</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>083585</t>
-        </is>
-      </c>
-      <c r="Y8" s="2">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Hoàng Thái</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>288992</t>
+        </is>
+      </c>
+      <c r="Y15" s="2">
         <v>46119</v>
       </c>
-      <c r="Z8">
+      <c r="Z15">
         <v>1</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1681684</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_THA_1679973</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Bùi Văn Kiệt</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0913720227</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>18/4 Đoàn Thị Liên</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ngô Sỹ Dụng</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0978456085</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Thôn Ngọc Nhị</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1. KH đã báo Cn: a Nguyễn Hữu Toàn - tư vấn lắp đặt nlmt
-2. KH đã báo qua: Gọi điện cho a Toàn thì thấy cúp máy, ntin thì ko trả lời.
-3. KH phản ánh: CN Có hẹn hnay để đến lắp đặt mà giờ vẫn chưa thấy có ai, cũng ko thấy phản hồi lí do hay gì gọi điện thì cúp máy. 
-4. KH yêu cầu: liên hệ cho KH trả lời chính xác cho KH ngày giờ cụ thể để KH còn sắp xếp công việc để ở nhà. Hnay KH đã mất công sắp xếp ở nhà mà ko có ai.</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>13:30 07/04/2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>13:30 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Võ Hoài Đàm Lê</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>083844</t>
-        </is>
-      </c>
-      <c r="Y9" s="2">
-        <v>46119</v>
-      </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tuyendv</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DNI_1668234</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Nguyễn Hoàng Dân</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0374281493</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Thanh Lương</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Inverter không hoạt động</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn: a Vũ kinh doanh, a Vũ bảo  để liên hệ cho bên lắp đặt đã có KT liên hệ trao đổi với KH 2 ngày nay.
-2. KH phản ánh: Hệ 7,4kw, ivt 6kw nhưng chạy 2 bên bơm ivt hơn chỉ được 3 kw thì chạy nổi, bật thêm 1 bơm bên 5kw rưỡi nữa thì tự nhảy đèn đỏ, ko chạy được, chỉ lưới điện không. Sự cố bị hòai, KT trao đổi với nhau qua điện thoại bảo KH xem có bị quá tải không, do nguồn điện đầu vào yếu quá, KH thấy ít nhất cũng phải đến ktra trực tiếp.
-3. KH yêu cầu: Có KT qua kiểm tra trực tiếp, xác định nguyên nhà và đưa ra phương án xử lý, khắc phục cho KH.</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>10:55 07/04/2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10:55 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="Y10" s="2">
-        <v>46119</v>
-      </c>
-      <c r="Z10">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_THA_1679973</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ngô Sỹ Dụng</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0978456085</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Thôn Ngọc Nhị</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Tiến độ triển khai</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a trường, a chạm, a Trung
 2. KH phản ánh: hàng chưa về, cn có hẹn m4 là bàn giao toàn bộ linh kiện để lắp đặt nhưng CN có phản hồi lý do là hàng từ hà nội chưa về được. KH đã thanh toán số tiền trong HĐ.
 3. KH yêu cầu: Phản hồi và tình trạng linh kiện đang di chuyển đến đâu rồi và chậm nhất là đến m10 phải có linh kiện, vật tư ở đây nếu ko KH sẽ chấm dứt HĐ.</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>10:02 07/04/2026</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>10:02 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>15:00 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Nguyễn Văn Trung</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>442962</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y16" s="2">
         <v>46119</v>
       </c>
-      <c r="Z11">
+      <c r="Z16">
         <v>1</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QNH_1616773</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Nghiêm Văn Trung</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0904867479</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>258 hoàng minh thảo</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1. KH đã báo chi nhánh, cn báo gọi lên tổng đài 
 2. KH phản ánh: Hướng dẫn a cách xem app cài đặt mới AIO và anh thấy apptomat bị nhảy . 
 3. KH yêu cầu: Báo KT hỗ trợ nhanh giúp anh, cho người qua kiểm tra cho anh apptomat.</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>08:50 07/04/2026</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>08:50 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>08:05 09/04/2026</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Lương Ngọc Hưng</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>284060</t>
         </is>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y17" s="2">
         <v>46119</v>
       </c>
-      <c r="Z12">
+      <c r="Z17">
         <v>1</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Acquy lưu trữ</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HDG_1610342</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Anh Quân</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0983448280</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>phường chu văn an</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Mất 1 string điện không vào ắc quy. Không đủ cung cấp cho tải nhà dùng . Anh cần đến kiêm tra trong ngày hôm nay.
 **Địa chỉ lắp đặt: số nhà 300, kim tân, xã đoài phương, thành phố hà nội.</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>16:23 06/04/2026</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>17:30 08/04/2026</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>Bùi Văn Hoàn</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>046275</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y18" s="2">
         <v>46118</v>
       </c>
-      <c r="Z13">
+      <c r="Z18">
         <v>2</v>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_CTO_1677645</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KHDN_NLMT_BDG_0161107</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Võ Ngọc Trí</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0909850679</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Đông Bình</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ LINH THUẬN PHONG</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0938002111</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Phường Phú Tân, Thành phố Thủ Dầu Một, Tỉnh Bình Dương</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Hiệu suất sản phẩm kém</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Báo lên tổng  đài .sự cố nlmt hiệu suất bán tải  không còn cao như trước , 5 kí còn 2 kí 2  kiểm tra lại cho anh</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>13:38 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>15:50 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Dương Văn Sang</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>033812</t>
-        </is>
-      </c>
-      <c r="Y14" s="2">
-        <v>46118</v>
-      </c>
-      <c r="Z14">
-        <v>2</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KHDN_NLMT_BDG_0161107</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ LINH THUẬN PHONG</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0938002111</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Phường Phú Tân, Thành phố Thủ Dầu Một, Tỉnh Bình Dương</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: hệ thống nlmt ở trạng thái báo động, ko ghi nhận dữ liệu, ko thấy số đầu ra.
 3. KH yêu cầu: KT qua kiểm tra thiết bị, khắc phục tình trạng này.</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>13:30 06/04/2026</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>23:10 09/04/2026</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Trần Doãn Lượng</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>455101</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y19" s="2">
         <v>46118</v>
       </c>
-      <c r="Z15">
+      <c r="Z19">
         <v>2</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNH_1660113</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Nguyễn Thanh Vũ</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0918451696</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>456</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Zalo</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>KH phản ánh: Nhà bị cháy, cháy 3 tấm pin năng lượng.
 KH yêu cầu: cần kỹ thuật hỗ trợ kiểm tra giúp hệ thống.</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>11:39 06/04/2026</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>07:40 10/04/2026</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Nguyễn Quốc Hưng</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>467401</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y20" s="2">
         <v>46118</v>
       </c>
-      <c r="Z16">
+      <c r="Z20">
         <v>2</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HYN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1679072</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HYN_1594620</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Thu Hằng</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0979556462</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Số 27 Đường 1 KDT Nam Lê Lợi</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Khiêm</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0941128289</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>lưu xá</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>- Đã liên hệ chi nhánh 
-- kí hợp đồng bên viettel nghệ an từ ngày 25/3,  trong hợp đồng kí 7- 10 ngày các bạn phải đưa thiết bị  cho chị, mà giờ quá thời gian vẫn chưa thấy  . Chi nhánh ở nghệ an báo là không có hàng, phải đợi từ ngoài hà nội. Thông báo chính xác lại cho chị khi nào mới có hàng để chị sắp xếp người ở nhà. Trong thời gian chị chờ các em tốn rất nhiều tiền điện</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>10:34 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>15:30 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Lê Ngọc Sơn</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>466571</t>
-        </is>
-      </c>
-      <c r="Y17" s="2">
-        <v>46118</v>
-      </c>
-      <c r="Z17">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1642483</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Nguyễn Việt Tuấn</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0898318593</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Xã Long Hải, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn: a Phan Hải Sơn
-2. KH phản ánh: Ko kết nối được app để theo dõi hiệu suất nlmt
-3. KH yêu cầu: Qua hỗ trợ kiểm tra cho KH</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>08:25 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>19:40 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Lê Đức Cảnh</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>291002</t>
-        </is>
-      </c>
-      <c r="Y18" s="2">
-        <v>46118</v>
-      </c>
-      <c r="Z18">
-        <v>2</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HYN</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HYN_1594620</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khiêm</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0941128289</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>lưu xá</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Sản phẩm không sử dụng được / không hoạt động</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>1. Cn báo hộ: SDT báo: 0868707197
 2.KH dùng NLMT hiện tại thiết bị ko hoạt động, ko sinh điện
@@ -3033,485 +3327,200 @@
 4.yc giao NV: 429217</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>08:00 08/04/2026</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>09:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>10:46 23/04/2026</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Chưa tính KPI</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>Đinh Văn Huyến</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>429217</t>
         </is>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y21" s="2">
         <v>46120</v>
       </c>
-      <c r="Z19">
+      <c r="Z21">
         <v>0</v>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CTO_1665852</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Phan Thị Phương Mai</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0357842266</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>51/12/7 đường 3/2</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>1. Chưa báo qua chi nhánh 
 2. Báo qua hotline 
 3,. Cúp CV không sài được</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>08:00 08/04/2026</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>09:00 09/04/2026</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Chưa tính KPI</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Phạm Minh Tiến</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>161573</t>
-        </is>
-      </c>
-      <c r="Y20" s="2">
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Võ Chí Trung</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>469593</t>
+        </is>
+      </c>
+      <c r="Y22" s="2">
         <v>46120</v>
       </c>
-      <c r="Z20">
+      <c r="Z22">
         <v>0</v>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1680392</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Đinh Quốc Tấn</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0979206868</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>số nhà 212, đường Hồng Liễu</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1. Khách hàng chưa báo chi nhánh 
-2. Đã báo qua hotline 
-3.Đã kí hợp đồng nlmt, mà không có thợ làm, lắp đặt . Anh kí từ ngày 29/3 .Trong 1 tuần là lắp đặt xong, mà 10 ngày vẫn chưa lắp</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>14:08 07/04/2026</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>14:08 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Nguyễn Đình Trường</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>181241</t>
-        </is>
-      </c>
-      <c r="Y21" s="2">
-        <v>46119</v>
-      </c>
-      <c r="Z21">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HCM_1682059</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH Xây Dựng Thương Mại Vũ Linh Phát</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0985417468</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Thửa đất số 181, tờ bản đồ só 45, đường lê quang định, tổ 1 khu phố khánh lộc</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn: Anh Phụng
-2. KH phản ánh: Chưa thấy có vật tư để lắp đặt nlmt, hơn 1 tháng trời rồi, sân với mái dọn đi rồi mà để mưa gió như thế. HĐ ký lại do chuyển cty, nên đã hơn 1 tháng trời.
-3. KH yêu cầu: liên hệ phản hồi lý do vật tư chậm trễ, và triển khai lắp đặt nlmt cho KH. Nếu ko phản hồi KH sẽ chấm dứt HĐ.</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>08:43 07/04/2026</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>08:43 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Phạm Xuân Vũ</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>235457</t>
-        </is>
-      </c>
-      <c r="Y22" s="2">
-        <v>46119</v>
-      </c>
-      <c r="Z22">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Tuyendv</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3776,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -4053,7 +4062,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4956,7 +4965,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4976,7 +4985,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNI_1675059</t>
+          <t>KHCN_NLMT_TNN_0200299</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4991,79 +5000,79 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu</t>
+          <t>Đinh Văn Chỉnh</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0981756789</t>
+          <t>0868632926</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Khu dịch vụ Đồng Giường</t>
+          <t>Phú Cường,</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn 1 tuần
-2. KH yêu cầu thanh lý HĐ bởi vì giá cao quá, KH muốn lấy lại tiền, và giải quyết nhanh.
-***SĐT phản ánh: 0965982906</t>
+          <t>KH dã báo CN
+KH đang sử dụng NLMT, hiện tại KH ko thấy phát sinh điện, bên điện lực báo ko thấy công tơ lên
+YC KT qua kiểm tra và xử lý cho KH</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09:42 03/04/2026</t>
+          <t>08:00 03/04/2026</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>18:15 13/04/2026</t>
+          <t>09:00 06/04/2026</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Lê Duy Tuấn</t>
+          <t>Trần Xuân Kương</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>293859</t>
+          <t>289759</t>
         </is>
       </c>
       <c r="Y33" s="2">
@@ -5079,24 +5088,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Anhnt631</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5111,12 +5120,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KHCN_NLMT_TNN_0200299</t>
+          <t>DH_B2C_CMU_1775089977159</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5124,6 +5133,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -5131,27 +5145,27 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Đinh Văn Chỉnh</t>
+          <t>Trần Thái Thịnh</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0868632926</t>
+          <t>0919000027</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Phú Cường,</t>
+          <t>chợ phường 3 cũ</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5166,155 +5180,10 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Inverter không hoạt động</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
-        <is>
-          <t>KH dã báo CN
-KH đang sử dụng NLMT, hiện tại KH ko thấy phát sinh điện, bên điện lực báo ko thấy công tơ lên
-YC KT qua kiểm tra và xử lý cho KH</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>08:00 03/04/2026</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>09:00 06/04/2026</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Trần Xuân Kương</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>289759</t>
-        </is>
-      </c>
-      <c r="Y34" s="2">
-        <v>46115</v>
-      </c>
-      <c r="Z34">
-        <v>5</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DH_B2C_CMU_1775089977159</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Trần Thái Thịnh</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0919000027</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>chợ phường 3 cũ</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Inverter không hoạt động</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH dang sd NLMT Hiện tại thiết bị ko hoạt động
@@ -5322,14 +5191,159 @@
 KH yc KT qua kiểm tra và xử lý</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>15:42 02/04/2026</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:20 10/04/2026</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lê Hoàng Thiên</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>292658</t>
+        </is>
+      </c>
+      <c r="Y34" s="2">
+        <v>46114</v>
+      </c>
+      <c r="Z34">
+        <v>6</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>tietvt16</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNI_1595675</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Duy</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0972480125</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Ấp Cây Cầy</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn: CN qua kiểm tra qua loa, đổ thừa này nọ
+2. KH phản ánh: Hệ của KH 10kw cũng chỉ thấy chạy được 5,6 kw điện. KH có lắp thêm 5 tấm nữa chạy cho mạnh cũng chỉ lên được 7 kw mà nắng gắt 35 độ. KH ktra thấy biến tần chạy khoảng 60%.
+3. KH yêu cầu: Qua kiểm tra tình trạng nguyên nhân để tăng hiệu suất đúng với hệ của KH.</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>15:42 02/04/2026</t>
+          <t>13:30 02/04/2026</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>14:20 10/04/2026</t>
+          <t>16:00 10/04/2026</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5339,17 +5353,17 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Lê Hoàng Thiên</t>
+          <t>Phan Thanh Sang</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>292658</t>
+          <t>083737</t>
         </is>
       </c>
       <c r="Y35" s="2">
@@ -5360,29 +5374,29 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5397,12 +5411,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Tấm pin NLMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNI_1595675</t>
+          <t>KHCN_PINNLMT_GLI_0299078</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5412,7 +5426,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5422,17 +5436,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nguyễn Thanh Duy</t>
+          <t>Bùi Quang Vinh</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0972480125</t>
+          <t>0983885630</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ấp Cây Cầy</t>
+          <t>Nayder</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5442,7 +5456,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5457,24 +5471,22 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Tấm pin bị rò rỉ/ Lỗi</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn: CN qua kiểm tra qua loa, đổ thừa này nọ
-2. KH phản ánh: Hệ của KH 10kw cũng chỉ thấy chạy được 5,6 kw điện. KH có lắp thêm 5 tấm nữa chạy cho mạnh cũng chỉ lên được 7 kw mà nắng gắt 35 độ. KH ktra thấy biến tần chạy khoảng 60%.
-3. KH yêu cầu: Qua kiểm tra tình trạng nguyên nhân để tăng hiệu suất đúng với hệ của KH.</t>
+          <t>hệ thống nlmt bị lỗi, viên pin bị lủng. Kĩ thuật báo theo dõi. Điện bị sụt</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>13:30 02/04/2026</t>
+          <t>15:36 01/04/2026</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>16:00 10/04/2026</t>
+          <t>17:30 11/04/2026</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5489,19 +5501,19 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Phan Thanh Sang</t>
+          <t>Nguyễn Thương</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>083737</t>
+          <t>468169</t>
         </is>
       </c>
       <c r="Y36" s="2">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5522,12 +5534,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5542,12 +5554,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tấm pin NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_GLI_0299078</t>
+          <t>KHCN_TT.GPTH_LAN_1530029</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5557,7 +5569,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5567,17 +5579,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Bùi Quang Vinh</t>
+          <t>Lê Thị Lụa</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0983885630</t>
+          <t>0975020753</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Nayder</t>
+          <t>152 Hùng Vương, KP 4,Thị trấn Tân Thạnh,Huyện Tân Thạnh,Tỉnh Long An</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5587,7 +5599,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -5602,153 +5614,10 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Tấm pin bị rò rỉ/ Lỗi</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
-        <is>
-          <t>hệ thống nlmt bị lỗi, viên pin bị lủng. Kĩ thuật báo theo dõi. Điện bị sụt</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>15:36 01/04/2026</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>17:30 11/04/2026</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Nguyễn Thương</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>468169</t>
-        </is>
-      </c>
-      <c r="Y37" s="2">
-        <v>46113</v>
-      </c>
-      <c r="Z37">
-        <v>7</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_LAN_1530029</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Lê Thị Lụa</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0975020753</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>152 Hùng Vương, KP 4,Thị trấn Tân Thạnh,Huyện Tân Thạnh,Tỉnh Long An</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: Ivt bị lỗi ko lên màn hình, ko xả và nạp được
@@ -5757,14 +5626,159 @@
 - SĐT liên hệ và phản ánh: 0962608008 chồng của KH</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>08:20 01/04/2026</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>08:00 30/04/2026</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Hào</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>075543</t>
+        </is>
+      </c>
+      <c r="Y37" s="2">
+        <v>46113</v>
+      </c>
+      <c r="Z37">
+        <v>7</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BNH_1634096</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Ân</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0988386838</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Xã Xuân Cẩm, Tỉnh Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: nhà KH có thêm ats của máy nổ, về nguyên tắc máy điện phải chạy nlmt, khi nlmt hết thì chạy máy nổ. Hiện tại thì khi mất điện ko chạy sang nlmt, và khi nlmt hết rồi vẫn ko thấy chạy máy nổ. 
+3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>08:20 01/04/2026</t>
+          <t>15:55 30/03/2026</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>08:00 30/04/2026</t>
+          <t>17:15 11/04/2026</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5774,24 +5788,24 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Hào</t>
+          <t>Phạm Văn Huy</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>075543</t>
+          <t>408869</t>
         </is>
       </c>
       <c r="Y38" s="2">
-        <v>46113</v>
+        <v>46111</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -5812,12 +5826,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5832,12 +5846,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1634096</t>
+          <t>KHCN_TT.GPTH_DTP_1618243</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5847,7 +5861,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5857,22 +5871,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Nguyễn Ngọc Ân</t>
+          <t>Nguyễn Thị Kim Dung</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0988386838</t>
+          <t>0946142525</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Xã Xuân Cẩm, Tỉnh Bắc Ninh</t>
+          <t>Ấp Tân Dân</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5892,24 +5906,23 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: nhà KH có thêm ats của máy nổ, về nguyên tắc máy điện phải chạy nlmt, khi nlmt hết thì chạy máy nổ. Hiện tại thì khi mất điện ko chạy sang nlmt, và khi nlmt hết rồi vẫn ko thấy chạy máy nổ. 
-3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
+          <t>ATS chuyển nguồn thiết bị hỏng.
+KH đã được hỗ trợ.</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>15:55 30/03/2026</t>
+          <t>09:49 31/03/2026</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>17:15 11/04/2026</t>
+          <t>17:00 15/04/2026</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5924,19 +5937,19 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Phạm Văn Huy</t>
+          <t>Lưu Văn Liêm</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>408869</t>
+          <t>324208</t>
         </is>
       </c>
       <c r="Y39" s="2">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="Z39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5957,12 +5970,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5977,12 +5990,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DTP_1618243</t>
+          <t>KHCN_PINNLMT_NAN_0334667</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5990,11 +6003,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -6002,22 +6010,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Kim Dung</t>
+          <t>Lê Trung An</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0946142525</t>
+          <t>0865878212</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ấp Tân Dân</t>
+          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6032,28 +6040,28 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ATS chuyển nguồn thiết bị hỏng.
-KH đã được hỗ trợ.</t>
+          <t>1. KH đã báo cn
+2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>09:49 31/03/2026</t>
+          <t>11:30 30/03/2026</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>17:00 15/04/2026</t>
+          <t>19:10 10/04/2026</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6063,24 +6071,24 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Lưu Văn Liêm</t>
+          <t>Nguyễn Minh Linh</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>324208</t>
+          <t>285776</t>
         </is>
       </c>
       <c r="Y40" s="2">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -6126,7 +6134,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_NAN_0334667</t>
+          <t>KHCN_TT.GPTH_NAN_1574225</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6134,6 +6142,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -6141,17 +6154,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Lê Trung An</t>
+          <t>Nguyên Văn Tú</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0865878212</t>
+          <t>0868081789</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+          <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6171,28 +6184,29 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn
-2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
+          <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
+2. KH phản ánh NLMT bị hỏng không sử dụng được
+3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>11:30 30/03/2026</t>
+          <t>08:00 30/03/2026</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>19:10 10/04/2026</t>
+          <t>20:10 15/04/2026</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6202,7 +6216,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6240,12 +6254,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6260,12 +6274,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1574225</t>
+          <t>KHCN_TT.GPTH_QNM_1510130</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6275,7 +6289,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6285,22 +6299,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Nguyên Văn Tú</t>
+          <t>Lê Phước Danh</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0868081789</t>
+          <t>0355557906</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
+          <t>Thôn Pà Dá,Xã Cà Dy,Huyện Nam Giang,Tỉnh Quảng Nam</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6315,7 +6329,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6325,19 +6339,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
-2. KH phản ánh NLMT bị hỏng không sử dụng được
-3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
+          <t>Lỗi pin ko lưu</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>08:00 30/03/2026</t>
+          <t>10:43 01/04/2026</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>20:10 15/04/2026</t>
+          <t>10:52 18/04/2026</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6352,19 +6364,19 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Linh</t>
+          <t>Lê Văn Trung</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>285776</t>
+          <t>161073</t>
         </is>
       </c>
       <c r="Y42" s="2">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="Z42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6385,12 +6397,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6405,12 +6417,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Acquy lưu trữ</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QNM_1510130</t>
+          <t>KHCN_TT.GPTH_HDG_1304417</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6420,7 +6432,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6430,22 +6442,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Lê Phước Danh</t>
+          <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0355557906</t>
+          <t>0377883716</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Thôn Pà Dá,Xã Cà Dy,Huyện Nam Giang,Tỉnh Quảng Nam</t>
+          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6470,17 +6482,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Lỗi pin ko lưu</t>
+          <t>KH chưa báo CN
+KH yêu cầu NVKT qua lại thiết bị inverter của KH 
+Số liên hệ:</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10:43 01/04/2026</t>
+          <t>08:00 26/03/2026</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>10:52 18/04/2026</t>
+          <t>09:46 19/04/2026</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6495,19 +6509,19 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Lê Văn Trung</t>
+          <t>Hoàng Văn Phong</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>161073</t>
+          <t>291011</t>
         </is>
       </c>
       <c r="Y43" s="2">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="Z43">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6533,7 +6547,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6553,7 +6567,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HDG_1304417</t>
+          <t>KHCN_TT.GPTH_BNH_1600729</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6563,7 +6577,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6573,17 +6587,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hồng Khánh</t>
+          <t>Nguyễn Khương</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0377883716</t>
+          <t>0977113014</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
+          <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6603,7 +6617,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6613,19 +6627,19 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>KH chưa báo CN
-KH yêu cầu NVKT qua lại thiết bị inverter của KH 
-Số liên hệ:</t>
+          <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
+2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
+3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>08:00 26/03/2026</t>
+          <t>09:20 25/03/2026</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>09:46 19/04/2026</t>
+          <t>18:30 30/03/2026</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6635,24 +6649,24 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Hoàng Văn Phong</t>
+          <t>nguyễn văn Tuần</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>291011</t>
+          <t>461581</t>
         </is>
       </c>
       <c r="Y44" s="2">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="Z44">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6678,7 +6692,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6698,7 +6712,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1600729</t>
+          <t>KHCN_TT.GPTH_VPC_1503902</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6708,7 +6722,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6718,17 +6732,17 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nguyễn Khương</t>
+          <t>Nguyễn Việt Hùng</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0977113014</t>
+          <t>0966547344</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Xã Tân Chi, Tỉnh Bắc Ninh</t>
+          <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -6738,7 +6752,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -6748,7 +6762,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6757,151 +6771,6 @@
         </is>
       </c>
       <c r="R45" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn nhưng bạn nv kinh doanh a Vượng chuyển công tác nên chuyển cho a Phong, a Phong lại chuyển công tác cho số người mới nhưng chưa thấy.
-2. KH phản ánh: Biểu đồ biến tần tăng giảm đột biến, sụt pin về 0,pv về 0, tất cả đều về 0, thi thoảng còn bị mất điện. Hôm vừa rồi đầu xuân vào app báo thấy mất kết nối điện lưới trong khi nhà xung quanh vẫn có, sau khi xem tbao ở trên app lại ko có bất kỳ tbao nào về biến tần bị ngắt hay gì cả. KH Kbt có ai can thiệp vào app không
-3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>09:20 25/03/2026</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>18:30 30/03/2026</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>nguyễn văn Tuần</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>461581</t>
-        </is>
-      </c>
-      <c r="Y45" s="2">
-        <v>46106</v>
-      </c>
-      <c r="Z45">
-        <v>14</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_VPC_1503902</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Nguyễn Việt Hùng</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0966547344</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Tự lập Mê Linh,Phường Hùng Vương,Thành phố Phúc Yên,Tỉnh Vĩnh Phúc</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH đang dùng NLMT hiện tại bị lỗi biến tần, ko kết nối được app
@@ -6909,14 +6778,159 @@
 NOTE: địa chỉ hiện tại của KH: thôn phú mỹ, xã tiến thắng, Hà Nội</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>15:34 24/03/2026</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>14:16 16/04/2026</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Phạm Văn Nghĩa</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>023020</t>
+        </is>
+      </c>
+      <c r="Y45" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z45">
+        <v>15</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_PTO_1620637</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Nguyễn Đình Mạnh</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0988308581</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>KH chưa báo CN
+KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
+KH yêu cầu chuyển KT xuống xử lý gấp</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>15:34 24/03/2026</t>
+          <t>15:09 24/03/2026</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>14:16 16/04/2026</t>
+          <t>21:10 23/04/2026</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6931,12 +6945,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Phạm Văn Nghĩa</t>
+          <t>Bùi Anh Nguyễn</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>023020</t>
+          <t>414445</t>
         </is>
       </c>
       <c r="Y46" s="2">
@@ -6969,7 +6983,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6979,47 +6993,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>CNTT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Camera 360 độ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_PTO_1620637</t>
+          <t>299/2025/HĐKT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Nguyễn Đình Mạnh</t>
+          <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0988308581</t>
+          <t>0869217169</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
+          <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7048,146 +7057,6 @@
         </is>
       </c>
       <c r="R47" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN
-KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
-KH yêu cầu chuyển KT xuống xử lý gấp</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>15:09 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>21:10 23/04/2026</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Bùi Anh Nguyễn</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>414445</t>
-        </is>
-      </c>
-      <c r="Y47" s="2">
-        <v>46105</v>
-      </c>
-      <c r="Z47">
-        <v>15</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CNTT</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Camera 360 độ</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>299/2025/HĐKT</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Ban Quản Lý Rừng Phòng Hộ Bắc Nghệ An</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0869217169</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Khối 11, Xã Quỳnh Lưu, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: camera 360 chưa kết nối được hệ thống điều khiển, chưa lên được tivi để xem và cũng như pccc rừng mùa khô.
@@ -7195,14 +7064,159 @@
 ***SĐT liên hệ: 0988867428, Anh Thức</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>08:45 24/03/2026</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>09:00 16/04/2026</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Võ Trọng Đức</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>293804</t>
+        </is>
+      </c>
+      <c r="Y47" s="2">
+        <v>46105</v>
+      </c>
+      <c r="Z47">
+        <v>15</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>tietvt16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Công tắc thông minh</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNG_1416913</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Lê Đắc Quỳ</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0915313915</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
+3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>08:45 24/03/2026</t>
+          <t>08:00 23/03/2026</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>09:00 16/04/2026</t>
+          <t>07:50 08/04/2026</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7212,28 +7226,28 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Võ Trọng Đức</t>
+          <t>Nguyễn Thanh Hoàng Thái</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>293804</t>
+          <t>288992</t>
         </is>
       </c>
       <c r="Y48" s="2">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="Z48">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -7243,19 +7257,19 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7265,17 +7279,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Công tắc thông minh</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1416913</t>
+          <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7285,7 +7299,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7295,22 +7309,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lê Đắc Quỳ</t>
+          <t>Dương Văn Quân</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0915313915</t>
+          <t>0359999199</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Phường Hòa Xuân, Thành phố Đà Nẵng</t>
+          <t>xã Hoàng Vân</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7325,160 +7339,15 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Vào được aio app smart home nhưng ko thấy có công tắc.
-3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>08:00 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>07:50 08/04/2026</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Nguyễn Thanh Hoàng Thái</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>288992</t>
-        </is>
-      </c>
-      <c r="Y49" s="2">
-        <v>46104</v>
-      </c>
-      <c r="Z49">
-        <v>16</v>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BGG_1597213</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Dương Văn Quân</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0359999199</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>xã Hoàng Vân</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -7486,14 +7355,159 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>08:00 23/03/2026</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>18:00 26/03/2026</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Trường</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>121999</t>
+        </is>
+      </c>
+      <c r="Y49" s="2">
+        <v>46104</v>
+      </c>
+      <c r="Z49">
+        <v>16</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HCM_1638575</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0911937779</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
+3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>08:00 23/03/2026</t>
+          <t>09:25 19/03/2026</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>18:00 26/03/2026</t>
+          <t>09:00 28/04/2026</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7503,24 +7517,24 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trường</t>
+          <t>Lê Đức Cảnh</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>121999</t>
+          <t>291002</t>
         </is>
       </c>
       <c r="Y50" s="2">
-        <v>46104</v>
+        <v>46100</v>
       </c>
       <c r="Z50">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -7566,7 +7580,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1638575</t>
+          <t>KHCN_TT.GPTH_HCM_1646383</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7581,22 +7595,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
+          <t>Nguyễn Hữu Nghĩa</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0911937779</t>
+          <t>0945919596</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
+          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -7616,29 +7630,27 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
-3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
+          <t>KH yc ktra nguyên nhân xảy ra sự cố Hệ NLMT bị sự cố lỗi. Nhiều lúc lấy điện lưới dùng không dùng điện NLMT.</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>09:25 19/03/2026</t>
+          <t>08:00 16/03/2026</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>09:00 28/04/2026</t>
+          <t>09:00 13/04/2026</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7648,7 +7660,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7662,10 +7674,10 @@
         </is>
       </c>
       <c r="Y51" s="2">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="Z51">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -7686,12 +7698,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7711,7 +7723,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1646383</t>
+          <t>KHCN_TT.GPTH_QTI_0991884</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7719,11 +7731,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -7731,27 +7738,27 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Nghĩa</t>
+          <t>Nguyễn Thị Như Mỹ</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0945919596</t>
+          <t>0963369267</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Phường Tam Thắng, Thành phố Hồ Chí Minh, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+          <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -7761,27 +7768,29 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>KH yc ktra nguyên nhân xảy ra sự cố Hệ NLMT bị sự cố lỗi. Nhiều lúc lấy điện lưới dùng không dùng điện NLMT.</t>
+          <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
+2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
+3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>08:00 16/03/2026</t>
+          <t>08:00 09/03/2026</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>09:00 13/04/2026</t>
+          <t>11:45 10/04/2026</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7791,24 +7800,24 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Trương Thành</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>462341</t>
         </is>
       </c>
       <c r="Y52" s="2">
-        <v>46097</v>
+        <v>46090</v>
       </c>
       <c r="Z52">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -7829,12 +7838,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7849,12 +7858,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QTI_0991884</t>
+          <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7862,6 +7871,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -7869,17 +7883,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Như Mỹ</t>
+          <t>Nguyễn Phú Quý</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0963369267</t>
+          <t>0947110192</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
+          <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -7889,7 +7903,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -7899,7 +7913,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -7908,151 +7922,6 @@
         </is>
       </c>
       <c r="R53" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
-2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
-3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>08:00 09/03/2026</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>11:45 10/04/2026</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Trương Thành</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>462341</t>
-        </is>
-      </c>
-      <c r="Y53" s="2">
-        <v>46090</v>
-      </c>
-      <c r="Z53">
-        <v>30</v>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_VTU_1502475</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Nguyễn Phú Quý</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>0947110192</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -8060,14 +7929,159 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>15:09 03/03/2026</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>12:55 15/03/2026</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lê Đức Cảnh</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>291002</t>
+        </is>
+      </c>
+      <c r="Y53" s="2">
+        <v>46084</v>
+      </c>
+      <c r="Z53">
+        <v>36</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_DNI_1659133</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0907002673</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1. Kh đã báo cn
+2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
+3. kh yc: YC cn hỗ trợ sớm</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>15:09 03/03/2026</t>
+          <t>13:30 23/02/2026</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>12:55 15/03/2026</t>
+          <t>17:45 29/03/2026</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -8077,24 +8091,24 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Lê Đức Bình</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>412105</t>
         </is>
       </c>
       <c r="Y54" s="2">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="Z54">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -8115,12 +8129,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8135,42 +8149,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_DNI_1659133</t>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+          <t>Trương Công An</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0907002673</t>
+          <t>0914531694</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+          <t>khối 2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -8200,19 +8214,18 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1. Kh đã báo cn
-2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
-3. kh yc: YC cn hỗ trợ sớm</t>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>13:30 23/02/2026</t>
+          <t>08:00 19/01/2026</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>17:45 29/03/2026</t>
+          <t>22:00 17/04/2026</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -8227,19 +8240,19 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Lê Đức Bình</t>
+          <t>Lê Văn Anh</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>412105</t>
+          <t>069170</t>
         </is>
       </c>
       <c r="Y55" s="2">
-        <v>46076</v>
+        <v>46041</v>
       </c>
       <c r="Z55">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -8265,7 +8278,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8280,12 +8293,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
+          <t>KHCN_TT.GPTH_TNN_0885867</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8293,11 +8306,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -8305,17 +8313,17 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Trương Công An</t>
+          <t>Nguyễn Đức Hùng</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0914531694</t>
+          <t>0396264028</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>khối 2</t>
+          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -8325,7 +8333,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -8345,18 +8353,19 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
+          <t>1. Đã báo CN: Chưa báo
+2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
+3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>08:00 19/01/2026</t>
+          <t>08:00 14/01/2026</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>22:00 17/04/2026</t>
+          <t>17:00 25/02/2026</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8371,19 +8380,19 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Lê Văn Anh</t>
+          <t>Trần Xuân Kương</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>069170</t>
+          <t>289759</t>
         </is>
       </c>
       <c r="Y56" s="2">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="Z56">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -8409,7 +8418,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8419,17 +8428,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>M&amp;E</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Bếp từ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNN_0885867</t>
+          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8437,6 +8446,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -8444,22 +8458,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Hùng</t>
+          <t>Nguyễn Quang Vũ</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0396264028</t>
+          <t>0983034568</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Xóm Ấp Chè, Xã Văn Hán, Huyện Đồng Hỷ, Tỉnh Thái Nguyên</t>
+          <t>CNCT Viettel Bắc Ninh</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8484,19 +8498,18 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1. Đã báo CN: Chưa báo
-2. KH báo sự cố: 1 cục pin lưu trữ không vào điện và khi mất điện lưới hệ không tải điện vào để sử dụng.
-3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
+          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
+Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>08:00 14/01/2026</t>
+          <t>08:00 05/01/2026</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>17:00 25/02/2026</t>
+          <t>09:35 10/04/2026</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8511,19 +8524,19 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Trần Xuân Kương</t>
+          <t>Đinh Thị Ngọc</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>289759</t>
+          <t>205029</t>
         </is>
       </c>
       <c r="Y57" s="2">
-        <v>46036</v>
+        <v>46027</v>
       </c>
       <c r="Z57">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -8532,12 +8545,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Anhnt631</t>
         </is>
       </c>
     </row>
@@ -8549,224 +8562,80 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M&amp;E</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bếp từ</t>
+          <t>Dịch vụ khác</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_HNI_2402026_CDV</t>
+          <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Silver</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Nguyễn Quang Vũ</t>
+          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0983034568</t>
+          <t>0962892720</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CNCT Viettel Bắc Ninh</t>
+          <t>...</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
-        <is>
-          <t>KH nội bộ VCC T12/2025 quay số trúng thưởng bếp từ đơn AIO, bếp không hoạt động. Yêu cầu Kt qua bảo hành gấp. 
-Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>08:00 05/01/2026</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>09:35 10/04/2026</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Đinh Thị Ngọc</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>205029</t>
-        </is>
-      </c>
-      <c r="Y58" s="2">
-        <v>46027</v>
-      </c>
-      <c r="Z58">
-        <v>93</v>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Anhnt631</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Dịch vụ khác</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>23092025/HĐTP-SPT-VIETTEL</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>0962892720</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -8774,53 +8643,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>08:00 10/12/2025</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>15:00 16/12/2025</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y59" s="2">
+      <c r="Y58" s="2">
         <v>46001</v>
       </c>
-      <c r="Z59">
+      <c r="Z58">
         <v>119</v>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -15,8 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -55,12 +56,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -358,7 +360,9 @@
   <dimension ref="A1:AC68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="20.7109375" style="2" customWidth="1"/>
+    <col min="25" max="25" width="20.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -595,15 +599,11 @@
 YC KT qua kiểm tra lại</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>09:00 10/04/2026</t>
-        </is>
+      <c r="S2" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T2" s="2">
+        <v>46122.08333333333</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -625,7 +625,7 @@
           <t>063049</t>
         </is>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y2" s="3">
         <v>46121</v>
       </c>
       <c r="Z2">
@@ -733,15 +733,11 @@
           <t>KH lên đơn từ 8.3 , nhưng chưa có KT liên hệ hẹn lịch</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>14:00 09/04/2026</t>
-        </is>
+      <c r="S3" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T3" s="2">
+        <v>46121.29166666667</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -750,7 +746,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -763,7 +759,7 @@
           <t>416919</t>
         </is>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y3" s="3">
         <v>46121</v>
       </c>
       <c r="Z3">
@@ -873,15 +869,11 @@
 3.YC KT qua kiểm tra và xử lý gấp cho KH</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>09:00 10/04/2026</t>
-        </is>
+      <c r="S4" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T4" s="2">
+        <v>46122.08333333333</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -890,7 +882,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -903,7 +895,7 @@
           <t>015857</t>
         </is>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="3">
         <v>46121</v>
       </c>
       <c r="Z4">
@@ -1016,15 +1008,11 @@
           <t>1 năm đầu tiên có vệ sinh. Những năm sau không có  gói vệ sinh định kỳ, đã tháo tấm pin không trả lại. Hứa tặng bên chị 2 camera . Đã gọi cho bạn Nguyễn Sinh Dũng, giám đốc không nghe máy, hứa sẽ đẩy việc đến hỗ trợ. Chị không thấy ai hỗ trợ lại.   Chị cần hỗ trợ sớm trong vòng 5 ngày</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>09:00 10/04/2026</t>
-        </is>
+      <c r="S5" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T5" s="2">
+        <v>46122.08333333333</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1033,7 +1021,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1046,7 +1034,7 @@
           <t>293859</t>
         </is>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y5" s="3">
         <v>46121</v>
       </c>
       <c r="Z5">
@@ -1160,15 +1148,11 @@
 - Anh muốn bảo dưỡng  vệ sinh tấm pin năng lượng mặt trời. Hỗ trợ cho anh</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>09:00 10/04/2026</t>
-        </is>
+      <c r="S6" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T6" s="2">
+        <v>46122.08333333333</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1177,7 +1161,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1190,7 +1174,7 @@
           <t>056298</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6" s="3">
         <v>46121</v>
       </c>
       <c r="Z6">
@@ -1304,15 +1288,11 @@
 - Trong hợp đồng 1 năm sẽ vệ sinh tấm pin nlmt. Mà giờ chưa ai liên hệ đến  làm cho anh.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>09:00 10/04/2026</t>
-        </is>
+      <c r="S7" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T7" s="2">
+        <v>46122.08333333333</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1321,7 +1301,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1334,7 +1314,7 @@
           <t>284469</t>
         </is>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="3">
         <v>46121</v>
       </c>
       <c r="Z7">
@@ -1448,15 +1428,11 @@
 - Kĩ thuật hẹn 15h mà vẫn chưa đến</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>17:15 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>17:15 09/04/2026</t>
-        </is>
+      <c r="S8" s="2">
+        <v>46120.42708333333</v>
+      </c>
+      <c r="T8" s="2">
+        <v>46121.42708333333</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1465,7 +1441,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1478,7 +1454,7 @@
           <t>291002</t>
         </is>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y8" s="3">
         <v>46120</v>
       </c>
       <c r="Z8">
@@ -1587,15 +1563,11 @@
 - Trong hợp đồng  nlmt đã kí sau 10  ngày sẽ lắp mà giờ sau 20 ngày vẫn chưa lắp cho anh</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>16:29 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>16:29 09/04/2026</t>
-        </is>
+      <c r="S9" s="2">
+        <v>46120.39513888889</v>
+      </c>
+      <c r="T9" s="2">
+        <v>46121.39513888889</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1604,7 +1576,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1617,7 +1589,7 @@
           <t>073560</t>
         </is>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y9" s="3">
         <v>46120</v>
       </c>
       <c r="Z9">
@@ -1730,15 +1702,11 @@
           <t>hỗ trợ cài đặt biến tần</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>16:16 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>16:16 09/04/2026</t>
-        </is>
+      <c r="S10" s="2">
+        <v>46120.38611111111</v>
+      </c>
+      <c r="T10" s="2">
+        <v>46121.38611111111</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1747,7 +1715,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1760,7 +1728,7 @@
           <t>441240</t>
         </is>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y10" s="3">
         <v>46120</v>
       </c>
       <c r="Z10">
@@ -1875,15 +1843,11 @@
 3.YC KT qua kiểm tra và xử lý cho KH</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>15:56 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>15:56 09/04/2026</t>
-        </is>
+      <c r="S11" s="2">
+        <v>46120.37222222222</v>
+      </c>
+      <c r="T11" s="2">
+        <v>46121.37222222222</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1892,7 +1856,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1905,7 +1869,7 @@
           <t>022357</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y11" s="3">
         <v>46120</v>
       </c>
       <c r="Z11">
@@ -2020,15 +1984,11 @@
 2. KH yêu cầu: Qua kiểm tra thiết bị và khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>14:13 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>14:13 09/04/2026</t>
-        </is>
+      <c r="S12" s="2">
+        <v>46120.30069444445</v>
+      </c>
+      <c r="T12" s="2">
+        <v>46121.30069444445</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2050,7 +2010,7 @@
           <t>293291</t>
         </is>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y12" s="3">
         <v>46120</v>
       </c>
       <c r="Z12">
@@ -2165,15 +2125,11 @@
 3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>13:30 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>13:30 09/04/2026</t>
-        </is>
+      <c r="S13" s="2">
+        <v>46120.27083333333</v>
+      </c>
+      <c r="T13" s="2">
+        <v>46121.27083333333</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2195,7 +2151,7 @@
           <t>460593</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y13" s="3">
         <v>46120</v>
       </c>
       <c r="Z13">
@@ -2310,15 +2266,11 @@
 2. KH yêu cầu: KT đến ktra cài đặt lại hệ thống cho KH.</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>11:29 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>11:29 09/04/2026</t>
-        </is>
+      <c r="S14" s="2">
+        <v>46120.18680555555</v>
+      </c>
+      <c r="T14" s="2">
+        <v>46121.18680555555</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2340,7 +2292,7 @@
           <t>437012</t>
         </is>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y14" s="3">
         <v>46120</v>
       </c>
       <c r="Z14">
@@ -2451,15 +2403,11 @@
 2. KH yêu cầu: CN cử KT xuống kiểm tra thiết bị và khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>10:19 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>10:19 09/04/2026</t>
-        </is>
+      <c r="S15" s="2">
+        <v>46120.13819444444</v>
+      </c>
+      <c r="T15" s="2">
+        <v>46121.13819444444</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2481,7 +2429,7 @@
           <t>418109</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" s="3">
         <v>46120</v>
       </c>
       <c r="Z15">
@@ -2591,15 +2539,11 @@
 3. KH yêu cầu: Cho nv xuống kiểm tra chất lượng tấm pin xem có vấn đề gì không, đo kiểm lại tấm pin.</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>10:03 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>10:03 09/04/2026</t>
-        </is>
+      <c r="S16" s="2">
+        <v>46120.12708333333</v>
+      </c>
+      <c r="T16" s="2">
+        <v>46121.12708333333</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2621,7 +2565,7 @@
           <t>285776</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y16" s="3">
         <v>46120</v>
       </c>
       <c r="Z16">
@@ -2736,15 +2680,11 @@
 3. KH yêu cầu: KT xuống kiểm tra, hỗ trợ, đưa phương án khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>08:48 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>20:20 09/04/2026</t>
-        </is>
+      <c r="S17" s="2">
+        <v>46120.075</v>
+      </c>
+      <c r="T17" s="2">
+        <v>46121.55555555555</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2753,7 +2693,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2766,7 +2706,7 @@
           <t>069197</t>
         </is>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y17" s="3">
         <v>46120</v>
       </c>
       <c r="Z17">
@@ -2881,15 +2821,11 @@
 3.YC KT qua kiểm tra và xử lý gấp</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>09:00 10/04/2026</t>
-        </is>
+      <c r="S18" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T18" s="2">
+        <v>46122.08333333333</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2898,7 +2834,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2911,7 +2847,7 @@
           <t>010490</t>
         </is>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y18" s="3">
         <v>46121</v>
       </c>
       <c r="Z18">
@@ -3026,15 +2962,11 @@
 3.YC KT qua kiểm tra và khắc phục gấp</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>08:00 09/04/2026</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>09:00 10/04/2026</t>
-        </is>
+      <c r="S19" s="2">
+        <v>46121.04166666667</v>
+      </c>
+      <c r="T19" s="2">
+        <v>46122.08333333333</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -3043,7 +2975,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Chưa tính KPI</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3056,7 +2988,7 @@
           <t>432845</t>
         </is>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y19" s="3">
         <v>46121</v>
       </c>
       <c r="Z19">
@@ -3164,15 +3096,11 @@
           <t>KH có đơn bảo dưỡng từ 6.4, nhưng hiện tại đã quá lịch đặt chưa có KT liên hệ</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>16:49 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>09:00 09/04/2026</t>
-        </is>
+      <c r="S20" s="2">
+        <v>46120.40902777778</v>
+      </c>
+      <c r="T20" s="2">
+        <v>46121.08333333333</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3194,7 +3122,7 @@
           <t>421271</t>
         </is>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y20" s="3">
         <v>46120</v>
       </c>
       <c r="Z20">
@@ -3308,15 +3236,11 @@
 - Điện nlmt bị lỗi. Thời tiết nóng cứ lúc tắt lúc bật</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>16:22 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>16:22 09/04/2026</t>
-        </is>
+      <c r="S21" s="2">
+        <v>46120.39027777778</v>
+      </c>
+      <c r="T21" s="2">
+        <v>46121.39027777778</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3325,7 +3249,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3338,7 +3262,7 @@
           <t>285776</t>
         </is>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y21" s="3">
         <v>46120</v>
       </c>
       <c r="Z21">
@@ -3453,15 +3377,11 @@
 2. KH yêu cầu: cài đặt đồng hồ đảo nguồn lại và giải thích cho KH thật là chuẩn.</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>11:31 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>11:31 09/04/2026</t>
-        </is>
+      <c r="S22" s="2">
+        <v>46120.18819444445</v>
+      </c>
+      <c r="T22" s="2">
+        <v>46121.18819444445</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3483,7 +3403,7 @@
           <t>285897</t>
         </is>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y22" s="3">
         <v>46120</v>
       </c>
       <c r="Z22">
@@ -3598,15 +3518,11 @@
 3. KH yêu cầu: KT xuống kiểm tra và xử lý dứt điểm tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>09:19 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>09:19 09/04/2026</t>
-        </is>
+      <c r="S23" s="2">
+        <v>46120.09652777778</v>
+      </c>
+      <c r="T23" s="2">
+        <v>46121.09652777778</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3628,7 +3544,7 @@
           <t>285987</t>
         </is>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y23" s="3">
         <v>46120</v>
       </c>
       <c r="Z23">
@@ -3741,15 +3657,11 @@
           <t>vệ sinh tấm pin nlmt, trên app báo 360k mà nhân viên lại báo lại 1 triệu. Báo vệ sinh 2 tuần nay mà chưa thấy ai gọi  (NV Ngô Bắc Việt ). Hỏi xem a Việt có phải người công ty hay không. Nếu không phải người công ty phải báo lại cho anh</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>08:00 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>09:00 09/04/2026</t>
-        </is>
+      <c r="S24" s="2">
+        <v>46120.04166666667</v>
+      </c>
+      <c r="T24" s="2">
+        <v>46121.08333333333</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3771,7 +3683,7 @@
           <t>048379</t>
         </is>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y24" s="3">
         <v>46120</v>
       </c>
       <c r="Z24">
@@ -3886,15 +3798,11 @@
 3. Điện nllmt 2 3 hôm nay hiệu số rất thấp.Giờ cao điểm trước đây thu được 5 6 kí giờ chỉ còn 2 3 kí</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>08:00 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>22:10 10/04/2026</t>
-        </is>
+      <c r="S25" s="2">
+        <v>46120.04166666667</v>
+      </c>
+      <c r="T25" s="2">
+        <v>46122.63194444445</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3903,7 +3811,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3916,7 +3824,7 @@
           <t>293804</t>
         </is>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y25" s="3">
         <v>46120</v>
       </c>
       <c r="Z25">
@@ -4031,15 +3939,11 @@
 YC KT qua kiểm tra bảo hành thiết bị cho KH</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>16:31 07/04/2026</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>16:31 22/04/2026</t>
-        </is>
+      <c r="S26" s="2">
+        <v>46119.39652777778</v>
+      </c>
+      <c r="T26" s="2">
+        <v>46134.39652777778</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -4061,7 +3965,7 @@
           <t>488066</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y26" s="3">
         <v>46119</v>
       </c>
       <c r="Z26">
@@ -4174,15 +4078,11 @@
           <t>Hệ thống không hoạt động</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>08:00 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>09:00 09/04/2026</t>
-        </is>
+      <c r="S27" s="2">
+        <v>46120.04166666667</v>
+      </c>
+      <c r="T27" s="2">
+        <v>46121.08333333333</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -4191,7 +4091,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4204,7 +4104,7 @@
           <t>324208</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y27" s="3">
         <v>46120</v>
       </c>
       <c r="Z27">
@@ -4319,15 +4219,11 @@
 3. KH yêu cầu: Phản hồi và tình trạng linh kiện đang di chuyển đến đâu rồi và chậm nhất là đến m10 phải có linh kiện, vật tư ở đây nếu ko KH sẽ chấm dứt HĐ.</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>10:02 07/04/2026</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>15:00 09/04/2026</t>
-        </is>
+      <c r="S28" s="2">
+        <v>46119.12638888889</v>
+      </c>
+      <c r="T28" s="2">
+        <v>46121.33333333333</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4349,7 +4245,7 @@
           <t>442962</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y28" s="3">
         <v>46119</v>
       </c>
       <c r="Z28">
@@ -4464,15 +4360,11 @@
 3. KH yêu cầu: Báo KT hỗ trợ nhanh giúp anh, cho người qua kiểm tra cho anh apptomat.</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>08:50 07/04/2026</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>08:05 09/04/2026</t>
-        </is>
+      <c r="S29" s="2">
+        <v>46119.07638888889</v>
+      </c>
+      <c r="T29" s="2">
+        <v>46121.04513888889</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4481,7 +4373,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4494,7 +4386,7 @@
           <t>284060</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y29" s="3">
         <v>46119</v>
       </c>
       <c r="Z29">
@@ -4608,15 +4500,11 @@
 **Địa chỉ lắp đặt: số nhà 300, kim tân, xã đoài phương, thành phố hà nội.</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>16:23 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>17:30 08/04/2026</t>
-        </is>
+      <c r="S30" s="2">
+        <v>46118.39097222222</v>
+      </c>
+      <c r="T30" s="2">
+        <v>46120.4375</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4638,7 +4526,7 @@
           <t>046275</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y30" s="3">
         <v>46118</v>
       </c>
       <c r="Z30">
@@ -4748,15 +4636,11 @@
 3. KH yêu cầu: KT qua kiểm tra thiết bị, khắc phục tình trạng này.</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>13:30 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>14:55 16/04/2026</t>
-        </is>
+      <c r="S31" s="2">
+        <v>46118.27083333333</v>
+      </c>
+      <c r="T31" s="2">
+        <v>46128.32986111111</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4778,7 +4662,7 @@
           <t>455101</t>
         </is>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y31" s="3">
         <v>46118</v>
       </c>
       <c r="Z31">
@@ -4892,15 +4776,11 @@
 KH yêu cầu: cần kỹ thuật hỗ trợ kiểm tra giúp hệ thống.</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>11:39 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>07:40 10/04/2026</t>
-        </is>
+      <c r="S32" s="2">
+        <v>46118.19375</v>
+      </c>
+      <c r="T32" s="2">
+        <v>46122.02777777778</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -4922,7 +4802,7 @@
           <t>467401</t>
         </is>
       </c>
-      <c r="Y32" s="2">
+      <c r="Y32" s="3">
         <v>46118</v>
       </c>
       <c r="Z32">
@@ -5037,15 +4917,11 @@
 3,. Cúp CV không sài được</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>08:00 08/04/2026</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>09:00 09/04/2026</t>
-        </is>
+      <c r="S33" s="2">
+        <v>46120.04166666667</v>
+      </c>
+      <c r="T33" s="2">
+        <v>46121.08333333333</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -5067,7 +4943,7 @@
           <t>469593</t>
         </is>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y33" s="3">
         <v>46120</v>
       </c>
       <c r="Z33">
@@ -5180,15 +5056,11 @@
           <t>Hôm nay mất điện không tự chuyển  sang điện mặt trời, bị mất điện nhà luôn. Anh không vào app giám sát theo dõi sản lượng được. kiểm tra lại cho anh</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>16:33 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>23:30 09/04/2026</t>
-        </is>
+      <c r="S34" s="2">
+        <v>46118.39791666667</v>
+      </c>
+      <c r="T34" s="2">
+        <v>46121.6875</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -5210,7 +5082,7 @@
           <t>292404</t>
         </is>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y34" s="3">
         <v>46118</v>
       </c>
       <c r="Z34">
@@ -5321,15 +5193,11 @@
 ***SĐT phản ánh và liên hệ: 0964109909</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>08:00 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>17:30 11/04/2026</t>
-        </is>
+      <c r="S35" s="2">
+        <v>46118.04166666667</v>
+      </c>
+      <c r="T35" s="2">
+        <v>46123.4375</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -5351,7 +5219,7 @@
           <t>023020</t>
         </is>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y35" s="3">
         <v>46118</v>
       </c>
       <c r="Z35">
@@ -5466,15 +5334,11 @@
 3. KH yêu cầu: Qua kiểm tra và mở hết công suất, và xem có chạy song song vừa điện lưới vừa nlmt được không, KH muốn lắp thêm hệ, và xem cần vệ sinh tấm pin nlmt nữa.</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>08:00 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>18:00 11/04/2026</t>
-        </is>
+      <c r="S36" s="2">
+        <v>46118.04166666667</v>
+      </c>
+      <c r="T36" s="2">
+        <v>46123.45833333333</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5496,7 +5360,7 @@
           <t>460719</t>
         </is>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y36" s="3">
         <v>46118</v>
       </c>
       <c r="Z36">
@@ -5612,15 +5476,11 @@
 ***SĐT phản ánh: 0966337575 và zalo Đình Đại</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>08:00 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>07:00 19/05/2026</t>
-        </is>
+      <c r="S37" s="2">
+        <v>46118.04166666667</v>
+      </c>
+      <c r="T37" s="2">
+        <v>46161</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5642,7 +5502,7 @@
           <t>007700</t>
         </is>
       </c>
-      <c r="Y37" s="2">
+      <c r="Y37" s="3">
         <v>46118</v>
       </c>
       <c r="Z37">
@@ -5752,15 +5612,11 @@
 3. KH yêu cầu: kiểm tra ats, giờ ko chuyển đổi được, ko xài được điện lưới.</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>13:30 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>11:00 11/04/2026</t>
-        </is>
+      <c r="S38" s="2">
+        <v>46118.27083333333</v>
+      </c>
+      <c r="T38" s="2">
+        <v>46123.16666666667</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5782,7 +5638,7 @@
           <t>427357</t>
         </is>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y38" s="3">
         <v>46118</v>
       </c>
       <c r="Z38">
@@ -5897,15 +5753,11 @@
 3. KH yêu cầu: Có trách nhiệm cam kết đúng giữa KH và bên Kinh doanh, và thực hiện đưa ra phương án xử lý để có sản lượng theo đúng cam kết. KH yêu cầu xử lý gấp.</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>08:00 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>09:00 14/04/2026</t>
-        </is>
+      <c r="S39" s="2">
+        <v>46118.04166666667</v>
+      </c>
+      <c r="T39" s="2">
+        <v>46126.08333333333</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -5927,7 +5779,7 @@
           <t>056298</t>
         </is>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y39" s="3">
         <v>46118</v>
       </c>
       <c r="Z39">
@@ -6042,15 +5894,11 @@
 3. KH yêu cầu: Kiểm tra lại và khắc phục dứt điểm cho KH.</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>14:33 03/04/2026</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>18:00 12/04/2026</t>
-        </is>
+      <c r="S40" s="2">
+        <v>46115.31458333333</v>
+      </c>
+      <c r="T40" s="2">
+        <v>46124.45833333333</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6072,7 +5920,7 @@
           <t>460719</t>
         </is>
       </c>
-      <c r="Y40" s="2">
+      <c r="Y40" s="3">
         <v>46115</v>
       </c>
       <c r="Z40">
@@ -6186,15 +6034,11 @@
 2. Cứ mỗi lần cấp điện lưới, lại bị nhảy biến tần bộp bộp bộp</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>08:00 06/04/2026</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>20:45 10/04/2026</t>
-        </is>
+      <c r="S41" s="2">
+        <v>46118.04166666667</v>
+      </c>
+      <c r="T41" s="2">
+        <v>46122.57291666667</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6203,7 +6047,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6216,7 +6060,7 @@
           <t>293804</t>
         </is>
       </c>
-      <c r="Y41" s="2">
+      <c r="Y41" s="3">
         <v>46118</v>
       </c>
       <c r="Z41">
@@ -6326,15 +6170,11 @@
 3. KH yêu cầu: qua kiểm tra, khắc phục dứt điểm tình trạng này.</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>13:42 03/04/2026</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>20:50 13/04/2026</t>
-        </is>
+      <c r="S42" s="2">
+        <v>46115.27916666667</v>
+      </c>
+      <c r="T42" s="2">
+        <v>46125.57638888889</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6356,7 +6196,7 @@
           <t>293859</t>
         </is>
       </c>
-      <c r="Y42" s="2">
+      <c r="Y42" s="3">
         <v>46115</v>
       </c>
       <c r="Z42">
@@ -6466,15 +6306,11 @@
 YC KT qua kiểm tra và xử lý cho KH</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>08:00 03/04/2026</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>09:00 06/04/2026</t>
-        </is>
+      <c r="S43" s="2">
+        <v>46115.04166666667</v>
+      </c>
+      <c r="T43" s="2">
+        <v>46118.08333333333</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -6496,7 +6332,7 @@
           <t>289759</t>
         </is>
       </c>
-      <c r="Y43" s="2">
+      <c r="Y43" s="3">
         <v>46115</v>
       </c>
       <c r="Z43">
@@ -6612,15 +6448,11 @@
 KH yc KT qua kiểm tra và xử lý</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>15:42 02/04/2026</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>14:20 10/04/2026</t>
-        </is>
+      <c r="S44" s="2">
+        <v>46114.3625</v>
+      </c>
+      <c r="T44" s="2">
+        <v>46122.30555555555</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6642,7 +6474,7 @@
           <t>292658</t>
         </is>
       </c>
-      <c r="Y44" s="2">
+      <c r="Y44" s="3">
         <v>46114</v>
       </c>
       <c r="Z44">
@@ -6757,15 +6589,11 @@
 3. KH yêu cầu: Qua kiểm tra tình trạng nguyên nhân để tăng hiệu suất đúng với hệ của KH.</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>13:30 02/04/2026</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>16:00 10/04/2026</t>
-        </is>
+      <c r="S45" s="2">
+        <v>46114.27083333333</v>
+      </c>
+      <c r="T45" s="2">
+        <v>46122.375</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -6787,7 +6615,7 @@
           <t>083737</t>
         </is>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y45" s="3">
         <v>46114</v>
       </c>
       <c r="Z45">
@@ -6900,15 +6728,11 @@
           <t>hệ thống nlmt bị lỗi, viên pin bị lủng. Kĩ thuật báo theo dõi. Điện bị sụt</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>15:36 01/04/2026</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>17:30 11/04/2026</t>
-        </is>
+      <c r="S46" s="2">
+        <v>46113.35833333334</v>
+      </c>
+      <c r="T46" s="2">
+        <v>46123.4375</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -6917,7 +6741,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6930,7 +6754,7 @@
           <t>468169</t>
         </is>
       </c>
-      <c r="Y46" s="2">
+      <c r="Y46" s="3">
         <v>46113</v>
       </c>
       <c r="Z46">
@@ -7047,15 +6871,11 @@
 - SĐT liên hệ và phản ánh: 0962608008 chồng của KH</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>08:20 01/04/2026</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>08:00 30/04/2026</t>
-        </is>
+      <c r="S47" s="2">
+        <v>46113.05555555555</v>
+      </c>
+      <c r="T47" s="2">
+        <v>46142.04166666667</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7077,7 +6897,7 @@
           <t>075543</t>
         </is>
       </c>
-      <c r="Y47" s="2">
+      <c r="Y47" s="3">
         <v>46113</v>
       </c>
       <c r="Z47">
@@ -7192,15 +7012,11 @@
 3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>15:55 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>17:15 11/04/2026</t>
-        </is>
+      <c r="S48" s="2">
+        <v>46111.37152777778</v>
+      </c>
+      <c r="T48" s="2">
+        <v>46123.42708333333</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7209,7 +7025,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -7222,7 +7038,7 @@
           <t>408869</t>
         </is>
       </c>
-      <c r="Y48" s="2">
+      <c r="Y48" s="3">
         <v>46111</v>
       </c>
       <c r="Z48">
@@ -7336,15 +7152,11 @@
 KH đã được hỗ trợ.</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>09:49 31/03/2026</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>17:00 15/04/2026</t>
-        </is>
+      <c r="S49" s="2">
+        <v>46112.11736111112</v>
+      </c>
+      <c r="T49" s="2">
+        <v>46127.41666666667</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7366,7 +7178,7 @@
           <t>324208</t>
         </is>
       </c>
-      <c r="Y49" s="2">
+      <c r="Y49" s="3">
         <v>46112</v>
       </c>
       <c r="Z49">
@@ -7475,15 +7287,11 @@
 2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>11:30 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>19:10 10/04/2026</t>
-        </is>
+      <c r="S50" s="2">
+        <v>46111.1875</v>
+      </c>
+      <c r="T50" s="2">
+        <v>46122.50694444445</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7505,7 +7313,7 @@
           <t>285776</t>
         </is>
       </c>
-      <c r="Y50" s="2">
+      <c r="Y50" s="3">
         <v>46111</v>
       </c>
       <c r="Z50">
@@ -7620,15 +7428,11 @@
 3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>08:00 30/03/2026</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>20:10 15/04/2026</t>
-        </is>
+      <c r="S51" s="2">
+        <v>46111.04166666667</v>
+      </c>
+      <c r="T51" s="2">
+        <v>46127.54861111111</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -7650,7 +7454,7 @@
           <t>285776</t>
         </is>
       </c>
-      <c r="Y51" s="2">
+      <c r="Y51" s="3">
         <v>46111</v>
       </c>
       <c r="Z51">
@@ -7763,15 +7567,11 @@
           <t>Lỗi pin ko lưu</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>10:43 01/04/2026</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>10:52 18/04/2026</t>
-        </is>
+      <c r="S52" s="2">
+        <v>46113.15486111111</v>
+      </c>
+      <c r="T52" s="2">
+        <v>46130.16111111111</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7793,7 +7593,7 @@
           <t>161073</t>
         </is>
       </c>
-      <c r="Y52" s="2">
+      <c r="Y52" s="3">
         <v>46113</v>
       </c>
       <c r="Z52">
@@ -7908,15 +7708,11 @@
 Số liên hệ:</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>08:00 26/03/2026</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>09:46 19/04/2026</t>
-        </is>
+      <c r="S53" s="2">
+        <v>46107.04166666667</v>
+      </c>
+      <c r="T53" s="2">
+        <v>46131.11527777778</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -7938,7 +7734,7 @@
           <t>291011</t>
         </is>
       </c>
-      <c r="Y53" s="2">
+      <c r="Y53" s="3">
         <v>46107</v>
       </c>
       <c r="Z53">
@@ -8053,15 +7849,11 @@
 3. KH yêu cầu: Kiểm tra biến tần cho KH, đã yêu cầu hãng xử lý rất nhiều lần rồi, nhưng giờ vẫn có tình trạng gặp lỗi. Ngoài ra KH yêu cầu là xử lý triệt để cho KH vì sắp tới mùa hè nó lên 3,4kw bị nhảy mà giờ còn kh thấy có tbao trên app.</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>09:20 25/03/2026</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>18:30 30/03/2026</t>
-        </is>
+      <c r="S54" s="2">
+        <v>46106.09722222222</v>
+      </c>
+      <c r="T54" s="2">
+        <v>46111.47916666667</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8083,7 +7875,7 @@
           <t>461581</t>
         </is>
       </c>
-      <c r="Y54" s="2">
+      <c r="Y54" s="3">
         <v>46106</v>
       </c>
       <c r="Z54">
@@ -8199,15 +7991,11 @@
 NOTE: địa chỉ hiện tại của KH: thôn phú mỹ, xã tiến thắng, Hà Nội</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>15:34 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>14:16 16/04/2026</t>
-        </is>
+      <c r="S55" s="2">
+        <v>46105.35694444444</v>
+      </c>
+      <c r="T55" s="2">
+        <v>46128.30277777778</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8229,7 +8017,7 @@
           <t>023020</t>
         </is>
       </c>
-      <c r="Y55" s="2">
+      <c r="Y55" s="3">
         <v>46105</v>
       </c>
       <c r="Z55">
@@ -8344,15 +8132,11 @@
 KH yêu cầu chuyển KT xuống xử lý gấp</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>15:09 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>21:10 23/04/2026</t>
-        </is>
+      <c r="S56" s="2">
+        <v>46105.33958333333</v>
+      </c>
+      <c r="T56" s="2">
+        <v>46135.59027777778</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -8374,7 +8158,7 @@
           <t>414445</t>
         </is>
       </c>
-      <c r="Y56" s="2">
+      <c r="Y56" s="3">
         <v>46105</v>
       </c>
       <c r="Z56">
@@ -8485,15 +8269,11 @@
 ***SĐT liên hệ: 0988867428, Anh Thức</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>08:45 24/03/2026</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>09:00 16/04/2026</t>
-        </is>
+      <c r="S57" s="2">
+        <v>46105.07291666667</v>
+      </c>
+      <c r="T57" s="2">
+        <v>46128.08333333333</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -8515,7 +8295,7 @@
           <t>293804</t>
         </is>
       </c>
-      <c r="Y57" s="2">
+      <c r="Y57" s="3">
         <v>46105</v>
       </c>
       <c r="Z57">
@@ -8630,15 +8410,11 @@
 3. KH yêu cầu: Qua hỗ trợ, kiểm tra thiết bị cho KH, KH sẵn sàng trả phí.</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>08:00 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>07:50 08/04/2026</t>
-        </is>
+      <c r="S58" s="2">
+        <v>46104.04166666667</v>
+      </c>
+      <c r="T58" s="2">
+        <v>46120.03472222222</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -8660,7 +8436,7 @@
           <t>288992</t>
         </is>
       </c>
-      <c r="Y58" s="2">
+      <c r="Y58" s="3">
         <v>46104</v>
       </c>
       <c r="Z58">
@@ -8776,15 +8552,11 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>08:00 23/03/2026</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>18:00 26/03/2026</t>
-        </is>
+      <c r="S59" s="2">
+        <v>46104.04166666667</v>
+      </c>
+      <c r="T59" s="2">
+        <v>46107.45833333333</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -8806,7 +8578,7 @@
           <t>121999</t>
         </is>
       </c>
-      <c r="Y59" s="2">
+      <c r="Y59" s="3">
         <v>46104</v>
       </c>
       <c r="Z59">
@@ -8921,15 +8693,11 @@
 3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>09:25 19/03/2026</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>09:00 28/04/2026</t>
-        </is>
+      <c r="S60" s="2">
+        <v>46100.10069444445</v>
+      </c>
+      <c r="T60" s="2">
+        <v>46140.08333333333</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -8951,7 +8719,7 @@
           <t>291002</t>
         </is>
       </c>
-      <c r="Y60" s="2">
+      <c r="Y60" s="3">
         <v>46100</v>
       </c>
       <c r="Z60">
@@ -9064,15 +8832,11 @@
           <t>KH yc ktra nguyên nhân xảy ra sự cố Hệ NLMT bị sự cố lỗi. Nhiều lúc lấy điện lưới dùng không dùng điện NLMT.</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>08:00 16/03/2026</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>09:00 13/04/2026</t>
-        </is>
+      <c r="S61" s="2">
+        <v>46097.04166666667</v>
+      </c>
+      <c r="T61" s="2">
+        <v>46125.08333333333</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -9081,7 +8845,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -9094,7 +8858,7 @@
           <t>291002</t>
         </is>
       </c>
-      <c r="Y61" s="2">
+      <c r="Y61" s="3">
         <v>46097</v>
       </c>
       <c r="Z61">
@@ -9204,15 +8968,11 @@
 3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>08:00 09/03/2026</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>11:45 10/04/2026</t>
-        </is>
+      <c r="S62" s="2">
+        <v>46090.04166666667</v>
+      </c>
+      <c r="T62" s="2">
+        <v>46122.19791666667</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -9221,7 +8981,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -9234,7 +8994,7 @@
           <t>462341</t>
         </is>
       </c>
-      <c r="Y62" s="2">
+      <c r="Y62" s="3">
         <v>46090</v>
       </c>
       <c r="Z62">
@@ -9350,15 +9110,11 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>15:09 03/03/2026</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>12:55 15/03/2026</t>
-        </is>
+      <c r="S63" s="2">
+        <v>46084.33958333333</v>
+      </c>
+      <c r="T63" s="2">
+        <v>46096.24652777778</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -9380,7 +9136,7 @@
           <t>291002</t>
         </is>
       </c>
-      <c r="Y63" s="2">
+      <c r="Y63" s="3">
         <v>46084</v>
       </c>
       <c r="Z63">
@@ -9495,15 +9251,11 @@
 3. kh yc: YC cn hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>13:30 23/02/2026</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>17:45 29/03/2026</t>
-        </is>
+      <c r="S64" s="2">
+        <v>46076.27083333333</v>
+      </c>
+      <c r="T64" s="2">
+        <v>46110.44791666667</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -9512,7 +9264,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -9525,7 +9277,7 @@
           <t>412105</t>
         </is>
       </c>
-      <c r="Y64" s="2">
+      <c r="Y64" s="3">
         <v>46076</v>
       </c>
       <c r="Z64">
@@ -9639,15 +9391,11 @@
 - KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>08:00 19/01/2026</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>22:00 17/04/2026</t>
-        </is>
+      <c r="S65" s="2">
+        <v>46041.04166666667</v>
+      </c>
+      <c r="T65" s="2">
+        <v>46129.625</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -9669,7 +9417,7 @@
           <t>069170</t>
         </is>
       </c>
-      <c r="Y65" s="2">
+      <c r="Y65" s="3">
         <v>46041</v>
       </c>
       <c r="Z65">
@@ -9779,15 +9527,11 @@
 3. Kh yêu cầu: KT qua kiểm tra cho Kh</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>08:00 14/01/2026</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>17:00 25/02/2026</t>
-        </is>
+      <c r="S66" s="2">
+        <v>46036.04166666667</v>
+      </c>
+      <c r="T66" s="2">
+        <v>46078.41666666667</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -9796,7 +9540,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9809,7 +9553,7 @@
           <t>289759</t>
         </is>
       </c>
-      <c r="Y66" s="2">
+      <c r="Y66" s="3">
         <v>46036</v>
       </c>
       <c r="Z66">
@@ -9923,15 +9667,11 @@
 Quà tặng trúng thưởng nên không có thông tin mã HĐ.</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>08:00 05/01/2026</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>09:35 10/04/2026</t>
-        </is>
+      <c r="S67" s="2">
+        <v>46027.04166666667</v>
+      </c>
+      <c r="T67" s="2">
+        <v>46122.10763888889</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -9940,7 +9680,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9953,7 +9693,7 @@
           <t>205029</t>
         </is>
       </c>
-      <c r="Y67" s="2">
+      <c r="Y67" s="3">
         <v>46027</v>
       </c>
       <c r="Z67">
@@ -10064,15 +9804,11 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>08:00 10/12/2025</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>15:00 16/12/2025</t>
-        </is>
+      <c r="S68" s="2">
+        <v>46001.04166666667</v>
+      </c>
+      <c r="T68" s="2">
+        <v>46007.33333333333</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10081,7 +9817,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -10094,7 +9830,7 @@
           <t>062146</t>
         </is>
       </c>
-      <c r="Y68" s="2">
+      <c r="Y68" s="3">
         <v>46001</v>
       </c>
       <c r="Z68">

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -511,3099 +511,3256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150501/GPTH/HĐMBLĐ-2025/CNCTTNH-STRIDESOLAR</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hồ Văn Lùng</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0397727564</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Tổ 8, Ấp Phước An, Xã Cầu Khởi, Tây Ninh</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1. Khách hàng cần hỗ trợ cài lại app monitor do đã đổi điện thoại mới
+2. Địa chỉ :-địa chỉ mới : Tổ 8, Ấp Phước An, Xã Cầu Khởi, Tây Ninh
+              -địa chỉ cũ :Tổ 8, Ấp Phước An, xã Phước Ninh, Huyện Dương Minh Châu, Tỉnh Tây Ninh
+3. KH cần hỗ trợ sớm để có thể sử dụng</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-04-24 14:07:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Nguyễn Tấn Tài</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>461237</t>
+        </is>
+      </c>
+      <c r="Y2" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1680693</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Trần Văn Thông</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0985675516</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Thôn 3</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ chuyên môn kém</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn: A Tú
+2. KH phản ánh: Trong quá trình lắp đặt bỏ sót rất nhiều vít trên tôn, KH mới sử dụng được 10 ngày và giờ dẫn đến tình trạng mưa nước dột xuống rất nhiều đến bàn bi a nhà KH. Trước đó KH cũng đã dặn đội thi công là làm phải để ý để bàn bi a ko bị dột nước.
+3. KH yêu cầu: Giải quyết tình hình này cho KH, và cho 1 lời giải thích đền bù thiệt hại và đưa hướng xử lý như thế nào.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-04-24 13:30:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Võ Trọng Đức</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>293804</t>
+        </is>
+      </c>
+      <c r="Y3" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_TNH_1678186</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Trần Thanh Toàn</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0334848340</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>496 tỉnh lộ 786</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1. KH đã báo Cn
+2.Pin lưu trữu không hiện trên app AIO
+3. yêu cầu CN liên hệ KH gấp</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-04-24 13:30:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trần Văn Quy</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>470911</t>
+        </is>
+      </c>
+      <c r="Y4" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Gói hỗ trợ kỹ thuật - Dịch vụ kiểm tra</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VCC_HS_HNI_1775703815264</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Đào Ngọc Tùng</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0833401194</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>520 ct4 sông đà mỹ đình</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>kt ko  liên hệ với kh</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-04-24 11:25:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-04-24 15:25:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lê Duy Tuấn</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>293859</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HYN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HYN_1648206</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Mai Thắng</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0975355366</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>tân dân, Xã Triệu Việt Vương, Tỉnh Hưng Yên, Xã Triệu Việt Vương, Tỉnh Hưng Yên</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>KH yêu cầu phản hồi về thông tin thiết bị mang đi bảo hành và trả lại thiết bị cho KH.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-04-24 09:42:00</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trần Văn Hùng</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>439110</t>
+        </is>
+      </c>
+      <c r="Y6" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_TNH_1524594</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Trần Công Hiển</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0395096687</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Trên app theo dõi hiệu suất nlmt KH đang thấy ko hiển thị thông số.
+3. KH yêu cầu: Qua kiểm tra hỗ trợ khắc phục tình trạng này</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-04-24 09:39:00</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nguyễn Quốc Hưng</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>467401</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HDG_1472655</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nguyễn Hữu Chỉnh</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0976024133</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Tòng Hóa</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>kh chưa báo chi nhánh
+Hệ thống nlmt chưa đạt đủ công suất pin lưu trữ chưa đạt sẳn lượng
+yêu cầu kt qua ktra</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-04-24 09:02:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Hoàn</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>070278</t>
+        </is>
+      </c>
+      <c r="Y8" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>THA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_THA_1558421</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Lê Anh Tuấn</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0948075858</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Phường Hạc Thành</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: mặt cảm ứng ivt đang bị lỗi ko vào cài đặt được, trên app theo dõi cũng ko thấy có công suất lưới và chỉ hiện mỗi thông số nguồn ắc quy.
 3. KH yêu cầu: Qua kiểm tra khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-04-24 08:00:00</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-04-28 09:00:00</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Mai Ngọc Tuấn</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>004914</t>
         </is>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y9" s="2">
         <v>46136</v>
       </c>
-      <c r="Z2">
+      <c r="Z9">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_VLG_1629375</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNG_1619560</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Huỳnh Long Định</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0978600429</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Xã Đại Điền</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Lê Thị Mai Anh</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0935045067</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Lô V5.B06.01 Khu Đô Thị FPT</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>CN 0348680595 báo sự cố hộ KH 
-1.	KH phản ánh: Mất kết nối lưới, trên hệ thống app KH xuất hiện mất thông hệ thống, tự mất kết nối rồi kết nối lại.
-2. KH yêu cầu: KH đã gặp tình trạng này nhiều lần, KH cần xử lý dứt điểm tình trạng này. CN báo sự cố có phản hồi là tình trạng này có thể là do thiết bị.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-04-23 17:22:00</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-04-24 17:22:00</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Đỗ Ngọc Nhân</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>073552</t>
-        </is>
-      </c>
-      <c r="Y3" s="2">
-        <v>46135</v>
-      </c>
-      <c r="Z3">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DNG_1619560</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lê Thị Mai Anh</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0935045067</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Lô V5.B06.01 Khu Đô Thị FPT</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>CN 0971759579 báo sự cố hộ KH
 1.	Kh phản ánh: KH đang nghi dây dc bị hỏng làm ảnh hưởng tới hiệu suất và cũng thấy hiệu suất giảm.
 2.	KH yêu cầu: kiểm tra gấp và khắc phục tình trạng này cho KH</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-04-23 15:09:00</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2026-04-24 15:09:00</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Nguyễn Công Triệu</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>433380</t>
         </is>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y10" s="2">
         <v>46135</v>
       </c>
-      <c r="Z4">
+      <c r="Z10">
         <v>1</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_CTO_1528697</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH DỊCH VỤ BẢO VỆ NGÀY &amp; ĐÊM TẠI THÀNH PHỐ CẦN THƠ</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0907334995</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>556a Cmt8, , , Cần Thơ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Inverter không hoạt động</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>CN 0974556234 báo sự cố hộ KH 0907334995
+1. KH phản ánh: : Ivt hỏng mấy tuần nay
+2. KH yêu cầu: Qua kiểm tra hỗ trợ, khắc phục tình trạng này</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-04-24 13:30:00</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Trương Mạnh Đức</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>064221</t>
+        </is>
+      </c>
+      <c r="Y11" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LCI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VCC_HS_LCI_1776647998406</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1645604</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nguyễn Quang Đại</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0822433477</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Phường Yên bái tỉnh Lào Cai, Phường Yên Bái, Tỉnh Lào Cai</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Dương</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0909289598</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Xuân Phương</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Kh hẹn lich bảo dưỡng điều hòa ngày 20/4 nhưng chưa có KT  liên hệ
-Yêu cầu KT liên hệ KH gấp</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-04-23 10:28:00</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-04-24 10:28:00</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Hỗ trợ lắp đặt</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn (KH ko nhớ tên)
+2. KH phản ánh:  đo đạc sai, ko chi tiết và phát sinh thêm vấn đề khiến cho hệ nlmt bị thò sang nhà hàng xóm và nước mưa rơi xuống nhà họ. KH đã báo CN và đưa ra 2 phương án: 1 là lắp nghiêng về nhà KH, 2 là lắp thêm cái máng. KH đã trao đổi với CN được 3 tháng rồi và phương án 1 thì CN bảo khó thực hiện, và thống nhất phương án t2 nhưng giờ vẫn chưa nhận được phản hồi.
+3. KH yêu cầu: Phản hồi lại thông tin này cho KH vào ngày hôm nay vì vấn đề này liên quan đến bảo hành các thứ sau này. Nếu ko thì KH trả lại hàng và lắp bên khác.</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-04-24 08:47:00</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:00:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lê Vi Tuấn Hiển</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>082934</t>
-        </is>
-      </c>
-      <c r="Y5" s="2">
-        <v>46135</v>
-      </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lê Duy Tuấn</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>293859</t>
+        </is>
+      </c>
+      <c r="Y12" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1685258</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Trần Hoài Phương</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0335573838</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Số 511, đường tỉnh lộ 7, ấp Bình Thượng 2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1. KH đã báo cn
 2. KH phản ánh: KH chưa tìm hiểu kỹ khi lắp đặt nlmt và phía bên tư vấn cũng chưa đến khảo sát, trao đổi trực tiếp với KH. Giờ KH xem lại tình hình là cảm thấy không phù hợp do KH còn có con nhỏ dưới 1t. KH cũng đã cọc 8tr với phía bên CN.
 3. KH yêu cầu: KH chấm dứt HĐ và mong muốn hoàn lại số tiền cọc.</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2026-04-24 08:00:00</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>2026-04-28 09:00:00</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Lê Khả Trung</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>017064</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y13" s="2">
         <v>46136</v>
       </c>
-      <c r="Z6">
+      <c r="Z13">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Tuyendv</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Tháo máy (dàn nóng &amp; dàn lạnh) Điều hòa treo tường</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VCC_HS_HCM_1776685746379</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1579472</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Toàn Lương</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0904234657</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>chung cư gatewayB</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Đặng Văn Thép</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0971528889</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Ngõ 9 Khúc Thủy</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Liên hệ chậm</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>KH đặt đơn làm vào sáng t7 25/4 mà chưa thấy có KT liên hệ lại xác nhận đơn. KH yêu cầu liên hệ lại với KH xác nhận có làm được không.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2026-04-24 08:00:00</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-04-24 14:00:00</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Lê Đức Cảnh</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>291002</t>
-        </is>
-      </c>
-      <c r="Y7" s="2">
-        <v>46136</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1685155</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Hường</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0977341203</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Xóm 17 18 Nghi Văn</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn: A Trường
-2. KH phản ánh: Hiện tại CN đang vi phạm HĐ về tiến độ triển khai lắp đặt và chuyển vật tư, đến giờ KH cũng vẫn chưa có vật tư để triển khai, CN có phải hồi là do hết hàng.
-3. KH yêu cầu: Phản hồi lại thông tin cho KH có vật tư và triển khai được không, nếu không thì hủy HĐ KH còn đặt chỗ khác.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2026-04-23 17:16:00</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-04-24 17:16:00</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Nguyễn Đình Trường</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>181241</t>
-        </is>
-      </c>
-      <c r="Y8" s="2">
-        <v>46135</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNI_1579472</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Đặng Văn Thép</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0971528889</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Ngõ 9 Khúc Thủy</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Ko kết nối được vào app để theo dõi hiệu suất nlmt.
 3. KH yêu cầu: Qua kiểm tra hỗ trợ cho KH kết nối lại app theo dõi hiệu suất</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-04-23 16:51:00</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2026-04-24 16:51:00</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Hoàng Văn Vương</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>285732</t>
         </is>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y14" s="2">
         <v>46135</v>
       </c>
-      <c r="Z9">
+      <c r="Z14">
         <v>1</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_TNN_0376884</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Lê Văn Bình</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0944666888</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Phường Sông Công</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>1. KH Chưa báo cn
 2.	KH phản ánh: Khi mất điện mọi khi nhà KH ko có pin lưu trữ chỉ có máy nổ và khi mất điện có máy nổ có cục tam giác cảnh báo đỏ và KH có bảo thợ ngoài đến ktra và đo đang ko có điện.
 3.	KH yêu cầu: Qua kiểm tra khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>2026-04-23 15:53:00</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>2026-04-24 15:53:00</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Đào Văn Thủy</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>023897</t>
-        </is>
-      </c>
-      <c r="Y10" s="2">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Nam</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>040191</t>
+        </is>
+      </c>
+      <c r="Y15" s="2">
         <v>46135</v>
       </c>
-      <c r="Z10">
+      <c r="Z15">
         <v>1</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>KHCN_TT_GPTH_CTO_1682180</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Lê Văn Mong</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0388145232</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>111/15 Ấp Vĩnh Lân</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Lắp đặt không đảm bảo</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1. KH đã p/á với a Hào ( nhân viên tư vấn) và được phản hồi do không đủ bình chứa điện và tư vấn lắp đặt thêm bình 
 2. HT NLMT hoàn thiện lắp đặt ngày 11/4,  Trong thời gian sử dụng HT không phát sinh đủ điện cho KH để sử dụng cho 1 ngày, sử dụng đến 9-10h đêm là hết, ,  KH  là người cao tuổi và không có hiểu biết về kỹ thuật,lựa chọn Viettel để ký HĐ do tin tưởng vào chất lượng và thương hiệu, phản ánh CN cần phải tính toán và lắp đặt HT NLMT có thể hỗ trợ đủ hiệu suất theo nhu cầu của KH, hiện tại HT đang chưa đáp ứng nhu cầu sử dụng của KH do đó KH chưa thể thanh toán
 3. KH thông tin muốn trao đổi trực tiếp với giám đốc chi nhánh để làm rõ các thông tin trong hợp đồng và thanh toán cho chi nhánh</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>2026-04-23 08:00:00</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-04-24 09:00:00</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-04-24 17:20:00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Phan Thanh Hào</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>482038</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y16" s="2">
         <v>46135</v>
       </c>
-      <c r="Z11">
+      <c r="Z16">
         <v>1</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>HUE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HUE_1684687</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Nguyễn Đình Kha</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>0969333355</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>82A, Đường Quảng Tế</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Tiến độ triển khai</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1.KH đã liên hệ với CN và đc phản hồi chưa có hàng
 2. KH đã ký thêm phụ lục để lắp đặt thêm Pin 16KWP từ ngày 08 và đã chuyển tiền một phần giá trị hợp đồng, tuy nhiên CN chưa hỗ trợ lắp đặt cho KH do thiếu vật tư thiết bị, App AIO của KH đã có thông tin HĐ và Phụ lục
 3. KH cần CN hỗ trợ lắp đặt sớm cho KH do thời gian đã lâu, liên hệ CN chưa có ngày lắp đặt cụ thể</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>2026-04-23 08:00:00</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-04-24 09:00:00</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-04-24 23:30:00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Đặng Hải Quan</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>192135</t>
         </is>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y17" s="2">
         <v>46135</v>
       </c>
-      <c r="Z12">
+      <c r="Z17">
         <v>1</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_AGG_1675992</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Trần Văn Hết</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0949070177</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Tổ 13, ấp 9 Chợ</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>-Kh báo chi nhánh: Anh hoàng 
 -KH phản ánh:  Hệ thống nlmt bị cúp điện lúc 3h chiều
 - KH yêu cầu: Xử lý nhanh giúp anh</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-04-23 08:00:00</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-04-24 09:00:00</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-04-26 12:05:00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>Lưu Hoàng Linh</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>432364</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y18" s="2">
         <v>46135</v>
       </c>
-      <c r="Z13">
+      <c r="Z18">
         <v>1</v>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNI_1662751</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Trần Hồng Phúc</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0918977063</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>A1/13C, Khu phố 1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>KH cần mẫu bổ sung số 01 để báo với điện lực gia đình đang sử dụng NLMT theo nghị định 13 
 Yêu cầu KT liên hệ lại KH gấp</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2026-04-23 09:57:00</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>2026-04-24 09:57:00</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Cao Thanh Quang</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>429027</t>
-        </is>
-      </c>
-      <c r="Y14" s="2">
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lê Anh Tuấn</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>285580</t>
+        </is>
+      </c>
+      <c r="Y19" s="2">
         <v>46135</v>
       </c>
-      <c r="Z14">
+      <c r="Z19">
         <v>1</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>HUE</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HUE_1685986</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Nguyễn Thanh Thủy</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>0352366757</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Bình Tiến</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Tiến độ triển khai</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>"1. KH đã nhắn tin cho nhân viên tư vấn tại chi nhánh, CN chưa hẹn lịch đến thực hiện cho KH
 2. Hệ thống NLMT của KH còn thiếu Catset DC và công đoạn đo điện trở nối đất về đúng giá trị trong hợp đồng chưa có
 3. KH cần hoàn thiện đủ các nội dung nêu trên để có thể quyết toán HĐ, cần KT tại CN hỗ trợ gấp"</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>2026-04-23 08:00:00</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-04-24 09:00:00</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-04-29 08:55:00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Nguyễn Văn Luân</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>433633</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y20" s="2">
         <v>46135</v>
       </c>
-      <c r="Z15">
+      <c r="Z20">
         <v>1</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HTH</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_CTO_1682133</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HTH_1656621</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Nhớ</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0839191319</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>KV Tân Quới</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Nguyễn Xuân Tuấn</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0984618861</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>TDP 7</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>"1. KH đã liên hệ tới CN và nhận phản hồi chưa có thiết bị
-2. KH đã ký HĐ lắp đặt Pin lưu trữ, CN đã thông tin cho KH ngày lắp đặt tuy nhiên chưa đến lắp đặt hệ thống 
-3.KH cần CN thông tin ngày cụ thể nào sẽ lắp đặt cho KH, thời gian lâu KH KHL</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>2026-04-23 08:00:00</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-04-24 09:00:00</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Phan Minh Luân</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>410840</t>
-        </is>
-      </c>
-      <c r="Y16" s="2">
-        <v>46135</v>
-      </c>
-      <c r="Z16">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Tuyendv</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KHDN_PINNLMT_NTN_0405670</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XĂNG DẦU XUÂN HẢI</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0902677233</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Xã Xuân Hải</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: cháy cục nối từ pin này sang pin khác, hiệu suất giảm so với trước kia.
-3. KH yêu cầu: Qua kiểm tra khắc phục tình trạng này.</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>2026-04-22 13:30:00</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-04-25 10:30:00</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Vương</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>069846</t>
-        </is>
-      </c>
-      <c r="Y17" s="2">
-        <v>46134</v>
-      </c>
-      <c r="Z17">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HTH</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HTH_1656621</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Nguyễn Xuân Tuấn</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0984618861</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>TDP 7</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh : Hệ 100kw và giờ chạy được chỉ hơn nửa công suất, chỉ có được 53kw đổ về. Trong khi nắng gắt ở Hà Tĩnh, trước lúc mới lắp đặt cũng phải 80 90kW. Sự cố từ trước kiểm tra thiết bị vẫn bình thường mà giờ sản lượng thấy ko đạt.
 3. KH yêu cầu: Qua kiểm tra, khống chế sản lượng, cho dải chạy ổn định cho KH.</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2026-04-22 13:30:00</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>2026-04-27 08:50:00</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Trịnh Xuân Bảo</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>471569</t>
         </is>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y21" s="2">
         <v>46134</v>
       </c>
-      <c r="Z18">
+      <c r="Z21">
         <v>2</v>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VCC_HS_HNI_1776068907530</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1685809</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Anhh Hòa</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0399785669</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>số 2 ngo 45 kim mã thượng, Phường Ba Đình, Thành phố Hà Nội</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Phạm Mạnh Tình</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0981707789</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Xóm Tân Nghĩa Nghi Xuân</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>KH BD 2 điều hòa vào 19/4 tới hôm nay có 1 chiếc bị chảy nước, nhỏ giọt. KH yêu cầu KT đến kiểm tra thiết bị và khắc phục tình trạng này.</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2026-04-22 08:15:00</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-04-24 18:00:00</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Lê Duy Tuấn</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>293859</t>
-        </is>
-      </c>
-      <c r="Y19" s="2">
-        <v>46134</v>
-      </c>
-      <c r="Z19">
-        <v>2</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1685809</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Phạm Mạnh Tình</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0981707789</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Xóm Tân Nghĩa Nghi Xuân</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Tiến độ triển khai</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ với NV tại CN tuy nhiên NV KNM
 2. KH thông tin CN đã hẹn đến thi công lắp đặt HT NLMT cho KH từ ngày 21, sau đó hẹn ngày 22 nhưng không có thông tin, KH đã liên hệ CN nhiều lần nhưng KTC, KH đã ký HĐ và đặt cọc để lắp đặt hệ thống NLMT, KH KHL và p/á nếu không lắp đặt được, KH có thể hủy HĐ và yêu cầu hoàn tiền
 3. KH cần CN phản hồi sớm và hỗ trợ lắp đặt cho KH</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-04-22 08:00:00</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-04-23 09:00:00</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-04-27 08:50:00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>Trần Thanh Tùng</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>416998</t>
         </is>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y22" s="2">
         <v>46134</v>
       </c>
-      <c r="Z20">
+      <c r="Z22">
         <v>2</v>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>Sonln15</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HYN_1619971</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Nguyễn Thị Ánh Nguyệt</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>0365854568</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>3 ngõ 56 đào nguyên phổ, Thị trấn Quỳnh Côi, Huyện Quỳnh Phụ, Tỉnh Thái Bình</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Từ ngày 17/04 App theo dõi NLMT của KH không có dữ liệu hệ thống NLMT, cài lại App vẫn không có dữ liệu HT, hệ thống không mất điện hay sụt điện tuy nhiên không đồng bộ với App
 3.KH cần KT hỗ trợ kiểm tra và khắc phục sớm cho KH</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>2026-04-22 08:00:00</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>2026-04-23 09:00:00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Nguyễn Thế Hiệu</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>059327</t>
         </is>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y23" s="2">
         <v>46134</v>
       </c>
-      <c r="Z21">
+      <c r="Z23">
         <v>2</v>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HYN</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HTH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HYN_1566553</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HTH_1613358</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ HẠ TẦNG LOGISTICS</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0981439612</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Số 1 phố Tú Mỡ,Phường Trung Hòa,Quận Cầu Giấy,Thành phố Hà Nội</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Sơn</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0986988032</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Xóm 1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>KH bị lỗi hệ thống giám sát NLMT, KH 
-CN SĐT:  382056880 báo hộ sự cố cho KH
-KH y/c KT qua hỗ trợ sớm</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>2026-04-20 13:54:00</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-04-24 12:15:00</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Hoàng Văn Phong</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>291011</t>
-        </is>
-      </c>
-      <c r="Y22" s="2">
-        <v>46132</v>
-      </c>
-      <c r="Z22">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HTH</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HTH_1524566</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Nguyễn Thanh Sơn</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0986988032</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Xóm 1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>1. KH đã báo CN 
 2. KH đã báo qua: ntin qua zalo CN Hà Tĩnh 
@@ -3611,290 +3768,290 @@
 4. KH yêu cầu: Qua kiểm tra, hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>2026-04-16 16:42:00</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>2026-04-17 16:42:00</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Trần Huy Hoàng</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>062253</t>
         </is>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y24" s="2">
         <v>46128</v>
       </c>
-      <c r="Z23">
+      <c r="Z24">
         <v>8</v>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1685313</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Hồ Thắng</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0979763771</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Đường D2 An Tây phường Tây Nam</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a Lê Văn Phụng
 2. KH phản ánh: Trước khi tư vấn KH muốn hỏi có thực hiện được thời gian đề ra hay ko để ký HĐ nhưng lúc kí hợp đồng xong chờ 4 ngày chưa có triển khai vật tư thi công. KH có yêu cầu chấm dứt HĐ và CN bảo sẽ thông báo lại với phía bên kinh doanh và sẽ phản hồi lại cho KH. Nhưng đến giờ KH vẫn chưa thấy phản hồi.
 3. KH yêu cầu: Phản hồi lại thông tin về số tiền cọc</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>2026-04-16 15:09:00</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>2026-04-28 09:00:00</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Lê Văn Phụng</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>033123</t>
         </is>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y25" s="2">
         <v>46128</v>
       </c>
-      <c r="Z24">
+      <c r="Z25">
         <v>8</v>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>Tuyendv</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Vật tư NLMT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_PTO_1641267</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Dương Đức Vinh</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>0979291583</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Khu Hưng Long</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Ý thức trách nhiệm</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>KH (work@namdd.dev) gửi mail phản ánh các vấn đề: 
 1.	Tiền dây dẫn thừa: Đề nghị Viettel Phú Thọ thực hiện việc bồi hoàn lại tiền cho phần dây điện thừa do thi công sai lệch ban đầu.
@@ -3904,185 +4061,45 @@
 6.	Thao tác điều khiển thiết bị từ xa không báo trước: Giải trình về việc tài khoản viettelsolar.phutho@gmail.com tự ý "Xóa dữ liệu báo động lỗi hồ quang" và "Vô hiệu hóa báo động chống sét" ngày 12/04/2026 mà không thông báo hay nắm rõ mục đích xóa.</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>2026-04-16 08:29:00</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>2026-04-30 18:20:00</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Nguyễn Tiến Đức</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>277285</t>
         </is>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y26" s="2">
         <v>46128</v>
       </c>
-      <c r="Z25">
+      <c r="Z26">
         <v>8</v>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Hệ thống an ninh - camera</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>030901-TDH/DVKT/HĐMB-2025/CNCTKHA-CTYITNINHHOA</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Đối tác</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH tm &amp; DV KỸ THUẬT IT Ninh Hòa</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0988647647</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>89 Trần Quý Cáp, Phường Ninh Hiệp, Thị xã Ninh Hoà, Khánh Hòa</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1. Đối tác đã báo cn: a Quốc, c Diệu Mai - kinh doanh
-2. Đối tác phản ánh: Có ký HĐ cung cấp, triển khai lắp đặt camera cho KH mà giờ vẫn làm chưa xong, lắp sai vị trí và chưa bàn giao. CN có hứa trước tết là làm xong và lý do là cuối năm là nhiều công việc nên dời sang sau tết nhưng giờ vẫn chưa triển khai bàn giao cho CĐT.
-3. Đối tác yêu cầu: Đốc thúc đội triển khai thi công triển khai lắp đặt nhanh, và bàn giao lại cho CĐT.</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:30:00</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-04-24 14:40:00</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Phạm Quốc Việt</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>284836</t>
-        </is>
-      </c>
-      <c r="Y26" s="2">
-        <v>46127</v>
-      </c>
-      <c r="Z26">
-        <v>9</v>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>IOC</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4636,12 +4653,12 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Đỗ Thanh Tùng</t>
+          <t>Nguyễn Văn Đằng</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>083858</t>
+          <t>283455</t>
         </is>
       </c>
       <c r="Y30" s="2">
@@ -5340,7 +5357,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-04-20 15:30:00</t>
+          <t>2026-04-25 16:50:00</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5350,7 +5367,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5393,7 +5410,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5408,12 +5425,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KHCN_NLMT_BTE_0218952</t>
+          <t>KHCN_TT.GPTH_CMU_1371520</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5423,7 +5440,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5433,22 +5450,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nguyễn Tước Vy</t>
+          <t>Huỳnh Văn Hão</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0964891591</t>
+          <t>0969227744</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>60/1</t>
+          <t>Phường 5,Thành phố Cà Mau,Tỉnh Cà Mau</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Life Care</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5468,28 +5485,29 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>KH gọi từ số 0384349062 báo Inverter không hoạt động
-YV KT qua kiểm tra và xử lý gấp</t>
+          <t>kh đã báo chi nhánh ( ko nhớ tên người bán)
+Biến tần lỗi và mất kết nối app
+kh yêu cầu kĩ thuật qua xử lý</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-04-10 13:30:00</t>
+          <t>2026-04-24 14:07:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-04-27 17:30:00</t>
+          <t>2026-04-28 09:00:00</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -5499,19 +5517,19 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Chế Minh Phước</t>
+          <t>Vũ Thái Sơn</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>447513</t>
+          <t>284625</t>
         </is>
       </c>
       <c r="Y36" s="2">
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="Z36">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5532,268 +5550,268 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KHCN_NLMT_BTE_0218952</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Nguyễn Tước Vy</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0964891591</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>60/1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Inverter không hoạt động</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>KH gọi từ số 0384349062 báo Inverter không hoạt động
+YV KT qua kiểm tra và xử lý gấp</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026-04-10 13:30:00</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-04-27 17:30:00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Chế Minh Phước</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>447513</t>
+        </is>
+      </c>
+      <c r="Y37" s="2">
+        <v>46122</v>
+      </c>
+      <c r="Z37">
+        <v>14</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QNH_1663601</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Đào Văn Đông</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0989420029</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>120 lý tự trọng (hoà lạc)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: Khi mất điện và khi mới có điện thì giật giật mất điện rồi lại có 3,4 lần trong khi pin 80% đầy điện.  Và hiện tượng ko an toàn bởi vì nhà sử dụng thang máy,  mà 3 4 lần như thế rất sợ. Thỉnh thoảng, khi mất điện xảy ra tình trạng này, giật giật mấy phát rồi có lưới pin.
 3. KH yêu cầu: Kiểm tra thiết bị, điện ở trong nhà và khắc phục tình trạng này.</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>2026-04-10 08:00:00</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>2026-04-26 15:05:00</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Vũ Duy Tùng</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>455203</t>
-        </is>
-      </c>
-      <c r="Y37" s="2">
-        <v>46122</v>
-      </c>
-      <c r="Z37">
-        <v>14</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1684187</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Cao Xuân Cường</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0967095136</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Xóm 9</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>- Mới gọi lên tổng đài 
-- Anh đã ký hd. Khi nào có thể lắp đặt nlmt cho anh</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>2026-04-10 08:00:00</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-04-13 09:00:00</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Bùi Đức Hào</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>024067</t>
         </is>
       </c>
       <c r="Y38" s="2">
@@ -5809,12 +5827,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -5846,250 +5864,250 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>KHCN_TT.GPTH_NAN_1684187</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Cao Xuân Cường</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0967095136</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Xóm 9</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Trong bán</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>- Mới gọi lên tổng đài 
+- Anh đã ký hd. Khi nào có thể lắp đặt nlmt cho anh</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-04-10 08:00:00</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-04-13 09:00:00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bùi Đức Hào</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>024067</t>
+        </is>
+      </c>
+      <c r="Y39" s="2">
+        <v>46122</v>
+      </c>
+      <c r="Z39">
+        <v>14</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Sonln15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>KHCN_TT.GPTH_NAN_1598580</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Hồ Văn Khương</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>0941663636</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Xóm 8</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>1. Khách hàng không báo qua chi nhánh 
 2. Khách chỉ báo qua hotline 
 3. Điện nllmt 2 3 hôm nay hiệu số rất thấp.Giờ cao điểm trước đây thu được 5 6 kí giờ chỉ còn 2 3 kí</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>2026-04-08 08:00:00</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>2026-04-15 18:50:00</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Võ Trọng Đức</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>293804</t>
         </is>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y40" s="2">
         <v>46120</v>
       </c>
-      <c r="Z39">
+      <c r="Z40">
         <v>16</v>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HDG_1610342</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Anh Quân</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0983448280</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>phường chu văn an</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Mất 1 string điện không vào ắc quy. Không đủ cung cấp cho tải nhà dùng . Anh cần đến kiêm tra trong ngày hôm nay.
-**Địa chỉ lắp đặt: số nhà 300, kim tân, xã đoài phương, thành phố hà nội.</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>2026-04-06 16:23:00</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-04-08 17:30:00</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Bùi Văn Hoàn</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>046275</t>
-        </is>
-      </c>
-      <c r="Y40" s="2">
-        <v>46118</v>
-      </c>
-      <c r="Z40">
-        <v>18</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -6115,80 +6133,224 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Acquy lưu trữ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HDG_1610342</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Anh Quân</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0983448280</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>phường chu văn an</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Mất 1 string điện không vào ắc quy. Không đủ cung cấp cho tải nhà dùng . Anh cần đến kiêm tra trong ngày hôm nay.
+**Địa chỉ lắp đặt: số nhà 300, kim tân, xã đoài phương, thành phố hà nội.</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:23:00</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:30:00</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bùi Văn Hoàn</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>046275</t>
+        </is>
+      </c>
+      <c r="Y41" s="2">
+        <v>46118</v>
+      </c>
+      <c r="Z41">
+        <v>18</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>140501-KD/HĐMBLĐ-2024/HONGANH-CNCTVPC</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH DỊCH VỤ THƯƠNG MẠI VẬN TẢI HỒNG ÁNH</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>0987221002</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Số nhà 85 thôn 1</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: a Nghĩa
 2. KH phản ánh: bị hỏng ắc quy
@@ -6196,458 +6358,319 @@
 ***SĐT phản ánh và liên hệ: 0964109909</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>2026-04-06 08:00:00</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>2026-05-05 17:30:00</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Phạm Văn Nghĩa</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>023020</t>
         </is>
       </c>
-      <c r="Y41" s="2">
+      <c r="Y42" s="2">
         <v>46118</v>
       </c>
-      <c r="Z41">
+      <c r="Z42">
         <v>18</v>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>truongdv17</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>KHCN_NLMT_TNN_0200299</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Đinh Văn Chỉnh</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>0868632926</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Phú Cường,</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>KH dã báo CN
 KH đang sử dụng NLMT, hiện tại KH ko thấy phát sinh điện, bên điện lực báo ko thấy công tơ lên
 YC KT qua kiểm tra và xử lý cho KH</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>2026-04-03 08:00:00</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>2026-05-02 16:44:00</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Trần Xuân Kương</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>289759</t>
         </is>
       </c>
-      <c r="Y42" s="2">
+      <c r="Y43" s="2">
         <v>46115</v>
       </c>
-      <c r="Z42">
+      <c r="Z43">
         <v>21</v>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1634096</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Nguyễn Ngọc Ân</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>0988386838</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Xã Xuân Cẩm, Tỉnh Bắc Ninh</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: nhà KH có thêm ats của máy nổ, về nguyên tắc máy điện phải chạy nlmt, khi nlmt hết thì chạy máy nổ. Hiện tại thì khi mất điện ko chạy sang nlmt, và khi nlmt hết rồi vẫn ko thấy chạy máy nổ. 
 3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>2026-03-30 15:55:00</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>2026-04-30 10:50:00</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>408869</t>
-        </is>
-      </c>
-      <c r="Y43" s="2">
-        <v>46111</v>
-      </c>
-      <c r="Z43">
-        <v>25</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>KHCN_PINNLMT_NAN_0334667</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Lê Trung An</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0865878212</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>1. KH đã báo cn
-2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2026-03-30 11:30:00</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-04-10 19:10:00</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Nguyễn Minh Linh</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>285776</t>
         </is>
       </c>
       <c r="Y44" s="2">
@@ -6700,249 +6723,245 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>KHCN_PINNLMT_NAN_0334667</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Lê Trung An</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0865878212</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1. KH đã báo cn
+2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-03-30 11:30:00</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-04-10 19:10:00</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Linh</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>285776</t>
+        </is>
+      </c>
+      <c r="Y45" s="2">
+        <v>46111</v>
+      </c>
+      <c r="Z45">
+        <v>25</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>KHCN_TT.GPTH_NAN_1574225</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Nguyên Văn Tú</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>0868081789</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
 2. KH phản ánh NLMT bị hỏng không sử dụng được
 3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>2026-03-30 08:00:00</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>2026-04-25 21:30:00</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Nguyễn Văn Tân</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>460719</t>
         </is>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y46" s="2">
         <v>46111</v>
       </c>
-      <c r="Z45">
+      <c r="Z46">
         <v>25</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>DNG</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_QNM_1510130</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Lê Phước Danh</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0355557906</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Thôn Pà Dá,Xã Cà Dy,Huyện Nam Giang,Tỉnh Quảng Nam</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Lỗi pin ko lưu</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026-04-01 10:43:00</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-04-18 10:52:00</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Lê Văn Trung</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>161073</t>
-        </is>
-      </c>
-      <c r="Y46" s="2">
-        <v>46113</v>
-      </c>
-      <c r="Z46">
-        <v>23</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6963,380 +6982,523 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Acquy lưu trữ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_QNM_1510130</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Lê Phước Danh</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0355557906</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Thôn Pà Dá,Xã Cà Dy,Huyện Nam Giang,Tỉnh Quảng Nam</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Lỗi pin ko lưu</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:43:00</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-04-18 10:52:00</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lê Văn Trung</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>161073</t>
+        </is>
+      </c>
+      <c r="Y47" s="2">
+        <v>46113</v>
+      </c>
+      <c r="Z47">
+        <v>23</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HDG_1304417</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>0377883716</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH yêu cầu NVKT qua lại thiết bị inverter của KH 
 Số liên hệ:</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>2026-03-26 08:00:00</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>2026-04-19 09:46:00</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Hoàng Văn Phong</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>291011</t>
         </is>
       </c>
-      <c r="Y47" s="2">
+      <c r="Y48" s="2">
         <v>46107</v>
       </c>
-      <c r="Z47">
+      <c r="Z48">
         <v>29</v>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_PTO_1620637</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Nguyễn Đình Mạnh</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0988308581</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Xã Thanh Cao, Huyện Lương Sơn, Tỉnh Hòa Bình</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH phản ánh: hệ thống bị lỗi, điện bật 10 -15s chớp 1 lần
 KH yêu cầu chuyển KT xuống xử lý gấp</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>2026-03-24 15:09:00</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>2026-05-18 07:55:00</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Bùi Anh Nguyễn</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>414445</t>
         </is>
       </c>
-      <c r="Y48" s="2">
+      <c r="Y49" s="2">
         <v>46105</v>
       </c>
-      <c r="Z48">
+      <c r="Z49">
         <v>31</v>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Dương Văn Quân</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>0359999199</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>xã Hoàng Vân</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -7344,430 +7506,430 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>2026-03-23 08:00:00</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>2026-03-26 18:00:00</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Nguyễn Văn Trường</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>121999</t>
         </is>
       </c>
-      <c r="Y49" s="2">
+      <c r="Y50" s="2">
         <v>46104</v>
       </c>
-      <c r="Z49">
+      <c r="Z50">
         <v>32</v>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1638575</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TAYOTO</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>0911937779</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>quốc lộ 55, Xã Hồ Tràm, Thành phố Hồ Chí Minh, Xã Hồ Tràm, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>1. KH chưa báo cn
 2. KH phản ánh: Sự cố từ TT_1772587360264 trước sau khi xử lý KH thấy hệ thống nlmt ko có ổn định, lâu lâu tự ngắt và phải bảo nv tắt 3 công tắc cp đi bật lại mãi mới được.
 3. KH yêu cầu: Kiểm tra lại hàng hóa xem có đúng với HĐ về chất lượng, hiệu suất không. Nếu có vấn đề thì thay mới tinh cho KH để hệ thống vận hành trơn tru.</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>2026-03-19 09:25:00</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>2026-04-28 09:00:00</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y50" s="2">
+      <c r="Y51" s="2">
         <v>46100</v>
       </c>
-      <c r="Z50">
+      <c r="Z51">
         <v>36</v>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>QTI</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QTI_0991884</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Nguyễn Thị Như Mỹ</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>0963369267</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>KP4, Thị trấn Cam Lộ, Huyện Cam Lộ, Tỉnh Quảng Trị</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a Nguyễn Đình Bằng bên nlmt
 2. KH phản ánh: Hệ thống inverter báo lỗi mã lỗi 01.M011 và ko đẩy ra sản lượng điện nlmt.
 3. KH yêu cầu: Điều KT qua hỗ trợ giúp KH.</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>2026-03-09 08:00:00</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>2026-04-22 18:20:00</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Trương Thành</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>462341</t>
         </is>
       </c>
-      <c r="Y51" s="2">
+      <c r="Y52" s="2">
         <v>46090</v>
       </c>
-      <c r="Z51">
+      <c r="Z52">
         <v>46</v>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VTU_1502475</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Nguyễn Phú Quý</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>0947110192</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>1. Đã báo chi nhánh chưa: chưa báo
 2.KH gọi điện lên TĐ
@@ -7775,330 +7937,186 @@
 4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>2026-03-03 15:09:00</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>2026-03-15 12:55:00</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Lê Đức Cảnh</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>291002</t>
         </is>
       </c>
-      <c r="Y52" s="2">
+      <c r="Y53" s="2">
         <v>46084</v>
       </c>
-      <c r="Z52">
+      <c r="Z53">
         <v>52</v>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_DNI_1659133</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>0907002673</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>1. Kh đã báo cn
 2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
 3. kh yc: YC cn hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>2026-02-23 13:30:00</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>2026-04-21 10:30:00</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Lê Đức Bình</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>412105</t>
         </is>
       </c>
-      <c r="Y53" s="2">
+      <c r="Y54" s="2">
         <v>46076</v>
       </c>
-      <c r="Z53">
+      <c r="Z54">
         <v>60</v>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Trương Công An</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>0914531694</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>khối 2</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>2026-01-19 08:00:00</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026-04-23 23:10:00</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Lê Văn Anh</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>069170</t>
-        </is>
-      </c>
-      <c r="Y54" s="2">
-        <v>46041</v>
-      </c>
-      <c r="Z54">
-        <v>95</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -8124,80 +8142,224 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Trương Công An</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0914531694</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>khối 2</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2026-01-19 08:00:00</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-04-23 23:10:00</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lê Văn Anh</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>069170</t>
+        </is>
+      </c>
+      <c r="Y55" s="2">
+        <v>46041</v>
+      </c>
+      <c r="Z55">
+        <v>95</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>DVKT</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Home Service</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Dịch vụ khác</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>0962892720</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -8205,53 +8367,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>2025-12-10 08:00:00</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>2025-12-16 15:00:00</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y55" s="2">
+      <c r="Y56" s="2">
         <v>46001</v>
       </c>
-      <c r="Z55">
+      <c r="Z56">
         <v>135</v>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -511,32 +511,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DVKT</t>
+          <t>GPTH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Home Service</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VCC_HS_TNN_1776255462417</t>
+          <t>KHCN_TT.GPTH_AGG_1651922</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,6 +544,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -551,22 +556,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Ngô Văn Khang</t>
+          <t>Huỳnh Trúc Linh</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0779966988</t>
+          <t>0397498197</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>TDP Trung</t>
+          <t>Ấp An Hòa</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -576,27 +581,29 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Liên hệ chậm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Kt chưa liên hệ  hẹn lịch</t>
+          <t>CN Chí - Công Trình Viet Tel Châu Đốc báo sự cố hộ KH qua zalo
+1. KH phản ánh: Hệ thống không nạp điện vô Pin lưu trữ.
+2. KH yêu cầu: KT qua kiểm tra hỗ trợ KH</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-04-29 13:30:00</t>
+          <t>2026-04-29 16:39:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -616,12 +623,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Trần Hiển Hảo</t>
+          <t>Phan Tấn Phúc</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>246914</t>
+          <t>191678</t>
         </is>
       </c>
       <c r="Y2" s="2">
@@ -632,7 +639,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -649,62 +656,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Bảo dưỡng vệ sinh máy giặt lồng đứng</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_BTN_1593493</t>
+          <t>VCC_HS_HNI_1776594492949</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẾ HỆ TƯƠNG LAI</t>
+          <t>Anhh Hùng</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0902000084</t>
+          <t>0912073567</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>120C Nguyễn Đình Chiểu</t>
+          <t>số 117 phố Cửa Lộc, Phường Thanh Xuân, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -724,24 +731,23 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tay nghề kém</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>- Kh báo qua chi nhánh: A Hưng 
-- Kh phản ánh: Inveter báo lỗi trên màn hình 
-- Kh yêu cầu: Xử lý sớm cho khách</t>
+          <t>- Chị có sử dụng dịch vụ bảo dưỡng máy giặt bên mình. Sau khi bảo dưỡng bị nước tràn ra ngoài. KH đã gọi thợ qua sửa 2 3 lần mà vẫn bị
+- KH yêu cầu: Thợ tốt đến khắc phục cho khách</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-04-29 13:30:00</t>
+          <t>2026-04-29 15:17:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -761,12 +767,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Hồ Văn Tuấn</t>
+          <t>Lê Duy Tuấn</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>046974</t>
+          <t>293859</t>
         </is>
       </c>
       <c r="Y3" s="2">
@@ -777,7 +783,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -794,1118 +800,1117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VCC_HS_TNN_1776255462417</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ngô Văn Khang</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0779966988</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TDP Trung</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Trước bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Liên hệ chậm</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Kt chưa liên hệ  hẹn lịch</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:30:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-05-04 09:00:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trần Hiển Hảo</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>246914</t>
+        </is>
+      </c>
+      <c r="Y4" s="2">
+        <v>46141</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HYN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HYN_1619748</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Mai Đức Xình</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0972678353</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Thôn Trạo Thôn</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CN 0868707197 báo sự cố hộ KH
+1. KH phản ánh: Đang bị mất điện lưới, pin ko đẩy lên được vì bị hỏng đảo chiều. Ngoài ra app theo dõi KH cũng đang ko vào được.
+2. KH yêu cầu: Qua kiểm tra, hỗ trợ khắc phục tình trạng này.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:33:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-05-04 09:00:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Đinh Văn Huyến</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>429217</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46141</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1653774</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Trương Đức Trung</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0917355379</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>299/72 Hùng Vương</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>- Chưa báo chi nhánh 
 - Kh phản ánh: Biến tần hiển thị không lên cả tuần nay 
 - KH yêu cầu: Xử lý sớm cho anh</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2026-04-29 13:30:00</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2026-05-04 09:00:00</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Nguyễn Quảng Ngãi</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>408751</t>
         </is>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y6" s="2">
         <v>46141</v>
       </c>
-      <c r="Z4">
+      <c r="Z6">
         <v>0</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNH_1688014</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Lưu Thị Bảo Trâm</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0854285411</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>242 Võ Thị Sáu, Khu phố 1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>- Kh chưa báo chi nhánh
 - Kh phản ánh:Đã đặt cọc tiền nlmt mà đến giờ vẫn chưa lăp đặt xong.5h chiều hôm qua hẹn hôm nay đến mà không thấy đến.Giao vật tư không báo sớm toàn báo sát giờ.Cách làm việc không đạt. Đã kí hợp đồng nhưng chưa lắp đặt nlmt mới tập kết vật tư 
 - Kh yêu cầu: Lắp đặt sớm cho khách</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-04-29 10:55:00</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2026-05-04 09:00:00</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Nguyễn Tấn Tài</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>461237</t>
         </is>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y7" s="2">
         <v>46141</v>
       </c>
-      <c r="Z5">
+      <c r="Z7">
         <v>0</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Tuyendv</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>KHCN_PINNLMT_KHA_0302267</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Đài Văn Linh</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0946546688</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>32 Trịnh Hòai Đức, Phường Vĩnh Hòa, Thành phố Nha Trang, Tỉnh Khánh Hòa</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Chi nhánh báo hộ sdt( 0343465634)
 Inveter lỗi 2 string lệch nhau về điện áp 
 Yeu cau kt xuong ktra cho kh</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-04-29 09:24:00</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-05-04 09:00:00</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Phan Trọng Nghĩa</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>234935</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y8" s="2">
         <v>46141</v>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1688637</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Tô Hoàng Ngân</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0919050550</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>223/9/5 Nguyễn Trãi, kp Long Phượng</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Ý thức trách nhiệm</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: A Hoàng
 2. KH phản ánh: CN là a Hoàng hứa hẹn là trong vòng 5 ngày sau khi đặt cọc ký HĐ sẽ lắp đặt NLMT cho KH mà giờ vẫn ko thấy đâu rồi cứ hẹn mãi hẹn mãi không biết đến khi nào. Và giờ khiến KH cứ phải đợi chờ suốt 5 ngày nay, KH rất bức xúc về cách làm việc của CN.
 3. KH yêu cầu: Sau khi đọc lại điều khoản về thời gian lắp đặt là 15 ngày, nếu chính xác 15 ngày chưa triển khai lắp đặt cho KH, KH yêu cầu là hủy HĐ và hoàn lại số tiền cọc.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-04-29 08:00:00</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-05-04 09:00:00</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Lưu Thế Hoàng</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>408736</t>
         </is>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y9" s="2">
         <v>46141</v>
       </c>
-      <c r="Z7">
+      <c r="Z9">
         <v>0</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Tuyendv</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1654300</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Trần Thị Hải</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0918893239</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>134 Phạm Hồng Thái</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>- Kh đã gọi qua chi nhánh( A Hậu) mà không nghe máy 
 - Kh phản ánh: Điện nlmt bị cúp điện. Trong khi đó trời nắng rất to, bình lưu trữ còn 4 5 nấc mà vẫn bị mất điện. 
 - Kh yêu cầu: Xử lý sớm cho khách</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-04-29 08:00:00</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2026-05-04 09:00:00</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Nguyễn Quảng Ngãi</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>408751</t>
         </is>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y10" s="2">
         <v>46141</v>
       </c>
-      <c r="Z8">
+      <c r="Z10">
         <v>0</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HDG_1399900</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Nguyễn Ngọc Miên</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0989435816</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>thôn phí xá,Xã Cẩm Hoàng,Huyện Cẩm Giàng,Tỉnh Hải Dương</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>- KH đã báo chi nhánh: A Thêm 
 -KH phản ánh: Pin nlmt không nạp xuống điện lưới 
 - Kh yêu cầu: Sớm xử lý lại cho khách</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>2026-04-28 17:23:00</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-04-29 17:23:00</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-05-04 17:30:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thêm</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>285987</t>
-        </is>
-      </c>
-      <c r="Y9" s="2">
-        <v>46140</v>
-      </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HPG_1684164</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Vũ Ngọc Tân</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0919165945</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>81 Phạm Duy Quyết</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>- KH báo qua cn: Chị Dừa 
-- KH yêu cầu: Đi lại một số dây tiếp điện cắm pin. Chưa tiếp silicon  ở phần khoan rút lõi. Tiếp điạ  từ tấm pin xuống biến tần. Cái cài C4 cần hất sang 1 bên để tránh nước rơi xuống điểm giao tiếp của 2 MC.</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2026-04-28 16:56:00</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-04-29 16:56:00</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Phạm Quang Tĩnh</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>015872</t>
-        </is>
-      </c>
-      <c r="Y10" s="2">
-        <v>46140</v>
-      </c>
-      <c r="Z10">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Anhnt631</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_KHA_1192187</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Phạm Thị Lư</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0327494384</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Thi trấn Cam Đức</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>- Kh chưa báo chi nhánh
-- Kh phản ánh:Cục pin nlmt bị kêu.Điện nlmt lúc có lúc không toàn vào điện lưới.Công ty về làm xong vẫn bị lại 
-- Kh yêu cầu: Ngày mai phải đến xử lý cho chị</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2026-04-28 16:39:00</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-04-29 16:39:00</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Trần Quốc Khang</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>466625</t>
         </is>
       </c>
       <c r="Y11" s="2">
@@ -1938,7 +1943,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1948,17 +1953,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M&amp;E</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Thiết bị chữa cháy, thoát hiểm</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VCC_YCTX_HNI_40519368378993120</t>
+          <t>KHCN_TT.GPTH_HPG_1684164</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1966,6 +1971,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -1973,22 +1983,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lưu Thùy Vân</t>
+          <t>Vũ Ngọc Tân</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0972117543</t>
+          <t>0919165945</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Xã Ngọc Hồi, Thành phố Hà Nội</t>
+          <t>81 Phạm Duy Quyết</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1998,54 +2008,53 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Trước bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
+          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>kh cần liên hệ Pccc
-Đã thấy lên yêu cầu tiếp xúc nhưng kt chưa liên hệ
-lắp hệ thống PCCC cho trường mần non</t>
+          <t>- KH báo qua cn: Chị Dừa 
+- KH yêu cầu: Đi lại một số dây tiếp điện cắm pin. Chưa tiếp silicon  ở phần khoan rút lõi. Tiếp điạ  từ tấm pin xuống biến tần. Cái cài C4 cần hất sang 1 bên để tránh nước rơi xuống điểm giao tiếp của 2 MC.</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-04-28 14:47:00</t>
+          <t>2026-04-28 16:56:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-04-29 14:47:00</t>
+          <t>2026-05-04 08:50:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Nguyễn Như Khánh</t>
+          <t>Phạm Quang Tĩnh</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>489838</t>
+          <t>015872</t>
         </is>
       </c>
       <c r="Y12" s="2">
@@ -2056,17 +2065,17 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>P.KD Cơ điện</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>P.KD Cơ điện</t>
+          <t>Anhnt631</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2516,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2522,12 +2531,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acquy lưu trữ</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_CTO_1646135</t>
+          <t>KHCN_PINNLMT_TVH_0269475</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2537,7 +2546,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2547,17 +2556,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thủy</t>
+          <t>Lâm Quốc Khỏe</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0938412134</t>
+          <t>0989181919</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ấp Tân Quới, Xã Tân Bình, Thành phố Cần Thơ</t>
+          <t>Mậu Thân</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2567,7 +2576,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2582,14 +2591,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Hiệu suất sản phẩm kém</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>"1.KH đã báo CN (A Khoa) và CN hướng dẫn KH gọi lên TĐ
-2.HT NLMT Bình Ắc quy bị lỗi không có chi tiết số điện đang lưu trữ, mức điện luôn thông báo 100%, nhà KH sử dụng máy cắt sắt bị yếu, máy ngưng liên tục,
-3. KH cần CN hỗ trợ đến kiểm tra và khắc phục sớm"</t>
+          <t>1. KH chưa báo CN
+2. HT NLMT hiệu suất thấp, HT 15KWP tuy nhiên hiệu suất hiện tại chưa được 7KWP ( 3 Tháng liên tục)
+3. KH cần KT đến hỗ trợ kiểm tra và xử lý giúp</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2599,7 +2608,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-04-29 20:20:00</t>
+          <t>2026-05-01 17:30:00</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2609,17 +2618,17 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Trần Diệp Anh</t>
+          <t>Thái Hữu Quang</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>436332</t>
+          <t>289679</t>
         </is>
       </c>
       <c r="Y16" s="2">
@@ -2652,7 +2661,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2672,7 +2681,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_TVH_0269475</t>
+          <t>KHCN_NLMT_CMU_0221392</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2682,7 +2691,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2692,17 +2701,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Lâm Quốc Khỏe</t>
+          <t>Lâm Quốc Việt</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0989181919</t>
+          <t>0985100340</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Mậu Thân</t>
+          <t>phường 162 dg bùi thí trg phg tân thành ca mau</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2727,24 +2736,24 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. HT NLMT hiệu suất thấp, HT 15KWP tuy nhiên hiệu suất hiện tại chưa được 7KWP ( 3 Tháng liên tục)
-3. KH cần KT đến hỗ trợ kiểm tra và xử lý giúp</t>
+          <t>Khách  hàng chưa báo chi nhánh  
+Pin năng lượng mặt trời sản lượng ra không kh đã theo dõi tren app ( hiệu suất không đạt ) 
+Yêu cầu kĩ thuật qua xử lý cho khách hàng</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-04-28 08:00:00</t>
+          <t>2026-04-28 13:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-04-29 09:00:00</t>
+          <t>2026-04-30 21:05:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2754,17 +2763,17 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Thái Hữu Quang</t>
+          <t>Võ Duy Khang</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>289679</t>
+          <t>473069</t>
         </is>
       </c>
       <c r="Y17" s="2">
@@ -2792,12 +2801,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2817,7 +2826,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KHCN_NLMT_CMU_0221392</t>
+          <t>KHCN_TT.GPTH_HPG_1640133</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2827,7 +2836,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2837,17 +2846,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lâm Quốc Việt</t>
+          <t>Nguyễn Thanh Sơn</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0985100340</t>
+          <t>0912708611</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>phường 162 dg bùi thí trg phg tân thành ca mau</t>
+          <t>2/212 Đà Nẵng,</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2857,7 +2866,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2872,24 +2881,24 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Khách  hàng chưa báo chi nhánh  
-Pin năng lượng mặt trời sản lượng ra không kh đã theo dõi tren app ( hiệu suất không đạt ) 
-Yêu cầu kĩ thuật qua xử lý cho khách hàng</t>
+          <t>Chi nhánh báo hooj kh ( 0365515300 )
+Lỗi Pin lưu trữ  ko lên bình sập nguồn
+Yêu  cầu kt qua xử lỹ cho kh</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-04-28 13:30:00</t>
+          <t>2026-04-28 08:00:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-04-29 13:30:00</t>
+          <t>2026-05-15 15:05:00</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2899,17 +2908,17 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Võ Duy Khang</t>
+          <t>Hoàng Hữu Tuấn</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>473069</t>
+          <t>037650</t>
         </is>
       </c>
       <c r="Y18" s="2">
@@ -2937,12 +2946,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2962,7 +2971,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HPG_1640133</t>
+          <t>KHCN_TT.GPTH_KGG_1562339</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2972,7 +2981,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2982,17 +2991,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nguyễn Thanh Sơn</t>
+          <t>Phan Ngọc Kiệt</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0912708611</t>
+          <t>0913994909</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2/212 Đà Nẵng,</t>
+          <t>Ấp Sua Đũa</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3002,7 +3011,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3012,29 +3021,29 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Chi nhánh báo hooj kh ( 0365515300 )
-Lỗi Pin lưu trữ  ko lên bình sập nguồn
-Yêu  cầu kt qua xử lỹ cho kh</t>
+          <t>- Đã báo qua chi nhánh: A Hoàng
+- Kh phản ánh: Trên app không hiển thị hiệu suất nlmt,tấm pin, biến tần,...
+- Kh yêu cầu: Xử lý nhanh cho khách</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-04-28 08:00:00</t>
+          <t>2026-04-28 14:44:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-05-15 15:05:00</t>
+          <t>2026-05-02 13:20:00</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3049,12 +3058,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Hoàng Hữu Tuấn</t>
+          <t>Doãn Tuấn Kiệt</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>037650</t>
+          <t>454453</t>
         </is>
       </c>
       <c r="Y19" s="2">
@@ -3082,12 +3091,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3107,7 +3116,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_KGG_1562339</t>
+          <t>KHCN_TT.GPTH_BNH_1662966</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3117,7 +3126,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3127,17 +3136,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Phan Ngọc Kiệt</t>
+          <t>Nguyễn Hải Nam</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0913994909</t>
+          <t>0912093999</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ấp Sua Đũa</t>
+          <t>Thôn Hương Thịnh</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3167,19 +3176,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>- Đã báo qua chi nhánh: A Hoàng
-- Kh phản ánh: Trên app không hiển thị hiệu suất nlmt,tấm pin, biến tần,...
-- Kh yêu cầu: Xử lý nhanh cho khách</t>
+          <t>đã báo chi nhánh
+Không theo dõi được hiệu suất qua app
+yêu cầu kt qua hỗ trợ</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-04-28 14:44:00</t>
+          <t>2026-04-28 13:43:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-05-02 13:20:00</t>
+          <t>2026-05-04 12:25:00</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3194,12 +3203,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Doãn Tuấn Kiệt</t>
+          <t>Phạm Văn Huy</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>454453</t>
+          <t>408869</t>
         </is>
       </c>
       <c r="Y20" s="2">
@@ -3227,12 +3236,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3252,7 +3261,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1662966</t>
+          <t>KHCN_TT.GPTH_DTP_1619705</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3272,17 +3281,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nguyễn Hải Nam</t>
+          <t>Nguyễn Văn Ly</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0912093999</t>
+          <t>0977749451</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Thôn Hương Thịnh</t>
+          <t>Ấp Mỹ An A</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3302,29 +3311,29 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>đã báo chi nhánh
-Không theo dõi được hiệu suất qua app
-yêu cầu kt qua hỗ trợ</t>
+          <t>Chưa báo chi nhánh 
+Kh nlmt bị biết tần bị nhẩy và tấm pin bị nứt 
+Yêu cầu chi nhánh qua hỗ trợ</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-04-28 13:43:00</t>
+          <t>2026-04-28 09:12:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-04-29 13:43:00</t>
+          <t>2026-05-05 16:05:00</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3334,17 +3343,17 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Phạm Văn Huy</t>
+          <t>Huỳnh Tấn Phát</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>408869</t>
+          <t>285548</t>
         </is>
       </c>
       <c r="Y21" s="2">
@@ -3372,12 +3381,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3397,7 +3406,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DTP_1619705</t>
+          <t>KHCN_PINNLMT_BGG_0387193</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3405,11 +3414,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3417,17 +3421,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Ly</t>
+          <t>Nịnh Văn Phúc</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0977749451</t>
+          <t>0985213406</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ấp Mỹ An A</t>
+          <t>Thôn đồng bụt, Xã Đèo Gia</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3437,7 +3441,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3452,24 +3456,24 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Chưa báo chi nhánh 
-Kh nlmt bị biết tần bị nhẩy và tấm pin bị nứt 
-Yêu cầu chi nhánh qua hỗ trợ</t>
+          <t>1. KH đã báo CN (KH ko nhớ rõ tên)
+2. KH phản ánh: Cách đây 4 hôm hệ của KH bị sét đánh, KH cũng ko rõ là ở đâu chỉ thấy áp ở tủ điện nhảy xuống, điện ko phát lên lưới và thấy bị hỏng.
+3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-04-28 09:12:00</t>
+          <t>2026-04-28 08:00:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-05-05 16:05:00</t>
+          <t>2026-05-10 14:05:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3484,12 +3488,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Huỳnh Tấn Phát</t>
+          <t>Nghiêm Minh Hải</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>285548</t>
+          <t>408900</t>
         </is>
       </c>
       <c r="Y22" s="2">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3542,7 +3546,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_BGG_0387193</t>
+          <t>KHCN_TT.GPTH_HNI_1613155</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3550,6 +3554,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3557,17 +3566,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nịnh Văn Phúc</t>
+          <t>Nguyễn Doãn Trường</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0985213406</t>
+          <t>0962465555</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Thôn đồng bụt, Xã Đèo Gia</t>
+          <t>số 164 Nguyễn Văn Giáp, Phường Từ Liêm, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3577,7 +3586,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3592,14 +3601,14 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN (KH ko nhớ rõ tên)
-2. KH phản ánh: Cách đây 4 hôm hệ của KH bị sét đánh, KH cũng ko rõ là ở đâu chỉ thấy áp ở tủ điện nhảy xuống, điện ko phát lên lưới và thấy bị hỏng.
-3. KH yêu cầu: KT qua kiểm tra, khắc phục tình trạng này cho KH.</t>
+          <t>1. KH đã báo cn: a Hà Hữu Giang
+2. KH phản ánh: Sự cố hiệu suất từ trước KT đã đến kiểm tra và trao đổi với KH đưa ra kết luận là do bên Kinh Doanh tư vấn lắp đặt sai nên tấm pin bị che khuất, che phủ nên ko đạt hiệu suất. Từ đầu lúc ký HĐ, KH đã trao đổi với a Tín là nên lắp hướng nào, hay nắng hướng nào và vị trí này tối đa hiệu suất là bnhieu. Hệ của KH là 36kw, bên kinh  doanh có cam kết là trung bình 1 ngày 100 số, và 6 tháng đầu sử dụng là từ 2900-3100 số mà giờ chỉ được 60-70 số 1 ngày, sản lượng ko đạt.
+3. KH yêu cầu: Có trách nhiệm cam kết đúng giữa KH và bên Kinh doanh, và thực hiện đưa ra phương án xử lý để có sản lượng theo đúng cam kết. KH yêu cầu xử lý gấp.</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3609,7 +3618,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-04-29 15:55:00</t>
+          <t>2026-05-07 10:10:00</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3619,17 +3628,17 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Nghiêm Minh Hải</t>
+          <t>Hoàng Văn Vương</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>408900</t>
+          <t>285732</t>
         </is>
       </c>
       <c r="Y23" s="2">
@@ -3657,12 +3666,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3682,7 +3691,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNI_1613155</t>
+          <t>KHCN_TT.GPTH_BPC_1427400</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3692,7 +3701,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3702,17 +3711,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nguyễn Doãn Trường</t>
+          <t>Công Ty Tnhh Phúc An Solutions</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0962465555</t>
+          <t>0972342939</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>số 164 Nguyễn Văn Giáp, Phường Từ Liêm, Thành phố Hà Nội</t>
+          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3742,9 +3751,9 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn: a Hà Hữu Giang
-2. KH phản ánh: Sự cố hiệu suất từ trước KT đã đến kiểm tra và trao đổi với KH đưa ra kết luận là do bên Kinh Doanh tư vấn lắp đặt sai nên tấm pin bị che khuất, che phủ nên ko đạt hiệu suất. Từ đầu lúc ký HĐ, KH đã trao đổi với a Tín là nên lắp hướng nào, hay nắng hướng nào và vị trí này tối đa hiệu suất là bnhieu. Hệ của KH là 36kw, bên kinh  doanh có cam kết là trung bình 1 ngày 100 số, và 6 tháng đầu sử dụng là từ 2900-3100 số mà giờ chỉ được 60-70 số 1 ngày, sản lượng ko đạt.
-3. KH yêu cầu: Có trách nhiệm cam kết đúng giữa KH và bên Kinh doanh, và thực hiện đưa ra phương án xử lý để có sản lượng theo đúng cam kết. KH yêu cầu xử lý gấp.</t>
+          <t>Đã báo chi nhánh  bình long tỉnh đồng nai
+Sự cố bát sạc không vào 
+Yêu cầu kt qua xửu lý cho kh</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3754,7 +3763,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-05-07 10:10:00</t>
+          <t>2026-05-01 10:05:00</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3769,12 +3778,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Hoàng Văn Vương</t>
+          <t>Phạm Trung Hiếu</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>285732</t>
+          <t>264250</t>
         </is>
       </c>
       <c r="Y24" s="2">
@@ -3802,12 +3811,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3827,7 +3836,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BPC_1427400</t>
+          <t>KHCN_PINNLMT_HTH_0281764</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3835,11 +3844,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3847,17 +3851,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Công Ty Tnhh Phúc An Solutions</t>
+          <t>Nguyễn Trường Sơn</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0972342939</t>
+          <t>0912435219</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>abc,Phường An Lộc,Thị xã Bình Long,Tỉnh Bình Phước</t>
+          <t>Phường Thanh Sen</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3882,14 +3886,14 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Đã báo chi nhánh  bình long tỉnh đồng nai
-Sự cố bát sạc không vào 
-Yêu cầu kt qua xửu lý cho kh</t>
+          <t>1. KH đã báo cn
+2. KH phản ánh: Bị mất kết nối app để theo dõi hiệu suất NLMT
+3. KH yêu cầu: Hỗ trợ KH kết nối lại app để xem hiệu suất</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3899,7 +3903,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-04-29 10:05:00</t>
+          <t>2026-04-30 08:15:00</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3909,17 +3913,17 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Phạm Trung Hiếu</t>
+          <t>Trịnh Xuân Bảo</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>264250</t>
+          <t>471569</t>
         </is>
       </c>
       <c r="Y25" s="2">
@@ -3952,7 +3956,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3967,12 +3971,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_HTH_0281764</t>
+          <t>KHCN_TT.GPTH_QNH_1258034</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3987,17 +3991,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nguyễn Trường Sơn</t>
+          <t>Mạc Văn Xuyên</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0912435219</t>
+          <t>0913262405</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Phường Thanh Sen</t>
+          <t>Tổ 4, khu 4D, Phường Hồng Hải, Thành phố Hạ Long, Tỉnh Quảng Ninh</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -4022,14 +4026,14 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Hiệu suất sản phẩm kém</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn
-2. KH phản ánh: Bị mất kết nối app để theo dõi hiệu suất NLMT
-3. KH yêu cầu: Hỗ trợ KH kết nối lại app để xem hiệu suất</t>
+          <t>1. KH chưa liên hệ với CN ( do thay đổi nhân sự nên chưa biết liên hệ ai)
+2. HT NLMT, điện nạp vào Ắc quy kém so với bình thường
+3. KH cần KT đến hỗ trợ kiểm tra và xử lý sớm</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-04-30 08:15:00</t>
+          <t>2026-05-07 15:10:00</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4049,17 +4053,17 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Trịnh Xuân Bảo</t>
+          <t>Đào Minh Đức</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>471569</t>
+          <t>290593</t>
         </is>
       </c>
       <c r="Y26" s="2">
@@ -4087,12 +4091,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4107,37 +4111,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Acquy lưu trữ</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QNH_1258034</t>
+          <t>KHDN_TT.GPTH_HCM_1619322</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Mạc Văn Xuyên</t>
+          <t>CÔNG TY TNHH BA DƯƠNG</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0913262405</t>
+          <t>0775252411</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Tổ 4, khu 4D, Phường Hồng Hải, Thành phố Hạ Long, Tỉnh Quảng Ninh</t>
+          <t>phú lợi</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4147,7 +4156,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4162,14 +4171,14 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ với CN ( do thay đổi nhân sự nên chưa biết liên hệ ai)
-2. HT NLMT, điện nạp vào Ắc quy kém so với bình thường
-3. KH cần KT đến hỗ trợ kiểm tra và xử lý sớm</t>
+          <t>Đã báo chi nhánh( ko nhớ tên )
+Kh bảo mỗi NLMT hỏng ,
+yêu cầu kt qua ktra</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4179,7 +4188,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-05-07 15:10:00</t>
+          <t>2026-05-04 08:15:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4194,12 +4203,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Đào Minh Đức</t>
+          <t>Trần Doãn Lượng</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>290593</t>
+          <t>455101</t>
         </is>
       </c>
       <c r="Y27" s="2">
@@ -4227,12 +4236,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4252,37 +4261,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_HCM_1619322</t>
+          <t>KHCN_TT.GPTH_NAN_1684316</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BA DƯƠNG</t>
+          <t>Phạm Minh Dũng</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0775252411</t>
+          <t>0987556799</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>phú lợi</t>
+          <t>Số 35 Đường Phan Huy Ích</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4292,29 +4296,28 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Đã báo chi nhánh( ko nhớ tên )
-Kh bảo mỗi NLMT hỏng ,
-yêu cầu kt qua ktra</t>
+          <t>kh gọi chi nhánh nhưng không ai phản hồi lại
+kh yêu cầu kt gọi lại cho kh để báo đúng ngày lắp đặt</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4324,7 +4327,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-04-29 09:00:00</t>
+          <t>2026-05-04 17:30:00</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4334,17 +4337,17 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Trần Doãn Lượng</t>
+          <t>Nguyễn Văn Tân</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>455101</t>
+          <t>460719</t>
         </is>
       </c>
       <c r="Y28" s="2">
@@ -4360,24 +4363,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HUE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4392,12 +4395,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1684316</t>
+          <t>KHCN_PINNLMT_TTH_0288329</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4405,6 +4408,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -4412,17 +4420,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Phạm Minh Dũng</t>
+          <t>Nguyễn Minh Nhật</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0987556799</t>
+          <t>0905750036</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Số 35 Đường Phan Huy Ích</t>
+          <t>150/2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4437,23 +4445,24 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Inverter không hoạt động</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>kh gọi chi nhánh nhưng không ai phản hồi lại
-kh yêu cầu kt gọi lại cho kh để báo đúng ngày lắp đặt</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: Ivt có vấn đề báo đỏ
+3. KH yêu cầu: Qua kiểm tra khắc phục</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4463,7 +4472,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-04-29 09:00:00</t>
+          <t>2026-05-07 09:00:00</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4473,17 +4482,17 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Tân</t>
+          <t>Lê Văn Đồng</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>460719</t>
+          <t>422252</t>
         </is>
       </c>
       <c r="Y29" s="2">
@@ -4499,24 +4508,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HUE</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4531,12 +4540,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_TTH_0288329</t>
+          <t>150501/GPTH/HĐMBLĐ-2025/CNCTTNH-STRIDESOLAR</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4544,11 +4553,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -4556,22 +4560,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Nhật</t>
+          <t>Hồ Văn Lùng</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0905750036</t>
+          <t>0397727564</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>150/2</t>
+          <t>Tổ 8, Ấp Phước An, Xã Cầu Khởi, Tây Ninh</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4586,155 +4590,15 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Inverter không hoạt động</t>
+          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: Ivt có vấn đề báo đỏ
-3. KH yêu cầu: Qua kiểm tra khắc phục</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>2026-04-28 08:00:00</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-05-07 09:00:00</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Lê Văn Đồng</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>422252</t>
-        </is>
-      </c>
-      <c r="Y30" s="2">
-        <v>46140</v>
-      </c>
-      <c r="Z30">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>150501/GPTH/HĐMBLĐ-2025/CNCTTNH-STRIDESOLAR</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Hồ Văn Lùng</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0397727564</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Tổ 8, Ấp Phước An, Xã Cầu Khởi, Tây Ninh</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Cài đặt hệ thống (APP/Mật khẩu)</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
         <is>
           <t>1. Khách hàng cần hỗ trợ cài lại app monitor do đã đổi điện thoại mới
 2. Địa chỉ :-địa chỉ mới : Tổ 8, Ấp Phước An, Xã Cầu Khởi, Tây Ninh
@@ -4742,14 +4606,159 @@
 3. KH cần hỗ trợ sớm để có thể sử dụng</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-04-24 14:07:00</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-04-30 08:45:00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nguyễn Đặng Vĩnh Phát</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>455619</t>
+        </is>
+      </c>
+      <c r="Y30" s="2">
+        <v>46136</v>
+      </c>
+      <c r="Z30">
+        <v>5</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HBH_1559029</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Phạm Công Chính</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0985511119</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Thôn 6</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Chưa báo chi nhánh
+Lỗi cảnh báo ác quy hiệu suất ko đạt 
+Yêu cầu kt qua ktra</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-04-24 14:07:00</t>
+          <t>2026-04-28 08:00:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-04-30 08:45:00</t>
+          <t>2026-05-13 11:30:00</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4759,38 +4768,38 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Nguyễn Đặng Vĩnh Phát</t>
+          <t>Lê Duy Tuấn</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>455619</t>
+          <t>293859</t>
         </is>
       </c>
       <c r="Y31" s="2">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4811,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4822,7 +4831,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HBH_1559029</t>
+          <t>KHCN_TT.GPTH_HDG_1472655</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4842,17 +4851,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Phạm Công Chính</t>
+          <t>Nguyễn Hữu Chỉnh</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0985511119</t>
+          <t>0976024133</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Thôn 6</t>
+          <t>Tòng Hóa</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4882,19 +4891,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Chưa báo chi nhánh
-Lỗi cảnh báo ác quy hiệu suất ko đạt 
-Yêu cầu kt qua ktra</t>
+          <t>kh chưa báo chi nhánh
+Hệ thống nlmt chưa đạt đủ công suất pin lưu trữ chưa đạt sẳn lượng
+yêu cầu kt qua ktra</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-04-28 08:00:00</t>
+          <t>2026-04-24 09:02:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-05-13 11:30:00</t>
+          <t>2026-05-04 17:15:00</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4909,19 +4918,19 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Lê Duy Tuấn</t>
+          <t>Nguyễn Văn Thêm</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>293859</t>
+          <t>285987</t>
         </is>
       </c>
       <c r="Y32" s="2">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="Z32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4942,12 +4951,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4967,7 +4976,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HDG_1472655</t>
+          <t>KHCN_TT.GPTH_DNG_1619560</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4987,22 +4996,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Chỉnh</t>
+          <t>Lê Thị Mai Anh</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0976024133</t>
+          <t>0935045067</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Tòng Hóa</t>
+          <t>Lô V5.B06.01 Khu Đô Thị FPT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5027,19 +5036,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>kh chưa báo chi nhánh
-Hệ thống nlmt chưa đạt đủ công suất pin lưu trữ chưa đạt sẳn lượng
-yêu cầu kt qua ktra</t>
+          <t>CN 0971759579 báo sự cố hộ KH
+1.	Kh phản ánh: KH đang nghi dây dc bị hỏng làm ảnh hưởng tới hiệu suất và cũng thấy hiệu suất giảm.
+2.	KH yêu cầu: kiểm tra gấp và khắc phục tình trạng này cho KH</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-04-24 09:02:00</t>
+          <t>2026-04-23 15:09:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-05-04 17:15:00</t>
+          <t>2026-04-24 15:09:00</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5049,24 +5058,24 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thêm</t>
+          <t>Nguyễn Công Triệu</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>285987</t>
+          <t>433380</t>
         </is>
       </c>
       <c r="Y33" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -5087,12 +5096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5112,7 +5121,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1619560</t>
+          <t>KHCN_TT.GPTH_DNI_1662751</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5122,7 +5131,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5132,22 +5141,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Lê Thị Mai Anh</t>
+          <t>Trần Hồng Phúc</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0935045067</t>
+          <t>0918977063</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Lô V5.B06.01 Khu Đô Thị FPT</t>
+          <t>A1/13C, Khu phố 1</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5162,34 +5171,33 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>CN 0971759579 báo sự cố hộ KH
-1.	Kh phản ánh: KH đang nghi dây dc bị hỏng làm ảnh hưởng tới hiệu suất và cũng thấy hiệu suất giảm.
-2.	KH yêu cầu: kiểm tra gấp và khắc phục tình trạng này cho KH</t>
+          <t>KH cần mẫu bổ sung số 01 để báo với điện lực gia đình đang sử dụng NLMT theo nghị định 13 
+Yêu cầu KT liên hệ lại KH gấp</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-04-23 15:09:00</t>
+          <t>2026-04-23 09:57:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-04-24 15:09:00</t>
+          <t>2026-04-24 09:57:00</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -5199,12 +5207,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Nguyễn Công Triệu</t>
+          <t>Lê Anh Tuấn</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>433380</t>
+          <t>285580</t>
         </is>
       </c>
       <c r="Y34" s="2">
@@ -5232,12 +5240,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5257,7 +5265,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNI_1662751</t>
+          <t>KHCN_TT.GPTH_HTH_1656621</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5267,7 +5275,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5277,17 +5285,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Trần Hồng Phúc</t>
+          <t>Nguyễn Xuân Tuấn</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0918977063</t>
+          <t>0984618861</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>A1/13C, Khu phố 1</t>
+          <t>TDP 7</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5307,55 +5315,56 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>KH cần mẫu bổ sung số 01 để báo với điện lực gia đình đang sử dụng NLMT theo nghị định 13 
-Yêu cầu KT liên hệ lại KH gấp</t>
+          <t>1. KH chưa báo cn
+2. KH phản ánh : Hệ 100kw và giờ chạy được chỉ hơn nửa công suất, chỉ có được 53kw đổ về. Trong khi nắng gắt ở Hà Tĩnh, trước lúc mới lắp đặt cũng phải 80 90kW. Sự cố từ trước kiểm tra thiết bị vẫn bình thường mà giờ sản lượng thấy ko đạt.
+3. KH yêu cầu: Qua kiểm tra, khống chế sản lượng, cho dải chạy ổn định cho KH.</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-04-23 09:57:00</t>
+          <t>2026-04-22 13:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-04-24 09:57:00</t>
+          <t>2026-05-01 08:15:00</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Lê Anh Tuấn</t>
+          <t>Trịnh Xuân Bảo</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>285580</t>
+          <t>471569</t>
         </is>
       </c>
       <c r="Y35" s="2">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -5381,7 +5390,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5401,7 +5410,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HTH_1656621</t>
+          <t>KHCN_TT.GPTH_NAN_1685809</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5411,7 +5420,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5421,17 +5430,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nguyễn Xuân Tuấn</t>
+          <t>Phạm Mạnh Tình</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0984618861</t>
+          <t>0981707789</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>TDP 7</t>
+          <t>Xóm Tân Nghĩa Nghi Xuân</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5446,34 +5455,34 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh : Hệ 100kw và giờ chạy được chỉ hơn nửa công suất, chỉ có được 53kw đổ về. Trong khi nắng gắt ở Hà Tĩnh, trước lúc mới lắp đặt cũng phải 80 90kW. Sự cố từ trước kiểm tra thiết bị vẫn bình thường mà giờ sản lượng thấy ko đạt.
-3. KH yêu cầu: Qua kiểm tra, khống chế sản lượng, cho dải chạy ổn định cho KH.</t>
+          <t>1. KH đã liên hệ với NV tại CN tuy nhiên NV KNM
+2. KH thông tin CN đã hẹn đến thi công lắp đặt HT NLMT cho KH từ ngày 21, sau đó hẹn ngày 22 nhưng không có thông tin, KH đã liên hệ CN nhiều lần nhưng KTC, KH đã ký HĐ và đặt cọc để lắp đặt hệ thống NLMT, KH KHL và p/á nếu không lắp đặt được, KH có thể hủy HĐ và yêu cầu hoàn tiền
+3. KH cần CN phản hồi sớm và hỗ trợ lắp đặt cho KH</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-04-22 13:30:00</t>
+          <t>2026-04-22 08:00:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-05-01 08:15:00</t>
+          <t>2026-04-30 14:40:00</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5483,17 +5492,17 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Trịnh Xuân Bảo</t>
+          <t>Trần Thanh Tùng</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>471569</t>
+          <t>416998</t>
         </is>
       </c>
       <c r="Y36" s="2">
@@ -5509,12 +5518,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5535,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5546,7 +5555,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1685809</t>
+          <t>KHCN_TT.GPTH_HTH_1613358</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5556,7 +5565,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5566,17 +5575,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Phạm Mạnh Tình</t>
+          <t>Nguyễn Thanh Sơn</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0981707789</t>
+          <t>0986988032</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Xóm Tân Nghĩa Nghi Xuân</t>
+          <t>Xóm 1</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5586,170 +5595,25 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai</t>
+          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
-        <is>
-          <t>1. KH đã liên hệ với NV tại CN tuy nhiên NV KNM
-2. KH thông tin CN đã hẹn đến thi công lắp đặt HT NLMT cho KH từ ngày 21, sau đó hẹn ngày 22 nhưng không có thông tin, KH đã liên hệ CN nhiều lần nhưng KTC, KH đã ký HĐ và đặt cọc để lắp đặt hệ thống NLMT, KH KHL và p/á nếu không lắp đặt được, KH có thể hủy HĐ và yêu cầu hoàn tiền
-3. KH cần CN phản hồi sớm và hỗ trợ lắp đặt cho KH</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2026-04-22 08:00:00</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-04-30 14:40:00</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Trần Thanh Tùng</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>416998</t>
-        </is>
-      </c>
-      <c r="Y37" s="2">
-        <v>46134</v>
-      </c>
-      <c r="Z37">
-        <v>7</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Sonln15</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>HTH</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HTH_1613358</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Nguyễn Thanh Sơn</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0986988032</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Xóm 1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
         <is>
           <t>1. KH đã báo CN 
 2. KH đã báo qua: ntin qua zalo CN Hà Tĩnh 
@@ -5757,145 +5621,145 @@
 4. KH yêu cầu: Qua kiểm tra, hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>2026-04-16 16:42:00</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>2026-05-04 18:15:00</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Trần Huy Hoàng</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>062253</t>
         </is>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y37" s="2">
         <v>46128</v>
       </c>
-      <c r="Z38">
+      <c r="Z37">
         <v>13</v>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Vật tư NLMT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_PTO_1641267</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Dương Đức Vinh</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0979291583</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Khu Hưng Long</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Ý thức trách nhiệm</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>KH (work@namdd.dev) gửi mail phản ánh các vấn đề: 
 1.	Tiền dây dẫn thừa: Đề nghị Viettel Phú Thọ thực hiện việc bồi hoàn lại tiền cho phần dây điện thừa do thi công sai lệch ban đầu.
@@ -5905,14 +5769,159 @@
 6.	Thao tác điều khiển thiết bị từ xa không báo trước: Giải trình về việc tài khoản viettelsolar.phutho@gmail.com tự ý "Xóa dữ liệu báo động lỗi hồ quang" và "Vô hiệu hóa báo động chống sét" ngày 12/04/2026 mà không thông báo hay nắm rõ mục đích xóa.</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:29:00</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:45:00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nguyễn Tiến Đức</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>277285</t>
+        </is>
+      </c>
+      <c r="Y38" s="2">
+        <v>46128</v>
+      </c>
+      <c r="Z38">
+        <v>13</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Tấm pin NLMT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DTP_1365872</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Nhà Nghỉ Cali</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0938500248</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Trần Quốc Toản,,Thị xã Hồng Ngự</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>- KH chưa báo chi nhánh 
+- Tấm pin nlmt cần hỗ trợ 2 cái. Hôm nọ kt lắp sai tấm pin nên bị đọng nước, phần trên thì đúng phần dưới thì sai. Có 2 cái sửa  thì 1 cái dùng được  1 cái không
+- KH cần hỗ trợ sớm</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-04-16 08:29:00</t>
+          <t>2026-04-14 16:24:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-04-30 18:20:00</t>
+          <t>2026-04-20 14:50:00</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5922,24 +5931,24 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Nguyễn Tiến Đức</t>
+          <t>Cao Phước Bạn</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>277285</t>
+          <t>079714</t>
         </is>
       </c>
       <c r="Y39" s="2">
-        <v>46128</v>
+        <v>46126</v>
       </c>
       <c r="Z39">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5960,12 +5969,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HUE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5980,12 +5989,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tấm pin NLMT</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DTP_1365872</t>
+          <t>KHCN_TT.GPTH_HUE_1672019</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5995,7 +6004,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6005,17 +6014,17 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Nhà Nghỉ Cali</t>
+          <t>Nguyễn Thị Thu</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0938500248</t>
+          <t>0357375875</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Trần Quốc Toản,,Thị xã Hồng Ngự</t>
+          <t>Thôn hà úc 1</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6040,155 +6049,10 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
-        <is>
-          <t>- KH chưa báo chi nhánh 
-- Tấm pin nlmt cần hỗ trợ 2 cái. Hôm nọ kt lắp sai tấm pin nên bị đọng nước, phần trên thì đúng phần dưới thì sai. Có 2 cái sửa  thì 1 cái dùng được  1 cái không
-- KH cần hỗ trợ sớm</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>2026-04-14 16:24:00</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-04-20 14:50:00</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Cao Phước Bạn</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>079714</t>
-        </is>
-      </c>
-      <c r="Y40" s="2">
-        <v>46126</v>
-      </c>
-      <c r="Z40">
-        <v>15</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>HUE</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HUE_1672019</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Thu</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0357375875</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Thôn hà úc 1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
         <is>
           <t>1. KH đã báo cn: a Hoàng Đình Nhâm
 2. KH phản ánh: KH đã báo cn nhiều lần nhưng chưa được hỗ trợ. Hệ của KH 6 cục pin nhưng chỉ thấy xả 3 cục và chỉ xài được 1 lúc là nó hết.
@@ -6196,14 +6060,158 @@
 ***SĐT phản ánh và liên hệ: 0706455040</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:30:00</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:30:00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Phạm Công Trang</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>066154</t>
+        </is>
+      </c>
+      <c r="Y40" s="2">
+        <v>46126</v>
+      </c>
+      <c r="Z40">
+        <v>15</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_TNN_1671803</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Vũ Hồng Cường</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0981049183</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>tổ dân phố tướng quân</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>- Chưa báo cho chi nhánh 
+- Lắp điện nlmt trên hệ thống hiển thị sai: hệ thống màn hình từ nhà mà nuôi ra điện ngoài, hướng dẫn tải app để theo dõi điện nlmt</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-04-14 13:30:00</t>
+          <t>2026-04-14 10:34:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-05-02 22:30:00</t>
+          <t>2026-04-30 10:57:00</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6213,17 +6221,17 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Phạm Công Trang</t>
+          <t>Trần Xuân Kương</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>066154</t>
+          <t>289759</t>
         </is>
       </c>
       <c r="Y41" s="2">
@@ -6251,12 +6259,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6271,12 +6279,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNN_1671803</t>
+          <t>KHCN_TT.GPTH_BTE_1573123</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6296,17 +6304,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Vũ Hồng Cường</t>
+          <t>Doanh Nghiệp Tư Nhân Thương Mại Sản Xuất Nước Mắm Ngọc Duy</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0981049183</t>
+          <t>0983043267</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>tổ dân phố tướng quân</t>
+          <t>Lô E, cụm công nghiệp thị trấn An Đức,Xã An Đức,Huyện Ba Tri,Tỉnh Bến Tre</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6316,7 +6324,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6326,7 +6334,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6336,18 +6344,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>- Chưa báo cho chi nhánh 
-- Lắp điện nlmt trên hệ thống hiển thị sai: hệ thống màn hình từ nhà mà nuôi ra điện ngoài, hướng dẫn tải app để theo dõi điện nlmt</t>
+          <t>- KH báo qua chị Phượng (CN) 
+- KH đang gặp sự cố ắc quy, 2 khối ắc quy 1 khối xả 1 khối không
+- Kh yêu cầu xử lý sớm</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-04-14 10:34:00</t>
+          <t>2026-04-13 11:04:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-04-30 10:57:00</t>
+          <t>2026-05-05 15:00:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6357,24 +6366,24 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Trần Xuân Kương</t>
+          <t>Nguyễn Duy Khôi</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>289759</t>
+          <t>449301</t>
         </is>
       </c>
       <c r="Y42" s="2">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="Z42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6395,12 +6404,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6415,12 +6424,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Acquy lưu trữ</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BTE_1573123</t>
+          <t>KHCN_TT.GPTH_HNM_1472269</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6430,7 +6439,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6440,17 +6449,17 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Doanh Nghiệp Tư Nhân Thương Mại Sản Xuất Nước Mắm Ngọc Duy</t>
+          <t>Nguyễn Mạnh Cường</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0983043267</t>
+          <t>0886848999</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Lô E, cụm công nghiệp thị trấn An Đức,Xã An Đức,Huyện Ba Tri,Tỉnh Bến Tre</t>
+          <t>Thôn Mỹ Xuyên,Xã Nhân Mỹ,Huyện Lý Nhân,Tỉnh Hà Nam</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -6475,24 +6484,24 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>- KH báo qua chị Phượng (CN) 
-- KH đang gặp sự cố ắc quy, 2 khối ắc quy 1 khối xả 1 khối không
-- Kh yêu cầu xử lý sớm</t>
+          <t>- Anh báo cho quản lý cho nhân viên xuống không giải quyết đươc nên mới gọi lên tổng đài  
+- Hỗ trợ  kết nối điện nlmt với app để theo dõi thông số. Trước mạng wifi bị hỏng  nên anh phải cài lại
+- Hỗ trợ nhanh giúp anh.</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-04-13 11:04:00</t>
+          <t>2026-04-13 16:37:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-05-05 15:00:00</t>
+          <t>2026-05-08 15:50:00</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6507,12 +6516,12 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Nguyễn Duy Khôi</t>
+          <t>Trần Văn Thành</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>449301</t>
+          <t>815150</t>
         </is>
       </c>
       <c r="Y43" s="2">
@@ -6540,12 +6549,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6560,12 +6569,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNM_1472269</t>
+          <t>KHCN_TT.GPTH_AGG_1641909</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6575,7 +6584,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6585,22 +6594,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Nguyễn Mạnh Cường</t>
+          <t>Nguyễn Ngọc Thanh Phương</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0886848999</t>
+          <t>0962310365</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Thôn Mỹ Xuyên,Xã Nhân Mỹ,Huyện Lý Nhân,Tỉnh Hà Nam</t>
+          <t>ấp Vĩnh Hưng</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6620,24 +6629,23 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>- Anh báo cho quản lý cho nhân viên xuống không giải quyết đươc nên mới gọi lên tổng đài  
-- Hỗ trợ  kết nối điện nlmt với app để theo dõi thông số. Trước mạng wifi bị hỏng  nên anh phải cài lại
-- Hỗ trợ nhanh giúp anh.</t>
+          <t>Trong thời gian vừa qua tôi quan sát thấy inverter hybrid có hiện tượng giảm huy động công suất DC từ tấm pin, dù trời vẫn nắng tốt và ổn định, bình lưu trữ vẫn chưa đầy và vẫn phải rút điện từ bình lưu trữ để cấp điện cho phụ tải AC. Mỗi lần hiện tượng này xảy ra kéo dài khoảng 15 - 30 phút vào thời điểm ngẫu nhiên trong ngày.
+VCC hỗ trợ để tìm ra được nguyên nhân và giải pháp cho vấn đề này.</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-04-13 16:37:00</t>
+          <t>2026-04-13 11:07:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-05-08 15:50:00</t>
+          <t>2026-04-14 11:07:00</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6647,17 +6655,17 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Trần Văn Thành</t>
+          <t>Đinh Quốc Việt</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>815150</t>
+          <t>408455</t>
         </is>
       </c>
       <c r="Y44" s="2">
@@ -6685,12 +6693,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6705,12 +6713,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_AGG_1641909</t>
+          <t>KHCN_TT.GPTH_NTN_1555023</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6730,22 +6738,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nguyễn Ngọc Thanh Phương</t>
+          <t>Lê Thị Thu Minh</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0962310365</t>
+          <t>0907563460</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ấp Vĩnh Hưng</t>
+          <t>Lô 63 Đường D2, Khu Đô Thị TT Đức Tài , Bình Thuận,Xã Cà Ná,Huyện Thuận Nam,Tỉnh Ninh Thuận</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6760,159 +6768,15 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
-        <is>
-          <t>Trong thời gian vừa qua tôi quan sát thấy inverter hybrid có hiện tượng giảm huy động công suất DC từ tấm pin, dù trời vẫn nắng tốt và ổn định, bình lưu trữ vẫn chưa đầy và vẫn phải rút điện từ bình lưu trữ để cấp điện cho phụ tải AC. Mỗi lần hiện tượng này xảy ra kéo dài khoảng 15 - 30 phút vào thời điểm ngẫu nhiên trong ngày.
-VCC hỗ trợ để tìm ra được nguyên nhân và giải pháp cho vấn đề này.</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>2026-04-13 11:07:00</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-04-14 11:07:00</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Đinh Quốc Việt</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>408455</t>
-        </is>
-      </c>
-      <c r="Y45" s="2">
-        <v>46125</v>
-      </c>
-      <c r="Z45">
-        <v>16</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NTN_1555023</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Lê Thị Thu Minh</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0907563460</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Lô 63 Đường D2, Khu Đô Thị TT Đức Tài , Bình Thuận,Xã Cà Ná,Huyện Thuận Nam,Tỉnh Ninh Thuận</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH đang sd NLMT nhưng hiện tại thiết bị ko xả điện
@@ -6920,14 +6784,159 @@
 ***địa chỉ lắp đặt: kilo 63, khu đô thị đức tài, xã hoài đức, tỉnh lâm đồng.</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-04-13 08:00:00</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-05-13 08:23:00</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Võ Văn Hoàng</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>417608</t>
+        </is>
+      </c>
+      <c r="Y45" s="2">
+        <v>46125</v>
+      </c>
+      <c r="Z45">
+        <v>16</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_QNH_1663601</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Đào Văn Đông</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0989420029</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>120 lý tự trọng (hoà lạc)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: Khi mất điện và khi mới có điện thì giật giật mất điện rồi lại có 3,4 lần trong khi pin 80% đầy điện.  Và hiện tượng ko an toàn bởi vì nhà sử dụng thang máy,  mà 3 4 lần như thế rất sợ. Thỉnh thoảng, khi mất điện xảy ra tình trạng này, giật giật mấy phát rồi có lưới pin.
+3. KH yêu cầu: Kiểm tra thiết bị, điện ở trong nhà và khắc phục tình trạng này.</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-04-13 08:00:00</t>
+          <t>2026-04-10 08:00:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-05-13 08:23:00</t>
+          <t>2026-04-30 13:10:00</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6937,24 +6946,24 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Võ Văn Hoàng</t>
+          <t>Vũ Duy Tùng</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>417608</t>
+          <t>455203</t>
         </is>
       </c>
       <c r="Y46" s="2">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="Z46">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6980,7 +6989,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7000,7 +7009,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QNH_1663601</t>
+          <t>KHCN_TT.GPTH_NAN_1684187</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7010,7 +7019,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -7020,17 +7029,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Đào Văn Đông</t>
+          <t>Cao Xuân Cường</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0989420029</t>
+          <t>0967095136</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>120 lý tự trọng (hoà lạc)</t>
+          <t>Xóm 9</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7040,29 +7049,28 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: Khi mất điện và khi mới có điện thì giật giật mất điện rồi lại có 3,4 lần trong khi pin 80% đầy điện.  Và hiện tượng ko an toàn bởi vì nhà sử dụng thang máy,  mà 3 4 lần như thế rất sợ. Thỉnh thoảng, khi mất điện xảy ra tình trạng này, giật giật mấy phát rồi có lưới pin.
-3. KH yêu cầu: Kiểm tra thiết bị, điện ở trong nhà và khắc phục tình trạng này.</t>
+          <t>- Mới gọi lên tổng đài 
+- Anh đã ký hd. Khi nào có thể lắp đặt nlmt cho anh</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -7072,7 +7080,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2026-04-30 13:10:00</t>
+          <t>2026-04-13 09:00:00</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -7082,17 +7090,17 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Vũ Duy Tùng</t>
+          <t>Bùi Đức Hào</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>455203</t>
+          <t>024067</t>
         </is>
       </c>
       <c r="Y47" s="2">
@@ -7108,12 +7116,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>Sonln15</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7133,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7145,7 +7153,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1684187</t>
+          <t>KHDN_TT.GPTH_QNH_1414133</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7155,42 +7163,42 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Cao Xuân Cường</t>
+          <t>Công Ty Cp Tư Vấn Xây Dựng Quảng Yên Hai Sáu Tám</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0967095136</t>
+          <t>0975106068</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Xóm 9</t>
+          <t>số 3, ngõ 59, đường Quỳnh Lâu</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Life Care</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Trong bán</t>
+          <t>Sau bán</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7200,23 +7208,24 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>- Mới gọi lên tổng đài 
-- Anh đã ký hd. Khi nào có thể lắp đặt nlmt cho anh</t>
+          <t>1. KH đã liên hệ CN (A Toàn,  A Hùng) tuy nhiên CN chưa hỗ trợ
+2. Theo các quy định mới thì điện áp mái phải có thông báo với điện lực, trước đó tư vấn bên công ty có nói là công ty sẽ hỗ trợ nội dung này 
+3. KH cần CN hỗ trợ hướng dẫn để hoàn thiện thủ tục, tranh sau này bị phạt</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-04-10 08:00:00</t>
+          <t>2026-04-28 15:52:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2026-04-13 09:00:00</t>
+          <t>2026-05-06 14:10:00</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7226,24 +7235,24 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bùi Đức Hào</t>
+          <t>Trần Cảnh Toàn</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>024067</t>
+          <t>132051</t>
         </is>
       </c>
       <c r="Y48" s="2">
-        <v>46122</v>
+        <v>46140</v>
       </c>
       <c r="Z48">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -7252,12 +7261,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7278,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7284,12 +7293,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_QNH_1414133</t>
+          <t>KHCN_TT.GPTH_HDG_1610342</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7304,32 +7313,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Công Ty Cp Tư Vấn Xây Dựng Quảng Yên Hai Sáu Tám</t>
+          <t>Anh Quân</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0975106068</t>
+          <t>0983448280</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>số 3, ngõ 59, đường Quỳnh Lâu</t>
+          <t>phường chu văn an</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Life Care</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -7339,56 +7348,55 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN (A Toàn,  A Hùng) tuy nhiên CN chưa hỗ trợ
-2. Theo các quy định mới thì điện áp mái phải có thông báo với điện lực, trước đó tư vấn bên công ty có nói là công ty sẽ hỗ trợ nội dung này 
-3. KH cần CN hỗ trợ hướng dẫn để hoàn thiện thủ tục, tranh sau này bị phạt</t>
+          <t>Mất 1 string điện không vào ắc quy. Không đủ cung cấp cho tải nhà dùng . Anh cần đến kiêm tra trong ngày hôm nay.
+**Địa chỉ lắp đặt: số nhà 300, kim tân, xã đoài phương, thành phố hà nội.</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-04-28 15:52:00</t>
+          <t>2026-04-06 16:23:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-04-29 15:52:00</t>
+          <t>2026-04-08 17:30:00</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Trần Cảnh Toàn</t>
+          <t>Bùi Văn Hoàn</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>132051</t>
+          <t>046275</t>
         </is>
       </c>
       <c r="Y49" s="2">
-        <v>46140</v>
+        <v>46118</v>
       </c>
       <c r="Z49">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -7414,7 +7422,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7434,37 +7442,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1598580</t>
+          <t>140501-KD/HĐMBLĐ-2024/HONGANH-CNCTVPC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Gold</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Hồ Văn Khương</t>
+          <t>CÔNG TY TNHH DỊCH VỤ THƯƠNG MẠI VẬN TẢI HỒNG ÁNH</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0941663636</t>
+          <t>0987221002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Xóm 8</t>
+          <t>Số nhà 85 thôn 1</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -7474,7 +7477,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -7489,294 +7492,10 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
-        <is>
-          <t>1. Khách hàng không báo qua chi nhánh 
-2. Khách chỉ báo qua hotline 
-3. Điện nllmt 2 3 hôm nay hiệu số rất thấp.Giờ cao điểm trước đây thu được 5 6 kí giờ chỉ còn 2 3 kí</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>2026-04-08 08:00:00</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-04-29 19:55:00</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Võ Trọng Đức</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>293804</t>
-        </is>
-      </c>
-      <c r="Y50" s="2">
-        <v>46120</v>
-      </c>
-      <c r="Z50">
-        <v>21</v>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HDG_1610342</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Anh Quân</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>0983448280</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>phường chu văn an</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Mất 1 string điện không vào ắc quy. Không đủ cung cấp cho tải nhà dùng . Anh cần đến kiêm tra trong ngày hôm nay.
-**Địa chỉ lắp đặt: số nhà 300, kim tân, xã đoài phương, thành phố hà nội.</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>2026-04-06 16:23:00</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-04-08 17:30:00</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Bùi Văn Hoàn</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>046275</t>
-        </is>
-      </c>
-      <c r="Y51" s="2">
-        <v>46118</v>
-      </c>
-      <c r="Z51">
-        <v>23</v>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>140501-KD/HĐMBLĐ-2024/HONGANH-CNCTVPC</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THƯƠNG MẠI VẬN TẢI HỒNG ÁNH</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>0987221002</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Số nhà 85 thôn 1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: a Nghĩa
 2. KH phản ánh: bị hỏng ắc quy
@@ -7784,14 +7503,299 @@
 ***SĐT phản ánh và liên hệ: 0964109909</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026-04-06 08:00:00</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-05-05 17:30:00</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Phạm Văn Nghĩa</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>023020</t>
+        </is>
+      </c>
+      <c r="Y50" s="2">
+        <v>46118</v>
+      </c>
+      <c r="Z50">
+        <v>23</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>truongdv17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>KHCN_NLMT_TNN_0200299</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Đinh Văn Chỉnh</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0868632926</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Phú Cường,</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>KH dã báo CN
+KH đang sử dụng NLMT, hiện tại KH ko thấy phát sinh điện, bên điện lực báo ko thấy công tơ lên
+YC KT qua kiểm tra và xử lý cho KH</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2026-04-03 08:00:00</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-05-02 16:44:00</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Trần Xuân Kương</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>289759</t>
+        </is>
+      </c>
+      <c r="Y51" s="2">
+        <v>46115</v>
+      </c>
+      <c r="Z51">
+        <v>26</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BNH_1634096</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Ân</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0988386838</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Xã Xuân Cẩm, Tỉnh Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1. KH chưa báo cn
+2. KH phản ánh: nhà KH có thêm ats của máy nổ, về nguyên tắc máy điện phải chạy nlmt, khi nlmt hết thì chạy máy nổ. Hiện tại thì khi mất điện ko chạy sang nlmt, và khi nlmt hết rồi vẫn ko thấy chạy máy nổ. 
+3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
+        </is>
+      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>2026-04-06 08:00:00</t>
+          <t>2026-03-30 15:55:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-05-05 17:30:00</t>
+          <t>2026-04-30 10:50:00</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7801,38 +7805,38 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Phạm Văn Nghĩa</t>
+          <t>Phạm Văn Huy</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>023020</t>
+          <t>408869</t>
         </is>
       </c>
       <c r="Y52" s="2">
-        <v>46118</v>
+        <v>46111</v>
       </c>
       <c r="Z52">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>P.Triển khai</t>
+          <t>VHKT</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>VHKT</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7848,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7864,7 +7868,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KHCN_NLMT_TNN_0200299</t>
+          <t>KHCN_PINNLMT_NAN_0334667</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7879,27 +7883,27 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Đinh Văn Chỉnh</t>
+          <t>Lê Trung An</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0868632926</t>
+          <t>0865878212</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Phú Cường,</t>
+          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -7909,29 +7913,28 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>KH dã báo CN
-KH đang sử dụng NLMT, hiện tại KH ko thấy phát sinh điện, bên điện lực báo ko thấy công tơ lên
-YC KT qua kiểm tra và xử lý cho KH</t>
+          <t>1. KH đã báo cn
+2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2026-04-03 08:00:00</t>
+          <t>2026-03-30 11:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-05-02 16:44:00</t>
+          <t>2026-04-10 19:10:00</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7941,24 +7944,24 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Trần Xuân Kương</t>
+          <t>Nguyễn Minh Linh</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>289759</t>
+          <t>285776</t>
         </is>
       </c>
       <c r="Y53" s="2">
-        <v>46115</v>
+        <v>46111</v>
       </c>
       <c r="Z53">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -7984,7 +7987,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8004,7 +8007,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1634096</t>
+          <t>KHCN_TT.GPTH_NAN_1574225</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -8014,7 +8017,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -8024,17 +8027,17 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nguyễn Ngọc Ân</t>
+          <t>Nguyên Văn Tú</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0988386838</t>
+          <t>0868081789</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Xã Xuân Cẩm, Tỉnh Bắc Ninh</t>
+          <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -8044,7 +8047,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -8064,19 +8067,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1. KH chưa báo cn
-2. KH phản ánh: nhà KH có thêm ats của máy nổ, về nguyên tắc máy điện phải chạy nlmt, khi nlmt hết thì chạy máy nổ. Hiện tại thì khi mất điện ko chạy sang nlmt, và khi nlmt hết rồi vẫn ko thấy chạy máy nổ. 
-3. KH yêu cầu: Kiểm tra trước nội dung về ats của máy nổ và nlmt. Và khắc phục tình trạng ko sử dụng này của KH.</t>
+          <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
+2. KH phản ánh NLMT bị hỏng không sử dụng được
+3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2026-03-30 15:55:00</t>
+          <t>2026-03-30 08:00:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-04-30 10:50:00</t>
+          <t>2026-05-04 17:00:00</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -8086,17 +8089,17 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Phạm Văn Huy</t>
+          <t>Nguyễn Văn Tân</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>408869</t>
+          <t>460719</t>
         </is>
       </c>
       <c r="Y54" s="2">
@@ -8124,12 +8127,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8144,12 +8147,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KHCN_PINNLMT_NAN_0334667</t>
+          <t>KHCN_TT.GPTH_QNM_1510130</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8157,6 +8160,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -8164,22 +8172,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Lê Trung An</t>
+          <t>Lê Phước Danh</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0865878212</t>
+          <t>0355557906</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>xóm 9, Xã Đại Sơn, Huyện Đô Lương, Tỉnh Nghệ An</t>
+          <t>Thôn Pà Dá,Xã Cà Dy,Huyện Nam Giang,Tỉnh Quảng Nam</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8194,28 +8202,27 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1. KH đã báo cn
-2. KH yêu cầu: Muốn hiện thông số trên app từ ivt qua điện lưới với điện dùng cho GĐ để báo điện lực.</t>
+          <t>Lỗi pin ko lưu</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2026-03-30 11:30:00</t>
+          <t>2026-04-01 10:43:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-04-10 19:10:00</t>
+          <t>2026-04-18 10:52:00</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -8230,19 +8237,19 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Linh</t>
+          <t>Lê Văn Trung</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>285776</t>
+          <t>161073</t>
         </is>
       </c>
       <c r="Y55" s="2">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="Z55">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -8268,7 +8275,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8288,7 +8295,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1574225</t>
+          <t>KHCN_TT.GPTH_HDG_1304417</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8308,17 +8315,17 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nguyên Văn Tú</t>
+          <t>Nguyễn Thị Hồng Khánh</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0868081789</t>
+          <t>0377883716</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1,Xã Yên Sơn,Huyện Đô Lương,Tỉnh Nghệ An</t>
+          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -8338,7 +8345,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -8348,19 +8355,19 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1. KH đã báo giám đốc chi nhánh nhưng chưa được xử lý dứt điểm
-2. KH phản ánh NLMT bị hỏng không sử dụng được
-3. KH yêu cầu kỹ thuật qua hỗ trợ thay aptomat to hơn</t>
+          <t>KH chưa báo CN
+KH yêu cầu NVKT qua lại thiết bị inverter của KH 
+Số liên hệ:</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>2026-03-30 08:00:00</t>
+          <t>2026-03-26 08:00:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026-04-28 18:15:00</t>
+          <t>2026-05-04 18:10:00</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8370,24 +8377,24 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Tân</t>
+          <t>Hoàng Văn Phong</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>460719</t>
+          <t>291011</t>
         </is>
       </c>
       <c r="Y56" s="2">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="Z56">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -8408,12 +8415,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8428,12 +8435,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Acquy lưu trữ</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QNM_1510130</t>
+          <t>KHCN_TT.GPTH_BGG_1597213</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8453,22 +8460,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Lê Phước Danh</t>
+          <t>Dương Văn Quân</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0355557906</t>
+          <t>0359999199</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Thôn Pà Dá,Xã Cà Dy,Huyện Nam Giang,Tỉnh Quảng Nam</t>
+          <t>xã Hoàng Vân</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8483,303 +8490,15 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
-        <is>
-          <t>Lỗi pin ko lưu</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>2026-04-01 10:43:00</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-04-18 10:52:00</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Lê Văn Trung</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>161073</t>
-        </is>
-      </c>
-      <c r="Y57" s="2">
-        <v>46113</v>
-      </c>
-      <c r="Z57">
-        <v>28</v>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>HYN</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HDG_1304417</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Hồng Khánh</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>0377883716</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Thôn Ngọc Loan,Xã Tân Quang,Huyện Văn Lâm,Tỉnh Hưng Yên</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN
-KH yêu cầu NVKT qua lại thiết bị inverter của KH 
-Số liên hệ:</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>2026-03-26 08:00:00</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-04-29 17:00:00</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Hoàng Văn Phong</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>291011</t>
-        </is>
-      </c>
-      <c r="Y58" s="2">
-        <v>46107</v>
-      </c>
-      <c r="Z58">
-        <v>34</v>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BGG_1597213</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Dương Văn Quân</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>0359999199</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>xã Hoàng Vân</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
         <is>
           <t>1.Đã báo chi nhánh chưa: chưa báo
 2.Đã báo qua đâu: DTV HPC
@@ -8787,14 +8506,303 @@
 4.KH yêu cầu KT qua kiểm tra cho KH</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:00:00</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-03-26 18:00:00</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Trường</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>121999</t>
+        </is>
+      </c>
+      <c r="Y57" s="2">
+        <v>46104</v>
+      </c>
+      <c r="Z57">
+        <v>37</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_DNI_1659133</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0907002673</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1. Kh đã báo cn
+2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
+3. kh yc: YC cn hỗ trợ sớm</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>2026-02-23 13:30:00</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-04-21 10:30:00</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lê Đức Bình</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>412105</t>
+        </is>
+      </c>
+      <c r="Y58" s="2">
+        <v>46076</v>
+      </c>
+      <c r="Z58">
+        <v>65</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1364237</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Trương Công An</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0914531694</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>khối 2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Bảo hành</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
+- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>2026-03-23 08:00:00</t>
+          <t>2026-01-19 08:00:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026-03-26 18:00:00</t>
+          <t>2026-05-02 14:35:00</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8804,24 +8812,24 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trường</t>
+          <t>Lê Văn Anh</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>121999</t>
+          <t>069170</t>
         </is>
       </c>
       <c r="Y59" s="2">
-        <v>46104</v>
+        <v>46041</v>
       </c>
       <c r="Z59">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -8842,62 +8850,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GPTH</t>
+          <t>DVKT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>Home Service</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Dịch vụ khác</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_VTU_1502475</t>
+          <t>23092025/HĐTP-SPT-VIETTEL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Nguyễn Phú Quý</t>
+          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0947110192</t>
+          <t>0962892720</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>120 Chu Mạnh Trinh,Phường 8,Thành phố Vũng Tàu,Tỉnh Bà Rịa - Vũng Tàu, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+          <t>...</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -8907,455 +8910,25 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Sau bán</t>
+          <t>Trong bán</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
-        <is>
-          <t>1. Đã báo chi nhánh chưa: chưa báo
-2.KH gọi điện lên TĐ
-3.KH phản ánh về vấn đề: KH lắp hệ NLMT 11KW, từ thời điểm tư vấn KH được NVKD tư vấn hàng ngày vào buổi tối hệ sẽ xả 80% công suất tương đương tầm 8KW – 9KW. KH sử dụng được 1 năm tới T12/2025 mới phát hiện ra sau 2 tháng lắp đặt mỗi ngày hệ chỉ xả 4KW. T12/2025 KH có báo lên tổng đài và KT có về kiểm tra lại thiết bị, KT báo do lỗi pin và mang đi bảo hành. Sau khi bảo hành thì mang về cho KH và KH theo dõi mấy ngày nay pin cũng chỉ xả tầm 7KW, không đúng công suất như NVKD tư vấn. Tính ra thì KH đang phải bỏ ra 1 khoản tiền lớn nhưng hiệu suất sử dụng lại rất thấp.
-4.KH yêu cầu Kt kiểm tra lại pin và CN đưa ra phương án xử lý vấn đề thiệt hại kinh tế cho KH khi sử dụng điện NLMT không hiệu quả.</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>2026-03-03 15:09:00</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-03-15 12:55:00</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Lê Đức Cảnh</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>291002</t>
-        </is>
-      </c>
-      <c r="Y60" s="2">
-        <v>46084</v>
-      </c>
-      <c r="Z60">
-        <v>57</v>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_DNI_1659133</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH KHOA HỌC KỸ THUẬT TOÀN CẦU</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>0907002673</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Lầu 19, Khu A, Số 4 Nguyễn Đình Chiểu, Phường Tân Định, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>1. Kh đã báo cn
-2. Kh phản ánh: Hệ của kh dạo này sd có hiện tượng liên tục bị sập. Kh đã báo kt và kt phản hồi do kh sd quá tải nhưng từ khi lắp đến nay kh báo chỉ dùng bằng đó thiết bị chứ ko hơn
-3. kh yc: YC cn hỗ trợ sớm</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>2026-02-23 13:30:00</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-04-21 10:30:00</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Lê Đức Bình</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>412105</t>
-        </is>
-      </c>
-      <c r="Y61" s="2">
-        <v>46076</v>
-      </c>
-      <c r="Z61">
-        <v>65</v>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1364237</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Trương Công An</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>0914531694</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>khối 2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>- KH phản ánh nhân sự Lê Văn Anh mang thiết bị ivt đi bảo hành từ 8/12/2025  tới nay 16/1/2026 vẫn chưa có ivt gửi về cho KH. Đã rất lâu và thiệt hại rất nhiều, trước đấy có mang ắc quy đi BH cũng k được giờ mang ivt đi hơn tháng chưa thấy phản hồi 
-- KH Yc ktra lại và phản hồi mang thiết bị về lắp đặt  lại cho KH</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>2026-01-19 08:00:00</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026-05-02 14:35:00</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Lê Văn Anh</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>069170</t>
-        </is>
-      </c>
-      <c r="Y62" s="2">
-        <v>46041</v>
-      </c>
-      <c r="Z62">
-        <v>100</v>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Dịch vụ khác</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>23092025/HĐTP-SPT-VIETTEL</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN SPT VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>0962892720</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
         <is>
           <t>- Đối tác Công ty cổ phần SPT Việt Nam (sdt phản ánh 0975014010) tiếp tục gọi tđ phản ánh về vấn đề chậm trễ tiến độ và thiếu nhân lực thi công cho dự án Thi công lắp đặt hệ thống Chiller. 
 - Kh báo hiện tại vẫn chậm tiến độ, cn ko thay đổi hay tiến triển thêm gì
@@ -9363,53 +8936,53 @@
 - Kh yc: Yc TCT có biện pháp xử lý rõ ràng cho kh</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>2025-12-10 08:00:00</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>2025-12-16 15:00:00</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Đặng Việt Phú</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>062146</t>
         </is>
       </c>
-      <c r="Y63" s="2">
+      <c r="Y60" s="2">
         <v>46001</v>
       </c>
-      <c r="Z63">
+      <c r="Z60">
         <v>140</v>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
         <is>
           <t>VHKT</t>
         </is>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>Truongdv17, Congnd15</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>vinhvv4</t>
+          <t>Thikd, Vinhvv4, Tuyendv</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Tuyendv</t>
+          <t>Thikd, Vinhvv4, Tuyendv</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>Thikd, Vinhvv4, Tuyendv</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>tietvt16</t>
+          <t>Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>Thikd, Vinhvv4, Tuyendv</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>Thikd, Vinhvv4, Tuyendv</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tuyendv</t>
+          <t>Thikd, Vinhvv4, Tuyendv</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Sonln15</t>
+          <t>Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>truongdv17</t>
+          <t>Truongdv17, Congnd15</t>
         </is>
       </c>
     </row>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Thikd, Vinhvv4, Tuyendv</t>
+          <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Thikd, Vinhvv4, Tuyendv</t>
+          <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Thikd, Vinhvv4, Tuyendv</t>
+          <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Thikd, Vinhvv4, Tuyendv</t>
+          <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Truongdv17, Congnd15</t>
+          <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Tienvt16, Anhnt631</t>
+          <t>N2 - Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Truongdv17, Congnd15</t>
+          <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Tienvt16, Anhnt631</t>
+          <t>N2 - Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Tienvt16, Anhnt631</t>
+          <t>N2 - Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Truongdv17, Congnd15</t>
+          <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Thikd, Vinhvv4, Tuyendv</t>
+          <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Thikd, Vinhvv4, Tuyendv</t>
+          <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
     </row>
@@ -17491,7 +17491,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Truongdv17, Congnd15</t>
+          <t>N1 - Truongdv17, Congnd15</t>
         </is>
       </c>
     </row>
@@ -17631,7 +17631,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Thikd, Vinhvv4, Tuyendv</t>
+          <t>N3 - Thikd, Ducnt84</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Tienvt16, Anhnt631</t>
+          <t>N2 - Tienvt16, Anhnt631</t>
         </is>
       </c>
     </row>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>N2 - Tienvt16, Anhnt631</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>N3 - Thikd, Ducnt84</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>N1 - Truongdv17, Congnd15</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
     </row>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -522,2730 +522,2879 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1670562</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Đặng Văn Hồng</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0972772889</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Khối Nam Trung</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1. KH đã được CN đến chuyển ATS đi bảo hành
+2. KH cần CN cập nhật tiến độ bảo hành, kiểm tra Ắc quy lưu trữ và xử lý sơ bộ cho KH</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-06 15:41:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-08-07 15:41:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Lê Công Hoàng</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>160675</t>
+        </is>
+      </c>
+      <c r="Y2" s="2">
+        <v>46240</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD2" s="2">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LDG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>020401-KD/HĐMBLĐ-2026/LDG-LADOFOODS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM LÂM ĐỒNG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>02633520290</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>31 ngô văn sở</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1. CN tạo sự cố cho KH
+2. Sau khi lắp HT NLMT bị lệch cos phi, dẫn tới bị phạt công suất phản kháng khoảng 3 tháng, Điện lực đã thông tin tới KH nhiều lần
+3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-06 15:22:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-07 15:22:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hồ Văn Tuấn</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>046974</t>
+        </is>
+      </c>
+      <c r="Y3" s="2">
+        <v>46240</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>N2 - Thaoltt16, Thikd</t>
+        </is>
+      </c>
+      <c r="AD3" s="2">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KHCN_PINNLMT_NTN_0343877</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Vương Đình Sang</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0967008678</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>kp4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>CN 0978866677 báo sự cố hộ KH
+1. KH phản ánh: đèn tín hiệu trong ivt nhấp nháy và báo lỗi màu đỏ, ko thấy có ra điện nlmt
+2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:41:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:41:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Vương</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>069846</t>
+        </is>
+      </c>
+      <c r="Y4" s="2">
+        <v>46240</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD4" s="2">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_AGG_1642699</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Võ Nam</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0939486129</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>C23-24 đường Trần Văn Trà</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN: A Hoàng
+2. KH phản ánh: pin lưu trữ nạp vào nhưng ko xả ra, đường dây lắp đặt trên mái bị hắt qua 1 bên do mưa bão, KH không biết có ảnh hưởng gì tới hệ nlmt không
+3. KH yêu cầu: qua kiểm tra lại phần đường dây và khắc phục lỗi pin lưu trữ</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-08-06 13:30:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:30:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Doãn Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>454453</t>
+        </is>
+      </c>
+      <c r="Y5" s="2">
+        <v>46240</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD5" s="2">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_1713443</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Trần Anh Tuấn</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0982754600</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>sn53, tổ 55</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1. KH đã báo CN (KH ko muốn nhắc tên)
 2. KH phản ánh: CN có thống nhất với KH là vào lắp đặt vào hôm nay nhưng đến hiện tại KH ko thấy có thông tin gì, liên lạc CN thì cũng ko được, ko chủ động báo lại cho KH mà dời lịch hẹn đã rất nhiều lần. KH phải bỏ việc ở nhà mà lại ko đúng hẹn, KH rất ko hài lòng về cách làm việc của CN
 3. KH yêu cầu: CN xuống triển khai lắp đặt cho KH theo đúng cam kết</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2026-08-06 13:30:00</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2026-08-07 13:30:00</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Phạm Duy Hưng</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>023224</t>
-        </is>
-      </c>
-      <c r="Y2" s="2">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trần Xuân Kương</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>289759</t>
+        </is>
+      </c>
+      <c r="Y6" s="2">
         <v>46240</v>
       </c>
-      <c r="Z2">
+      <c r="Z6">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD2" s="2">
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD6" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1630213</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1641082</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nguyễn Hữu Luận</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0972390672</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>nghi trung</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lê Anh Sơn</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0705209574</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Xóm 6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1. KH đã báo KT anh Hải
-2.Hệ thống NLMT không phát ra điện, KH bị sự cố báo sáng 6/8 nhưng chưa được hỗ trợ 
-3. Yêu cầu CN hỗ trợ KH</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-08-06 13:30:00</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-08-07 13:30:00</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Tống Văn Chung</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>017941</t>
-        </is>
-      </c>
-      <c r="Y3" s="2">
-        <v>46240</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD3" s="2">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1641082</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lê Anh Sơn</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0705209574</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Xóm 6</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: ko thấy có điện nlmt, mất điện lưới cũng ko thấy có, pin lưu trữ cũng ko thấy xả điện ra để sử dụng
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-08-06 09:24:00</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2026-08-07 09:24:00</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Tống Văn Chung</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>017941</t>
-        </is>
-      </c>
-      <c r="Y4" s="2">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Cao Minh Tăng</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>185895</t>
+        </is>
+      </c>
+      <c r="Y7" s="2">
         <v>46240</v>
       </c>
-      <c r="Z4">
+      <c r="Z7">
         <v>0</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD4" s="2">
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD7" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNH_1605674</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Quán Năm Trí</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0906610708</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>tổ 7, khu phố Hòa Bình</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>CN Nguyễn Huy Thanh báo sự cố hộ KH qua zalo
 1. KH phản ánh:  báo hệ thống nlmt lỗi, tự lấy điện lưới nạp bình , đã bị lâu ngày.
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-08-06 08:15:00</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-08-07 08:15:00</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Nguyễn Quốc Hưng</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>467401</t>
         </is>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y8" s="2">
         <v>46240</v>
       </c>
-      <c r="Z5">
+      <c r="Z8">
         <v>0</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD5" s="2">
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD8" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1630198</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Công Ty TNHH Hoa Sen Hoàn Mỹ</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0979111959</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>L2-06B, Khu biệt thư kinh doanh An Khánh, phường Tây Mỗ,Quận Nam Từ Liêm,Thành phố Hà Nội</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Life Care</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>KH chưa báo Cn 
 KH phản ánh:  Đường nối từ trên tầng mái xuống tầng tủ điện bị dẫn nước mưa, hiện đã ngừng hoạt động. Cần bảo hành sớm.
 Yêu cầu KT qua ktra hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-08-06 09:29:00</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-08-07 09:29:00</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Khương Văn Độ</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>450945</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y9" s="2">
         <v>46240</v>
       </c>
-      <c r="Z6">
+      <c r="Z9">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD6" s="2">
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD9" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNI_1665624</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Nguyễn Thị Loan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0988386589</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>phường Tam phước, khu phố thiên bình</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Nghiệp vụ chuyên môn kém</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: anh Tùng - nhân viên tư vấn
 2. KH phản ánh: lúc tư vấn KH có trao đổi rõ về nhu cầu cũng như mong muốn của KH là sử dụng điện ban ngày, ko tích điện ban đêm và khi mất điện muốn có điện nlmt để sử dụng, nhưng giờ mất điện lần đầu tiên KH không có điện nlmt để sử dụng. KH có trao đổi với CN là anh Tùng nhưng CN phản hồi là phải thay cục pin và bộ chuyển đổi hết 70tr, KH ko đồng ý với phương án này do tư vấn KH đã trao đổi rõ, CN cũng có hẹn KH trưa nay xuống hỗ trợ nhưng giờ cũng ko thấy đâu. Hệ của KH sử dụng cũng ko đạt được mục đích, điện ko tiết kiệm như KH mong muốn chỉ đạt được 1/3 hiệu suất. Ngoài ra KH cũng ko nhận được bản HĐ cứng
 3. KH yêu cầu: KH bức xúc và cho rằng đây là lỗi nhân viên tư vấn yêu cầu cung cấp bản HĐ và đưa ra phương án xử lý như nào về TH này</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-08-06 08:00:00</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2026-08-07 09:00:00</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Trần Hải Tùng</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>245696</t>
         </is>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y10" s="2">
         <v>46240</v>
       </c>
-      <c r="Z7">
+      <c r="Z10">
         <v>0</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD7" s="2">
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD10" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VLG_1608965</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Việt</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0938144335</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Nhà a. Việt Ấp La Gì</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>CN 0979707700 báo sự cố hộ KH
 1. KH phản ánh: pin lưu trữ nắng to mà đạt công suất thấp từ sáng tới 3h chiều chỉ đạt được 50% pin, KH cũng theo dõi ít thế này mấy ngày nay rồi
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>2026-08-05 16:01:00</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-08-06 16:01:00</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:30:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Lê Huỳnh Đức</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>282831</t>
         </is>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y11" s="2">
         <v>46239</v>
       </c>
-      <c r="Z8">
+      <c r="Z11">
         <v>1</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD8" s="2">
-        <v>46239</v>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD11" s="2">
+        <v>46240</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_TNN_1703191</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Hà Văn Nhâm</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0942600789</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>xóm Xuân Đào</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1. KH đã liên hệ CN
+2. KH đã lắp đặt HT NLMT tuy nhiên chỉ số điện tiêu dùng không thấy giảm , tiền điện cần thanh toán không có chênh lệch nhiều với thời điểm trước khi lắp đặt HT NLMT
+3. KH cần CN đến kiểm tra và giải đáp cho KH</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-08-06 14:18:00</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:18:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vũ Minh Tân</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>026598</t>
+        </is>
+      </c>
+      <c r="Y12" s="2">
+        <v>46240</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD12" s="2">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>TQG</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TQG_1683316</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Lâm Văn Tùng</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0988507908</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Hưng Thành</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>KH đã báo KT nhưng chưa được hỗ trợ 
 KH báo pin lưu trữ của KH bị hỏng đã tháo mang đi bảo hành và đã được trả về, tuy nhiên KT chưa mang pin lưu trữ đến trả và lắp đặt lại cho KH 
 Yêu cầu CN cho KT qua hỗ trợ lắp đặt lại cho KH</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2026-08-06 13:30:00</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>2026-08-07 13:30:00</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Dương Hoàng Giang</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>075214</t>
-        </is>
-      </c>
-      <c r="Y9" s="2">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Đỗ Văn Hiệp</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>468087</t>
+        </is>
+      </c>
+      <c r="Y13" s="2">
         <v>46240</v>
       </c>
-      <c r="Z9">
+      <c r="Z13">
         <v>0</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD9" s="2">
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD13" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNH_1684192</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Lưu Tuyết Mai</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0774194919</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>56 Trần Văn Giàu</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>CN 0357162662 báo sự cố hộ KH 
 1. KH phản ánh: mưa bị dột mái nhà nlmt 
 2. KH yêu cầu: kiểm tra, và xử lý lại phần thi công</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-08-06 11:30:00</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2026-08-07 11:30:00</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Huỳnh Nhật Tiến</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>466027</t>
         </is>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y14" s="2">
         <v>46240</v>
       </c>
-      <c r="Z10">
+      <c r="Z14">
         <v>0</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD10" s="2">
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD14" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_NLMT_TVH_0236267</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Phạm Văn Chính</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0868119929</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>ấp trường hội</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: cả tháng nay hệ nlmt ko hoạt động
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>2026-08-06 09:40:00</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>2026-08-07 09:40:00</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thành Được</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>292723</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y15" s="2">
         <v>46240</v>
       </c>
-      <c r="Z11">
+      <c r="Z15">
         <v>0</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD11" s="2">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD15" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>HYN</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LDG</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Thang máy</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VCC_YCTX_HYN_1785916613808</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Acquy lưu trữ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_LDG_1666341</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Vương Thanh Ngân</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0983052994</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Vin ocean park 2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nguyễn Lê Hoàng</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0868038186</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Thôn 2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Trước bán</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Tư vấn sản phẩm/dịch vụ</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>YCTX NLMT lịch hẹn 6/8 nhưng KH cần liên hệ tư vấn gấp</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2026-08-06 08:00:00</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:00:00</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Vũ Duy Cương</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>095581</t>
-        </is>
-      </c>
-      <c r="Y12" s="2">
-        <v>46240</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>P.KD Cơ điện</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>P.KD Cơ điện</t>
-        </is>
-      </c>
-      <c r="AD12" s="2">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DLK</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CNTT</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sản phẩm CNTT</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_DLK_1691084</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Trường Mầm non Sơn Ca</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0916710766</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>425 Nguyễn Huệ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1. KH chưa báo CN: KH ko còn giữ SĐT liên hệ
-2. KH cần hỗ trợ cung cấp bản hợp đồng cứng để KH lưu lại 
-*** liên hệ trước SĐT đky HĐ là chị phó hiệu trưởng trường, nếu ko liên hệ được thì liên hệ với SĐT phản ánh 0868731084</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2026-08-05 15:24:00</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:24:00</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Trương Hoàng Tâm</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>083388</t>
-        </is>
-      </c>
-      <c r="Y13" s="2">
-        <v>46239</v>
-      </c>
-      <c r="Z13">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>N2 - Thaoltt16, Thikd</t>
-        </is>
-      </c>
-      <c r="AD13" s="2">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LDG</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_LDG_1666341</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Nguyễn Lê Hoàng</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0868038186</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Thôn 2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>1. CN báo sự cố cho KH (987251444_
 2. Ắc quy lưu trữ của KH không vào điện
 3. KH cần CN hỗ trợ khắc phục sớm</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>2026-08-05 14:26:00</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-08-06 14:26:00</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:40:00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Trần Văn Dương</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>166553</t>
         </is>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y16" s="2">
         <v>46239</v>
       </c>
-      <c r="Z14">
+      <c r="Z16">
         <v>1</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD14" s="2">
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD16" s="2">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng vệ sinh máy giặt lồng ngang</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DH_B2C_TNH_1784967521845</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Trần Thị Tuyết</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0963733097</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>đường Đình Chánh</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Đơn hàng DVKT được hỗ trợ thực hiện ngày 26/07 tuy nhiên ngày 27/07 cửa xả máy giặt của KH đang gặp sự cố cần CN đến kiểm tra và hỗ trợ khắc phục sớm</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:00:00</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-08-09 18:00:00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Huỳnh Tiến Lộc</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>492960</t>
+        </is>
+      </c>
+      <c r="Y17" s="2">
         <v>46239</v>
       </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD17" s="2">
+        <v>46241</v>
+      </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng vệ sinh máy giặt lồng ngang</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DH_B2C_TNH_1784967521845</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BLU_1609539</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Trần Thị Tuyết</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0963733097</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>đường Đình Chánh</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Võ Kim Nguyên</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0968680580</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Hộ Phòng</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Đơn hàng DVKT được hỗ trợ thực hiện ngày 26/07 tuy nhiên ngày 27/07 cửa xả máy giặt của KH đang gặp sự cố cần CN đến kiểm tra và hỗ trợ khắc phục sớm</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>2026-08-05 08:00:00</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-08-09 18:00:00</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Huỳnh Tiến Lộc</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>492960</t>
-        </is>
-      </c>
-      <c r="Y15" s="2">
-        <v>46239</v>
-      </c>
-      <c r="Z15">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD15" s="2">
-        <v>46241</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BLU_1609539</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Võ Kim Nguyên</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0968680580</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Hộ Phòng</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>KH đã báo CN
 KH phản ánh biến tần không phát được điện  nữa,
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-08-04 16:03:00</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>2026-08-25 23:55:00</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Đào Trí Nam</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>433398</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y18" s="2">
         <v>46238</v>
       </c>
-      <c r="Z16">
+      <c r="Z18">
         <v>2</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD16" s="2">
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD18" s="2">
         <v>46248</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>M&amp;E</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Thang máy</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>100601-XD/HĐXL-2025/BNH-HOANGTRONGHIEU</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Hoàng Trọng Hiếu</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0986912000</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Thị trấn Đồi Ngô,Huyện Lục Nam,Tỉnh Bắc Giang</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>1. KH đã báo CN 
 2. KH chưa được hỗ trợ về việc lắp thang hàng và tiến độ về công trình đang bị chậm nửa năm rồi  KH muốn được đền bù HĐ
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2026-08-04 14:20:00</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>2026-08-11 18:15:00</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>nguyễn văn Tuần</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>461581</t>
         </is>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y19" s="2">
         <v>46238</v>
       </c>
-      <c r="Z17">
+      <c r="Z19">
         <v>2</v>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD17" s="2">
+      <c r="AD19" s="2">
         <v>46241</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1685190</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HNI_1701257</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Cường</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0946243858</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Khối 6</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Nguyễn Đức Minh</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0988651214</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Số nhà 9 ngõ 79, la tinh 1, Xã An Khánh, Thành phố Hà Nội, Xã An Khánh, Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Life Care</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>KH báo CN, CN báo gọi TĐ
-KH báo sự cố NLMT khi mất điện không tự đảo át
-Yêu cầu CN cho KT qua ktra cho KH</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>2026-08-04 10:26:00</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-08-06 15:35:00</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Võ Văn Quyết</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>494782</t>
-        </is>
-      </c>
-      <c r="Y18" s="2">
-        <v>46238</v>
-      </c>
-      <c r="Z18">
-        <v>2</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD18" s="2">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNI_1701257</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Nguyễn Đức Minh</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0988651214</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Số nhà 9 ngõ 79, la tinh 1, Xã An Khánh, Thành phố Hà Nội, Xã An Khánh, Thành phố Hà Nội</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Life Care</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH phản ánh: Tháng này biến tần solax nhà mình báo 501 số điện mà evn báo 630 số điện chênh hơn 100 số mình muốn hỏi vì sao nó lại chênh nhiều tới vậy
 Yêu cầu CN cho KT qua ktra hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>2026-08-05 16:33:00</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-08-06 16:33:00</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:50:00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Hoàng Văn Vương</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>285732</t>
         </is>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y20" s="2">
         <v>46239</v>
       </c>
-      <c r="Z19">
+      <c r="Z20">
         <v>1</v>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD19" s="2">
-        <v>46239</v>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD20" s="2">
+        <v>46241</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1688216</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Nguyễn Hạnh Phúc</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>0974977999</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Yên Hòa</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1. KH đã liê hệ CN
 2. Hiện tại HT NLMT đấu dây điện đang bị lệch và có hiện tượng quá tải do chịu tải nhà
@@ -3254,471 +3403,325 @@
 Địa chỉ lắp đặt: Xóm Châu Quang, Xã Quy Hợp, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2026-08-05 13:30:00</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-08-06 13:30:00</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:50:00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>Cao Đức Thùy</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>434727</t>
         </is>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y21" s="2">
         <v>46239</v>
       </c>
-      <c r="Z20">
+      <c r="Z21">
         <v>1</v>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD20" s="2">
-        <v>46239</v>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD21" s="2">
+        <v>46243</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>HCM</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1707660</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Lan Anh</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0792459635</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Tổ 3, Khu phố Đông Hải</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. Hiện vật tư thiết bị của HT NLMT đã tập kết đủ tại nhà KH tuy nhiên CN chưa hỗ trợ lắp đặt
 3. KH cần CN đến lắp đặt và hoàn thiện HT NLMT cho KH để có thể phục vụ hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-08-05 08:00:00</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>2026-08-09 18:20:00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Nguyễn Huy Nam</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>081021</t>
         </is>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y22" s="2">
         <v>46239</v>
       </c>
-      <c r="Z21">
+      <c r="Z22">
         <v>1</v>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD21" s="2">
+      <c r="AD22" s="2">
         <v>46241</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1632398</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Hoàng Tiến Nam</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>0984556118</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Triệu xuyên 3, Long Xuyên</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. KH phản ánh Inverter của KH có thể bị ảnh hường bởi sét đánh, hiện không có điện lưới và điện NLMT
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>2026-08-04 16:07:00</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>2026-08-06 23:55:00</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>292404</t>
-        </is>
-      </c>
-      <c r="Y22" s="2">
-        <v>46238</v>
-      </c>
-      <c r="Z22">
-        <v>2</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD22" s="2">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VCC_HS_HNI_1782011730755</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Doãn Thị Minh Lân</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0869345777</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>số 15 ngõ 98 Hoàng Ngân, Phường Yên Hòa, Thành phố Hà Nội</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Đơn hàng xong từ 23/6 KH bdvs 2 chiếc điều hòa thì có 1 điều hòa bị chảy nước có liên hệ với KT và đã đến kiểm tra, khắc phục 1 lần rồi nhưng giờ vẫn bị lại. KH cần qua hỗ trợ khắc phục dứt điểm lại tình trạng này</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>2026-08-04 13:30:00</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-08-07 23:35:00</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Lê Duy Tuấn</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>293859</t>
         </is>
       </c>
       <c r="Y23" s="2">
@@ -3729,7 +3732,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3754,85 +3757,231 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DVKT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Home Service</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VCC_HS_HNI_1782011730755</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Doãn Thị Minh Lân</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0869345777</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>số 15 ngõ 98 Hoàng Ngân, Phường Yên Hòa, Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Đơn bảo dưỡng hết hạn bảo hành</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Đơn hàng xong từ 23/6 KH bdvs 2 chiếc điều hòa thì có 1 điều hòa bị chảy nước có liên hệ với KT và đã đến kiểm tra, khắc phục 1 lần rồi nhưng giờ vẫn bị lại. KH cần qua hỗ trợ khắc phục dứt điểm lại tình trạng này</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:30:00</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-08-07 23:35:00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lê Duy Tuấn</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>293859</t>
+        </is>
+      </c>
+      <c r="Y24" s="2">
+        <v>46238</v>
+      </c>
+      <c r="Z24">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD24" s="2">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>KHDN_PINNLMT_BGG_0308304</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>CÔNG TY CP TƯ VẤN VÀ PHÁT TRIỂN CDIS</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0972782888</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Tổ dân phố Cung Nhượng 2, Phường Thọ Xương, Thành phố Bắc Giang, Tỉnh Bắc Giang</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: A Viêt
 2. KH phản ánh: trên phần mềm báo lỗi adapter
@@ -3840,735 +3989,735 @@
 ***đ/c sau sáp nhập: Số 30 đường nhật đức, phường bắc giang, tỉnh bắc ninh</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>2026-08-04 08:37:00</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>2026-08-07 18:35:00</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Phùng Văn Thủy</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>034451</t>
         </is>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y25" s="2">
         <v>46238</v>
       </c>
-      <c r="Z24">
+      <c r="Z25">
         <v>2</v>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD24" s="2">
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD25" s="2">
         <v>46239</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>DTP</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DTP_1632890</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Phan Thị Huệ Trinh</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>0917456519</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Ấp Thị</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>CN 0977477773 báo sự cố hộ KH
 1. KH phản ánh: cục ats nhảy liên tục, ko sử dụng được điện nlmt
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>2026-08-04 08:00:00</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>2026-08-06 10:40:00</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Đỗ Trọng Phú</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>073764</t>
         </is>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y26" s="2">
         <v>46238</v>
       </c>
-      <c r="Z25">
+      <c r="Z26">
         <v>2</v>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD25" s="2">
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD26" s="2">
         <v>46239</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QNH_1510875</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Bùi Văn Hoàng</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0981327963</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Số 261 Nguyễn Văn Cừ, Hoàng Hoa Thám,Phường Mạo Khê,Thị xã Đông Triều,Tỉnh Quảng Ninh</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: ivt chỉ sạc vào pin chứ ko xả ra, KH có 2 ivt nhưng chỉ bị 1 cái
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>2026-08-03 15:26:00</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>2026-08-07 18:00:00</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Đỗ Thanh Tùng</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>083858</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y27" s="2">
         <v>46237</v>
       </c>
-      <c r="Z26">
+      <c r="Z27">
         <v>3</v>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD26" s="2">
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD27" s="2">
         <v>46239</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>DLK</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DLK_1626932</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Phan Công An</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>0326387374</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Thôn 1A, Xã Ea Drông</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Inverter của KH hiển thị thông tin không chính xác, HT NLMT tự đóng ngắt liên tục
 3.KH cần CN đến hỗ trợ và khắc phục sớm</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>2026-08-03 11:49:00</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>2026-08-07 07:35:00</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Phạm Duy Bộ</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>411337</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y28" s="2">
         <v>46237</v>
       </c>
-      <c r="Z27">
+      <c r="Z28">
         <v>3</v>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD27" s="2">
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD28" s="2">
         <v>46239</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1423965</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Anh Nghĩa</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>0919666690</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Khóm 10,Thị trấn Sông Đốc,Huyện Trần Văn Thờ, Xã Trần Văn Thời, Tỉnh Cà Mau</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>KH chưa báo CN 
 KH phản ánh trên app đang báo lỗi mất điện NLMT và mất ắc quy, bị sáng nay 
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>2026-08-03 11:33:00</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>2026-08-09 08:40:00</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Trần Hoàng Huy</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>410724</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y29" s="2">
         <v>46237</v>
       </c>
-      <c r="Z28">
+      <c r="Z29">
         <v>3</v>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD28" s="2">
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD29" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Acquy lưu trữ</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HPG_1698568</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Công ty TNHH Stride Solar Solutions</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>0889812340</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>385 Trần Nguyên Đán</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Hỗ trợ lắp đặt</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>1. CN hỗ trợ KH
 2. KH hỗ trợ bổ sung tiếp địa cho Ăc quy lưu trữ HT NLMT
@@ -4577,1238 +4726,1090 @@
 Địa chỉ lắp đặt: 385 Trần Nguyên Đán, Phường Trần Hưng Đạo, Thành phố Hải Phòng</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>2026-08-03 11:03:00</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>2026-08-09 17:00:00</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Bùi Văn Đạt</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>285126</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y30" s="2">
         <v>46237</v>
       </c>
-      <c r="Z29">
+      <c r="Z30">
         <v>3</v>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD29" s="2">
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD30" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1706322</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Lê Mạnh Tài</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0965876576</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Khối 2</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Inverter không hoạt động</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: ivt ko hoạt động, ko lên đèn nguồn, theo dõi trên app mất giám sát
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>2026-08-03 08:00:00</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>2026-08-19 16:25:00</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Nguyễn Minh Linh</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>285776</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y31" s="2">
         <v>46237</v>
       </c>
-      <c r="Z30">
+      <c r="Z31">
         <v>3</v>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD30" s="2">
+      <c r="AD31" s="2">
         <v>46245</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1710463</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Trần Trung Kiên</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>0822909809</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Ấp Phước Thạnh 2</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>1. KH đã báo CN, anh Luân bên lắp đặt
 2. hệ thống pin NLMT đầy trên 95% nhưng vẫn lấy điện lưới nhiều trong 15 phút rồi mới chuyển sang chạy từ pin, thường thì có lấy từ mạng lưới có chục giây thôi mà 15 phút như kia là quá lâu 
 3. Yêu cầu CN hỗ trợ KH, xem có cấu hình sai đâu không</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>2026-08-03 08:56:00</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>2026-08-07 03:30:00</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Huỳnh Tấn Đạt</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>433394</t>
         </is>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y32" s="2">
         <v>46237</v>
       </c>
-      <c r="Z31">
+      <c r="Z32">
         <v>3</v>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD31" s="2">
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD32" s="2">
         <v>46238</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>LDG</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_LDG_1708977</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Huỳnh Công Danh</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>0817728000</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Thôn 4, Hàm Đức</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>KH đã báo CN 
 KH phản ánh cục ATS bị đảo chiều ( nhảy qua nhảy lại giữa điện lưới và điện NLMT ) 
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>2026-08-03 08:00:00</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>2026-08-13 17:30:00</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Lê Xuân Lữ</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>429132</t>
         </is>
       </c>
-      <c r="Y32" s="2">
+      <c r="Y33" s="2">
         <v>46237</v>
       </c>
-      <c r="Z32">
+      <c r="Z33">
         <v>3</v>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD32" s="2">
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD33" s="2">
         <v>46242</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Thiết bị trung tâm HC</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>1101/2025/HĐTC/HSNA-VCC</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HOA SEN NGHỆ AN</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>02383668111</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Lô CN 1-8, KCN Đông Hồi, Xã Quỳnh Lập, Thị xã Hoàng Mai, Tỉnh Nghệ An</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>KH chưa báo CN 
 KH phản ánh màn hình LED của KH bị hỏng không sử dụng được, KH không biết nguyên nhân tại sao
 Yêu cầu CN liên hệ và hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>2026-08-03 08:00:00</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>2026-08-07 23:55:00</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Võ Trọng Đức</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>293804</t>
         </is>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y34" s="2">
         <v>46237</v>
       </c>
-      <c r="Z33">
+      <c r="Z34">
         <v>3</v>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>HS</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD33" s="2">
+      <c r="AD34" s="2">
         <v>46239</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Acquy lưu trữ</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1345359</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Nguyễn Đức Xuân</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>0338136456</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>yên dũng Bắc Ninh</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Ắc quy lưu trữ sạc đầy nhưng không xả, trên App theo dõi khi dùng tải nhà cao hơn hiệu suất của HT NLMT không thấy bù điện lưới 
 3. KH cần CN đến kiêm tra sớm</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>2026-08-03 08:00:00</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>2026-08-15 17:05:00</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Hoàng Văn Chính</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>284663</t>
         </is>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y35" s="2">
         <v>46237</v>
       </c>
-      <c r="Z34">
+      <c r="Z35">
         <v>3</v>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD34" s="2">
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD35" s="2">
         <v>46243</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1663022</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Nguyễn Quốc Anh</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>0974441357</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Bắc Hồng Lĩnh</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>1. CN báo sự cố cho KH
 2. KH đang không theo dõi đươc hiệu suất NLMT trên App
 3. KH cần CN đến hỗ trợ khắc phục sớm</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>2026-07-31 15:53:00</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>2026-08-07 17:00:00</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Trần Văn Việt</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>044155</t>
         </is>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y36" s="2">
         <v>46234</v>
       </c>
-      <c r="Z35">
+      <c r="Z36">
         <v>6</v>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>VHKT</t>
-        </is>
-      </c>
-      <c r="AD35" s="2">
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>VHKT</t>
+        </is>
+      </c>
+      <c r="AD36" s="2">
         <v>46237</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1712640</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Phạm Trọng Hoà</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>0975650515</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Lai Sơn</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Trong bán</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>CN 0985814499 báo sự cố hộ KH
 1. KH phản ánh: KH mới lắp thêm 10 tấm pin ban đầu là 36 và hiện tại là 46 tấm pin nhưng hiệu suất vẫn như lúc ban đầu
 2. KH yêu cầu: qua kiểm tra, đo đạc lại xem để xác định nguyên nhân là do che bóng hay gì không để KH còn đưa ra phương án xử lý</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>2026-07-31 09:22:00</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>2026-08-14 23:40:00</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Lê Duy Tuấn</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>293859</t>
         </is>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y37" s="2">
         <v>46234</v>
       </c>
-      <c r="Z36">
+      <c r="Z37">
         <v>6</v>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD36" s="2">
+      <c r="AD37" s="2">
         <v>46241</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1711253</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Trần Ngọc Ý</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0868787567</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Tổ Thân Ái</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Trong bán</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1. KH đã liên hệ CN
-2. KH cần lắp thêm 2 tấm pin NLMT do thiếu công suát và CN đã chuyển vật tư đến cho KH tuy nhiên chưa hỗ trợ lắp đặt
-3. KH cần CN thông tin cụ thể thời gian lắp đặt cũng như hoàn thiện để KH có thể thanh toán cho CN</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2026-07-29 16:34:00</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-08-10 08:20:00</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Võ Trọng Đức</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>293804</t>
-        </is>
-      </c>
-      <c r="Y37" s="2">
-        <v>46232</v>
-      </c>
-      <c r="Z37">
-        <v>8</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
-        </is>
-      </c>
-      <c r="AD37" s="2">
-        <v>46238</v>
       </c>
     </row>
     <row r="38">

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -1349,7 +1349,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD21" s="2">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD26" s="2">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD38" s="2">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD44" s="2">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD45" s="2">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD50" s="2">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD54" s="2">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD58" s="2">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD59" s="2">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD61" s="2">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD66" s="2">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AD67" s="2">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD69" s="2">
@@ -11353,12 +11353,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD75" s="2">

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -1642,7 +1642,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -934,12 +934,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD4" s="2">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD5" s="2">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD7" s="2">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD8" s="2">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD9" s="2">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD10" s="2">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD11" s="2">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD12" s="2">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD13" s="2">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD16" s="2">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD17" s="2">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD18" s="2">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD19" s="2">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AD21" s="2">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD22" s="2">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD23" s="2">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD24" s="2">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AD25" s="2">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD26" s="2">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD27" s="2">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
       <c r="AD28" s="2">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD29" s="2">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD30" s="2">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD31" s="2">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD32" s="2">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD34" s="2">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD38" s="2">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD39" s="2">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD40" s="2">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD47" s="2">
@@ -7704,12 +7704,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD50" s="2">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD55" s="2">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
       <c r="AD58" s="2">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD59" s="2">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
       <c r="AD60" s="2">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>P.Triển khai</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>VHKT</t>
+          <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
       <c r="AD61" s="2">

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,11 +355,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AE61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="25" max="25" width="20.7109375" style="2" customWidth="1"/>
-    <col min="30" max="30" width="20.7109375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
+    <col min="31" max="31" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -485,30 +485,35 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>date_fix</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>thoi_gian_ton</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>he_thong</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>phong_dieuhanh</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>am_chot</t>
-        </is>
-      </c>
       <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>am</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>date_mid_2</t>
         </is>
@@ -630,28 +635,33 @@
           <t>443712</t>
         </is>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>4615732</t>
+        </is>
+      </c>
+      <c r="Z2" s="2">
         <v>46255</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD2" s="2">
+      <c r="AE2" s="2">
         <v>46256</v>
       </c>
     </row>
@@ -773,28 +783,33 @@
           <t>064620</t>
         </is>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4615731</t>
+        </is>
+      </c>
+      <c r="Z3" s="2">
         <v>46254</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>1</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD3" s="2">
+      <c r="AE3" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -921,28 +936,33 @@
           <t>289759</t>
         </is>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4615730</t>
+        </is>
+      </c>
+      <c r="Z4" s="2">
         <v>46254</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>1</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD4" s="2">
+      <c r="AE4" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -1069,28 +1089,33 @@
           <t>069197</t>
         </is>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>4615725</t>
+        </is>
+      </c>
+      <c r="Z5" s="2">
         <v>46255</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD5" s="2">
+      <c r="AE5" s="2">
         <v>46256</v>
       </c>
     </row>
@@ -1215,28 +1240,33 @@
           <t>014387</t>
         </is>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>4615724</t>
+        </is>
+      </c>
+      <c r="Z6" s="2">
         <v>46255</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD6" s="2">
+      <c r="AE6" s="2">
         <v>46256</v>
       </c>
     </row>
@@ -1345,7 +1375,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1358,28 +1388,33 @@
           <t>054647</t>
         </is>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>4615716</t>
+        </is>
+      </c>
+      <c r="Z7" s="2">
         <v>46254</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>1</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -1493,7 +1528,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1506,28 +1541,33 @@
           <t>470289</t>
         </is>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4615713</t>
+        </is>
+      </c>
+      <c r="Z8" s="2">
         <v>46254</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>1</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD8" s="2">
+      <c r="AE8" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -1641,7 +1681,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1654,28 +1694,33 @@
           <t>119420</t>
         </is>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>4615711</t>
+        </is>
+      </c>
+      <c r="Z9" s="2">
         <v>46254</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>1</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD9" s="2">
+      <c r="AE9" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -1802,28 +1847,33 @@
           <t>285732</t>
         </is>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>4615710</t>
+        </is>
+      </c>
+      <c r="Z10" s="2">
         <v>46254</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>1</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD10" s="2">
+      <c r="AE10" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -1937,7 +1987,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1950,28 +2000,33 @@
           <t>083858</t>
         </is>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>4615704</t>
+        </is>
+      </c>
+      <c r="Z11" s="2">
         <v>46254</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>1</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD11" s="2">
+      <c r="AE11" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -2085,7 +2140,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2098,28 +2153,33 @@
           <t>256745</t>
         </is>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>4615700</t>
+        </is>
+      </c>
+      <c r="Z12" s="2">
         <v>46254</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>1</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD12" s="2">
+      <c r="AE12" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -2233,7 +2293,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2246,28 +2306,33 @@
           <t>044155</t>
         </is>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>4615698</t>
+        </is>
+      </c>
+      <c r="Z13" s="2">
         <v>46254</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>1</v>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD13" s="2">
+      <c r="AE13" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -2389,28 +2454,33 @@
           <t>266744</t>
         </is>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>4615692</t>
+        </is>
+      </c>
+      <c r="Z14" s="2">
         <v>46253</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>2</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD14" s="2">
+      <c r="AE14" s="2">
         <v>46256</v>
       </c>
     </row>
@@ -2537,28 +2607,33 @@
           <t>440290</t>
         </is>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>4615690</t>
+        </is>
+      </c>
+      <c r="Z15" s="2">
         <v>46253</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>2</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD15" s="2">
+      <c r="AE15" s="2">
         <v>46261</v>
       </c>
     </row>
@@ -2683,28 +2758,33 @@
           <t>293859</t>
         </is>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>4615676</t>
+        </is>
+      </c>
+      <c r="Z16" s="2">
         <v>46252</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>3</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD16" s="2">
+      <c r="AE16" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -2829,28 +2909,33 @@
           <t>293859</t>
         </is>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>4615672</t>
+        </is>
+      </c>
+      <c r="Z17" s="2">
         <v>46252</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>3</v>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD17" s="2">
+      <c r="AE17" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -2977,28 +3062,33 @@
           <t>245696</t>
         </is>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>4615669</t>
+        </is>
+      </c>
+      <c r="Z18" s="2">
         <v>46252</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>3</v>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD18" s="2">
+      <c r="AE18" s="2">
         <v>46258</v>
       </c>
     </row>
@@ -3123,28 +3213,33 @@
           <t>461581</t>
         </is>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>4615658</t>
+        </is>
+      </c>
+      <c r="Z19" s="2">
         <v>46252</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <v>3</v>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD19" s="2">
+      <c r="AE19" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -3271,28 +3366,33 @@
           <t>007721</t>
         </is>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>4615655</t>
+        </is>
+      </c>
+      <c r="Z20" s="2">
         <v>46252</v>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <v>3</v>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD20" s="2">
+      <c r="AE20" s="2">
         <v>46260</v>
       </c>
     </row>
@@ -3419,28 +3519,33 @@
           <t>488276</t>
         </is>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>4615652</t>
+        </is>
+      </c>
+      <c r="Z21" s="2">
         <v>46252</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>3</v>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD21" s="2">
+      <c r="AE21" s="2">
         <v>46259</v>
       </c>
     </row>
@@ -3567,28 +3672,33 @@
           <t>454453</t>
         </is>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>4615648</t>
+        </is>
+      </c>
+      <c r="Z22" s="2">
         <v>46252</v>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <v>3</v>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD22" s="2">
+      <c r="AE22" s="2">
         <v>46252</v>
       </c>
     </row>
@@ -3715,28 +3825,33 @@
           <t>285926</t>
         </is>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>4615646</t>
+        </is>
+      </c>
+      <c r="Z23" s="2">
         <v>46251</v>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <v>4</v>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD23" s="2">
+      <c r="AE23" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -3863,28 +3978,33 @@
           <t>265011</t>
         </is>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>4615644</t>
+        </is>
+      </c>
+      <c r="Z24" s="2">
         <v>46251</v>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <v>4</v>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD24" s="2">
+      <c r="AE24" s="2">
         <v>46258</v>
       </c>
     </row>
@@ -4011,28 +4131,33 @@
           <t>069538</t>
         </is>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>4615642</t>
+        </is>
+      </c>
+      <c r="Z25" s="2">
         <v>46251</v>
       </c>
-      <c r="Z25">
+      <c r="AA25">
         <v>4</v>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD25" s="2">
+      <c r="AE25" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -4154,28 +4279,33 @@
           <t>471823</t>
         </is>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>4615622</t>
+        </is>
+      </c>
+      <c r="Z26" s="2">
         <v>46251</v>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <v>4</v>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD26" s="2">
+      <c r="AE26" s="2">
         <v>46256</v>
       </c>
     </row>
@@ -4302,28 +4432,33 @@
           <t>460719</t>
         </is>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>4615615</t>
+        </is>
+      </c>
+      <c r="Z27" s="2">
         <v>46251</v>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <v>4</v>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD27" s="2">
+      <c r="AE27" s="2">
         <v>46253</v>
       </c>
     </row>
@@ -4450,28 +4585,33 @@
           <t>415003</t>
         </is>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>4615612</t>
+        </is>
+      </c>
+      <c r="Z28" s="2">
         <v>46251</v>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <v>4</v>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD28" s="2">
+      <c r="AE28" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -4598,28 +4738,33 @@
           <t>410194</t>
         </is>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>4615610</t>
+        </is>
+      </c>
+      <c r="Z29" s="2">
         <v>46251</v>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <v>4</v>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD29" s="2">
+      <c r="AE29" s="2">
         <v>46253</v>
       </c>
     </row>
@@ -4746,28 +4891,33 @@
           <t>079457</t>
         </is>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>4615609</t>
+        </is>
+      </c>
+      <c r="Z30" s="2">
         <v>46251</v>
       </c>
-      <c r="Z30">
+      <c r="AA30">
         <v>4</v>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD30" s="2">
+      <c r="AE30" s="2">
         <v>46253</v>
       </c>
     </row>
@@ -4894,28 +5044,33 @@
           <t>472623</t>
         </is>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>4615589</t>
+        </is>
+      </c>
+      <c r="Z31" s="2">
         <v>46251</v>
       </c>
-      <c r="Z31">
+      <c r="AA31">
         <v>4</v>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD31" s="2">
+      <c r="AE31" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -5042,28 +5197,33 @@
           <t>437012</t>
         </is>
       </c>
-      <c r="Y32" s="2">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>4615585</t>
+        </is>
+      </c>
+      <c r="Z32" s="2">
         <v>46251</v>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <v>4</v>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD32" s="2">
+      <c r="AE32" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -5185,28 +5345,33 @@
           <t>429132</t>
         </is>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>4615580</t>
+        </is>
+      </c>
+      <c r="Z33" s="2">
         <v>46251</v>
       </c>
-      <c r="Z33">
+      <c r="AA33">
         <v>4</v>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD33" s="2">
+      <c r="AE33" s="2">
         <v>46257</v>
       </c>
     </row>
@@ -5333,28 +5498,33 @@
           <t>411337</t>
         </is>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>4615579</t>
+        </is>
+      </c>
+      <c r="Z34" s="2">
         <v>46251</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>4</v>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD34" s="2">
+      <c r="AE34" s="2">
         <v>46251</v>
       </c>
     </row>
@@ -5481,28 +5651,33 @@
           <t>455619</t>
         </is>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>4615553</t>
+        </is>
+      </c>
+      <c r="Z35" s="2">
         <v>46248</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>7</v>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD35" s="2">
+      <c r="AE35" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -5629,28 +5804,33 @@
           <t>285926</t>
         </is>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>4615536</t>
+        </is>
+      </c>
+      <c r="Z36" s="2">
         <v>46247</v>
       </c>
-      <c r="Z36">
+      <c r="AA36">
         <v>8</v>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD36" s="2">
+      <c r="AE36" s="2">
         <v>46255</v>
       </c>
     </row>
@@ -5777,28 +5957,33 @@
           <t>493996</t>
         </is>
       </c>
-      <c r="Y37" s="2">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>4615525</t>
+        </is>
+      </c>
+      <c r="Z37" s="2">
         <v>46248</v>
       </c>
-      <c r="Z37">
+      <c r="AA37">
         <v>7</v>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD37" s="2">
+      <c r="AE37" s="2">
         <v>46257</v>
       </c>
     </row>
@@ -5925,28 +6110,33 @@
           <t>292658</t>
         </is>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>4615522</t>
+        </is>
+      </c>
+      <c r="Z38" s="2">
         <v>46247</v>
       </c>
-      <c r="Z38">
+      <c r="AA38">
         <v>8</v>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>46252</v>
       </c>
     </row>
@@ -6073,28 +6263,33 @@
           <t>417025</t>
         </is>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>4615505</t>
+        </is>
+      </c>
+      <c r="Z39" s="2">
         <v>46247</v>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <v>8</v>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD39" s="2">
+      <c r="AE39" s="2">
         <v>46251</v>
       </c>
     </row>
@@ -6216,28 +6411,33 @@
           <t>416269</t>
         </is>
       </c>
-      <c r="Y40" s="2">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>4615494</t>
+        </is>
+      </c>
+      <c r="Z40" s="2">
         <v>46246</v>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <v>9</v>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD40" s="2">
+      <c r="AE40" s="2">
         <v>46251</v>
       </c>
     </row>
@@ -6364,28 +6564,33 @@
           <t>071042</t>
         </is>
       </c>
-      <c r="Y41" s="2">
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>4615476</t>
+        </is>
+      </c>
+      <c r="Z41" s="2">
         <v>46246</v>
       </c>
-      <c r="Z41">
+      <c r="AA41">
         <v>9</v>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD41" s="2">
+      <c r="AE41" s="2">
         <v>46254</v>
       </c>
     </row>
@@ -6512,28 +6717,33 @@
           <t>466027</t>
         </is>
       </c>
-      <c r="Y42" s="2">
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>4615461</t>
+        </is>
+      </c>
+      <c r="Z42" s="2">
         <v>46245</v>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <v>10</v>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD42" s="2">
+      <c r="AE42" s="2">
         <v>46253</v>
       </c>
     </row>
@@ -6660,28 +6870,33 @@
           <t>292658</t>
         </is>
       </c>
-      <c r="Y43" s="2">
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4615434</t>
+        </is>
+      </c>
+      <c r="Z43" s="2">
         <v>46244</v>
       </c>
-      <c r="Z43">
+      <c r="AA43">
         <v>11</v>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD43" s="2">
+      <c r="AE43" s="2">
         <v>46253</v>
       </c>
     </row>
@@ -6808,28 +7023,33 @@
           <t>166553</t>
         </is>
       </c>
-      <c r="Y44" s="2">
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>4615329</t>
+        </is>
+      </c>
+      <c r="Z44" s="2">
         <v>46239</v>
       </c>
-      <c r="Z44">
+      <c r="AA44">
         <v>16</v>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD44" s="2">
+      <c r="AE44" s="2">
         <v>46252</v>
       </c>
     </row>
@@ -6951,28 +7171,33 @@
           <t>461581</t>
         </is>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>4615316</t>
+        </is>
+      </c>
+      <c r="Z45" s="2">
         <v>46238</v>
       </c>
-      <c r="Z45">
+      <c r="AA45">
         <v>17</v>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD45" s="2">
+      <c r="AE45" s="2">
         <v>46241</v>
       </c>
     </row>
@@ -7099,28 +7324,33 @@
           <t>292404</t>
         </is>
       </c>
-      <c r="Y46" s="2">
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>4615297</t>
+        </is>
+      </c>
+      <c r="Z46" s="2">
         <v>46238</v>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <v>17</v>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD46" s="2">
+      <c r="AE46" s="2">
         <v>46252</v>
       </c>
     </row>
@@ -7247,28 +7477,33 @@
           <t>411337</t>
         </is>
       </c>
-      <c r="Y47" s="2">
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>4615275</t>
+        </is>
+      </c>
+      <c r="Z47" s="2">
         <v>46237</v>
       </c>
-      <c r="Z47">
+      <c r="AA47">
         <v>18</v>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD47" s="2">
+      <c r="AE47" s="2">
         <v>46250</v>
       </c>
     </row>
@@ -7395,28 +7630,33 @@
           <t>410724</t>
         </is>
       </c>
-      <c r="Y48" s="2">
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>4615274</t>
+        </is>
+      </c>
+      <c r="Z48" s="2">
         <v>46237</v>
       </c>
-      <c r="Z48">
+      <c r="AA48">
         <v>18</v>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD48" s="2">
+      <c r="AE48" s="2">
         <v>46247</v>
       </c>
     </row>
@@ -7543,28 +7783,33 @@
           <t>016825</t>
         </is>
       </c>
-      <c r="Y49" s="2">
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>4615167</t>
+        </is>
+      </c>
+      <c r="Z49" s="2">
         <v>46232</v>
       </c>
-      <c r="Z49">
+      <c r="AA49">
         <v>23</v>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>N1 - Congnd15, Tienvt16</t>
         </is>
       </c>
-      <c r="AD49" s="2">
+      <c r="AE49" s="2">
         <v>46250</v>
       </c>
     </row>
@@ -7691,28 +7936,33 @@
           <t>290593</t>
         </is>
       </c>
-      <c r="Y50" s="2">
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>4615145</t>
+        </is>
+      </c>
+      <c r="Z50" s="2">
         <v>46231</v>
       </c>
-      <c r="Z50">
+      <c r="AA50">
         <v>24</v>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD50" s="2">
+      <c r="AE50" s="2">
         <v>46248</v>
       </c>
     </row>
@@ -7834,28 +8084,33 @@
           <t>450613</t>
         </is>
       </c>
-      <c r="Y51" s="2">
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>4615039</t>
+        </is>
+      </c>
+      <c r="Z51" s="2">
         <v>46227</v>
       </c>
-      <c r="Z51">
+      <c r="AA51">
         <v>28</v>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD51" s="2">
+      <c r="AE51" s="2">
         <v>46241</v>
       </c>
     </row>
@@ -7982,28 +8237,33 @@
           <t>034451</t>
         </is>
       </c>
-      <c r="Y52" s="2">
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>4614938</t>
+        </is>
+      </c>
+      <c r="Z52" s="2">
         <v>46223</v>
       </c>
-      <c r="Z52">
+      <c r="AA52">
         <v>32</v>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD52" s="2">
+      <c r="AE52" s="2">
         <v>46243</v>
       </c>
     </row>
@@ -8125,28 +8385,33 @@
           <t>418109</t>
         </is>
       </c>
-      <c r="Y53" s="2">
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>4614881</t>
+        </is>
+      </c>
+      <c r="Z53" s="2">
         <v>46223</v>
       </c>
-      <c r="Z53">
+      <c r="AA53">
         <v>32</v>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD53" s="2">
+      <c r="AE53" s="2">
         <v>46242</v>
       </c>
     </row>
@@ -8273,28 +8538,33 @@
           <t>447039</t>
         </is>
       </c>
-      <c r="Y54" s="2">
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>4614836</t>
+        </is>
+      </c>
+      <c r="Z54" s="2">
         <v>46219</v>
       </c>
-      <c r="Z54">
+      <c r="AA54">
         <v>36</v>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD54" s="2">
+      <c r="AE54" s="2">
         <v>46240</v>
       </c>
     </row>
@@ -8417,28 +8687,33 @@
           <t>061031</t>
         </is>
       </c>
-      <c r="Y55" s="2">
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>4614164</t>
+        </is>
+      </c>
+      <c r="Z55" s="2">
         <v>46199</v>
       </c>
-      <c r="Z55">
+      <c r="AA55">
         <v>56</v>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD55" s="2">
+      <c r="AE55" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -8565,28 +8840,33 @@
           <t>190116</t>
         </is>
       </c>
-      <c r="Y56" s="2">
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>4614161</t>
+        </is>
+      </c>
+      <c r="Z56" s="2">
         <v>46198</v>
       </c>
-      <c r="Z56">
+      <c r="AA56">
         <v>57</v>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD56" s="2">
+      <c r="AE56" s="2">
         <v>46232</v>
       </c>
     </row>
@@ -8713,28 +8993,33 @@
           <t>289758</t>
         </is>
       </c>
-      <c r="Y57" s="2">
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>4614075</t>
+        </is>
+      </c>
+      <c r="Z57" s="2">
         <v>46197</v>
       </c>
-      <c r="Z57">
+      <c r="AA57">
         <v>58</v>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD57" s="2">
+      <c r="AE57" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -8862,28 +9147,33 @@
           <t>285126</t>
         </is>
       </c>
-      <c r="Y58" s="2">
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>4613034</t>
+        </is>
+      </c>
+      <c r="Z58" s="2">
         <v>46168</v>
       </c>
-      <c r="Z58">
+      <c r="AA58">
         <v>87</v>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>N3 - Truongdv17, Duyph5</t>
         </is>
       </c>
-      <c r="AD58" s="2">
+      <c r="AE58" s="2">
         <v>46180</v>
       </c>
     </row>
@@ -9010,28 +9300,33 @@
           <t>084001</t>
         </is>
       </c>
-      <c r="Y59" s="2">
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>4612987</t>
+        </is>
+      </c>
+      <c r="Z59" s="2">
         <v>46167</v>
       </c>
-      <c r="Z59">
+      <c r="AA59">
         <v>88</v>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD59" s="2">
+      <c r="AE59" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -9151,28 +9446,33 @@
           <t>051104</t>
         </is>
       </c>
-      <c r="Y60" s="2">
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>4612554</t>
+        </is>
+      </c>
+      <c r="Z60" s="2">
         <v>46156</v>
       </c>
-      <c r="Z60">
+      <c r="AA60">
         <v>99</v>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>N4 - Nhungntt27, Anhnt631</t>
         </is>
       </c>
-      <c r="AD60" s="2">
+      <c r="AE60" s="2">
         <v>46197</v>
       </c>
     </row>
@@ -9299,28 +9599,33 @@
           <t>057076</t>
         </is>
       </c>
-      <c r="Y61" s="2">
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>4612186</t>
+        </is>
+      </c>
+      <c r="Z61" s="2">
         <v>46146</v>
       </c>
-      <c r="Z61">
+      <c r="AA61">
         <v>109</v>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>N2 - Thaoltt16, Thikd</t>
         </is>
       </c>
-      <c r="AD61" s="2">
+      <c r="AE61" s="2">
         <v>46205</v>
       </c>
     </row>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE2" s="2">
@@ -816,7 +816,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE3" s="2">
@@ -967,7 +967,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE4" s="2">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE5" s="2">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE6" s="2">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE7" s="2">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE8" s="2">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE9" s="2">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE10" s="2">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE11" s="2">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE12" s="2">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE13" s="2">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE14" s="2">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE15" s="2">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE16" s="2">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE17" s="2">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE18" s="2">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE19" s="2">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE20" s="2">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE21" s="2">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE22" s="2">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE23" s="2">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE24" s="2">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE25" s="2">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE26" s="2">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE27" s="2">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE28" s="2">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE29" s="2">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE30" s="2">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE31" s="2">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE32" s="2">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE33" s="2">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE34" s="2">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE35" s="2">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE36" s="2">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE37" s="2">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE38" s="2">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE39" s="2">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE40" s="2">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE41" s="2">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE42" s="2">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE43" s="2">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE44" s="2">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE45" s="2">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE46" s="2">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE47" s="2">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE48" s="2">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE49" s="2">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE50" s="2">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE51" s="2">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE52" s="2">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>N1 - Congnd15, Tienvt16</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE53" s="2">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE54" s="2">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE55" s="2">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE56" s="2">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE57" s="2">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE58" s="2">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>N3 - Truongdv17, Duyph5</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE59" s="2">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE60" s="2">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>N4 - Nhungntt27, Anhnt631</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE61" s="2">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>N2 - Thaoltt16, Thikd</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE62" s="2">

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AE47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -522,12 +522,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_AGG_1663371</t>
+          <t>KHCN_TT.GPTH_BGG_1335039</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -567,17 +567,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Cũng</t>
+          <t>Phạm Văn Trọng</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0918526462</t>
+          <t>0368067663</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95 Trương Vĩnh Ký</t>
+          <t>Thôn Hưng Đạo,Xã Đông Lỗ (cũ)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -602,24 +602,24 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. KH dùng 2 đồng hồ với thời gian chuyển đổi công tơ là 15 ngày tuy nhiên hết 15 ngày không chuyển đổi mà nhảy CB dẫn đến mất điện NLMT
-3. KH cần CNCT liên hệ và đến hỗ trợ sớm</t>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: mất kết nối ko vào được app theo dõi nlmt 
+3. KH yêu cầu: qua kiểm tra, hỗ trợ KH kết nối lại app</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-24 14:25:00</t>
+          <t>2026-08-25 08:00:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-25 14:25:00</t>
+          <t>2026-08-26 09:00:00</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -634,21 +634,21 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Phạm Tứ Thiện Tâm</t>
+          <t>Nguyễn Trọng Tạ</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>189073</t>
+          <t>075226</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>4615830</t>
+          <t>4615836</t>
         </is>
       </c>
       <c r="Z2" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -665,401 +665,862 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE2" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_KHA_1638770</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Phạm Đình Văn</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0971895577</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Mỹ Lợi</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Lắp đặt không đảm bảo</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN: về các phản ánh trước TT_1781057405553
+2. KH phản ánh: hiện tại KH theo dõi trên app thấy chạy ra ngoài điện lưới trước đó anh Văn Hoàng - quản lý khu vực có cho a Thái Ngọc đến xử lý sự cố nhưng khi lắp đặt lại thì thấy ko đúng so với thiết kế và hệ nlmt giờ cũng ko sử dụng được chỉ thấy dùng điện lưới
++ Thiếu thiết bị chống sét, thấy tháo ra còn giờ ko thấy luôn
++ Thiếu CB tổng, biến tần chạy nhưng điện ko qua biến tần, chạy trực tiếp từ điện lưới
+3. KH yêu cầu: qua kiểm tra, đấu nối lại tủ điện cho đúng để KH sử dụng được nlmt</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-25 08:00:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:00:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tán Minh Hoàng Long</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>008016</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4615834</t>
+        </is>
+      </c>
+      <c r="Z3" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Đăng</t>
+        </is>
+      </c>
+      <c r="AE3" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_HPG_1628819</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Phạm Văn Hương</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0395074737</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Thôn Minh Hưng</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN
+2. KH phản ánh: pin lưu trữ ko nạp vào ko xả ra
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:08:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:08:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nguyễn Tiến Mạnh</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>182255</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4615832</t>
+        </is>
+      </c>
+      <c r="Z4" s="2">
+        <v>46258</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE4" s="2">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_TNN_1684307</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nhuyễn Văn Hùng</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0972772168</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TDP Trung Thành 7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Lắp đặt không đảm bảo</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN: KT tên Thân
+2. KH phản ánh: dùng 2 công tơ chạy điện 3 pha, khi lắp đảo chiều không đẩy bù điện nlmt dẫn đến điện tăng. KT đã qua hỗ trợ nhưng KH yêu cầu KT chịu hoàn toàn trách nhiệm, CN cũng đã hẹn nhiều ngày xuống giải quyết nhưng ko xuống, KH đánh giá CN thiếu trách nhiệm
+3. KH yêu cầu: Đại diện CN Thái Nguyên xuống làm việc với KH</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:45:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:45:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thao</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>289758</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>4615831</t>
+        </is>
+      </c>
+      <c r="Z5" s="2">
+        <v>46258</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE5" s="2">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DTP_1683398</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NGUYỄN NGỌC HUY</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0348470707</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ấp tân ninh</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Thiếu thiết bị đi kèm/Lắp đặt sai quy cách</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1. KH đã báo CN
+2. KH phản ánh: lắp thiếu cầu giao chống sét, CN đã xuống kiểm tra chất lượng thì mới biết thiếu
+3. KH yêu cầu: hoàn thiện lắp đặt đảm bảo an toàn cho KH</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:35:00</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:35:00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trần Duy Khánh</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>422532</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>4615817</t>
+        </is>
+      </c>
+      <c r="Z6" s="2">
+        <v>46258</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="AE6" s="2">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>290902-2968-KD/HĐMBLÐ-2025/CNCTDNI-STRIDESOLAR</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Nguyễn Thị Thu Hương</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0376664322</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Tổ 14, ấp Láng Lớn, xã Cẩm Mỹ, Đồng Nai</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1. Đối tác báo sự cố cho KH
 2.Do KH đổi Wifi nên App theo dõi hiệu suất NLMT không kết nối được, Hệ thống sản xuất điện rất ít
 3. KH cần CNCT hỗ trợ kiểm tra tấm pin, kết nối App theo dõi hiệu suất sớm</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-08-24 13:30:00</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2026-08-25 13:30:00</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Phan Khắc Lương</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>074938</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ngô Minh Hoàng</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>119059</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>4615816</t>
         </is>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z7" s="2">
         <v>46258</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE3" s="2">
+      <c r="AE7" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1635605</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_NAN_1682943</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Cao Kỳ Ngộ</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0977727894</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Xóm Khoa Đà, Xã Hưng Nguyên, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Phạm Đình Phương</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0911141678</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Khối Lam Thanh</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1. KH chưa liên hệ CN
-2. KH không theo dõi được hiệu suất HT NLMT trên App
-3. KH cần CN hỗ trợ khắc phục sớm</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:54:00</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-08-25 11:54:00</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Nguyễn Đình Tuấn</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>427222</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>4615815</t>
-        </is>
-      </c>
-      <c r="Z4" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE4" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1682943</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Phạm Đình Phương</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0911141678</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Khối Lam Thanh</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>1. CN báo sự cố cho KH
 2. Ắc quy lưu trữ còn 80% nhưng ko xả, không có sản lượng điện NLMT
@@ -1067,500 +1528,46 @@
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-08-24 11:09:00</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-08-25 11:09:00</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Trần Văn Việt</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>044155</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>4615814</t>
-        </is>
-      </c>
-      <c r="Z5" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE5" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DVKT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Home Service</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Bảo dưỡng Điều hòa treo tường (9.000BTU ÷ 12.000 BTU)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VCC_HS_CMU_1786800483199</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Nguyễn Bích Tuyền</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0915527547</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Huỳnh Thúc Kháng, Phường Hòa Thành, Tỉnh Cà Mau</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Sau bảo dưỡng thiết bị bị hỏng</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1. KH đã báo CN (Nhân sự KT xử lý đơn hàng Lương Nhật Hào
-495282)
-2. Nội dung PA:  Sau bảo dưỡng điều hòa nhân viên KT lắp ráp dàn lạnh không khít, KT hẹn qua khắc phục không qua, KH nhắn tin không trả lời.
-3. CN cắt cử nhân sự qua khắc phục cho KH</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2026-08-24 09:20:00</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:20:00</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Lê Vủ Luân</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>248306</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>4615813</t>
-        </is>
-      </c>
-      <c r="Z6" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>HS</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="AE6" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNI_1633841</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Dương Văn Cao</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0912837489</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>846 Bạch Đằng</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1. CN báo sự cố cho KH
-2.Hiệu suất HT NLMT của KH chỉ đạt hơn 10 số điện, trung bình cần đạt hơn 30 số
-3. KH cần CN liên hệ và đến kiểm tra sớm</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2026-08-24 13:30:00</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:30:00</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Vũ Bá Mạnh</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>463951</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>4615807</t>
-        </is>
-      </c>
-      <c r="Z7" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE7" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DNI_1711273</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Lê Điền</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0839074679</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ấp 2 xuân đường TpĐồng Nai</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.KH đã liên hệ CN
-2. KH cần CN hỗ trợ cung cấp hồ sơ kỹ thuật và các chứng từ liên quan đến HT NLMT để có thể thông tin cho bên điện lực</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2026-08-24 11:49:00</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-08-25 11:49:00</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Trần Hải Tùng</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>245696</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>4615806</t>
         </is>
       </c>
       <c r="Z8" s="2">
         <v>46258</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1574,7 +1581,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE8" s="2">
@@ -1584,284 +1591,278 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNI_1711273</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lê Điền</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0839074679</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ấp 2 xuân đường TpĐồng Nai</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hỗ trợ</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.KH đã liên hệ CN
+2. KH cần CN hỗ trợ cung cấp hồ sơ kỹ thuật và các chứng từ liên quan đến HT NLMT để có thể thông tin cho bên điện lực</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:49:00</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-08-28 14:05:00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Trong hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Trần Hải Tùng</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>245696</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>4615806</t>
+        </is>
+      </c>
+      <c r="Z9" s="2">
+        <v>46258</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="AE9" s="2">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DNG</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNG_1670030</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Nguyễn Văn Quý</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0932534811</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>12 Phan Văn Đáng</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>1. KH chưa liên hệ CN
 2. Hiện nhà KH vẫn có điện lưới và điện NLMT tuy nhiên không thấy hiển thị thông tin trên App và Tủ điện, thời gian trước nhân sự Thái có hỗ trợ cho KH
 3. KH cần CNCT hỗ trợ khắc phục sớm</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-08-24 08:18:00</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-08-25 08:18:00</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-08-25 18:40:00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Lê Văn Hậu</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>488276</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>4615801</t>
-        </is>
-      </c>
-      <c r="Z9" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>Đăng</t>
-        </is>
-      </c>
-      <c r="AE9" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_NAN_1616022</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Nguyễn Anh Tuấn</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0985655492</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>xóm Hưng Nhân, Xã Xuân Lam, Huyện Hưng Nguyên, Tỉnh Nghệ An</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>KH chưa báo KT
-KH báo sự cố không theo dõi được hiệu suất NLMT qua app, vào app không hiển thị thông tin gì 
-Yêu cầu CN cho KT qua ktra hõ trợ cho KH</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2026-08-24 13:30:00</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:30:00</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Nguyễn Đình Tuấn</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>427222</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4615794</t>
         </is>
       </c>
       <c r="Z10" s="2">
         <v>46258</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -1875,7 +1876,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE10" s="2">
@@ -1992,7 +1993,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2014,7 +2015,7 @@
         <v>46258</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2038,12 +2039,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2063,7 +2064,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>010402-GP&amp;DVKT/GPTH/HĐMB-2024/KHA-TAVANSONLONG</t>
+          <t>KHCN_TT.GPTH_BNH_1699993</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2071,6 +2072,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -2078,17 +2084,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Tạ Văn Sơn Long</t>
+          <t>Nguyễn Công Công</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0973705677</t>
+          <t>0972870377</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Phường Nam Nha Trang</t>
+          <t>Yên Viên</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2098,7 +2104,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2113,14 +2119,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1. KH đã được CN đến kiểm tra tuy nhiên chưa hỗ trợ khắc phục dứt điểm
-2. Hiện 2 Pin lưu trữ của KH đang hoạt động chưa ổn định, 1 pin lưu trữ NLMT của KH dùng đến 11h là ngắt và dùng điện lưới sạc, Pin lưu trữ thứ 2 xả điện lúc 2h sáng đến 20% là dừng
-3. Hiện KH cần CNCT hỗ trợ thiết lập lại thời gian sạc và xả của Pin lưu trữ</t>
+          <t>1. KH đã được CNCT liên hệ và hướng dẫn xử lý sơ bộ
+2. 1 ATS chống sét trong tủ nguồn của KH có dấu hiệu bị chập, cháy
+3. KH cần CNCT hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2130,7 +2136,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:00:00</t>
+          <t>2026-08-25 18:35:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2145,28 +2151,28 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Phan Trọng Nghĩa</t>
+          <t>Phạm Văn Huy</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>234935</t>
+          <t>408869</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4615789</t>
+          <t>4615786</t>
         </is>
       </c>
       <c r="Z12" s="2">
         <v>46258</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2176,7 +2182,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Đăng</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE12" s="2">
@@ -2186,12 +2192,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2206,12 +2212,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HCM_1642483</t>
+          <t>KHCN_TT.GPTH_HYN_1639428</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2231,17 +2237,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nguyễn Việt Tuấn</t>
+          <t>Bùi Quang Vũ</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0898318593</t>
+          <t>0886102896</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Khu phố Hải Sơn, Xã Long Hải, Thành phố Hồ Chí Minh</t>
+          <t>Thôn Văn Tràng</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2266,14 +2272,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>KH chưa báo Cn 
-KH báo sự cố dù trời nắng rất to nhưng vẫn lấy điện lưới
-Yêu cầu Cn cho KT qua ktra xử lý cho KH</t>
+          <t>1. KH đã liên hệ CN
+2. Ăc quy lưu trữ chỉ sạc được khoảng 80%
+3. KH cần CNCT hỗ trợ đến kiểm tra sớm</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2283,39 +2289,39 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:00:00</t>
+          <t>2026-08-30 17:15:00</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Lê Đức Cảnh</t>
+          <t>Trần Minh Vương</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>291002</t>
+          <t>276581</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>4615788</t>
+          <t>4615785</t>
         </is>
       </c>
       <c r="Z13" s="2">
         <v>46258</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2329,11 +2335,11 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE13" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="14">
@@ -2344,7 +2350,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2364,7 +2370,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1699993</t>
+          <t>KHCN_TT.GPTH_HNM_1573163</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2374,7 +2380,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2384,17 +2390,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Nguyễn Công Công</t>
+          <t>Trần Văn Túy</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0972870377</t>
+          <t>0944220696</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Yên Viên</t>
+          <t>Phường Phủ Lý, Ninh Bình</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2419,14 +2425,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1. KH đã được CNCT liên hệ và hướng dẫn xử lý sơ bộ
-2. 1 ATS chống sét trong tủ nguồn của KH có dấu hiệu bị chập, cháy
-3. KH cần CNCT hỗ trợ kiểm tra và khắc phục sớm</t>
+          <t>1. KH đã liên hệ CN
+2. HT NLMT của KH có Pin lưu trữ tuy nhiên mất điện lưới là hệ thống dừng hoạt động
+3. KH cần CNCT đến kiểm tra sớm</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2441,7 +2447,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2451,24 +2457,24 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Phạm Văn Huy</t>
+          <t>Trần Văn Thành</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>408869</t>
+          <t>815150</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>4615786</t>
+          <t>4615782</t>
         </is>
       </c>
       <c r="Z14" s="2">
         <v>46258</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2497,7 +2503,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2512,12 +2518,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Acquy lưu trữ</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HYN_1639428</t>
+          <t>KHCN_TT.GPTH_TNN_1633636</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2537,17 +2543,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Bùi Quang Vũ</t>
+          <t>Nguyễn Minh Phúc</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0886102896</t>
+          <t>0868101535</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Thôn Văn Tràng</t>
+          <t>Cổng CNTT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2572,56 +2578,46 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Ăc quy lưu trữ chỉ sạc được khoảng 80%
-3. KH cần CNCT hỗ trợ đến kiểm tra sớm</t>
+          <t>KH báo Anh Thao KT nhưng chưa được hỗ trợ 
+KH báo sự cố hệ thống NLMT hiện tại không theo dõi được trên app, vào app chỉ thấy hiển thị màn hình trắng tinh
+Yêu cầu CN cho KT qua ktra hõ trợ KH</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-24 08:00:00</t>
+          <t>2026-08-24 13:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-30 17:15:00</t>
+          <t>2026-08-25 13:30:00</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Đang tiến hành</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Trần Minh Vương</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>276581</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>4615785</t>
+          <t>4615779</t>
         </is>
       </c>
       <c r="Z15" s="2">
         <v>46258</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -2639,18 +2635,18 @@
         </is>
       </c>
       <c r="AE15" s="2">
-        <v>46261</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2670,7 +2666,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNM_1573163</t>
+          <t>KHCN_TT.GPTH_AGG_1695678</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2680,7 +2676,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2690,17 +2686,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Trần Văn Túy</t>
+          <t>Lê Hồng Ân</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0944220696</t>
+          <t>0939801111</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Phường Phủ Lý, Ninh Bình</t>
+          <t>Tổ 18 Rạch Hàm, Hàm Ninh, Đặc khu Phú Quốc</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2710,7 +2706,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2720,19 +2716,18 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. HT NLMT của KH có Pin lưu trữ tuy nhiên mất điện lưới là hệ thống dừng hoạt động
-3. KH cần CNCT đến kiểm tra sớm</t>
+          <t>KH cần CN hỗ trợ cung cấp:
+Hóa đơn và các chứng từ liên quan đến HT NLMT, ngoài ra trong quá trình sử dụng khi KH bật, tắt một số CB trong tủ nguồn không thấy có tác động đến HT NLMT, cần CNCT giải đáp</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2747,7 +2742,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2757,24 +2752,24 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Dương Văn Tuất</t>
+          <t>Nguyễn Ngọc Hải</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>068916</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>4615782</t>
+          <t>4615773</t>
         </is>
       </c>
       <c r="Z16" s="2">
         <v>46258</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE16" s="2">
@@ -2798,12 +2793,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2818,12 +2813,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNN_1633636</t>
+          <t>KHCN_TT.GPTH_TTH_1611393</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2833,7 +2828,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2843,17 +2838,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Phúc</t>
+          <t>Hồ Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0868101535</t>
+          <t>0966929265</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cổng CNTT</t>
+          <t>Hương Văn, Phường Hương Hương Trà Huế</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2878,29 +2873,29 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>KH báo Anh Thao KT nhưng chưa được hỗ trợ 
-KH báo sự cố hệ thống NLMT hiện tại không theo dõi được trên app, vào app chỉ thấy hiển thị màn hình trắng tinh
-Yêu cầu CN cho KT qua ktra hõ trợ KH</t>
+          <t>1. KH chưa liên hệ CN
+2. Biến tần của KH thông tin không có điện lưới trong khi nhà KH vẫn có điện, App theo dõi hiệu suất không có thông tin của HT NLMT từ đầu tháng
+3. KH cần CNCT hỗ trợ kiểm tra sớm</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 08:00:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-25 13:30:00</t>
+          <t>2026-08-25 09:00:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2910,24 +2905,24 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thao</t>
+          <t>Phạm Văn Kiện</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>289758</t>
+          <t>422329</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>4615779</t>
+          <t>4615758</t>
         </is>
       </c>
       <c r="Z17" s="2">
         <v>46258</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -2941,7 +2936,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE17" s="2">
@@ -2951,12 +2946,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2976,7 +2971,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_AGG_1695678</t>
+          <t>KHCN_TT.GPTH_BGG_1335514</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2996,17 +2991,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lê Hồng Ân</t>
+          <t>Nguyễn Thích Điện</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0939801111</t>
+          <t>0978586057</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Tổ 18 Rạch Hàm, Hàm Ninh, Đặc khu Phú Quốc</t>
+          <t>Xã Quang Thịnh,Huyện Lạng Giang (cũ)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3026,33 +3021,34 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>KH cần CN hỗ trợ cung cấp:
-Hóa đơn và các chứng từ liên quan đến HT NLMT, ngoài ra trong quá trình sử dụng khi KH bật, tắt một số CB trong tủ nguồn không thấy có tác động đến HT NLMT, cần CNCT giải đáp</t>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: mất kết nối, ko đăng nhập được app theo dõi
+3. KH yêu cầu: qua hỗ trợ KH kết nối lại app</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-24 08:00:00</t>
+          <t>2026-08-21 09:10:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:00:00</t>
+          <t>2026-08-26 09:55:00</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3062,24 +3058,24 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Nguyễn Ngọc Hải</t>
+          <t>Vũ Hà Thanh</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>111519</t>
+          <t>007721</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>4615773</t>
+          <t>4615728</t>
         </is>
       </c>
       <c r="Z18" s="2">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -3093,11 +3089,11 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE18" s="2">
-        <v>46258</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="19">
@@ -3108,7 +3104,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3118,17 +3114,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>M&amp;E</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Thang máy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1605266</t>
+          <t>10092025-GP&amp;DVKT/HĐMBLĐ-2025/HNI-NGUYENNGOCDUONG</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3148,17 +3144,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Phan Cao Cường</t>
+          <t>Nguyễn Ngọc Dương</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0971739656</t>
+          <t>0909289598</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Xã Lam Thành</t>
+          <t>Phương Xuân Phương</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3178,34 +3174,32 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Phàn nàn, Góp Ý</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Chất lượng, dịch vụ, Giá cả</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Khi KH tắt ATS điện lưới thì hệ thống sẽ dừng hoạt động, không xả điện từ Pin lưu trữ dù còn điện, Khi KH theo dõi thì không có hiển thị công suất điện lưới dù tại thời điểm theo dõi điện lưới vẫn hoạt động
-3. KH cần CNCT liên hệ và kiểm tra cho KH vào ngày 24/08</t>
+          <t>KH phản ánh gay gắt và rất bức xúc do Thang máy liên tục gặp sự cố dừng, kẹt và không hoạt động, ngày 20/08 KH bị kẹt trong thang máy 5 phút và rất lo ngại trường hợp trẻ nhỏ trong gia đình gặp sự cố với thiết bị, Yêu cầu CNCT có phương hướng xử lý khắc phục dứt điểm cho KH</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-24 08:00:00</t>
+          <t>2026-08-21 08:00:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:00:00</t>
+          <t>2026-08-28 16:55:00</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3215,28 +3209,28 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Lê Công Hoàng</t>
+          <t>Ngô Đức Tân</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>160675</t>
+          <t>484844</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>4615768</t>
+          <t>4615724</t>
         </is>
       </c>
       <c r="Z19" s="2">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3256,12 +3250,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HUE</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3276,12 +3270,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TTH_1611393</t>
+          <t>KHCN_TT.GPTH_PTO_1654586</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3291,7 +3285,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3301,17 +3295,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Hồ Thị Mỹ Hạnh</t>
+          <t>Vũ Hồng Lạc</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0966929265</t>
+          <t>0947304568</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Hương Văn, Phường Hương Hương Trà Huế</t>
+          <t>Thiên nga 3-206, Vinhomes cổ loa, xã Xuân Canh, Đông Hội, Mai Lâm, huyện Đông Anh, thành phố Hà Nội (Vinhomes Global Gate), Vinhomes cổ loa</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3336,24 +3330,24 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Biến tần của KH thông tin không có điện lưới trong khi nhà KH vẫn có điện, App theo dõi hiệu suất không có thông tin của HT NLMT từ đầu tháng
-3. KH cần CNCT hỗ trợ kiểm tra sớm</t>
+          <t>1. KH đã báo CN
+2. KH phản ánh: thi thoảng ngắt kết nối app theo dõi nlmt, hiện lỗi "giao tiếp giữa nhà máy và thiết bị bị ngắt kết nối"
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-24 08:00:00</t>
+          <t>2026-08-20 10:33:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:00:00</t>
+          <t>2026-09-10 10:10:00</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3363,29 +3357,29 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Phạm Văn Kiện</t>
+          <t>Lê Trung Kiên</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>422329</t>
+          <t>119420</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>4615758</t>
+          <t>4615711</t>
         </is>
       </c>
       <c r="Z20" s="2">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -3399,11 +3393,11 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Đăng</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE20" s="2">
-        <v>46258</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="21">
@@ -3414,7 +3408,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3434,7 +3428,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNN_1709791</t>
+          <t>KHCN_TT.GPTH_HNI_1685619</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3444,7 +3438,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3454,22 +3448,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PHẠM THÁI HƯNG</t>
+          <t>Trần Tuấn Việt</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0979806040</t>
+          <t>0982296655</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Tổ 7</t>
+          <t>Vườn Đào Tuấn Việt, SN 15, Ngõ 264/18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3484,28 +3478,29 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Hướng dẫn, hỗ trợ sử dụng sản phẩm</t>
+          <t>Hiệu suất sản phẩm kém</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.KH chưa liên hệ CN
-2. KH cần CNCT hỗ trợ kiểm tra HT NLMT đã lắp đặt đầy đủ hạng mục tiếp địa hay chưa</t>
+          <t>KH đã báo KT 
+KH báo sự cố:  Biến tần tự động ngắt/dừng hoạt động mỗi khi điện nguồn vào bị tụt xuống dưới 180V. Khi đó, hệ thống tự động chuyển sang dùng 100% điện lưới thay vì dùng điện mặt trời. Hệ thống chỉ chạy điện mặt trời khi ngắt/tắt thủ công nguồn điện lưới. Hệ thống điện mặt trời gần như không có tác dụng (90% thời gian từ lúc lắp đặt vẫn phải dùng điện lưới), tiền điện mỗi tháng không giảm so với trước (vẫn hơn 3 triệu/tháng).
+Yêu cầu CN cho KT qua ktra lại và xử lý cho KH</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-21 17:24:00</t>
+          <t>2026-08-20 10:03:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:35:00</t>
+          <t>2026-09-03 18:25:00</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3515,29 +3510,29 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Đào Quyết Chiến</t>
+          <t>Hoàng Văn Vương</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>085573</t>
+          <t>285732</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>4615757</t>
+          <t>4615710</t>
         </is>
       </c>
       <c r="Z21" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="AA21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -3555,7 +3550,7 @@
         </is>
       </c>
       <c r="AE21" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="22">
@@ -3566,7 +3561,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3586,7 +3581,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BGG_1335514</t>
+          <t>250501-KD/GPTH/HĐMBLĐ-2022/HBH-VUVIETTUNG</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3594,11 +3589,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3606,17 +3596,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nguyễn Thích Điện</t>
+          <t>Vũ Việt Tùng</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0978586057</t>
+          <t>0989463899</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Xã Quang Thịnh,Huyện Lạng Giang (cũ)</t>
+          <t>Khu 7 -Xã Lạc Thủy - Phú Thọ</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3626,7 +3616,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3641,24 +3631,24 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mất kết nối, ko đăng nhập được app theo dõi
-3. KH yêu cầu: qua hỗ trợ KH kết nối lại app</t>
+          <t>1. KH đã báo CN: a Dũng
+2. KH phản ánh: toàn bộ sản lượng điện nlmt lên hết điện lưới, có báo CN và KT hỗ trợ cài đặt từ xa nhưng vẫn chưa khắc phục được
+3. KH yêu cầu: qua kiểm tra trực tiếp và khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:00</t>
+          <t>2026-08-19 11:20:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-08-26 09:55:00</t>
+          <t>2026-08-25 09:15:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3673,28 +3663,28 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Vũ Hà Thanh</t>
+          <t>Lê Hoàng Chung</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>007721</t>
+          <t>266744</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4615728</t>
+          <t>4615692</t>
         </is>
       </c>
       <c r="Z22" s="2">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="AA22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3708,18 +3698,18 @@
         </is>
       </c>
       <c r="AE22" s="2">
-        <v>46257</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3729,17 +3719,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>M&amp;E</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Thang máy</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10092025-GP&amp;DVKT/HĐMBLĐ-2025/HNI-NGUYENNGOCDUONG</t>
+          <t>KHCN_TT.GPTH_CTO_1703516</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3759,22 +3749,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nguyễn Ngọc Dương</t>
+          <t>Nguyễn Hân Hoan</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0909289598</t>
+          <t>0981205207</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Phương Xuân Phương</t>
+          <t>ấp tân thành</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3789,27 +3779,29 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Phàn nàn, Góp Ý</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>KH phản ánh gay gắt và rất bức xúc do Thang máy liên tục gặp sự cố dừng, kẹt và không hoạt động, ngày 20/08 KH bị kẹt trong thang máy 5 phút và rất lo ngại trường hợp trẻ nhỏ trong gia đình gặp sự cố với thiết bị, Yêu cầu CNCT có phương hướng xử lý khắc phục dứt điểm cho KH</t>
+          <t>1. CN báo sự cố cho KH
+2. Biến tần báo lỗi COM báo đỏ
+3. KH cần CN kiểm tra và khăc phục sớm</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-21 08:00:00</t>
+          <t>2026-08-19 09:49:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-08-28 16:55:00</t>
+          <t>2026-09-04 22:20:00</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3819,33 +3811,33 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Ngô Đức Tân</t>
+          <t>Trương Minh Khoa</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>484844</t>
+          <t>440290</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>4615724</t>
+          <t>4615690</t>
         </is>
       </c>
       <c r="Z23" s="2">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="AA23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3855,11 +3847,11 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE23" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="24">
@@ -3890,7 +3882,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNI_0919577</t>
+          <t>KHCN_TT.GPTH_DNI_1675332</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3898,6 +3890,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3905,22 +3902,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Đỗ Văn Định</t>
+          <t>Nguyễn Trọng Thuỷ</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0909803787</t>
+          <t>0986565857</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ấp 1, Xã Tân Hiệp, Huyện Long Thành (cũ)</t>
+          <t>ấp 7</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3940,24 +3937,24 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Hội
-2. KH phản ánh: tắt hết tủ điện nhưng trên app theo dõi biểu đồ điện lươi vẫn vào 8-10kw
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+          <t>1. KH đã báo chi nhánh - Nhân viên Hải Tùng
+2. Nội dung sự cố: ATS bị cháy cầu trì, đã báo nhân sự Hải Tùng của chi nhánh nhưng chưa được xử lý. CN báo sẽ đổi ATS khác nhưng chưa có hàng, KH đã đợi khoảng hơn 2 tháng nhưng chưa được hỗ trợ.
+3. KHYC: CN hỗ trợ sớm (Viettel  báo giá 12tr KH đồng ý nhưng đợi lâu chưa được thay, KH cần hỗ trợ gấp do gia đình kinh doanh nhà nghỉ KS)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-20 13:30:00</t>
+          <t>2026-08-18 09:09:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-08-29 17:00:00</t>
+          <t>2026-08-31 17:00:00</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3972,24 +3969,24 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Phùng Duy San</t>
+          <t>Trần Hải Tùng</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>054647</t>
+          <t>245696</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>4615716</t>
+          <t>4615669</t>
         </is>
       </c>
       <c r="Z24" s="2">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="AA24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
@@ -4018,7 +4015,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4038,37 +4035,37 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_PTO_1654586</t>
+          <t>KHDN_NLMT_BNH_0171103</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Vũ Hồng Lạc</t>
+          <t>NGUYỄN VĂN ÍCH</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0947304568</t>
+          <t>0987363058</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Thiên nga 3-206, Vinhomes cổ loa, xã Xuân Canh, Đông Hội, Mai Lâm, huyện Đông Anh, thành phố Hà Nội (Vinhomes Global Gate), Vinhomes cổ loa</t>
+          <t>Thị trấn Lim, Huyện Tiên Du, Tỉnh Bắc Ninh</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4088,29 +4085,27 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: thi thoảng ngắt kết nối app theo dõi nlmt, hiện lỗi "giao tiếp giữa nhà máy và thiết bị bị ngắt kết nối"
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+          <t>Phản ánh từ trước TT_1783915287625 CN đã có BBLV với KH về thiết bị ivt mang đi bảo hành và xác nhận thời điểm lắp đặt lại thiết bị là 15/8 nhưng đến hiện tại là 18/8 KH vẫn chưa thấy có thông tin gì. KH rất bức xúc yêu cầu CN liên hệ là xuống lắp đặt cho KH theo BBLV</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-20 10:33:00</t>
+          <t>2026-08-18 11:15:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-10 10:10:00</t>
+          <t>2026-08-25 18:40:00</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4120,29 +4115,29 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Lê Trung Kiên</t>
+          <t>Nguyễn Văn Tuần</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>119420</t>
+          <t>461581</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>4615711</t>
+          <t>4615658</t>
         </is>
       </c>
       <c r="Z25" s="2">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="AA25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
@@ -4160,7 +4155,7 @@
         </is>
       </c>
       <c r="AE25" s="2">
-        <v>46264</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="26">
@@ -4171,7 +4166,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4191,7 +4186,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNI_1685619</t>
+          <t>KHCN_TT.GPTH_BNH_1665718</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4201,7 +4196,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4211,22 +4206,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Trần Tuấn Việt</t>
+          <t>Chu Văn Thao</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0982296655</t>
+          <t>0969032689</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Vườn Đào Tuấn Việt, SN 15, Ngõ 264/18</t>
+          <t>Thôn Ngoẹn</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4241,29 +4236,29 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>KH đã báo KT 
-KH báo sự cố:  Biến tần tự động ngắt/dừng hoạt động mỗi khi điện nguồn vào bị tụt xuống dưới 180V. Khi đó, hệ thống tự động chuyển sang dùng 100% điện lưới thay vì dùng điện mặt trời. Hệ thống chỉ chạy điện mặt trời khi ngắt/tắt thủ công nguồn điện lưới. Hệ thống điện mặt trời gần như không có tác dụng (90% thời gian từ lúc lắp đặt vẫn phải dùng điện lưới), tiền điện mỗi tháng không giảm so với trước (vẫn hơn 3 triệu/tháng).
-Yêu cầu CN cho KT qua ktra lại và xử lý cho KH</t>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: hệ nlmt ko hoạt động, đèn ở pin lưu trữ và cả hệ đều thấy tắt
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-20 10:03:00</t>
+          <t>2026-08-18 09:07:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-03 18:25:00</t>
+          <t>2026-09-03 10:15:00</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4278,24 +4273,24 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Hoàng Văn Vương</t>
+          <t>Vũ Hà Thanh</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>285732</t>
+          <t>007721</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>4615710</t>
+          <t>4615655</t>
         </is>
       </c>
       <c r="Z26" s="2">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="AA26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -4313,18 +4308,18 @@
         </is>
       </c>
       <c r="AE26" s="2">
-        <v>46261</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4344,7 +4339,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>250501-KD/GPTH/HĐMBLĐ-2022/HBH-VUVIETTUNG</t>
+          <t>KHCN_TT.GPTH_KGG_1586960</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4352,6 +4347,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -4359,17 +4359,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Vũ Việt Tùng</t>
+          <t>Nguyễn Văn Non Em</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0989463899</t>
+          <t>0353397777</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Khu 7 -Xã Lạc Thủy - Phú Thọ</t>
+          <t>Xã Vĩnh Phước A,Huyện Gò Quao (cũ)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4389,29 +4389,29 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Lắp đặt không đảm bảo</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Dũng
-2. KH phản ánh: toàn bộ sản lượng điện nlmt lên hết điện lưới, có báo CN và KT hỗ trợ cài đặt từ xa nhưng vẫn chưa khắc phục được
-3. KH yêu cầu: qua kiểm tra trực tiếp và khắc phục tình trạng này</t>
+          <t>1. KH đã báo CN: anh Bang
+2. KH phản ánh: vừa mới đây KH phát hiện ra do thấy có mùi khét và đứt phần dây tiếp địa, KH có ra kiểm tra thì là cọc tiếp địa bằng sắt chứ không phải cọc đồng như trong HĐ. KH có trao đổi với anh Bang thì phản hồi là tính nhầm
+3. KH yêu cầu: thay thế cọc tiếp địa bằng đồng và giải trình vấn đề này cho KH</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-19 11:20:00</t>
+          <t>2026-08-17 17:03:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:15:00</t>
+          <t>2026-09-01 17:15:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4426,28 +4426,28 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Lê Hoàng Chung</t>
+          <t>Phạm Thanh Duy</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>266744</t>
+          <t>285926</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>4615692</t>
+          <t>4615646</t>
         </is>
       </c>
       <c r="Z27" s="2">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4457,22 +4457,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE27" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Hệ thống NLMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_CTO_1703516</t>
+          <t>KHCN_TT.GPTH_QNH_1655231</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4512,22 +4512,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Nguyễn Hân Hoan</t>
+          <t>Hà Văn Hiệp</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0981205207</t>
+          <t>0334263627</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ấp tân thành</t>
+          <t>Đông Hải</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4552,19 +4552,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. Biến tần báo lỗi COM báo đỏ
-3. KH cần CN kiểm tra và khăc phục sớm</t>
+          <t>1. KH đã báo CN: a Trường
+2. KH phản ánh: pin lưu trữ ko nạp vào ko xả ra
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-19 09:49:00</t>
+          <t>2026-08-17 15:03:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-04 22:20:00</t>
+          <t>2026-08-31 17:30:00</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4574,29 +4574,29 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Trương Minh Khoa</t>
+          <t>Đinh Mạnh Trường</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>440290</t>
+          <t>265011</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>4615690</t>
+          <t>4615644</t>
         </is>
       </c>
       <c r="Z28" s="2">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
@@ -4610,22 +4610,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE28" s="2">
-        <v>46261</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNI_1675332</t>
+          <t>KHCN_TT.GPTH_HNI_1648836</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4665,22 +4665,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Nguyễn Trọng Thuỷ</t>
+          <t>Lê Hữu Nghị</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0986565857</t>
+          <t>0398757686</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ấp 7</t>
+          <t>số 1 ngõ 136 đường Cổ Linh, Phường Long Biên, Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4700,24 +4700,24 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1. KH đã báo chi nhánh - Nhân viên Hải Tùng
-2. Nội dung sự cố: ATS bị cháy cầu trì, đã báo nhân sự Hải Tùng của chi nhánh nhưng chưa được xử lý. CN báo sẽ đổi ATS khác nhưng chưa có hàng, KH đã đợi khoảng hơn 2 tháng nhưng chưa được hỗ trợ.
-3. KHYC: CN hỗ trợ sớm (Viettel  báo giá 12tr KH đồng ý nhưng đợi lâu chưa được thay, KH cần hỗ trợ gấp do gia đình kinh doanh nhà nghỉ KS)</t>
+          <t>KH đã báo KT nhưng chưa được hỗ trợ
+KH báo sự cố hệ thống  có lắp bộ tủ đảo công tơ 15 ngày tự đảo. Gần đây hệ không đảo sau 15 ngày nữa
+Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-18 09:09:00</t>
+          <t>2026-08-17 08:00:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-08-31 17:00:00</t>
+          <t>2026-08-28 23:55:00</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4732,24 +4732,24 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Trần Hải Tùng</t>
+          <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>245696</t>
+          <t>292404</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>4615669</t>
+          <t>4615585</t>
         </is>
       </c>
       <c r="Z29" s="2">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -4763,22 +4763,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE29" s="2">
-        <v>46258</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4798,37 +4798,37 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KHDN_NLMT_BNH_0171103</t>
+          <t>KHCN_TT.GPTH_DLK_1648454</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NGUYỄN VĂN ÍCH</t>
+          <t>Huỳnh Chí Băng</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0987363058</t>
+          <t>0366448992</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Thị trấn Lim, Huyện Tiên Du, Tỉnh Bắc Ninh</t>
+          <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4848,27 +4848,29 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Tiến độ triển khai chậm</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Phản ánh từ trước TT_1783915287625 CN đã có BBLV với KH về thiết bị ivt mang đi bảo hành và xác nhận thời điểm lắp đặt lại thiết bị là 15/8 nhưng đến hiện tại là 18/8 KH vẫn chưa thấy có thông tin gì. KH rất bức xúc yêu cầu CN liên hệ là xuống lắp đặt cho KH theo BBLV</t>
+          <t>1. KH đã liên hệ CN
+2. Từ P/á mã TT_1786152323690, KH phản ánh sau khi CNCT đến kiểm tra và kết luận tủ cháy đã báo giá cho KH chi phí thay tủ là 50%, KH hiện đang không đồng ý do thiết bị vẫn trong hạn bảo hành
+3. KH cần CNCT liên hệ và có hướng khắc phục, xử lý cho KH gấp</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-18 11:15:00</t>
+          <t>2026-08-17 08:00:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-08-25 18:40:00</t>
+          <t>2026-08-18 09:00:00</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4878,29 +4880,29 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Tuần</t>
+          <t>Phạm Duy Bộ</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>461581</t>
+          <t>411337</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>4615658</t>
+          <t>4615579</t>
         </is>
       </c>
       <c r="Z30" s="2">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -4914,22 +4916,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE30" s="2">
-        <v>46255</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4949,12 +4951,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1665718</t>
+          <t>010401-KD/HĐMBLĐ/2025/TNH-BBMALL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4964,22 +4966,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Chu Văn Thao</t>
+          <t>Phạm Đức Thọ</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0969032689</t>
+          <t>0708666999</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Thôn Ngoẹn</t>
+          <t>Số 110, Đường Âu Cơ</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4989,7 +4991,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4999,7 +5001,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -5010,18 +5012,18 @@
       <c r="R31" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
-2. KH phản ánh: hệ nlmt ko hoạt động, đèn ở pin lưu trữ và cả hệ đều thấy tắt
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+2. KH phản ánh: hệ nlmt ko chạy được, hệ bám tải, có 2 pha chỉ 1 pha sáng, trên app kiểm tra ko thấy hoạt động
+3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-18 09:07:00</t>
+          <t>2026-08-14 11:18:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:00</t>
+          <t>2026-08-29 23:25:00</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -5031,33 +5033,33 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Vũ Hà Thanh</t>
+          <t>Nguyễn Đặng Vĩnh Phát</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>007721</t>
+          <t>455619</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>4615655</t>
+          <t>4615553</t>
         </is>
       </c>
       <c r="Z31" s="2">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5067,11 +5069,11 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE31" s="2">
-        <v>46260</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="32">
@@ -5102,7 +5104,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_KGG_1586960</t>
+          <t>KHCN_TT.GPTH_KGG_1571883</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -5112,7 +5114,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5122,17 +5124,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Non Em</t>
+          <t>Lê Đoan Thanh Khiết</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0353397777</t>
+          <t>0817585822</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Xã Vĩnh Phước A,Huyện Gò Quao (cũ)</t>
+          <t>Chợ 30/4</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -5152,29 +5154,29 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Khiếu nại</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Lắp đặt không đảm bảo</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: anh Bang
-2. KH phản ánh: vừa mới đây KH phát hiện ra do thấy có mùi khét và đứt phần dây tiếp địa, KH có ra kiểm tra thì là cọc tiếp địa bằng sắt chứ không phải cọc đồng như trong HĐ. KH có trao đổi với anh Bang thì phản hồi là tính nhầm
-3. KH yêu cầu: thay thế cọc tiếp địa bằng đồng và giải trình vấn đề này cho KH</t>
+          <t>CN 0967884099 báo sự cố hộ KH 
+1. KH phản ánh: pin lưu trữ bị lỗi ko vào điện
+2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-17 17:03:00</t>
+          <t>2026-08-13 17:14:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-08-24 18:35:00</t>
+          <t>2026-08-29 15:01:00</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -5199,14 +5201,14 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>4615646</t>
+          <t>4615536</t>
         </is>
       </c>
       <c r="Z32" s="2">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -5224,18 +5226,18 @@
         </is>
       </c>
       <c r="AE32" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5255,7 +5257,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_QNH_1655231</t>
+          <t>KHCN_TT.GPTH_BLU_1564891</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5275,17 +5277,17 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Hà Văn Hiệp</t>
+          <t>Phan Hoàng Triều</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0334263627</t>
+          <t>0942357900</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Đông Hải</t>
+          <t>Nhà máy</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -5305,7 +5307,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5315,19 +5317,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Trường
-2. KH phản ánh: pin lưu trữ ko nạp vào ko xả ra
+          <t>1. KH đã báo CN 
+2. KH phản ánh: KH có 2 ivt, hiện tại 1 ivt ko hoạt động
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-17 15:03:00</t>
+          <t>2026-08-13 16:21:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-08-31 17:30:00</t>
+          <t>2026-09-08 10:37:00</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5337,29 +5339,29 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Đinh Mạnh Trường</t>
+          <t>Lê Hoàng Thiên</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>265011</t>
+          <t>292658</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>4615644</t>
+          <t>4615522</t>
         </is>
       </c>
       <c r="Z33" s="2">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -5373,22 +5375,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE33" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5408,7 +5410,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNG_1674015</t>
+          <t>KHCN_TT.GPTH_DTP_1622998</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5428,17 +5430,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Nguyễn Năm</t>
+          <t>Lê Văn Hải</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0905640232</t>
+          <t>0918029932</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>138 Huỳnh Thúc Kháng</t>
+          <t>Khóm Trà Đư</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -5448,7 +5450,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5468,19 +5470,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>CN 0364023755 báo sự cố hộ KH
-1. KH phản ánh: 2,3 ngày nay hệ KH 10 tấm pin, 2 string nhưng hiện tại chỉ chạy được 5 tấm, 1 string
-2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
+          <t>CN 0973575722 báo sự cố hộ KH
+1. KH phản ánh: có 1 biến tần ko hoạt động, lỗi nhảy màn hình
+2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-17 14:24:00</t>
+          <t>2026-08-12 09:12:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-10 14:00:00</t>
+          <t>2026-08-29 14:50:00</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5490,29 +5492,29 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Việt</t>
+          <t>Lê Văn Quốc Bảo</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>069538</t>
+          <t>071042</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>4615642</t>
+          <t>4615476</t>
         </is>
       </c>
       <c r="Z34" s="2">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -5526,22 +5528,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Đăng</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE34" s="2">
-        <v>46263</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5561,7 +5563,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNI_1648836</t>
+          <t>KHCN_TT.GPTH_TNH_1678459</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5571,7 +5573,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5581,22 +5583,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Lê Hữu Nghị</t>
+          <t>Nguyễn Kim Vân</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0398757686</t>
+          <t>0946872682</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>số 1 ngõ 136 đường Cổ Linh, Phường Long Biên, Thành phố Hà Nội</t>
+          <t>số 10 Phạm Thị Đẩu</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5611,7 +5613,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5621,19 +5623,19 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>KH đã báo KT nhưng chưa được hỗ trợ
-KH báo sự cố hệ thống  có lắp bộ tủ đảo công tơ 15 ngày tự đảo. Gần đây hệ không đảo sau 15 ngày nữa
-Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
+          <t>1. KH chưa liên hệ CN
+2. App theo dõi HT NLMT của KH báo ngoại tuyến
+3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-17 08:00:00</t>
+          <t>2026-08-11 14:33:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-08-28 23:55:00</t>
+          <t>2026-08-27 20:23:00</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5648,24 +5650,24 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Nguyễn Hoàng Minh</t>
+          <t>Huỳnh Nhật Tiến</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>292404</t>
+          <t>466027</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>4615585</t>
+          <t>4615461</t>
         </is>
       </c>
       <c r="Z35" s="2">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -5679,22 +5681,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE35" s="2">
-        <v>46256</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5714,7 +5716,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DLK_1648454</t>
+          <t>KHCN_TT.GPTH_CMU_1693389</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5734,27 +5736,27 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Huỳnh Chí Băng</t>
+          <t>Đinh Văn Huân</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0366448992</t>
+          <t>0919102429</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
+          <t>Đường Tôn Đức Thắng, Khóm 17</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5764,7 +5766,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5774,19 +5776,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Từ P/á mã TT_1786152323690, KH phản ánh sau khi CNCT đến kiểm tra và kết luận tủ cháy đã báo giá cho KH chi phí thay tủ là 50%, KH hiện đang không đồng ý do thiết bị vẫn trong hạn bảo hành
-3. KH cần CNCT liên hệ và có hướng khắc phục, xử lý cho KH gấp</t>
+          <t>1.CN báo sự cố cho KH
+2. KH không theo dõi được hiệu suất NLMT trên App, chỉ số =0
+3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-17 08:00:00</t>
+          <t>2026-08-10 14:03:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-08-18 09:00:00</t>
+          <t>2026-08-29 17:13:00</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5796,29 +5798,29 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Phạm Duy Bộ</t>
+          <t>Lê Hoàng Thiên</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>411337</t>
+          <t>292658</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>4615579</t>
+          <t>4615434</t>
         </is>
       </c>
       <c r="Z36" s="2">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="AA36">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -5832,11 +5834,11 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Đăng</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE36" s="2">
-        <v>46251</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="37">
@@ -5847,7 +5849,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5857,57 +5859,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>M&amp;E</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Thang máy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KHDN_TT.GPTH_HNI_1703384</t>
+          <t>100601-XD/HĐXL-2025/BNH-HOANGTRONGHIEU</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Diamond</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NĂNG LƯỢNG XANH HANAPA</t>
+          <t>Hoàng Trọng Hiếu</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0988551979</t>
+          <t>0986912000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Số nhà 5</t>
+          <t>Thị trấn Đồi Ngô,Huyện Lục Nam,Tỉnh Bắc Giang</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -5917,30 +5914,29 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Minh
-2. KH phản ánh: mất điện lưới nhưng ko nhảy sang điện nlmt để sử dụng
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này
-Địa chỉ Lắp đặt:5/3 Phường Đình Bảng, Từ Sơn, Bắc Ninh</t>
+          <t>1. KH đã báo CN 
+2. KH chưa được hỗ trợ về việc lắp thang hàng và tiến độ về công trình đang bị chậm nửa năm rồi  KH muốn được đền bù HĐ
+3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-14 14:56:00</t>
+          <t>2026-08-04 14:20:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-08-25 08:35:00</t>
+          <t>2026-08-11 18:15:00</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5950,33 +5946,33 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Vinh</t>
+          <t>Nguyễn Văn Tuần</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>413306</t>
+          <t>461581</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>4615569</t>
+          <t>4615316</t>
         </is>
       </c>
       <c r="Z37" s="2">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5990,18 +5986,18 @@
         </is>
       </c>
       <c r="AE37" s="2">
-        <v>46253</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6016,42 +6012,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>010401-KD/HĐMBLĐ/2025/TNH-BBMALL</t>
+          <t>KHCN_TT.GPTH_HNI_1617012</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Khách hàng doanh nghiệp</t>
+          <t>Khách hàng cá nhân</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Phạm Đức Thọ</t>
+          <t>Hoàng Tiến Nam</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0708666999</t>
+          <t>0984556118</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Số 110, Đường Âu Cơ</t>
+          <t>Triệu xuyên 3, Long Xuyên</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -6071,7 +6067,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6081,19 +6077,19 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: hệ nlmt ko chạy được, hệ bám tải, có 2 pha chỉ 1 pha sáng, trên app kiểm tra ko thấy hoạt động
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
+          <t>1. KH đã liên hệ CN
+2. KH phản ánh Inverter của KH có thể bị ảnh hường bởi sét đánh, hiện không có điện lưới và điện NLMT
+3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-14 11:18:00</t>
+          <t>2026-08-04 16:07:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-08-29 23:25:00</t>
+          <t>2026-09-02 19:13:00</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -6108,28 +6104,28 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Nguyễn Đặng Vĩnh Phát</t>
+          <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>455619</t>
+          <t>292404</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>4615553</t>
+          <t>4615297</t>
         </is>
       </c>
       <c r="Z38" s="2">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6139,11 +6135,11 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE38" s="2">
-        <v>46255</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="39">
@@ -6154,7 +6150,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6174,7 +6170,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_KGG_1571883</t>
+          <t>KHCN_TT.GPTH_CMU_1423965</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -6194,17 +6190,17 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Lê Đoan Thanh Khiết</t>
+          <t>Anh Nghĩa</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0817585822</t>
+          <t>0919666690</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Chợ 30/4</t>
+          <t>Khóm 10,Thị trấn Sông Đốc,Huyện Trần Văn Thờ, Xã Trần Văn Thời, Tỉnh Cà Mau</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -6234,19 +6230,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>CN 0967884099 báo sự cố hộ KH 
-1. KH phản ánh: pin lưu trữ bị lỗi ko vào điện
-2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+          <t>KH chưa báo CN 
+KH phản ánh trên app đang báo lỗi mất điện NLMT và mất ắc quy, bị sáng nay 
+Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:14:00</t>
+          <t>2026-08-03 11:33:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-08-29 15:01:00</t>
+          <t>2026-09-05 14:05:00</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -6261,24 +6257,24 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Phạm Thanh Duy</t>
+          <t>Trần Hoàng Huy</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>285926</t>
+          <t>410724</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>4615536</t>
+          <t>4615274</t>
         </is>
       </c>
       <c r="Z39" s="2">
-        <v>46247</v>
+        <v>46237</v>
       </c>
       <c r="AA39">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -6296,18 +6292,18 @@
         </is>
       </c>
       <c r="AE39" s="2">
-        <v>46255</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6327,7 +6323,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BLU_1564891</t>
+          <t>KHCN_TT.GPTH_QNH_1644996</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -6347,17 +6343,17 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Phan Hoàng Triều</t>
+          <t>Vũ Tú</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0942357900</t>
+          <t>0967618822</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Nhà máy</t>
+          <t>Tổ 5 khu 5</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6367,7 +6363,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -6377,7 +6373,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6387,19 +6383,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN 
-2. KH phản ánh: KH có 2 ivt, hiện tại 1 ivt ko hoạt động
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+          <t>KH chưa báo CN 
+KH phản ánh điện NLMT của KH không hoạt động, mất điện là k sử dụng được luôn, kiểm tra trên hệ thống vẫn có điện
+Yêu cầu quản lý điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-13 16:21:00</t>
+          <t>2026-07-28 14:51:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-09-08 10:37:00</t>
+          <t>2026-08-31 17:00:00</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6409,29 +6405,29 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Lê Hoàng Thiên</t>
+          <t>Đào Minh Đức</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>292658</t>
+          <t>290593</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>4615522</t>
+          <t>4615145</t>
         </is>
       </c>
       <c r="Z40" s="2">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="AA40">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -6445,11 +6441,11 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE40" s="2">
-        <v>46260</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="41">
@@ -6460,7 +6456,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6480,17 +6476,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1709916</t>
+          <t>KHDN_TT.GPTH_HNI_1325140</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6500,17 +6496,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Hồ Thị Mai</t>
+          <t>CÔNG TY CỔ PHẦN ĐO ĐẠC VÀ BẢN ĐỒ PHÚC AN</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0978008192</t>
+          <t>0914335390</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>xóm 5</t>
+          <t>Khu tái định cư phía Bắc sông Thiếp,Xã Uy Nỗ,Huyện Đông Anh,Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6520,7 +6516,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -6530,7 +6526,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6540,19 +6536,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. HT NLMT của KH đang lỗi ATS không điều khiển được qua WIfi, hiện chưa thiết lập được
-3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
+          <t>1. KH đã báo CN 0969054066 
+2. KH phản ánh: KH theo dõi trên app tấm pin nlmt ko sản xuất ra điện, báo lỗi cung DC
+3. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-13 13:30:00</t>
+          <t>2026-07-16 16:12:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-08-24 18:30:00</t>
+          <t>2026-08-30 22:45:00</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6567,24 +6563,24 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Võ Ngọc Vinh</t>
+          <t>Nguyễn Ngọc Sơn</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>417025</t>
+          <t>447039</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>4615505</t>
+          <t>4614836</t>
         </is>
       </c>
       <c r="Z41" s="2">
-        <v>46247</v>
+        <v>46219</v>
       </c>
       <c r="AA41">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -6602,7 +6598,7 @@
         </is>
       </c>
       <c r="AE41" s="2">
-        <v>46252</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="42">
@@ -6613,7 +6609,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6633,7 +6629,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DTP_1622998</t>
+          <t>KHCN_TT.GPTH_DNI_1619779</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6653,22 +6649,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Lê Văn Hải</t>
+          <t>Bùi Quang Thuận</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0918029932</t>
+          <t>0913774928</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Khóm Trà Đư</t>
+          <t>Tân Phú Đồng Nai</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6693,19 +6689,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>CN 0973575722 báo sự cố hộ KH
-1. KH phản ánh: có 1 biến tần ko hoạt động, lỗi nhảy màn hình
-2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+          <t>1. KH đã liên hệ CN
+2. Khi mất điện lưới hệ thống NLMT của KH không nhảy ATS, Biến tần Inverter hiện rất nóng
+3. KH cần CN đến kiêm tra cho KH sớm</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-12 09:12:00</t>
+          <t>2026-06-25 15:40:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-08-29 14:50:00</t>
+          <t>2026-09-02 10:39:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6720,24 +6716,24 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Lê Văn Quốc Bảo</t>
+          <t>Nguyễn Văn Thi</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>071042</t>
+          <t>190116</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>4615476</t>
+          <t>4614161</t>
         </is>
       </c>
       <c r="Z42" s="2">
-        <v>46246</v>
+        <v>46198</v>
       </c>
       <c r="AA42">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -6755,18 +6751,18 @@
         </is>
       </c>
       <c r="AE42" s="2">
-        <v>46254</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6786,7 +6782,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNH_1678459</t>
+          <t>KHCN_TT.GPTH_TNN_1652755</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6796,7 +6792,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6806,17 +6802,17 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Nguyễn Kim Vân</t>
+          <t>Dương Minh Học</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0946872682</t>
+          <t>0984662540</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>số 10 Phạm Thị Đẩu</t>
+          <t>Thuần Pháp</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -6846,19 +6842,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. App theo dõi HT NLMT của KH báo ngoại tuyến
-3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
+          <t>KH chưa báo CN
+KH phản ánh 8 ngày nay NLMT k dùng được, k theo dõi được cả trên điện thoại và hệ thống, Kh giờ chỉ dùng dc điện lưới, KH đã báo cho anh Quý phụ trách lắp nhưng không phản hồi
+Yêu cầu KT liên hệ và xuống kiểm tra cho KH</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-11 14:33:00</t>
+          <t>2026-06-24 13:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-08-27 20:23:00</t>
+          <t>2026-07-27 13:10:00</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6868,29 +6864,29 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Huỳnh Nhật Tiến</t>
+          <t>Nguyễn Văn Thao</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>466027</t>
+          <t>289758</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>4615461</t>
+          <t>4614075</t>
         </is>
       </c>
       <c r="Z43" s="2">
-        <v>46245</v>
+        <v>46197</v>
       </c>
       <c r="AA43">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -6904,22 +6900,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE43" s="2">
-        <v>46253</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6939,7 +6935,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_CMU_1693389</t>
+          <t>KHCN_TT.GPTH_HCM_1624133</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6959,17 +6955,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Đinh Văn Huân</t>
+          <t>Nguyễn Văn Hạ</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0919102429</t>
+          <t>0971550074</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Đường Tôn Đức Thắng, Khóm 17</t>
+          <t>Thăng Long</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6989,7 +6985,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bảo hành</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6998,1225 +6994,6 @@
         </is>
       </c>
       <c r="R44" t="inlineStr">
-        <is>
-          <t>1.CN báo sự cố cho KH
-2. KH không theo dõi được hiệu suất NLMT trên App, chỉ số =0
-3. KH cần CN liên hệ và hỗ trợ sớm</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>2026-08-10 14:03:00</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-08-29 17:13:00</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Lê Hoàng Thiên</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>292658</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>4615434</t>
-        </is>
-      </c>
-      <c r="Z44" s="2">
-        <v>46244</v>
-      </c>
-      <c r="AA44">
-        <v>14</v>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="AE44" s="2">
-        <v>46253</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Thang máy</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>100601-XD/HĐXL-2025/BNH-HOANGTRONGHIEU</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Hoàng Trọng Hiếu</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0986912000</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Thị trấn Đồi Ngô,Huyện Lục Nam,Tỉnh Bắc Giang</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Happycall</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>1. KH đã báo CN 
-2. KH chưa được hỗ trợ về việc lắp thang hàng và tiến độ về công trình đang bị chậm nửa năm rồi  KH muốn được đền bù HĐ
-3. Yêu cầu CN hỗ trợ KH</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>2026-08-04 14:20:00</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-08-11 18:15:00</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Tuần</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>461581</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>4615316</t>
-        </is>
-      </c>
-      <c r="Z45" s="2">
-        <v>46238</v>
-      </c>
-      <c r="AA45">
-        <v>20</v>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE45" s="2">
-        <v>46241</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNI_1617012</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Hoàng Tiến Nam</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0984556118</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Triệu xuyên 3, Long Xuyên</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>1. KH đã liên hệ CN
-2. KH phản ánh Inverter của KH có thể bị ảnh hường bởi sét đánh, hiện không có điện lưới và điện NLMT
-3. KH cần CN liên hệ và đến kiểm tra sớm</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026-08-04 16:07:00</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-09-02 19:13:00</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Nguyễn Hoàng Minh</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>292404</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>4615297</t>
-        </is>
-      </c>
-      <c r="Z46" s="2">
-        <v>46238</v>
-      </c>
-      <c r="AA46">
-        <v>20</v>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE46" s="2">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_CMU_1423965</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Anh Nghĩa</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>0919666690</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Khóm 10,Thị trấn Sông Đốc,Huyện Trần Văn Thờ, Xã Trần Văn Thời, Tỉnh Cà Mau</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN 
-KH phản ánh trên app đang báo lỗi mất điện NLMT và mất ắc quy, bị sáng nay 
-Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>2026-08-03 11:33:00</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-09-05 14:05:00</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Trần Hoàng Huy</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>410724</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>4615274</t>
-        </is>
-      </c>
-      <c r="Z47" s="2">
-        <v>46237</v>
-      </c>
-      <c r="AA47">
-        <v>21</v>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="AE47" s="2">
-        <v>46253</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_QNH_1644996</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Vũ Tú</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0967618822</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Tổ 5 khu 5</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN 
-KH phản ánh điện NLMT của KH không hoạt động, mất điện là k sử dụng được luôn, kiểm tra trên hệ thống vẫn có điện
-Yêu cầu quản lý điều kĩ thuật liên hệ và hỗ trợ KH</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>2026-07-28 14:51:00</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:00:00</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Đào Minh Đức</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>290593</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>4615145</t>
-        </is>
-      </c>
-      <c r="Z48" s="2">
-        <v>46231</v>
-      </c>
-      <c r="AA48">
-        <v>27</v>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE48" s="2">
-        <v>46248</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>KHDN_TT.GPTH_HNI_1325140</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐO ĐẠC VÀ BẢN ĐỒ PHÚC AN</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>0914335390</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Khu tái định cư phía Bắc sông Thiếp,Xã Uy Nỗ,Huyện Đông Anh,Thành phố Hà Nội</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>1. KH đã báo CN 0969054066 
-2. KH phản ánh: KH theo dõi trên app tấm pin nlmt ko sản xuất ra điện, báo lỗi cung DC
-3. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>2026-07-16 16:12:00</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-08-30 22:45:00</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Nguyễn Ngọc Sơn</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>447039</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>4614836</t>
-        </is>
-      </c>
-      <c r="Z49" s="2">
-        <v>46219</v>
-      </c>
-      <c r="AA49">
-        <v>39</v>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE49" s="2">
-        <v>46241</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DNI_1619779</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Bùi Quang Thuận</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0913774928</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Tân Phú Đồng Nai</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>1. KH đã liên hệ CN
-2. Khi mất điện lưới hệ thống NLMT của KH không nhảy ATS, Biến tần Inverter hiện rất nóng
-3. KH cần CN đến kiêm tra cho KH sớm</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>2026-06-25 15:40:00</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-09-02 10:39:00</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Thi</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>190116</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>4614161</t>
-        </is>
-      </c>
-      <c r="Z50" s="2">
-        <v>46198</v>
-      </c>
-      <c r="AA50">
-        <v>60</v>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="AE50" s="2">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_TNN_1652755</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Dương Minh Học</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>0984662540</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Thuần Pháp</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Bảo hành</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>KH chưa báo CN
-KH phản ánh 8 ngày nay NLMT k dùng được, k theo dõi được cả trên điện thoại và hệ thống, Kh giờ chỉ dùng dc điện lưới, KH đã báo cho anh Quý phụ trách lắp nhưng không phản hồi
-Yêu cầu KT liên hệ và xuống kiểm tra cho KH</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>2026-06-24 13:30:00</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-07-27 13:10:00</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Quá hạn</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Thao</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>289758</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>4614075</t>
-        </is>
-      </c>
-      <c r="Z51" s="2">
-        <v>46197</v>
-      </c>
-      <c r="AA51">
-        <v>61</v>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE51" s="2">
-        <v>46213</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HCM_1624133</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Hạ</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>0971550074</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Thăng Long</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
         <is>
           <t>chi nhánh báo hộ 0382691111
 Biến tần hoạt động không ổn định
@@ -8224,515 +7001,515 @@
 Yêu cầu kt qua ktra cho khách hàng</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>2026-05-26 13:30:00</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>2026-06-20 18:00:00</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Bùi Văn Đạt</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>285126</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>4613034</t>
         </is>
       </c>
-      <c r="Z52" s="2">
+      <c r="Z44" s="2">
         <v>46168</v>
       </c>
-      <c r="AA52">
-        <v>90</v>
-      </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AA44">
+        <v>91</v>
+      </c>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE52" s="2">
+      <c r="AE44" s="2">
         <v>46180</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>HUE</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_TTH_1626383</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT PHÚ HƯNG</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>0985005322</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>19 Trưng Nữ Vương</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ cho CN
 2. Hiệu Suất NLMT của KH bị giảm khoảng 15%, trước đây ngày nắng tốt phát sinh được 30kw/h hiện tại phát sinh được 25kw/h, CN kiểm tra và thông tin do Inverter bị nóng nên giảm hiệu suất
 3. KH cần CN hỗ trợ và khắc phục giúp HT NLMT của KH hoạt động bình thường</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>2026-05-25 15:45:00</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>2026-08-31 17:35:00</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Ngô Hữu Hòa</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>084001</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>4612987</t>
         </is>
       </c>
-      <c r="Z53" s="2">
+      <c r="Z45" s="2">
         <v>46167</v>
       </c>
-      <c r="AA53">
-        <v>91</v>
-      </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AA45">
+        <v>92</v>
+      </c>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>Đăng</t>
         </is>
       </c>
-      <c r="AE53" s="2">
+      <c r="AE45" s="2">
         <v>46216</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Tấm pin NLMT</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BKN_1083931</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Lã Xuân Trường</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>0904124569</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>tổ 10</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>KH phản ánh 2 tấm Pin bị nứt, vỡ, võng. Yêu cầu kiểm tra, thay thế theo bảo hành</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>2026-05-14 10:50:00</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>2026-08-25 14:50:00</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Quản Đức Trọng</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>051104</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>4612554</t>
         </is>
       </c>
-      <c r="Z54" s="2">
+      <c r="Z46" s="2">
         <v>46156</v>
       </c>
-      <c r="AA54">
-        <v>102</v>
-      </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AA46">
+        <v>103</v>
+      </c>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE54" s="2">
+      <c r="AE46" s="2">
         <v>46207</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>DLK</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DLK_1665021</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Chu Thị Xuân</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>0842474849</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>thôn Nam Anh</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>Chưa báo chi nhánh 
 Đang bị nứt 1 tấm pin ở mặt dưới, công suất không đạt
 Yêu cầu kt qua ktra cho khách  hàng</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>2026-05-04 08:00:00</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>2026-08-31 15:30:00</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Khôi</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>057076</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>4612186</t>
         </is>
       </c>
-      <c r="Z55" s="2">
+      <c r="Z47" s="2">
         <v>46146</v>
       </c>
-      <c r="AA55">
-        <v>112</v>
-      </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AA47">
+        <v>113</v>
+      </c>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>Đăng</t>
         </is>
       </c>
-      <c r="AE55" s="2">
+      <c r="AE47" s="2">
         <v>46205</v>
       </c>
     </row>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE47"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -547,218 +547,522 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>KHCN_TT.GPTH_BNH_1673975</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Giang Văn Nam</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0972284808</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Đồng Cờ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>HPC KH phản ánh chưa thấy thi công cọc tiếp địa, IVT sờ tay vào thấy tê tay 
+Yêu cầu CN cho KT qua ktra hỗ trợ KH</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:42:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:42:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Tuần</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>461581</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>4615837</t>
+        </is>
+      </c>
+      <c r="Z2" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE2" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>KHCN_TT.GPTH_BGG_1335039</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Phạm Văn Trọng</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0368067663</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Thôn Hưng Đạo,Xã Đông Lỗ (cũ)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: mất kết nối ko vào được app theo dõi nlmt 
 3. KH yêu cầu: qua kiểm tra, hỗ trợ KH kết nối lại app</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-25 08:00:00</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-26 09:00:00</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Nguyễn Trọng Tạ</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>075226</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>4615836</t>
         </is>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z3" s="2">
         <v>46259</v>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <v>0</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE2" s="2">
+      <c r="AE3" s="2">
         <v>46259</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DBN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Acquy lưu trữ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DBN_1706843</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nguyễn Mai Nguyệt</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0352373577</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bản Sa Lông 2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>KH đa báo CN
+KH báo sự cố điện chấp chờn, thiết bị lúc có điện lúc không. pin lưu trữ phát ra tiếng kêu liên tục</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-25 08:32:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-08-26 08:32:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hoàng Thị Thu Hoài</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>485638</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4615835</t>
+        </is>
+      </c>
+      <c r="Z4" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE4" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>KHA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_KHA_1638770</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Phạm Đình Văn</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0971895577</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Mỹ Lợi</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Lắp đặt không đảm bảo</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: về các phản ánh trước TT_1781057405553
 2. KH phản ánh: hiện tại KH theo dõi trên app thấy chạy ra ngoài điện lưới trước đó anh Văn Hoàng - quản lý khu vực có cho a Thái Ngọc đến xử lý sự cố nhưng khi lắp đặt lại thì thấy ko đúng so với thiết kế và hệ nlmt giờ cũng ko sử dụng được chỉ thấy dùng điện lưới
@@ -767,760 +1071,1066 @@
 3. KH yêu cầu: qua kiểm tra, đấu nối lại tủ điện cho đúng để KH sử dụng được nlmt</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2026-08-25 08:00:00</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:00:00</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:30:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Tán Minh Hoàng Long</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>008016</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Võ Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>466089</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>4615834</t>
         </is>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z5" s="2">
         <v>46259</v>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <v>0</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Đăng</t>
         </is>
       </c>
-      <c r="AE3" s="2">
+      <c r="AE5" s="2">
         <v>46259</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HPG_1628819</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Phạm Văn Hương</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0395074737</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Thôn Minh Hưng</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: pin lưu trữ ko nạp vào ko xả ra
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2026-08-24 16:08:00</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2026-08-25 16:08:00</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Nguyễn Tiến Mạnh</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>182255</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>4615832</t>
         </is>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z6" s="2">
         <v>46258</v>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <v>1</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE4" s="2">
+      <c r="AE6" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_1684307</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Nhuyễn Văn Hùng</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0972772168</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TDP Trung Thành 7</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Lắp đặt không đảm bảo</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: KT tên Thân
 2. KH phản ánh: dùng 2 công tơ chạy điện 3 pha, khi lắp đảo chiều không đẩy bù điện nlmt dẫn đến điện tăng. KT đã qua hỗ trợ nhưng KH yêu cầu KT chịu hoàn toàn trách nhiệm, CN cũng đã hẹn nhiều ngày xuống giải quyết nhưng ko xuống, KH đánh giá CN thiếu trách nhiệm
 3. KH yêu cầu: Đại diện CN Thái Nguyên xuống làm việc với KH</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-08-24 15:45:00</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2026-08-25 15:45:00</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thao</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>289758</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>4615831</t>
         </is>
       </c>
-      <c r="Z5" s="2">
+      <c r="Z7" s="2">
         <v>46258</v>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <v>1</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE5" s="2">
+      <c r="AE7" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_VLG_1637914</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Huỳnh Văn Lập</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0974336798</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ấp 3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1. KH chưa liên hệ CN
+2. Biến tần của KH bị tắt, không hoạt động, App báo ngoại tuyến
+3. KH cần CNCT hỗ trợ kiểm tra và khắc phục sớm</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:08:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:08:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Đỗ Ngọc Nhân</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>073552</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4615821</t>
+        </is>
+      </c>
+      <c r="Z8" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="AE8" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_QNH_1681152</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nguyễn Mạnh Hùng</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0984684287</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>số nhà 16 ngõ 28 phan đình phùng hà khánh cao xanh</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1. KH chưa liên hệ CN
+2. Hiện nhà KH đang bị mất điện, KH kiểm tra vật tư thiết bị của HT NLMT không có sự cố hay bị nhảy ATS
+3. KH cần CNCT liên hệ và đến hỗ trợ gấp</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:04:00</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:04:00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Sơn</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>021937</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>4615820</t>
+        </is>
+      </c>
+      <c r="Z9" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE9" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>DTP</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DTP_1683398</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>NGUYỄN NGỌC HUY</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0348470707</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>ấp tân ninh</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Thiếu thiết bị đi kèm/Lắp đặt sai quy cách</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: lắp thiếu cầu giao chống sét, CN đã xuống kiểm tra chất lượng thì mới biết thiếu
 3. KH yêu cầu: hoàn thiện lắp đặt đảm bảo an toàn cho KH</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-08-24 15:35:00</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2026-08-25 15:35:00</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Trần Duy Khánh</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>422532</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>4615817</t>
         </is>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z10" s="2">
         <v>46258</v>
       </c>
-      <c r="AA6">
+      <c r="AA10">
         <v>1</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE6" s="2">
+      <c r="AE10" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>290902-2968-KD/HĐMBLÐ-2025/CNCTDNI-STRIDESOLAR</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Nguyễn Thị Thu Hương</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0376664322</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Tổ 14, ấp Láng Lớn, xã Cẩm Mỹ, Đồng Nai</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>1. Đối tác báo sự cố cho KH
 2.Do KH đổi Wifi nên App theo dõi hiệu suất NLMT không kết nối được, Hệ thống sản xuất điện rất ít
 3. KH cần CNCT hỗ trợ kiểm tra tấm pin, kết nối App theo dõi hiệu suất sớm</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>2026-08-24 13:30:00</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>2026-08-25 13:30:00</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Ngô Minh Hoàng</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>119059</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>4615816</t>
         </is>
       </c>
-      <c r="Z7" s="2">
+      <c r="Z11" s="2">
         <v>46258</v>
       </c>
-      <c r="AA7">
+      <c r="AA11">
         <v>1</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE7" s="2">
+      <c r="AE11" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>NAN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_NAN_1682943</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Phạm Đình Phương</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0911141678</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Khối Lam Thanh</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1. CN báo sự cố cho KH
 2. Ắc quy lưu trữ còn 80% nhưng ko xả, không có sản lượng điện NLMT
@@ -1528,1698 +2138,1104 @@
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>2026-08-24 11:09:00</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-08-25 11:09:00</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:30:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Trần Văn Việt</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>044155</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>4615814</t>
         </is>
       </c>
-      <c r="Z8" s="2">
+      <c r="Z12" s="2">
         <v>46258</v>
       </c>
-      <c r="AA8">
+      <c r="AA12">
         <v>1</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE8" s="2">
+      <c r="AE12" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNI_1711273</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Lê Điền</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0839074679</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>ấp 2 xuân đường TpĐồng Nai</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1.KH đã liên hệ CN
 2. KH cần CN hỗ trợ cung cấp hồ sơ kỹ thuật và các chứng từ liên quan đến HT NLMT để có thể thông tin cho bên điện lực</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2026-08-24 11:49:00</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>2026-08-28 14:05:00</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Trần Hải Tùng</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>245696</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>4615806</t>
         </is>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z13" s="2">
         <v>46258</v>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <v>1</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE9" s="2">
+      <c r="AE13" s="2">
         <v>46260</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DNG</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DNG_1670030</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_DNI_1614483</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Quý</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0932534811</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>12 Phan Văn Đáng</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Bùi Thị Tuyết Lan</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0382305668</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Xã Thống Nhất,null,Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1. KH chưa liên hệ CN
-2. Hiện nhà KH vẫn có điện lưới và điện NLMT tuy nhiên không thấy hiển thị thông tin trên App và Tủ điện, thời gian trước nhân sự Thái có hỗ trợ cho KH
-3. KH cần CNCT hỗ trợ khắc phục sớm</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2026-08-24 08:18:00</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-08-25 18:40:00</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Lê Văn Hậu</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>488276</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4615801</t>
-        </is>
-      </c>
-      <c r="Z10" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA10">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>Đăng</t>
-        </is>
-      </c>
-      <c r="AE10" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DNI_1614483</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Bùi Thị Tuyết Lan</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0382305668</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Xã Thống Nhất,null,Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Hiện KH không theo dõi được Hiệu suất HT NLMT trên App
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-08-24 08:00:00</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2026-08-26 19:20:00</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Trần Quốc Khang</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>459729</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>4615790</t>
         </is>
       </c>
-      <c r="Z11" s="2">
+      <c r="Z14" s="2">
         <v>46258</v>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <v>1</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE11" s="2">
+      <c r="AE14" s="2">
         <v>46259</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BNH_1699993</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Nguyễn Công Công</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>0972870377</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Yên Viên</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>1. KH đã được CNCT liên hệ và hướng dẫn xử lý sơ bộ
 2. 1 ATS chống sét trong tủ nguồn của KH có dấu hiệu bị chập, cháy
 3. KH cần CNCT hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>2026-08-24 08:00:00</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>2026-08-25 18:35:00</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Phạm Văn Huy</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>408869</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>4615786</t>
         </is>
       </c>
-      <c r="Z12" s="2">
+      <c r="Z15" s="2">
         <v>46258</v>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <v>1</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE12" s="2">
+      <c r="AE15" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HYN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Acquy lưu trữ</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HYN_1639428</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Bùi Quang Vũ</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0886102896</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Thôn Văn Tràng</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Ăc quy lưu trữ chỉ sạc được khoảng 80%
 3. KH cần CNCT hỗ trợ đến kiểm tra sớm</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>2026-08-24 08:00:00</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>2026-08-30 17:15:00</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Trần Minh Vương</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>276581</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>4615785</t>
         </is>
       </c>
-      <c r="Z13" s="2">
+      <c r="Z16" s="2">
         <v>46258</v>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <v>1</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE13" s="2">
+      <c r="AE16" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_HNM_1573163</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_TNN_1633636</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Trần Văn Túy</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0944220696</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Phường Phủ Lý, Ninh Bình</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Nguyễn Minh Phúc</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0868101535</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Cổng CNTT</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>1. KH đã liên hệ CN
-2. HT NLMT của KH có Pin lưu trữ tuy nhiên mất điện lưới là hệ thống dừng hoạt động
-3. KH cần CNCT đến kiểm tra sớm</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>2026-08-24 08:00:00</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:00:00</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Trần Văn Thành</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>815150</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>4615782</t>
-        </is>
-      </c>
-      <c r="Z14" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA14">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE14" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_TNN_1633636</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Nguyễn Minh Phúc</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0868101535</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Cổng CNTT</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>KH báo Anh Thao KT nhưng chưa được hỗ trợ 
 KH báo sự cố hệ thống NLMT hiện tại không theo dõi được trên app, vào app chỉ thấy hiển thị màn hình trắng tinh
 Yêu cầu CN cho KT qua ktra hõ trợ KH</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>2026-08-24 13:30:00</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>2026-08-25 13:30:00</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thao</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>289758</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>4615779</t>
         </is>
       </c>
-      <c r="Z15" s="2">
+      <c r="Z17" s="2">
         <v>46258</v>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <v>1</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE15" s="2">
+      <c r="AE17" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KV3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AGG</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HUE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_AGG_1695678</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_TTH_1611393</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Lê Hồng Ân</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0939801111</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Tổ 18 Rạch Hàm, Hàm Ninh, Đặc khu Phú Quốc</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Hồ Thị Mỹ Hạnh</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0966929265</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Hương Văn, Phường Hương Hương Trà Huế</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Hỗ trợ</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>KH cần CN hỗ trợ cung cấp:
-Hóa đơn và các chứng từ liên quan đến HT NLMT, ngoài ra trong quá trình sử dụng khi KH bật, tắt một số CB trong tủ nguồn không thấy có tác động đến HT NLMT, cần CNCT giải đáp</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>2026-08-24 08:00:00</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:00:00</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Nguyễn Ngọc Hải</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>111519</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>4615773</t>
-        </is>
-      </c>
-      <c r="Z16" s="2">
-        <v>46258</v>
-      </c>
-      <c r="AA16">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="AE16" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>HUE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Inverter</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_TTH_1611393</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Hồ Thị Mỹ Hạnh</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0966929265</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Hương Văn, Phường Hương Hương Trà Huế</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>1. KH chưa liên hệ CN
 2. Biến tần của KH thông tin không có điện lưới trong khi nhà KH vẫn có điện, App theo dõi hiệu suất không có thông tin của HT NLMT từ đầu tháng
 3. KH cần CNCT hỗ trợ kiểm tra sớm</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-08-24 08:00:00</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:00:00</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:25:00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Phạm Văn Kiện</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>422329</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>4615758</t>
         </is>
       </c>
-      <c r="Z17" s="2">
+      <c r="Z18" s="2">
         <v>46258</v>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <v>1</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Đăng</t>
         </is>
       </c>
-      <c r="AE17" s="2">
+      <c r="AE18" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1335514</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Nguyễn Thích Điện</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0978586057</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Xã Quang Thịnh,Huyện Lạng Giang (cũ)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: mất kết nối, ko đăng nhập được app theo dõi
 3. KH yêu cầu: qua hỗ trợ KH kết nối lại app</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2026-08-21 09:10:00</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>2026-08-26 09:55:00</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Vũ Hà Thanh</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>007721</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>4615728</t>
-        </is>
-      </c>
-      <c r="Z18" s="2">
-        <v>46255</v>
-      </c>
-      <c r="AA18">
-        <v>4</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE18" s="2">
-        <v>46257</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HNI</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>M&amp;E</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Thang máy</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>10092025-GP&amp;DVKT/HĐMBLĐ-2025/HNI-NGUYENNGOCDUONG</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Nguyễn Ngọc Dương</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0909289598</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Phương Xuân Phương</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Phàn nàn, Góp Ý</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>KH phản ánh gay gắt và rất bức xúc do Thang máy liên tục gặp sự cố dừng, kẹt và không hoạt động, ngày 20/08 KH bị kẹt trong thang máy 5 phút và rất lo ngại trường hợp trẻ nhỏ trong gia đình gặp sự cố với thiết bị, Yêu cầu CNCT có phương hướng xử lý khắc phục dứt điểm cho KH</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2026-08-21 08:00:00</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-08-28 16:55:00</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Ngô Đức Tân</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>484844</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>4615724</t>
         </is>
       </c>
       <c r="Z19" s="2">
@@ -3230,7 +3246,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3244,7 +3260,7 @@
         </is>
       </c>
       <c r="AE19" s="2">
-        <v>46258</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="20">
@@ -3255,882 +3271,882 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>M&amp;E</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Thang máy</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10092025-GP&amp;DVKT/HĐMBLĐ-2025/HNI-NGUYENNGOCDUONG</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Dương</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0909289598</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Phương Xuân Phương</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Phàn nàn, Góp Ý</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Chất lượng, dịch vụ, Giá cả</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>KH phản ánh gay gắt và rất bức xúc do Thang máy liên tục gặp sự cố dừng, kẹt và không hoạt động, ngày 20/08 KH bị kẹt trong thang máy 5 phút và rất lo ngại trường hợp trẻ nhỏ trong gia đình gặp sự cố với thiết bị, Yêu cầu CNCT có phương hướng xử lý khắc phục dứt điểm cho KH</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:00:00</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-08-28 16:55:00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ngô Đức Tân</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>484844</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>4615724</t>
+        </is>
+      </c>
+      <c r="Z20" s="2">
+        <v>46255</v>
+      </c>
+      <c r="AA20">
+        <v>4</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE20" s="2">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_PTO_1654586</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Vũ Hồng Lạc</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>0947304568</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Thiên nga 3-206, Vinhomes cổ loa, xã Xuân Canh, Đông Hội, Mai Lâm, huyện Đông Anh, thành phố Hà Nội (Vinhomes Global Gate), Vinhomes cổ loa</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1. KH đã báo CN
 2. KH phản ánh: thi thoảng ngắt kết nối app theo dõi nlmt, hiện lỗi "giao tiếp giữa nhà máy và thiết bị bị ngắt kết nối"
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2026-08-20 10:33:00</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>2026-09-10 10:10:00</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Lê Trung Kiên</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>119420</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>4615711</t>
         </is>
       </c>
-      <c r="Z20" s="2">
+      <c r="Z21" s="2">
         <v>46254</v>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <v>5</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE20" s="2">
+      <c r="AE21" s="2">
         <v>46264</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1685619</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Trần Tuấn Việt</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0982296655</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Vườn Đào Tuấn Việt, SN 15, Ngõ 264/18</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Hiệu suất sản phẩm kém</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>KH đã báo KT 
 KH báo sự cố:  Biến tần tự động ngắt/dừng hoạt động mỗi khi điện nguồn vào bị tụt xuống dưới 180V. Khi đó, hệ thống tự động chuyển sang dùng 100% điện lưới thay vì dùng điện mặt trời. Hệ thống chỉ chạy điện mặt trời khi ngắt/tắt thủ công nguồn điện lưới. Hệ thống điện mặt trời gần như không có tác dụng (90% thời gian từ lúc lắp đặt vẫn phải dùng điện lưới), tiền điện mỗi tháng không giảm so với trước (vẫn hơn 3 triệu/tháng).
 Yêu cầu CN cho KT qua ktra lại và xử lý cho KH</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-08-20 10:03:00</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>2026-09-03 18:25:00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Hoàng Văn Vương</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>285732</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>4615710</t>
         </is>
       </c>
-      <c r="Z21" s="2">
+      <c r="Z22" s="2">
         <v>46254</v>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <v>5</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE21" s="2">
+      <c r="AE22" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>PTO</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>250501-KD/GPTH/HĐMBLĐ-2022/HBH-VUVIETTUNG</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Vũ Việt Tùng</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>0989463899</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Khu 7 -Xã Lạc Thủy - Phú Thọ</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: a Dũng
 2. KH phản ánh: toàn bộ sản lượng điện nlmt lên hết điện lưới, có báo CN và KT hỗ trợ cài đặt từ xa nhưng vẫn chưa khắc phục được
 3. KH yêu cầu: qua kiểm tra trực tiếp và khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>2026-08-19 11:20:00</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>2026-08-25 09:15:00</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Quá hạn</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>Lê Hoàng Chung</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>266744</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>4615692</t>
         </is>
       </c>
-      <c r="Z22" s="2">
+      <c r="Z23" s="2">
         <v>46253</v>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <v>6</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE22" s="2">
+      <c r="AE23" s="2">
         <v>46256</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CTO_1703516</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Nguyễn Hân Hoan</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>0981205207</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>ấp tân thành</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>1. CN báo sự cố cho KH
 2. Biến tần báo lỗi COM báo đỏ
 3. KH cần CN kiểm tra và khăc phục sớm</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>2026-08-19 09:49:00</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>2026-09-04 22:20:00</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Trương Minh Khoa</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>440290</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>4615690</t>
         </is>
       </c>
-      <c r="Z23" s="2">
+      <c r="Z24" s="2">
         <v>46253</v>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <v>6</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE23" s="2">
+      <c r="AE24" s="2">
         <v>46261</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNI_1675332</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Nguyễn Trọng Thuỷ</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>0986565857</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>ấp 7</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>1. KH đã báo chi nhánh - Nhân viên Hải Tùng
 2. Nội dung sự cố: ATS bị cháy cầu trì, đã báo nhân sự Hải Tùng của chi nhánh nhưng chưa được xử lý. CN báo sẽ đổi ATS khác nhưng chưa có hàng, KH đã đợi khoảng hơn 2 tháng nhưng chưa được hỗ trợ.
 3. KHYC: CN hỗ trợ sớm (Viettel  báo giá 12tr KH đồng ý nhưng đợi lâu chưa được thay, KH cần hỗ trợ gấp do gia đình kinh doanh nhà nghỉ KS)</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>2026-08-18 09:09:00</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>2026-08-31 17:00:00</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Trần Hải Tùng</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>245696</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>4615669</t>
-        </is>
-      </c>
-      <c r="Z24" s="2">
-        <v>46252</v>
-      </c>
-      <c r="AA24">
-        <v>7</v>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="AE24" s="2">
-        <v>46258</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KHDN_NLMT_BNH_0171103</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Khách hàng doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>NGUYỄN VĂN ÍCH</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0987363058</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Thị trấn Lim, Huyện Tiên Du, Tỉnh Bắc Ninh</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Tiến độ triển khai chậm</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Phản ánh từ trước TT_1783915287625 CN đã có BBLV với KH về thiết bị ivt mang đi bảo hành và xác nhận thời điểm lắp đặt lại thiết bị là 15/8 nhưng đến hiện tại là 18/8 KH vẫn chưa thấy có thông tin gì. KH rất bức xúc yêu cầu CN liên hệ là xuống lắp đặt cho KH theo BBLV</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>2026-08-18 11:15:00</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-08-25 18:40:00</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Tuần</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>461581</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>4615658</t>
         </is>
       </c>
       <c r="Z25" s="2">
@@ -4151,11 +4167,11 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE25" s="2">
-        <v>46255</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="26">
@@ -4186,2814 +4202,2965 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>KHDN_NLMT_BNH_0171103</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NGUYỄN VĂN ÍCH</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0987363058</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Thị trấn Lim, Huyện Tiên Du, Tỉnh Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Khiếu nại</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Tiến độ triển khai chậm</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Phản ánh từ trước TT_1783915287625 CN đã có BBLV với KH về thiết bị ivt mang đi bảo hành và xác nhận thời điểm lắp đặt lại thiết bị là 15/8 nhưng đến hiện tại là 18/8 KH vẫn chưa thấy có thông tin gì. KH rất bức xúc yêu cầu CN liên hệ là xuống lắp đặt cho KH theo BBLV</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026-08-18 11:15:00</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-08-25 18:40:00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Tuần</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>461581</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>4615658</t>
+        </is>
+      </c>
+      <c r="Z26" s="2">
+        <v>46252</v>
+      </c>
+      <c r="AA26">
+        <v>7</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE26" s="2">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>KHCN_TT.GPTH_BNH_1665718</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Chu Văn Thao</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0969032689</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Thôn Ngoẹn</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: hệ nlmt ko hoạt động, đèn ở pin lưu trữ và cả hệ đều thấy tắt
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>2026-08-18 09:07:00</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>2026-09-03 10:15:00</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Vũ Hà Thanh</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>007721</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>4615655</t>
         </is>
       </c>
-      <c r="Z26" s="2">
+      <c r="Z27" s="2">
         <v>46252</v>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <v>7</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE26" s="2">
+      <c r="AE27" s="2">
         <v>46260</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_KGG_1586960</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Nguyễn Văn Non Em</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>0353397777</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Xã Vĩnh Phước A,Huyện Gò Quao (cũ)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Lắp đặt không đảm bảo</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: anh Bang
 2. KH phản ánh: vừa mới đây KH phát hiện ra do thấy có mùi khét và đứt phần dây tiếp địa, KH có ra kiểm tra thì là cọc tiếp địa bằng sắt chứ không phải cọc đồng như trong HĐ. KH có trao đổi với anh Bang thì phản hồi là tính nhầm
 3. KH yêu cầu: thay thế cọc tiếp địa bằng đồng và giải trình vấn đề này cho KH</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>2026-08-17 17:03:00</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>2026-09-01 17:15:00</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Phạm Thanh Duy</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>285926</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>4615646</t>
         </is>
       </c>
-      <c r="Z27" s="2">
+      <c r="Z28" s="2">
         <v>46251</v>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <v>8</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE27" s="2">
+      <c r="AE28" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QNH_1655231</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Hà Văn Hiệp</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>0334263627</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Đông Hải</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>1. KH đã báo CN: a Trường
 2. KH phản ánh: pin lưu trữ ko nạp vào ko xả ra
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>2026-08-17 15:03:00</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>2026-08-31 17:30:00</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Đinh Mạnh Trường</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>265011</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>4615644</t>
         </is>
       </c>
-      <c r="Z28" s="2">
+      <c r="Z29" s="2">
         <v>46251</v>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <v>8</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE28" s="2">
+      <c r="AE29" s="2">
         <v>46258</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1648836</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Lê Hữu Nghị</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>0398757686</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>số 1 ngõ 136 đường Cổ Linh, Phường Long Biên, Thành phố Hà Nội</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Zalo</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>KH đã báo KT nhưng chưa được hỗ trợ
 KH báo sự cố hệ thống  có lắp bộ tủ đảo công tơ 15 ngày tự đảo. Gần đây hệ không đảo sau 15 ngày nữa
 Yêu cầu CN cho KT qua ktra xử lý cho KH</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>2026-08-17 08:00:00</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>2026-08-28 23:55:00</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>292404</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>4615585</t>
         </is>
       </c>
-      <c r="Z29" s="2">
+      <c r="Z30" s="2">
         <v>46251</v>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <v>8</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE29" s="2">
+      <c r="AE30" s="2">
         <v>46256</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>DLK</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DLK_1648454</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Huỳnh Chí Băng</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0366448992</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Xã Ea Khăl, Tỉnh Đắk Lắk</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Từ P/á mã TT_1786152323690, KH phản ánh sau khi CNCT đến kiểm tra và kết luận tủ cháy đã báo giá cho KH chi phí thay tủ là 50%, KH hiện đang không đồng ý do thiết bị vẫn trong hạn bảo hành
 3. KH cần CNCT liên hệ và có hướng khắc phục, xử lý cho KH gấp</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>2026-08-17 08:00:00</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>2026-08-18 09:00:00</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Phạm Duy Bộ</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>411337</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>4615579</t>
         </is>
       </c>
-      <c r="Z30" s="2">
+      <c r="Z31" s="2">
         <v>46251</v>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <v>8</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>Đăng</t>
         </is>
       </c>
-      <c r="AE30" s="2">
+      <c r="AE31" s="2">
         <v>46251</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>010401-KD/HĐMBLĐ/2025/TNH-BBMALL</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Phạm Đức Thọ</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>0708666999</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Số 110, Đường Âu Cơ</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: hệ nlmt ko chạy được, hệ bám tải, có 2 pha chỉ 1 pha sáng, trên app kiểm tra ko thấy hoạt động
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này gấp</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>2026-08-14 11:18:00</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>2026-08-29 23:25:00</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Nguyễn Đặng Vĩnh Phát</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>455619</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>4615553</t>
         </is>
       </c>
-      <c r="Z31" s="2">
+      <c r="Z32" s="2">
         <v>46248</v>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <v>11</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE31" s="2">
+      <c r="AE32" s="2">
         <v>46255</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_KGG_1571883</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Lê Đoan Thanh Khiết</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>0817585822</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Chợ 30/4</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>CN 0967884099 báo sự cố hộ KH 
 1. KH phản ánh: pin lưu trữ bị lỗi ko vào điện
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>2026-08-13 17:14:00</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>2026-08-29 15:01:00</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Phạm Thanh Duy</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>285926</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>4615536</t>
         </is>
       </c>
-      <c r="Z32" s="2">
+      <c r="Z33" s="2">
         <v>46247</v>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <v>12</v>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE32" s="2">
+      <c r="AE33" s="2">
         <v>46255</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BLU_1564891</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Phan Hoàng Triều</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>0942357900</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Nhà máy</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>1. KH đã báo CN 
 2. KH phản ánh: KH có 2 ivt, hiện tại 1 ivt ko hoạt động
 3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>2026-08-13 16:21:00</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>2026-09-08 10:37:00</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Trong hạn</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Lê Hoàng Thiên</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>292658</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>4615522</t>
         </is>
       </c>
-      <c r="Z33" s="2">
+      <c r="Z34" s="2">
         <v>46247</v>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <v>12</v>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE33" s="2">
+      <c r="AE34" s="2">
         <v>46260</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>DTP</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DTP_1622998</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Lê Văn Hải</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>0918029932</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Khóm Trà Đư</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>CN 0973575722 báo sự cố hộ KH
 1. KH phản ánh: có 1 biến tần ko hoạt động, lỗi nhảy màn hình
 2. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>2026-08-12 09:12:00</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>2026-08-29 14:50:00</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Lê Văn Quốc Bảo</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>071042</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>4615476</t>
         </is>
       </c>
-      <c r="Z34" s="2">
+      <c r="Z35" s="2">
         <v>46246</v>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <v>13</v>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE34" s="2">
+      <c r="AE35" s="2">
         <v>46254</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>TNH</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNH_1678459</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Nguyễn Kim Vân</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>0946872682</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>số 10 Phạm Thị Đẩu</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>1. KH chưa liên hệ CN
 2. App theo dõi HT NLMT của KH báo ngoại tuyến
 3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>2026-08-11 14:33:00</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>2026-08-27 20:23:00</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Huỳnh Nhật Tiến</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>466027</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>4615461</t>
         </is>
       </c>
-      <c r="Z35" s="2">
+      <c r="Z36" s="2">
         <v>46245</v>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <v>14</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE35" s="2">
+      <c r="AE36" s="2">
         <v>46253</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1693389</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Đinh Văn Huân</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>0919102429</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Đường Tôn Đức Thắng, Khóm 17</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>1.CN báo sự cố cho KH
 2. KH không theo dõi được hiệu suất NLMT trên App, chỉ số =0
 3. KH cần CN liên hệ và hỗ trợ sớm</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>2026-08-10 14:03:00</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>2026-08-29 17:13:00</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Lê Hoàng Thiên</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>292658</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Võ Duy Khang</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>473069</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>4615434</t>
         </is>
       </c>
-      <c r="Z36" s="2">
+      <c r="Z37" s="2">
         <v>46244</v>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <v>15</v>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE36" s="2">
+      <c r="AE37" s="2">
         <v>46253</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>M&amp;E</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Thang máy</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>100601-XD/HĐXL-2025/BNH-HOANGTRONGHIEU</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Hoàng Trọng Hiếu</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>0986912000</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Thị trấn Đồi Ngô,Huyện Lục Nam,Tỉnh Bắc Giang</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Happycall</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Khiếu nại</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>1. KH đã báo CN 
 2. KH chưa được hỗ trợ về việc lắp thang hàng và tiến độ về công trình đang bị chậm nửa năm rồi  KH muốn được đền bù HĐ
 3. Yêu cầu CN hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>2026-08-04 14:20:00</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>2026-08-11 18:15:00</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Nguyễn Văn Tuần</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>461581</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>4615316</t>
         </is>
       </c>
-      <c r="Z37" s="2">
+      <c r="Z38" s="2">
         <v>46238</v>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <v>21</v>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>IOC</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE37" s="2">
+      <c r="AE38" s="2">
         <v>46241</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Inverter</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HNI_1617012</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Hoàng Tiến Nam</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>0984556118</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Triệu xuyên 3, Long Xuyên</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. KH phản ánh Inverter của KH có thể bị ảnh hường bởi sét đánh, hiện không có điện lưới và điện NLMT
 3. KH cần CN liên hệ và đến kiểm tra sớm</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>2026-08-04 16:07:00</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>2026-09-02 19:13:00</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Minh</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>292404</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>4615297</t>
         </is>
       </c>
-      <c r="Z38" s="2">
+      <c r="Z39" s="2">
         <v>46238</v>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <v>21</v>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE38" s="2">
+      <c r="AE39" s="2">
         <v>46252</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>CMU</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_CMU_1423965</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Anh Nghĩa</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>0919666690</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Khóm 10,Thị trấn Sông Đốc,Huyện Trần Văn Thờ, Xã Trần Văn Thời, Tỉnh Cà Mau</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>KH chưa báo CN 
 KH phản ánh trên app đang báo lỗi mất điện NLMT và mất ắc quy, bị sáng nay 
 Yêu cầu quản lí điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>2026-08-03 11:33:00</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>2026-09-05 14:05:00</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Trần Hoàng Huy</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>410724</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>4615274</t>
         </is>
       </c>
-      <c r="Z39" s="2">
+      <c r="Z40" s="2">
         <v>46237</v>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <v>22</v>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE39" s="2">
+      <c r="AE40" s="2">
         <v>46253</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_QNH_1644996</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Vũ Tú</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>0967618822</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Tổ 5 khu 5</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>KH chưa báo CN 
 KH phản ánh điện NLMT của KH không hoạt động, mất điện là k sử dụng được luôn, kiểm tra trên hệ thống vẫn có điện
 Yêu cầu quản lý điều kĩ thuật liên hệ và hỗ trợ KH</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>2026-07-28 14:51:00</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>2026-08-31 17:00:00</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Đào Minh Đức</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>290593</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>4615145</t>
         </is>
       </c>
-      <c r="Z40" s="2">
+      <c r="Z41" s="2">
         <v>46231</v>
       </c>
-      <c r="AA40">
+      <c r="AA41">
         <v>28</v>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE40" s="2">
+      <c r="AE41" s="2">
         <v>46248</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>HNI</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_HNI_1325140</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>CÔNG TY CỔ PHẦN ĐO ĐẠC VÀ BẢN ĐỒ PHÚC AN</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>0914335390</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Khu tái định cư phía Bắc sông Thiếp,Xã Uy Nỗ,Huyện Đông Anh,Thành phố Hà Nội</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>1. KH đã báo CN 0969054066 
 2. KH phản ánh: KH theo dõi trên app tấm pin nlmt ko sản xuất ra điện, báo lỗi cung DC
 3. KH yêu cầu: Qua kiểm tra, khắc phục tình trạng này</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>2026-07-16 16:12:00</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>2026-08-30 22:45:00</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Nguyễn Ngọc Sơn</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>447039</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>4614836</t>
         </is>
       </c>
-      <c r="Z41" s="2">
+      <c r="Z42" s="2">
         <v>46219</v>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <v>40</v>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE41" s="2">
+      <c r="AE42" s="2">
         <v>46241</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DNI_1619779</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Bùi Quang Thuận</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>0913774928</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Tân Phú Đồng Nai</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
 2. Khi mất điện lưới hệ thống NLMT của KH không nhảy ATS, Biến tần Inverter hiện rất nóng
 3. KH cần CN đến kiêm tra cho KH sớm</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>2026-06-25 15:40:00</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>2026-09-02 10:39:00</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thi</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>190116</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>4614161</t>
         </is>
       </c>
-      <c r="Z42" s="2">
+      <c r="Z43" s="2">
         <v>46198</v>
       </c>
-      <c r="AA42">
+      <c r="AA43">
         <v>61</v>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AE42" s="2">
+      <c r="AE43" s="2">
         <v>46232</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_TNN_1652755</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Dương Minh Học</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>0984662540</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Thuần Pháp</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Bảo hành</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>KH chưa báo CN
 KH phản ánh 8 ngày nay NLMT k dùng được, k theo dõi được cả trên điện thoại và hệ thống, Kh giờ chỉ dùng dc điện lưới, KH đã báo cho anh Quý phụ trách lắp nhưng không phản hồi
 Yêu cầu KT liên hệ và xuống kiểm tra cho KH</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>2026-06-24 13:30:00</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>2026-07-27 13:10:00</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Nguyễn Văn Thao</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>289758</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>4614075</t>
         </is>
       </c>
-      <c r="Z43" s="2">
+      <c r="Z44" s="2">
         <v>46197</v>
       </c>
-      <c r="AA43">
+      <c r="AA44">
         <v>62</v>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE43" s="2">
+      <c r="AE44" s="2">
         <v>46213</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_HCM_1624133</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Nguyễn Văn Hạ</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>0971550074</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Thăng Long</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>chi nhánh báo hộ 0382691111
 Biến tần hoạt động không ổn định
@@ -7001,515 +7168,515 @@
 Yêu cầu kt qua ktra cho khách hàng</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>2026-05-26 13:30:00</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>2026-06-20 18:00:00</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Quá hạn</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Bùi Văn Đạt</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>285126</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>4613034</t>
         </is>
       </c>
-      <c r="Z44" s="2">
+      <c r="Z45" s="2">
         <v>46168</v>
       </c>
-      <c r="AA44">
+      <c r="AA45">
         <v>91</v>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>Hiếu</t>
         </is>
       </c>
-      <c r="AE44" s="2">
+      <c r="AE45" s="2">
         <v>46180</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>HUE</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>KHDN_TT.GPTH_TTH_1626383</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VIỆT PHÚ HƯNG</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>0985005322</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>19 Trưng Nữ Vương</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ cho CN
 2. Hiệu Suất NLMT của KH bị giảm khoảng 15%, trước đây ngày nắng tốt phát sinh được 30kw/h hiện tại phát sinh được 25kw/h, CN kiểm tra và thông tin do Inverter bị nóng nên giảm hiệu suất
 3. KH cần CN hỗ trợ và khắc phục giúp HT NLMT của KH hoạt động bình thường</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>2026-05-25 15:45:00</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>2026-08-31 17:35:00</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Ngô Hữu Hòa</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>084001</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>4612987</t>
         </is>
       </c>
-      <c r="Z45" s="2">
+      <c r="Z46" s="2">
         <v>46167</v>
       </c>
-      <c r="AA45">
+      <c r="AA46">
         <v>92</v>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Đăng</t>
         </is>
       </c>
-      <c r="AE45" s="2">
+      <c r="AE46" s="2">
         <v>46216</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Tấm pin NLMT</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_BKN_1083931</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Lã Xuân Trường</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0904124569</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>tổ 10</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Nhân viên nội bộ VCC</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Hot</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>KH phản ánh 2 tấm Pin bị nứt, vỡ, võng. Yêu cầu kiểm tra, thay thế theo bảo hành</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>2026-05-14 10:50:00</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:50:00</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Quản Đức Trọng</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>051104</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>4612554</t>
-        </is>
-      </c>
-      <c r="Z46" s="2">
-        <v>46156</v>
-      </c>
-      <c r="AA46">
-        <v>103</v>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE46" s="2">
-        <v>46207</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Tấm pin NLMT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BKN_1083931</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Lã Xuân Trường</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0904124569</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>tổ 10</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>KH phản ánh 2 tấm Pin bị nứt, vỡ, võng. Yêu cầu kiểm tra, thay thế theo bảo hành</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-05-14 10:50:00</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:50:00</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Quản Đức Trọng</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>051104</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>4612554</t>
+        </is>
+      </c>
+      <c r="Z47" s="2">
+        <v>46156</v>
+      </c>
+      <c r="AA47">
+        <v>103</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE47" s="2">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>KV2</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>DLK</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_DLK_1665021</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Chu Thị Xuân</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>0842474849</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>thôn Nam Anh</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>Chưa báo chi nhánh 
 Đang bị nứt 1 tấm pin ở mặt dưới, công suất không đạt
 Yêu cầu kt qua ktra cho khách  hàng</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>2026-05-04 08:00:00</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>2026-08-31 15:30:00</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>Đang tiến hành</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Nguyễn Hoàng Khôi</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>057076</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>4612186</t>
         </is>
       </c>
-      <c r="Z47" s="2">
+      <c r="Z48" s="2">
         <v>46146</v>
       </c>
-      <c r="AA47">
+      <c r="AA48">
         <v>113</v>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>AIO</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>P.Triển khai</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>Đăng</t>
         </is>
       </c>
-      <c r="AE47" s="2">
+      <c r="AE48" s="2">
         <v>46205</v>
       </c>
     </row>

--- a/data/3.R_pakh.xlsx
+++ b/data/3.R_pakh.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="26" max="26" width="20.7109375" style="2" customWidth="1"/>
@@ -522,12 +522,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1673975</t>
+          <t>KHCN_TT.GPTH_HCM_1656523</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -567,22 +567,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Giang Văn Nam</t>
+          <t>Lê Duy Huế</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0972284808</t>
+          <t>0968115214</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Đồng Cờ</t>
+          <t>129T Huỳnh Văn Cù</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -602,23 +602,24 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>HPC KH phản ánh chưa thấy thi công cọc tiếp địa, IVT sờ tay vào thấy tê tay 
-Yêu cầu CN cho KT qua ktra hỗ trợ KH</t>
+          <t>1. KH chưa liên hệ CN
+2. KHoảng 4-5 ngày nay hiệu suất của HT NLMT đang giảm, hiện tại chỉ sản xuất được khoảng hơn 3 kí trong khi trước đó là được hơn 6 kí dù trời nắng đẹp, đèn báo trên tủ điện chỉ hiện mờ mờ
+3. KH cần CNCT hỗ trợ kiểm tra sớm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:42:00</t>
+          <t>2026-08-25 13:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:42:00</t>
+          <t>2026-08-26 13:30:00</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -633,17 +634,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Tuần</t>
+          <t>Nguyễn Quốc Thịnh</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>461581</t>
+          <t>067889</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>4615837</t>
+          <t>4615839</t>
         </is>
       </c>
       <c r="Z2" s="2">
@@ -664,7 +665,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE2" s="2">
@@ -674,436 +675,434 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>KV3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Acquy lưu trữ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BLU_1597245</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Đặng Bá Hiệp</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0947877533</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Ấp Long Hoà</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Nhân viên nội bộ VCC</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.CN báo sự cố cho KH
+2. Ăc quy lưu trữ của KH 1 thiết bị xả điện còn 1 thiết bị không xả  điện
+3.KH cần CNCT liên hệ và đến hỗ trợ</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-25 11:54:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:54:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vũ Thái Sơn</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>284625</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4615838</t>
+        </is>
+      </c>
+      <c r="Z3" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+      <c r="AE3" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>KV1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>BNH</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KHCN_TT.GPTH_BNH_1673975</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Khách hàng cá nhân</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Giang Văn Nam</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0972284808</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Đồng Cờ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Happycall</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Lắp đặt sai quy cách, thiếu vật tư, thiết bị, phụ kiện đi kèm</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>HPC KH phản ánh chưa thấy thi công cọc tiếp địa, IVT sờ tay vào thấy tê tay 
+Yêu cầu CN cho KT qua ktra hỗ trợ KH</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:42:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:42:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Tuần</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>461581</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4615837</t>
+        </is>
+      </c>
+      <c r="Z4" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Hiếu</t>
+        </is>
+      </c>
+      <c r="AE4" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hệ thống NLMT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_BGG_1335039</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Phạm Văn Trọng</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0368067663</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Thôn Hưng Đạo,Xã Đông Lỗ (cũ)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1. KH chưa báo CN
 2. KH phản ánh: mất kết nối ko vào được app theo dõi nlmt 
 3. KH yêu cầu: qua kiểm tra, hỗ trợ KH kết nối lại app</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2026-08-25 08:00:00</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2026-08-26 09:00:00</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Chưa thực hiện</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Nguyễn Trọng Tạ</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>075226</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>4615836</t>
-        </is>
-      </c>
-      <c r="Z3" s="2">
-        <v>46259</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE3" s="2">
-        <v>46259</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DBN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Acquy lưu trữ</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_DBN_1706843</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nguyễn Mai Nguyệt</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0352373577</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Bản Sa Lông 2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>KH đa báo CN
-KH báo sự cố điện chấp chờn, thiết bị lúc có điện lúc không. pin lưu trữ phát ra tiếng kêu liên tục</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026-08-25 08:32:00</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-08-26 08:32:00</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hoàng Thị Thu Hoài</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>485638</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>4615835</t>
-        </is>
-      </c>
-      <c r="Z4" s="2">
-        <v>46259</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="AE4" s="2">
-        <v>46259</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>KV2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KHA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_KHA_1638770</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Phạm Đình Văn</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0971895577</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Mỹ Lợi</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Khiếu nại</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Lắp đặt không đảm bảo</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1. KH đã báo CN: về các phản ánh trước TT_1781057405553
-2. KH phản ánh: hiện tại KH theo dõi trên app thấy chạy ra ngoài điện lưới trước đó anh Văn Hoàng - quản lý khu vực có cho a Thái Ngọc đến xử lý sự cố nhưng khi lắp đặt lại thì thấy ko đúng so với thiết kế và hệ nlmt giờ cũng ko sử dụng được chỉ thấy dùng điện lưới
-+ Thiếu thiết bị chống sét, thấy tháo ra còn giờ ko thấy luôn
-+ Thiếu CB tổng, biến tần chạy nhưng điện ko qua biến tần, chạy trực tiếp từ điện lưới
-3. KH yêu cầu: qua kiểm tra, đấu nối lại tủ điện cho đúng để KH sử dụng được nlmt</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-08-25 08:00:00</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-08-26 11:30:00</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Đang tiến hành</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Võ Ngọc Thịnh</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>466089</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>4615834</t>
         </is>
       </c>
       <c r="Z5" s="2">
@@ -1124,7 +1123,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Đăng</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE5" s="2">
@@ -1236,7 +1235,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1440,282 +1439,282 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>KV2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPTH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NLMT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KHDN_TT.GPTH_DLK_1713152</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Khách hàng doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH VẬN TẢI THƯƠNG MẠI NGỌC GIÀU</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0905397268</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Khu Phố Đông Phước</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sau bán</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sự cố</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>KH đã báo CN
+KH phản ánh hiện tại thiết bị không theo dõi được hiệu xuất trên app
+Yêu cầu CN cho KT qua ktra hõ trợ KH</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:35:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:35:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Chưa thực hiện</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Sắp quá hạn</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trương Hoàng Tâm</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>083388</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4615822</t>
+        </is>
+      </c>
+      <c r="Z8" s="2">
+        <v>46259</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>AIO</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>P.Triển khai</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Đăng</t>
+        </is>
+      </c>
+      <c r="AE8" s="2">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>KV3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>VLG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GPTH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>NLMT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hệ thống NLMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>KHCN_TT.GPTH_VLG_1637914</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>B2C</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Huỳnh Văn Lập</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0974336798</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>ấp 3</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Hotline</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Bình thường</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Sau bán</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Sự cố</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1. KH chưa liên hệ CN
 2. Biến tần của KH bị tắt, không hoạt động, App báo ngoại tuyến
 3. KH cần CNCT hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-08-25 09:08:00</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-08-26 09:08:00</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Đang tiến hành</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>Sắp quá hạn</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Đỗ Ngọc Nhân</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>073552</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nguyễn Duy Khôi</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>449301</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>4615821</t>
-        </is>
-      </c>
-      <c r="Z8" s="2">
-        <v>46259</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>AIO</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>P.Triển khai</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="AE8" s="2">
-        <v>46259</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KV1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GPTH</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NLMT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Hệ thống NLMT</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KHCN_TT.GPTH_QNH_1681152</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>B2C</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Khách hàng cá nhân</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Nguyễn Mạnh Hùng</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0984684287</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>số nhà 16 ngõ 28 phan đình phùng hà khánh cao xanh</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Bình thường</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Sau bán</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Sự cố</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1. KH chưa liên hệ CN
-2. Hiện nhà KH đang bị mất điện, KH kiểm tra vật tư thiết bị của HT NLMT không có sự cố hay bị nhảy ATS
-3. KH cần CNCT liên hệ và đến hỗ trợ gấp</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:04:00</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-08-26 09:04:00</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Sắp quá hạn</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Nguyễn Thanh Sơn</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>021937</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>4615820</t>
         </is>
       </c>
       <c r="Z9" s="2">
@@ -1736,7 +1735,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE9" s="2">
@@ -1848,7 +1847,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1991,17 +1990,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-08-25 13:30:00</t>
+          <t>2026-08-31 17:35:00</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2041,18 +2040,18 @@
         </is>
       </c>
       <c r="AE11" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2072,7 +2071,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_NAN_1682943</t>
+          <t>KHCN_TT.GPTH_DNI_1711273</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2080,11 +2079,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -2092,22 +2086,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Phạm Đình Phương</t>
+          <t>Lê Điền</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0911141678</t>
+          <t>0839074679</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Khối Lam Thanh</t>
+          <t>ấp 2 xuân đường TpĐồng Nai</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Nhân viên nội bộ VCC</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2122,30 +2116,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1. CN báo sự cố cho KH
-2. Ắc quy lưu trữ còn 80% nhưng ko xả, không có sản lượng điện NLMT
-Khi mất điện lưới không dùng được HT NLMT
-3. KH cần CN liên hệ và hỗ trợ sớm</t>
+          <t>1.KH đã liên hệ CN
+2. KH cần CN hỗ trợ cung cấp hồ sơ kỹ thuật và các chứng từ liên quan đến HT NLMT để có thể thông tin cho bên điện lực</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-08-24 11:09:00</t>
+          <t>2026-08-24 11:49:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-08-25 14:30:00</t>
+          <t>2026-08-28 14:05:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2155,22 +2147,22 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Trần Văn Việt</t>
+          <t>Trần Hải Tùng</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>044155</t>
+          <t>245696</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4615814</t>
+          <t>4615806</t>
         </is>
       </c>
       <c r="Z12" s="2">
@@ -2191,22 +2183,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE12" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2226,7 +2218,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNI_1711273</t>
+          <t>KHCN_TT.GPTH_BNH_1699993</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2234,6 +2226,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -2241,17 +2238,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lê Điền</t>
+          <t>Nguyễn Công Công</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0839074679</t>
+          <t>0972870377</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ấp 2 xuân đường TpĐồng Nai</t>
+          <t>Yên Viên</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2271,28 +2268,29 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hỗ trợ</t>
+          <t>Sự cố</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Thủ tục/giấy tờ/ Hóa đơn/ Hồ sơ lắp đặt</t>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.KH đã liên hệ CN
-2. KH cần CN hỗ trợ cung cấp hồ sơ kỹ thuật và các chứng từ liên quan đến HT NLMT để có thể thông tin cho bên điện lực</t>
+          <t>1. KH đã được CNCT liên hệ và hướng dẫn xử lý sơ bộ
+2. 1 ATS chống sét trong tủ nguồn của KH có dấu hiệu bị chập, cháy
+3. KH cần CNCT hỗ trợ kiểm tra và khắc phục sớm</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-08-24 11:49:00</t>
+          <t>2026-08-24 08:00:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-08-28 14:05:00</t>
+          <t>2026-08-25 18:35:00</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2302,22 +2300,22 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Trần Hải Tùng</t>
+          <t>Phạm Văn Huy</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>245696</t>
+          <t>408869</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>4615806</t>
+          <t>4615786</t>
         </is>
       </c>
       <c r="Z13" s="2">
@@ -2338,22 +2336,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE13" s="2">
-        <v>46260</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2368,12 +2366,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hệ thống NLMT</t>
+          <t>Acquy lưu trữ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_DNI_1614483</t>
+          <t>KHCN_TT.GPTH_HYN_1639428</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2383,7 +2381,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2393,17 +2391,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Bùi Thị Tuyết Lan</t>
+          <t>Bùi Quang Vũ</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0382305668</t>
+          <t>0886102896</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Xã Thống Nhất,null,Tỉnh Đồng Nai</t>
+          <t>Thôn Văn Tràng</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2428,14 +2426,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>1. KH đã liên hệ CN
-2. Hiện KH không theo dõi được Hiệu suất HT NLMT trên App
-3. KH cần CN liên hệ và đến hỗ trợ sớm</t>
+2. Ăc quy lưu trữ chỉ sạc được khoảng 80%
+3. KH cần CNCT hỗ trợ đến kiểm tra sớm</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2445,7 +2443,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-08-26 19:20:00</t>
+          <t>2026-08-30 17:15:00</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2455,22 +2453,22 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Trần Quốc Khang</t>
+          <t>Trần Minh Vương</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>459729</t>
+          <t>276581</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>4615790</t>
+          <t>4615785</t>
         </is>
       </c>
       <c r="Z14" s="2">
@@ -2491,11 +2489,11 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Đạt</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE14" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="15">
@@ -2506,7 +2504,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2526,7 +2524,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BNH_1699993</t>
+          <t>KHCN_TT.GPTH_TNN_1633636</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2546,17 +2544,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nguyễn Công Công</t>
+          <t>Nguyễn Minh Phúc</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0972870377</t>
+          <t>0868101535</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Yên Viên</t>
+          <t>Cổng CNTT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2581,24 +2579,24 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Thiết bị vỡ, hỏng, chập cháy</t>
+          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1. KH đã được CNCT liên hệ và hướng dẫn xử lý sơ bộ
-2. 1 ATS chống sét trong tủ nguồn của KH có dấu hiệu bị chập, cháy
-3. KH cần CNCT hỗ trợ kiểm tra và khắc phục sớm</t>
+          <t>KH báo Anh Thao KT nhưng chưa được hỗ trợ 
+KH báo sự cố hệ thống NLMT hiện tại không theo dõi được trên app, vào app chỉ thấy hiển thị màn hình trắng tinh
+Yêu cầu CN cho KT qua ktra hõ trợ KH</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-24 08:00:00</t>
+          <t>2026-08-24 13:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-08-25 18:35:00</t>
+          <t>2026-08-28 11:25:00</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2608,22 +2606,22 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Phạm Văn Huy</t>
+          <t>Nguyễn Văn Thao</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>408869</t>
+          <t>289758</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>4615786</t>
+          <t>4615779</t>
         </is>
       </c>
       <c r="Z15" s="2">
@@ -2648,18 +2646,18 @@
         </is>
       </c>
       <c r="AE15" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HUE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2674,12 +2672,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Acquy lưu trữ</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HYN_1639428</t>
+          <t>KHCN_TT.GPTH_TTH_1611393</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2689,7 +2687,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2699,17 +2697,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Bùi Quang Vũ</t>
+          <t>Hồ Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0886102896</t>
+          <t>0966929265</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Thôn Văn Tràng</t>
+          <t>Hương Văn, Phường Hương Hương Trà Huế</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2734,14 +2732,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Chất lượng, hiệu suất của sản phẩm/hệ thống thấp</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1. KH đã liên hệ CN
-2. Ăc quy lưu trữ chỉ sạc được khoảng 80%
-3. KH cần CNCT hỗ trợ đến kiểm tra sớm</t>
+          <t>1. KH chưa liên hệ CN
+2. Biến tần của KH thông tin không có điện lưới trong khi nhà KH vẫn có điện, App theo dõi hiệu suất không có thông tin của HT NLMT từ đầu tháng
+3. KH cần CNCT hỗ trợ kiểm tra sớm</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2751,7 +2749,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-08-30 17:15:00</t>
+          <t>2026-08-27 11:00:00</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2761,22 +2759,22 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Trần Minh Vương</t>
+          <t>Phạm Văn Kiện</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>276581</t>
+          <t>422329</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>4615785</t>
+          <t>4615758</t>
         </is>
       </c>
       <c r="Z16" s="2">
@@ -2797,11 +2795,11 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đăng</t>
         </is>
       </c>
       <c r="AE16" s="2">
-        <v>46261</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="17">
@@ -2812,7 +2810,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2832,7 +2830,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TNN_1633636</t>
+          <t>KHCN_TT.GPTH_BGG_1335514</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2852,17 +2850,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Phúc</t>
+          <t>Nguyễn Thích Điện</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0868101535</t>
+          <t>0978586057</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cổng CNTT</t>
+          <t>Xã Quang Thịnh,Huyện Lạng Giang (cũ)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2872,7 +2870,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Bình thường</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2892,24 +2890,24 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>KH báo Anh Thao KT nhưng chưa được hỗ trợ 
-KH báo sự cố hệ thống NLMT hiện tại không theo dõi được trên app, vào app chỉ thấy hiển thị màn hình trắng tinh
-Yêu cầu CN cho KT qua ktra hõ trợ KH</t>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: mất kết nối, ko đăng nhập được app theo dõi
+3. KH yêu cầu: qua hỗ trợ KH kết nối lại app</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-21 09:10:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-08-25 13:30:00</t>
+          <t>2026-08-26 09:55:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Chưa thực hiện</t>
+          <t>Đang tiến hành</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2919,24 +2917,24 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thao</t>
+          <t>Vũ Hà Thanh</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>289758</t>
+          <t>007721</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>4615779</t>
+          <t>4615728</t>
         </is>
       </c>
       <c r="Z17" s="2">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="AA17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -2954,18 +2952,18 @@
         </is>
       </c>
       <c r="AE17" s="2">
-        <v>46258</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HUE</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2975,17 +2973,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NLMT</t>
+          <t>M&amp;E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Thang máy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_TTH_1611393</t>
+          <t>10092025-GP&amp;DVKT/HĐMBLĐ-2025/HNI-NGUYENNGOCDUONG</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2995,7 +2993,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3005,17 +3003,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hồ Thị Mỹ Hạnh</t>
+          <t>Nguyễn Ngọc Dương</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0966929265</t>
+          <t>0909289598</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Hương Văn, Phường Hương Hương Trà Huế</t>
+          <t>Phương Xuân Phương</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3035,29 +3033,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Phàn nàn, Góp Ý</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
+          <t>Chất lượng, dịch vụ, Giá cả</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1. KH chưa liên hệ CN
-2. Biến tần của KH thông tin không có điện lưới trong khi nhà KH vẫn có điện, App theo dõi hiệu suất không có thông tin của HT NLMT từ đầu tháng
-3. KH cần CNCT hỗ trợ kiểm tra sớm</t>
+          <t>KH phản ánh gay gắt và rất bức xúc do Thang máy liên tục gặp sự cố dừng, kẹt và không hoạt động, ngày 20/08 KH bị kẹt trong thang máy 5 phút và rất lo ngại trường hợp trẻ nhỏ trong gia đình gặp sự cố với thiết bị, Yêu cầu CNCT có phương hướng xử lý khắc phục dứt điểm cho KH</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-24 08:00:00</t>
+          <t>2026-08-21 08:00:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-08-25 12:25:00</t>
+          <t>2026-08-28 16:55:00</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -3072,28 +3068,28 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Phạm Văn Kiện</t>
+          <t>Ngô Đức Tân</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>422329</t>
+          <t>484844</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>4615758</t>
+          <t>4615724</t>
         </is>
       </c>
       <c r="Z18" s="2">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3103,7 +3099,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Đăng</t>
+          <t>Hiếu</t>
         </is>
       </c>
       <c r="AE18" s="2">
@@ -3118,7 +3114,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3138,7 +3134,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_BGG_1335514</t>
+          <t>250501-KD/GPTH/HĐMBLĐ-2022/HBH-VUVIETTUNG</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3146,11 +3142,6 @@
           <t>B2C</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3158,17 +3149,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nguyễn Thích Điện</t>
+          <t>Vũ Việt Tùng</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0978586057</t>
+          <t>0989463899</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Xã Quang Thịnh,Huyện Lạng Giang (cũ)</t>
+          <t>Khu 7 -Xã Lạc Thủy - Phú Thọ</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3178,7 +3169,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Hot</t>
+          <t>Bình thường</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3193,24 +3184,24 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Không kết nối được app/Wifi và không theo dõi được hiệu suất</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1. KH chưa báo CN
-2. KH phản ánh: mất kết nối, ko đăng nhập được app theo dõi
-3. KH yêu cầu: qua hỗ trợ KH kết nối lại app</t>
+          <t>1. KH đã báo CN: a Dũng
+2. KH phản ánh: toàn bộ sản lượng điện nlmt lên hết điện lưới, có báo CN và KT hỗ trợ cài đặt từ xa nhưng vẫn chưa khắc phục được
+3. KH yêu cầu: qua kiểm tra trực tiếp và khắc phục tình trạng này</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-21 09:10:00</t>
+          <t>2026-08-19 11:20:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-08-26 09:55:00</t>
+          <t>2026-08-25 09:15:00</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3220,33 +3211,33 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Quá hạn</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Vũ Hà Thanh</t>
+          <t>Lê Hoàng Chung</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>007721</t>
+          <t>266744</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>4615728</t>
+          <t>4615692</t>
         </is>
       </c>
       <c r="Z19" s="2">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="AA19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>AIO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3260,18 +3251,18 @@
         </is>
       </c>
       <c r="AE19" s="2">
-        <v>46257</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3281,17 +3272,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M&amp;E</t>
+          <t>NLMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Thang máy</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10092025-GP&amp;DVKT/HĐMBLĐ-2025/HNI-NGUYENNGOCDUONG</t>
+          <t>KHCN_TT.GPTH_CTO_1703516</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3311,22 +3302,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nguyễn Ngọc Dương</t>
+          <t>Nguyễn Hân Hoan</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0909289598</t>
+          <t>0981205207</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Phương Xuân Phương</t>
+          <t>ấp tân thành</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Nhân viên nội bộ VCC</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3341,27 +3332,29 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Phàn nàn, Góp Ý</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Chất lượng, dịch vụ, Giá cả</t>
+          <t>Sản phẩm/Hệ thống lỗi/không hoạt động</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>KH phản ánh gay gắt và rất bức xúc do Thang máy liên tục gặp sự cố dừng, kẹt và không hoạt động, ngày 20/08 KH bị kẹt trong thang máy 5 phút và rất lo ngại trường hợp trẻ nhỏ trong gia đình gặp sự cố với thiết bị, Yêu cầu CNCT có phương hướng xử lý khắc phục dứt điểm cho KH</t>
+          <t>1. CN báo sự cố cho KH
+2. Biến tần báo lỗi COM báo đỏ
+3. KH cần CN kiểm tra và khăc phục sớm</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-21 08:00:00</t>
+          <t>2026-08-19 09:49:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-08-28 16:55:00</t>
+          <t>2026-09-04 22:20:00</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3371,33 +3364,33 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Sắp quá hạn</t>
+          <t>Trong hạn</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Ngô Đức Tân</t>
+          <t>Trương Minh Khoa</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>484844</t>
+          <t>440290</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>4615724</t>
+          <t>4615690</t>
         </is>
       </c>
       <c r="Z20" s="2">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="AA20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>AIO</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3407,22 +3400,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE20" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3442,7 +3435,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_PTO_1654586</t>
+          <t>KHCN_TT.GPTH_DNI_1675332</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3462,22 +3455,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Vũ Hồng Lạc</t>
+          <t>Nguyễn Trọng Thuỷ</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0947304568</t>
+          <t>0986565857</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Thiên nga 3-206, Vinhomes cổ loa, xã Xuân Canh, Đông Hội, Mai Lâm, huyện Đông Anh, thành phố Hà Nội (Vinhomes Global Gate), Vinhomes cổ loa</t>
+          <t>ấp 7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hotline</t>
+          <t>Happycall</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3497,24 +3490,24 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Lỗi kết nối giữa thiết bị và hệ thống theo dõi</t>
+          <t>Thiết bị vỡ, hỏng, chập cháy</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN
-2. KH phản ánh: thi thoảng ngắt kết nối app theo dõi nlmt, hiện lỗi "giao tiếp giữa nhà máy và thiết bị bị ngắt kết nối"
-3. KH yêu cầu: qua kiểm tra, khắc phục tình trạng này</t>
+          <t>1. KH đã báo chi nhánh - Nhân viên Hải Tùng
+2. Nội dung sự cố: ATS bị cháy cầu trì, đã báo nhân sự Hải Tùng của chi nhánh nhưng chưa được xử lý. CN báo sẽ đổi ATS khác nhưng chưa có hàng, KH đã đợi khoảng hơn 2 tháng nhưng chưa được hỗ trợ.
+3. KHYC: CN hỗ trợ sớm (Viettel  báo giá 12tr KH đồng ý nhưng đợi lâu chưa được thay, KH cần hỗ trợ gấp do gia đình kinh doanh nhà nghỉ KS)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-20 10:33:00</t>
+          <t>2026-08-18 09:09:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-10 10:10:00</t>
+          <t>2026-08-31 17:00:00</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3524,29 +3517,29 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Lê Trung Kiên</t>
+          <t>Trần Hải Tùng</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>119420</t>
+          <t>245696</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>4615711</t>
+          <t>4615669</t>
         </is>
       </c>
       <c r="Z21" s="2">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -3560,11 +3553,11 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Hiếu</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="AE21" s="2">
-        <v>46264</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="22">
@@ -3575,7 +3568,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3595,12 +3588,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KHCN_TT.GPTH_HNI_1685619</t>
+          <t>KHDN_NLMT_BNH_0171103</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3610,27 +3603,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Khách hàng cá nhân</t>
+          <t>Khách hàng doanh nghiệp</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Trần Tuấn Việt</t>
+          <t>NGUYỄN VĂN ÍCH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0982296655</t>
+          <t>0987363058</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Vườn Đào Tuấn Việt, SN 15, Ngõ 264/18</t>
+          <t>Thị trấn Lim, Huyện Tiên Du, Tỉnh Bắc Ninh</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Happycall</t>
+          <t>Hotline</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3645,29 +3638,27 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Khiếu nại</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Hiệu suất sản phẩm kém</t>
+          <t>Tiến độ triển khai chậm</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>KH đã báo KT 
-KH báo sự cố:  Biến tần tự động ngắt/dừng hoạt động mỗi khi điện nguồn vào bị tụt xuống dưới 180V. Khi đó, hệ thống tự động chuyển sang dùng 100% điện lưới thay vì dùng điện mặt trời. Hệ thống chỉ chạy điện mặt trời khi ngắt/tắt thủ công nguồn điện lưới. Hệ thống điện mặt trời gần như không có tác dụng (90% thời gian từ lúc lắp đặt vẫn phải dùng điện lưới), tiền điện mỗi tháng không giảm so với trước (vẫn hơn 3 triệu/tháng).
-Yêu cầu CN cho KT qua ktra lại và xử lý cho KH</t>
+          <t>Phản ánh từ trước TT_1783915287625 CN đã có BBLV với KH về thiết bị ivt mang đi bảo hành và xác nhận thời điểm lắp đặt lại thiết bị là 15/8 nhưng đến hiện tại là 18/8 KH vẫn chưa thấy có thông tin gì. KH rất bức xúc yêu cầu CN liên hệ là xuống lắp đặt cho KH theo BBLV</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-20 10:03:00</t>
+          <t>2026-08-18 11:15:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-03 18:25:00</t>
+          <t>2026-08-25 18:40:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3677,29 +3668,29 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Trong hạn</t>
+          <t>Sắp quá hạn</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Hoàng Văn Vương</t>
+          <t>Nguyễn Văn Tuần</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>285732</t>
+          <t>461581</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4615710</t>
+          <t>4615658</t>
         </is>
       </c>
       <c r="Z22" s="2">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -3717,7 +3708,7 @@
         </is>
       </c>
       <c r="AE22" s="2">
-        <v>46261</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="23">
@@ -3728,7 +3719,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3748,7 +3739,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>250501-KD/GPTH/HĐMBLĐ-2022/HBH-VUVIETTUNG</t>
+          <t>KHCN_TT.GPTH_BNH_1665718</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3756,6 +3747,11 @@
           <t>B2C</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Khách hàng cá nhân</t>
@@ -3763,17 +3759,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Vũ Việt Tùng</t>
+          <t>Chu Văn Thao</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0989463899</t>
+          <t>0969032689</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Khu 7 -Xã Lạc Thủy - Phú Thọ</t>
+          <t>Thôn Ngoẹn</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3793,7 +3789,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sự cố</t>
+          <t>Bảo hành</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3803,19 +3799,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1. KH đã báo CN: a Dũng
-2. KH phản ánh: toàn bộ sản lượng điện nlmt lên hết điện lưới, có báo CN và KT hỗ trợ cài đặt từ xa nhưng vẫn chưa khắc phục được
-3. KH yêu cầu: qua kiểm tra trực tiếp và khắc phục tình trạng này</t>
+          <t>1. KH chưa báo CN
+2. KH phản ánh: hệ nlmt ko hoạt động, đèn ở pin lưu trữ và cả hệ đều thấy t